--- a/Коломна_маршруты_28-30.10.2026.xlsx
+++ b/Коломна_маршруты_28-30.10.2026.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Сводка по сотрудникам'!$A$4:$S$43</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Маршруты'!$A$1:$Q$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Маршруты'!$A$1:$Q$119</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3363,25 +3363,54 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>уточнить</t>
-        </is>
-      </c>
-      <c r="F41" s="6" t="n"/>
-      <c r="G41" s="6" t="n"/>
-      <c r="H41" s="6" t="n"/>
-      <c r="I41" s="6" t="n"/>
-      <c r="J41" s="6" t="n"/>
-      <c r="K41" s="7" t="n"/>
-      <c r="L41" s="6" t="n"/>
-      <c r="M41" s="6" t="n"/>
-      <c r="N41" s="9" t="n"/>
-      <c r="O41" s="9" t="n"/>
-      <c r="P41" s="9" t="n"/>
-      <c r="Q41" s="10" t="n"/>
-      <c r="R41" s="9" t="n"/>
+          <t>Автобус / поезд через Ростов</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>3500</v>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>3500</v>
+      </c>
+      <c r="H41" s="6" t="n">
+        <v>4000</v>
+      </c>
+      <c r="I41" s="6" t="n">
+        <v>4000</v>
+      </c>
+      <c r="J41" s="6" t="n">
+        <v>1800</v>
+      </c>
+      <c r="K41" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" s="8">
+        <f>F41+H41+J41+K41*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="M41" s="8">
+        <f>G41+I41+J41+K41*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="N41" s="9" t="n">
+        <v>6793</v>
+      </c>
+      <c r="O41" s="9" t="n">
+        <v>7132</v>
+      </c>
+      <c r="P41" s="9" t="n">
+        <v>4800</v>
+      </c>
+      <c r="Q41" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" s="11">
+        <f>N41+O41+P41+Q41*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
       <c r="S41" s="5" t="inlineStr">
         <is>
-          <t>Нет данных Туту по Донецку — см. лист «Маршруты»</t>
+          <t>Эконом: прямой автобус (~20 ч). Удобный: до Ростова + поезд в купе; трансферы вкл. Донецк—Ростов ~1 500 ₽ в каждую сторону</t>
         </is>
       </c>
     </row>
@@ -3563,7 +3592,7 @@
     <row r="45">
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>Сотрудников в списке: 39 (Донецк не посчитан). Ориентир на 65 человек — пропорционально.</t>
+          <t>Сотрудников в списке: 39 . Ориентир на 65 человек — пропорционально.</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q114"/>
+  <dimension ref="A1:Q119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10960,437 +10989,421 @@
     <row r="107">
       <c r="A107" s="15" t="inlineStr">
         <is>
-          <t>Донецк</t>
+          <t>Донецк (ДНР)</t>
         </is>
       </c>
       <c r="B107" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="C107" s="16" t="inlineStr">
-        <is>
-          <t>Все варианты</t>
-        </is>
-      </c>
-      <c r="D107" s="16" t="inlineStr">
+      <c r="C107" s="17" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D107" s="17" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E107" s="17" t="inlineStr">
+        <is>
+          <t>Автобус (сидячее место), напр. «Восточный экспресс», «Донавтолайнс»</t>
+        </is>
+      </c>
+      <c r="F107" s="17" t="inlineStr">
+        <is>
+          <t>рейс ~09:15–12:00</t>
+        </is>
+      </c>
+      <c r="G107" s="16" t="inlineStr">
+        <is>
+          <t>27.10 ~09:15–12:00</t>
+        </is>
+      </c>
+      <c r="H107" s="16" t="inlineStr">
+        <is>
+          <t>28.10 06:00–07:00</t>
+        </is>
+      </c>
+      <c r="I107" s="16" t="inlineStr">
+        <is>
+          <t>Москва, АС «Новоясеневская» / м. «Домодедовская»</t>
+        </is>
+      </c>
+      <c r="J107" s="18" t="n">
+        <v>3500</v>
+      </c>
+      <c r="K107" s="18" t="n">
+        <v>3500</v>
+      </c>
+      <c r="L107" s="16" t="inlineStr">
+        <is>
+          <t>Метро до Комсомольской (~50 мин) → электричка 08:47 РЭКС / 09:48 → такси</t>
+        </is>
+      </c>
+      <c r="M107" s="16" t="inlineStr">
+        <is>
+          <t>~11:00–12:00</t>
+        </is>
+      </c>
+      <c r="N107" s="16" t="inlineStr"/>
+      <c r="O107" s="19" t="inlineStr">
+        <is>
+          <t>https://vekspress-bus.ru/marshrutyi/doneczk-moskva.html</t>
+        </is>
+      </c>
+      <c r="P107" s="16" t="inlineStr">
+        <is>
+          <t>~20 ч в автобусе. Многие рейсы ходят через день: уточнить дату у перевозчика. Цена 3 500–4 000 ₽, оплата при посадке</t>
+        </is>
+      </c>
+      <c r="Q107" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>Донецк (ДНР)</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C108" s="10" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D108" s="10" t="inlineStr">
+        <is>
+          <t>Удобный</t>
+        </is>
+      </c>
+      <c r="E108" s="10" t="inlineStr">
+        <is>
+          <t>Автобус/такси до Ростова + поезд «Ингушетия», купе</t>
+        </is>
+      </c>
+      <c r="F108" s="10" t="inlineStr">
+        <is>
+          <t>145С</t>
+        </is>
+      </c>
+      <c r="G108" s="5" t="inlineStr">
+        <is>
+          <t>27.10 ~06:00 из Донецка; поезд из Ростова в 10:30</t>
+        </is>
+      </c>
+      <c r="H108" s="5" t="inlineStr">
+        <is>
+          <t>28.10 07:24</t>
+        </is>
+      </c>
+      <c r="I108" s="5" t="inlineStr">
+        <is>
+          <t>Москва, Казанский</t>
+        </is>
+      </c>
+      <c r="J108" s="9" t="n">
+        <v>6793</v>
+      </c>
+      <c r="K108" s="9" t="n">
+        <v>6793</v>
+      </c>
+      <c r="L108" s="5" t="inlineStr">
+        <is>
+          <t>Казанский вокзал → электричка до ст. Коломна (490–620 ₽) + такси 10 мин (~300 ₽) (08:47 РЭКС → 10:28)</t>
+        </is>
+      </c>
+      <c r="M108" s="5" t="inlineStr">
+        <is>
+          <t>~10:45</t>
+        </is>
+      </c>
+      <c r="N108" s="5" t="inlineStr"/>
+      <c r="O108" s="20" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2064000&amp;nnst2=2000000</t>
+        </is>
+      </c>
+      <c r="P108" s="5" t="inlineStr">
+        <is>
+          <t>Донецк → Ростов ~4 ч (автобус/такси ~1 500 ₽, уточнить). Прямых поездов и самолётов Донецк — Москва в 2026 г. нет</t>
+        </is>
+      </c>
+      <c r="Q108" s="5" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>Донецк (ДНР)</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>В2: после 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E107" s="16" t="inlineStr">
-        <is>
-          <t>уточнить</t>
-        </is>
-      </c>
-      <c r="F107" s="16" t="inlineStr"/>
-      <c r="G107" s="16" t="inlineStr"/>
-      <c r="H107" s="16" t="inlineStr"/>
-      <c r="I107" s="16" t="inlineStr"/>
-      <c r="J107" s="16" t="n"/>
-      <c r="K107" s="16" t="n"/>
-      <c r="L107" s="16" t="inlineStr"/>
-      <c r="M107" s="16" t="inlineStr"/>
-      <c r="N107" s="16" t="inlineStr"/>
-      <c r="O107" s="16" t="inlineStr"/>
-      <c r="P107" s="16" t="inlineStr">
-        <is>
-          <t>На Туту нет билетов из Донецка (ДНР). Варианты: поезд Донецк — Москва на rzd.ru; автобус; или машина/автобус до Ростова + самолёт Платов → Москва. Уточнить город (есть Донецк и в Ростовской обл.)</t>
-        </is>
-      </c>
-      <c r="Q107" s="16" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="15" t="inlineStr">
-        <is>
-          <t>Пенза</t>
-        </is>
-      </c>
-      <c r="B108" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C108" s="16" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D108" s="16" t="inlineStr">
-        <is>
-          <t>Альтернатива: поезд</t>
-        </is>
-      </c>
-      <c r="E108" s="16" t="inlineStr">
-        <is>
-          <t>Поезд «Сура», купе (сидячий 3 030)</t>
-        </is>
-      </c>
-      <c r="F108" s="16" t="inlineStr">
-        <is>
-          <t>052М</t>
-        </is>
-      </c>
-      <c r="G108" s="16" t="inlineStr">
-        <is>
-          <t>27.10 21:35</t>
-        </is>
-      </c>
-      <c r="H108" s="16" t="inlineStr">
-        <is>
-          <t>28.10 07:59</t>
-        </is>
-      </c>
-      <c r="I108" s="16" t="inlineStr">
-        <is>
-          <t>Москва, Казанский</t>
-        </is>
-      </c>
-      <c r="J108" s="24" t="n">
-        <v>3967</v>
-      </c>
-      <c r="K108" s="24" t="n">
-        <v>3967</v>
-      </c>
-      <c r="L108" s="16" t="inlineStr">
-        <is>
-          <t>Казанский вокзал → электричка до ст. Коломна (490–620 ₽) + такси 10 мин (~300 ₽) (09:48 → 11:36)</t>
-        </is>
-      </c>
-      <c r="M108" s="16" t="inlineStr">
-        <is>
-          <t>~12:00</t>
-        </is>
-      </c>
-      <c r="N108" s="16" t="inlineStr"/>
-      <c r="O108" s="19" t="inlineStr">
-        <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2024120&amp;nnst2=2000000</t>
-        </is>
-      </c>
-      <c r="P108" s="16" t="inlineStr">
-        <is>
-          <t>Основной вариант — машина (лист «Авто»)</t>
-        </is>
-      </c>
-      <c r="Q108" s="16" t="inlineStr">
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>Автобус/такси до Ростова + поезд, купе</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="inlineStr">
+        <is>
+          <t>153Э</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="inlineStr">
+        <is>
+          <t>Ростов 27.10 12:18</t>
+        </is>
+      </c>
+      <c r="H109" s="5" t="inlineStr">
+        <is>
+          <t>28.10 09:40</t>
+        </is>
+      </c>
+      <c r="I109" s="5" t="inlineStr">
+        <is>
+          <t>Москва, Павелецкий</t>
+        </is>
+      </c>
+      <c r="J109" s="21" t="n">
+        <v>5592</v>
+      </c>
+      <c r="K109" s="21" t="n">
+        <v>5592</v>
+      </c>
+      <c r="L109" s="5" t="inlineStr">
+        <is>
+          <t>Павелецкий → метро до Комсомольской (~20 мин) → электричка от Казанского + такси (12:54 → 15:15)</t>
+        </is>
+      </c>
+      <c r="M109" s="5" t="inlineStr">
+        <is>
+          <t>~15:30</t>
+        </is>
+      </c>
+      <c r="N109" s="5" t="inlineStr"/>
+      <c r="O109" s="20" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2064000&amp;nnst2=2000000</t>
+        </is>
+      </c>
+      <c r="P109" s="5" t="inlineStr">
+        <is>
+          <t>Дешевле, приезд к ~15:30</t>
+        </is>
+      </c>
+      <c r="Q109" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="15" t="inlineStr">
-        <is>
-          <t>Саранск</t>
-        </is>
-      </c>
-      <c r="B109" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C109" s="16" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D109" s="16" t="inlineStr">
-        <is>
-          <t>Альтернатива: поезд</t>
-        </is>
-      </c>
-      <c r="E109" s="16" t="inlineStr">
-        <is>
-          <t>Поезд, купе</t>
-        </is>
-      </c>
-      <c r="F109" s="16" t="inlineStr">
-        <is>
-          <t>041Й</t>
-        </is>
-      </c>
-      <c r="G109" s="16" t="inlineStr">
-        <is>
-          <t>27.10 20:40</t>
-        </is>
-      </c>
-      <c r="H109" s="16" t="inlineStr">
-        <is>
-          <t>28.10 05:50</t>
-        </is>
-      </c>
-      <c r="I109" s="16" t="inlineStr">
-        <is>
-          <t>Москва, Казанский</t>
-        </is>
-      </c>
-      <c r="J109" s="24" t="n">
-        <v>4394</v>
-      </c>
-      <c r="K109" s="24" t="n">
-        <v>4394</v>
-      </c>
-      <c r="L109" s="16" t="inlineStr">
-        <is>
-          <t>Казанский вокзал → электричка до ст. Коломна (490–620 ₽) + такси 10 мин (~300 ₽) (07:22 → 09:15)</t>
-        </is>
-      </c>
-      <c r="M109" s="16" t="inlineStr">
-        <is>
-          <t>~09:30</t>
-        </is>
-      </c>
-      <c r="N109" s="16" t="inlineStr">
-        <is>
-          <t>ранний заезд</t>
-        </is>
-      </c>
-      <c r="O109" s="19" t="inlineStr">
-        <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2024700&amp;nnst2=2000000</t>
-        </is>
-      </c>
-      <c r="P109" s="16" t="inlineStr">
-        <is>
-          <t>Основной вариант — машина</t>
-        </is>
-      </c>
-      <c r="Q109" s="16" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
-      </c>
-    </row>
     <row r="110">
-      <c r="A110" s="15" t="inlineStr">
-        <is>
-          <t>Тамбов</t>
-        </is>
-      </c>
-      <c r="B110" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C110" s="16" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D110" s="16" t="inlineStr">
-        <is>
-          <t>Альтернатива: поезд</t>
-        </is>
-      </c>
-      <c r="E110" s="16" t="inlineStr">
-        <is>
-          <t>Поезд, сидячий (купе 2 868)</t>
-        </is>
-      </c>
-      <c r="F110" s="16" t="inlineStr">
-        <is>
-          <t>135Ж</t>
-        </is>
-      </c>
-      <c r="G110" s="16" t="inlineStr">
-        <is>
-          <t>27.10 21:56</t>
-        </is>
-      </c>
-      <c r="H110" s="16" t="inlineStr">
-        <is>
-          <t>28.10 07:22</t>
-        </is>
-      </c>
-      <c r="I110" s="16" t="inlineStr">
-        <is>
-          <t>Москва, Павелецкий</t>
-        </is>
-      </c>
-      <c r="J110" s="24" t="n">
-        <v>1979</v>
-      </c>
-      <c r="K110" s="24" t="n">
-        <v>1979</v>
-      </c>
-      <c r="L110" s="16" t="inlineStr">
-        <is>
-          <t>Павелецкий → метро до Комсомольской (~20 мин) → электричка от Казанского + такси (08:47 РЭКС → 10:28)</t>
-        </is>
-      </c>
-      <c r="M110" s="16" t="inlineStr">
-        <is>
-          <t>~10:45</t>
-        </is>
-      </c>
-      <c r="N110" s="16" t="inlineStr"/>
-      <c r="O110" s="19" t="inlineStr">
-        <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2014700&amp;nnst2=2000000</t>
-        </is>
-      </c>
-      <c r="P110" s="16" t="inlineStr">
-        <is>
-          <t>Основной вариант — машина. Купе осталось 1 место</t>
-        </is>
-      </c>
-      <c r="Q110" s="16" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
-      </c>
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>Донецк (ДНР)</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>В3: к утру 29.10</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="inlineStr">
+        <is>
+          <t>как В1</t>
+        </is>
+      </c>
+      <c r="F110" s="5" t="inlineStr"/>
+      <c r="G110" s="5" t="inlineStr"/>
+      <c r="H110" s="5" t="inlineStr"/>
+      <c r="I110" s="5" t="inlineStr"/>
+      <c r="J110" s="5" t="n"/>
+      <c r="K110" s="5" t="n"/>
+      <c r="L110" s="5" t="inlineStr"/>
+      <c r="M110" s="5" t="inlineStr"/>
+      <c r="N110" s="5" t="inlineStr"/>
+      <c r="O110" s="5" t="inlineStr"/>
+      <c r="P110" s="5" t="inlineStr">
+        <is>
+          <t>Прямой поезд Ростов 06:52 → Голутвин 04:50 (213*С, 6 234 ₽) — неудобное время прибытия</t>
+        </is>
+      </c>
+      <c r="Q110" s="5" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="15" t="inlineStr">
-        <is>
-          <t>Липецк</t>
-        </is>
-      </c>
-      <c r="B111" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="C111" s="16" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D111" s="16" t="inlineStr">
-        <is>
-          <t>Альтернатива: поезд</t>
-        </is>
-      </c>
-      <c r="E111" s="16" t="inlineStr">
-        <is>
-          <t>Поезд, купе</t>
-        </is>
-      </c>
-      <c r="F111" s="16" t="inlineStr">
-        <is>
-          <t>033С</t>
-        </is>
-      </c>
-      <c r="G111" s="16" t="inlineStr">
-        <is>
-          <t>27.10 23:15</t>
-        </is>
-      </c>
-      <c r="H111" s="16" t="inlineStr">
-        <is>
-          <t>28.10 08:08</t>
-        </is>
-      </c>
-      <c r="I111" s="16" t="inlineStr">
-        <is>
-          <t>Москва, Павелецкий</t>
-        </is>
-      </c>
-      <c r="J111" s="24" t="n">
-        <v>4049</v>
-      </c>
-      <c r="K111" s="24" t="n">
-        <v>4049</v>
-      </c>
-      <c r="L111" s="16" t="inlineStr">
-        <is>
-          <t>Павелецкий → метро до Комсомольской (~20 мин) → электричка от Казанского + такси (09:48 → 11:36)</t>
-        </is>
-      </c>
-      <c r="M111" s="16" t="inlineStr">
-        <is>
-          <t>~12:00</t>
-        </is>
-      </c>
-      <c r="N111" s="16" t="inlineStr"/>
-      <c r="O111" s="19" t="inlineStr">
-        <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2014130&amp;nnst2=2000000</t>
-        </is>
-      </c>
-      <c r="P111" s="16" t="inlineStr">
-        <is>
-          <t>Основной вариант — одна машина на троих</t>
-        </is>
-      </c>
-      <c r="Q111" s="16" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
-      </c>
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>Донецк (ДНР)</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C111" s="7" t="inlineStr">
+        <is>
+          <t>Обратно</t>
+        </is>
+      </c>
+      <c r="D111" s="7" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E111" s="7" t="inlineStr">
+        <is>
+          <t>Автобус (сидячее место)</t>
+        </is>
+      </c>
+      <c r="F111" s="7" t="inlineStr">
+        <is>
+          <t>рейс ~11:00–13:00</t>
+        </is>
+      </c>
+      <c r="G111" s="5" t="inlineStr">
+        <is>
+          <t>31.10 днём</t>
+        </is>
+      </c>
+      <c r="H111" s="5" t="inlineStr">
+        <is>
+          <t>01.11 утро</t>
+        </is>
+      </c>
+      <c r="I111" s="5" t="inlineStr">
+        <is>
+          <t>Москва, АС «Новоясеневская» → Донецк</t>
+        </is>
+      </c>
+      <c r="J111" s="6" t="n">
+        <v>4000</v>
+      </c>
+      <c r="K111" s="6" t="n">
+        <v>4000</v>
+      </c>
+      <c r="L111" s="5" t="inlineStr">
+        <is>
+          <t>31.10: электричка до Казанского + метро</t>
+        </is>
+      </c>
+      <c r="M111" s="5" t="inlineStr"/>
+      <c r="N111" s="5" t="inlineStr">
+        <is>
+          <t>+1 ночь 30→31</t>
+        </is>
+      </c>
+      <c r="O111" s="20" t="inlineStr">
+        <is>
+          <t>https://vekspress-bus.ru/marshrutyi/doneczk-moskva.html</t>
+        </is>
+      </c>
+      <c r="P111" s="5" t="inlineStr">
+        <is>
+          <t>Вечерние автобусы 30.10 уходят до ~21–23 ч — после конференции впритык</t>
+        </is>
+      </c>
+      <c r="Q111" s="5" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="15" t="inlineStr">
-        <is>
-          <t>Воронеж</t>
-        </is>
-      </c>
-      <c r="B112" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="C112" s="16" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D112" s="16" t="inlineStr">
-        <is>
-          <t>Альтернатива: поезд</t>
-        </is>
-      </c>
-      <c r="E112" s="16" t="inlineStr">
-        <is>
-          <t>Поезд «Ингушетия», купе</t>
-        </is>
-      </c>
-      <c r="F112" s="16" t="inlineStr">
-        <is>
-          <t>145С</t>
-        </is>
-      </c>
-      <c r="G112" s="16" t="inlineStr">
-        <is>
-          <t>27.10 23:17</t>
-        </is>
-      </c>
-      <c r="H112" s="16" t="inlineStr">
-        <is>
-          <t>28.10 07:24</t>
-        </is>
-      </c>
-      <c r="I112" s="16" t="inlineStr">
-        <is>
-          <t>Москва, Казанский</t>
-        </is>
-      </c>
-      <c r="J112" s="24" t="n">
-        <v>4045</v>
-      </c>
-      <c r="K112" s="24" t="n">
-        <v>4045</v>
-      </c>
-      <c r="L112" s="16" t="inlineStr">
-        <is>
-          <t>Казанский вокзал → электричка до ст. Коломна (490–620 ₽) + такси 10 мин (~300 ₽) (08:47 РЭКС → 10:28)</t>
-        </is>
-      </c>
-      <c r="M112" s="16" t="inlineStr">
-        <is>
-          <t>~10:45</t>
-        </is>
-      </c>
-      <c r="N112" s="16" t="inlineStr"/>
-      <c r="O112" s="19" t="inlineStr">
-        <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2014000&amp;nnst2=2000000</t>
-        </is>
-      </c>
-      <c r="P112" s="16" t="inlineStr">
-        <is>
-          <t>Или 213*С 21:09 — прямо до Голутвина (Коломна) в 04:50</t>
-        </is>
-      </c>
-      <c r="Q112" s="16" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
-      </c>
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>Донецк (ДНР)</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C112" s="10" t="inlineStr">
+        <is>
+          <t>Обратно</t>
+        </is>
+      </c>
+      <c r="D112" s="10" t="inlineStr">
+        <is>
+          <t>Удобный</t>
+        </is>
+      </c>
+      <c r="E112" s="10" t="inlineStr">
+        <is>
+          <t>Поезд «Ингушетия», купе + автобус до Донецка</t>
+        </is>
+      </c>
+      <c r="F112" s="10" t="inlineStr">
+        <is>
+          <t>146Э</t>
+        </is>
+      </c>
+      <c r="G112" s="5" t="inlineStr">
+        <is>
+          <t>30.10 23:23</t>
+        </is>
+      </c>
+      <c r="H112" s="5" t="inlineStr">
+        <is>
+          <t>31.10 19:35 (Ростов)</t>
+        </is>
+      </c>
+      <c r="I112" s="5" t="inlineStr">
+        <is>
+          <t>Ростов-Главный</t>
+        </is>
+      </c>
+      <c r="J112" s="9" t="n">
+        <v>7132</v>
+      </c>
+      <c r="K112" s="9" t="n">
+        <v>7132</v>
+      </c>
+      <c r="L112" s="5" t="inlineStr">
+        <is>
+          <t>Электричка 18:43 → Казанский 20:47</t>
+        </is>
+      </c>
+      <c r="M112" s="5" t="inlineStr"/>
+      <c r="N112" s="5" t="inlineStr"/>
+      <c r="O112" s="20" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2064000</t>
+        </is>
+      </c>
+      <c r="P112" s="5" t="inlineStr">
+        <is>
+          <t>Ночь в поезде; из Ростова в Донецк ~4 ч, дома ~00:00. Также 092М «Таврия» 23:30, 9 721 ₽</t>
+        </is>
+      </c>
+      <c r="Q112" s="5" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="15" t="inlineStr">
         <is>
-          <t>Орёл</t>
+          <t>Пенза</t>
         </is>
       </c>
       <c r="B113" s="16" t="n">
@@ -11408,38 +11421,38 @@
       </c>
       <c r="E113" s="16" t="inlineStr">
         <is>
-          <t>Поезд, купе</t>
+          <t>Поезд «Сура», купе (сидячий 3 030)</t>
         </is>
       </c>
       <c r="F113" s="16" t="inlineStr">
         <is>
-          <t>084С</t>
+          <t>052М</t>
         </is>
       </c>
       <c r="G113" s="16" t="inlineStr">
         <is>
-          <t>27.10 23:37</t>
+          <t>27.10 21:35</t>
         </is>
       </c>
       <c r="H113" s="16" t="inlineStr">
         <is>
-          <t>28.10 08:40</t>
+          <t>28.10 07:59</t>
         </is>
       </c>
       <c r="I113" s="16" t="inlineStr">
         <is>
-          <t>Москва, Киевский</t>
+          <t>Москва, Казанский</t>
         </is>
       </c>
       <c r="J113" s="24" t="n">
-        <v>3655</v>
+        <v>3967</v>
       </c>
       <c r="K113" s="24" t="n">
-        <v>3655</v>
+        <v>3967</v>
       </c>
       <c r="L113" s="16" t="inlineStr">
         <is>
-          <t>Киевский → метро до Комсомольской (~25 мин) → электричка + такси (09:48 → 11:36)</t>
+          <t>Казанский вокзал → электричка до ст. Коломна (490–620 ₽) + такси 10 мин (~300 ₽) (09:48 → 11:36)</t>
         </is>
       </c>
       <c r="M113" s="16" t="inlineStr">
@@ -11450,12 +11463,12 @@
       <c r="N113" s="16" t="inlineStr"/>
       <c r="O113" s="19" t="inlineStr">
         <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2000140&amp;nnst2=2000000</t>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2024120&amp;nnst2=2000000</t>
         </is>
       </c>
       <c r="P113" s="16" t="inlineStr">
         <is>
-          <t>Основной вариант — машина вместе с Брянском</t>
+          <t>Основной вариант — машина (лист «Авто»)</t>
         </is>
       </c>
       <c r="Q113" s="16" t="inlineStr">
@@ -11467,86 +11480,475 @@
     <row r="114">
       <c r="A114" s="15" t="inlineStr">
         <is>
+          <t>Саранск</t>
+        </is>
+      </c>
+      <c r="B114" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C114" s="16" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D114" s="16" t="inlineStr">
+        <is>
+          <t>Альтернатива: поезд</t>
+        </is>
+      </c>
+      <c r="E114" s="16" t="inlineStr">
+        <is>
+          <t>Поезд, купе</t>
+        </is>
+      </c>
+      <c r="F114" s="16" t="inlineStr">
+        <is>
+          <t>041Й</t>
+        </is>
+      </c>
+      <c r="G114" s="16" t="inlineStr">
+        <is>
+          <t>27.10 20:40</t>
+        </is>
+      </c>
+      <c r="H114" s="16" t="inlineStr">
+        <is>
+          <t>28.10 05:50</t>
+        </is>
+      </c>
+      <c r="I114" s="16" t="inlineStr">
+        <is>
+          <t>Москва, Казанский</t>
+        </is>
+      </c>
+      <c r="J114" s="24" t="n">
+        <v>4394</v>
+      </c>
+      <c r="K114" s="24" t="n">
+        <v>4394</v>
+      </c>
+      <c r="L114" s="16" t="inlineStr">
+        <is>
+          <t>Казанский вокзал → электричка до ст. Коломна (490–620 ₽) + такси 10 мин (~300 ₽) (07:22 → 09:15)</t>
+        </is>
+      </c>
+      <c r="M114" s="16" t="inlineStr">
+        <is>
+          <t>~09:30</t>
+        </is>
+      </c>
+      <c r="N114" s="16" t="inlineStr">
+        <is>
+          <t>ранний заезд</t>
+        </is>
+      </c>
+      <c r="O114" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2024700&amp;nnst2=2000000</t>
+        </is>
+      </c>
+      <c r="P114" s="16" t="inlineStr">
+        <is>
+          <t>Основной вариант — машина</t>
+        </is>
+      </c>
+      <c r="Q114" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="15" t="inlineStr">
+        <is>
+          <t>Тамбов</t>
+        </is>
+      </c>
+      <c r="B115" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C115" s="16" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D115" s="16" t="inlineStr">
+        <is>
+          <t>Альтернатива: поезд</t>
+        </is>
+      </c>
+      <c r="E115" s="16" t="inlineStr">
+        <is>
+          <t>Поезд, сидячий (купе 2 868)</t>
+        </is>
+      </c>
+      <c r="F115" s="16" t="inlineStr">
+        <is>
+          <t>135Ж</t>
+        </is>
+      </c>
+      <c r="G115" s="16" t="inlineStr">
+        <is>
+          <t>27.10 21:56</t>
+        </is>
+      </c>
+      <c r="H115" s="16" t="inlineStr">
+        <is>
+          <t>28.10 07:22</t>
+        </is>
+      </c>
+      <c r="I115" s="16" t="inlineStr">
+        <is>
+          <t>Москва, Павелецкий</t>
+        </is>
+      </c>
+      <c r="J115" s="24" t="n">
+        <v>1979</v>
+      </c>
+      <c r="K115" s="24" t="n">
+        <v>1979</v>
+      </c>
+      <c r="L115" s="16" t="inlineStr">
+        <is>
+          <t>Павелецкий → метро до Комсомольской (~20 мин) → электричка от Казанского + такси (08:47 РЭКС → 10:28)</t>
+        </is>
+      </c>
+      <c r="M115" s="16" t="inlineStr">
+        <is>
+          <t>~10:45</t>
+        </is>
+      </c>
+      <c r="N115" s="16" t="inlineStr"/>
+      <c r="O115" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2014700&amp;nnst2=2000000</t>
+        </is>
+      </c>
+      <c r="P115" s="16" t="inlineStr">
+        <is>
+          <t>Основной вариант — машина. Купе осталось 1 место</t>
+        </is>
+      </c>
+      <c r="Q115" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="15" t="inlineStr">
+        <is>
+          <t>Липецк</t>
+        </is>
+      </c>
+      <c r="B116" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C116" s="16" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D116" s="16" t="inlineStr">
+        <is>
+          <t>Альтернатива: поезд</t>
+        </is>
+      </c>
+      <c r="E116" s="16" t="inlineStr">
+        <is>
+          <t>Поезд, купе</t>
+        </is>
+      </c>
+      <c r="F116" s="16" t="inlineStr">
+        <is>
+          <t>033С</t>
+        </is>
+      </c>
+      <c r="G116" s="16" t="inlineStr">
+        <is>
+          <t>27.10 23:15</t>
+        </is>
+      </c>
+      <c r="H116" s="16" t="inlineStr">
+        <is>
+          <t>28.10 08:08</t>
+        </is>
+      </c>
+      <c r="I116" s="16" t="inlineStr">
+        <is>
+          <t>Москва, Павелецкий</t>
+        </is>
+      </c>
+      <c r="J116" s="24" t="n">
+        <v>4049</v>
+      </c>
+      <c r="K116" s="24" t="n">
+        <v>4049</v>
+      </c>
+      <c r="L116" s="16" t="inlineStr">
+        <is>
+          <t>Павелецкий → метро до Комсомольской (~20 мин) → электричка от Казанского + такси (09:48 → 11:36)</t>
+        </is>
+      </c>
+      <c r="M116" s="16" t="inlineStr">
+        <is>
+          <t>~12:00</t>
+        </is>
+      </c>
+      <c r="N116" s="16" t="inlineStr"/>
+      <c r="O116" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2014130&amp;nnst2=2000000</t>
+        </is>
+      </c>
+      <c r="P116" s="16" t="inlineStr">
+        <is>
+          <t>Основной вариант — одна машина на троих</t>
+        </is>
+      </c>
+      <c r="Q116" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="15" t="inlineStr">
+        <is>
+          <t>Воронеж</t>
+        </is>
+      </c>
+      <c r="B117" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C117" s="16" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D117" s="16" t="inlineStr">
+        <is>
+          <t>Альтернатива: поезд</t>
+        </is>
+      </c>
+      <c r="E117" s="16" t="inlineStr">
+        <is>
+          <t>Поезд «Ингушетия», купе</t>
+        </is>
+      </c>
+      <c r="F117" s="16" t="inlineStr">
+        <is>
+          <t>145С</t>
+        </is>
+      </c>
+      <c r="G117" s="16" t="inlineStr">
+        <is>
+          <t>27.10 23:17</t>
+        </is>
+      </c>
+      <c r="H117" s="16" t="inlineStr">
+        <is>
+          <t>28.10 07:24</t>
+        </is>
+      </c>
+      <c r="I117" s="16" t="inlineStr">
+        <is>
+          <t>Москва, Казанский</t>
+        </is>
+      </c>
+      <c r="J117" s="24" t="n">
+        <v>4045</v>
+      </c>
+      <c r="K117" s="24" t="n">
+        <v>4045</v>
+      </c>
+      <c r="L117" s="16" t="inlineStr">
+        <is>
+          <t>Казанский вокзал → электричка до ст. Коломна (490–620 ₽) + такси 10 мин (~300 ₽) (08:47 РЭКС → 10:28)</t>
+        </is>
+      </c>
+      <c r="M117" s="16" t="inlineStr">
+        <is>
+          <t>~10:45</t>
+        </is>
+      </c>
+      <c r="N117" s="16" t="inlineStr"/>
+      <c r="O117" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2014000&amp;nnst2=2000000</t>
+        </is>
+      </c>
+      <c r="P117" s="16" t="inlineStr">
+        <is>
+          <t>Или 213*С 21:09 — прямо до Голутвина (Коломна) в 04:50</t>
+        </is>
+      </c>
+      <c r="Q117" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="15" t="inlineStr">
+        <is>
+          <t>Орёл</t>
+        </is>
+      </c>
+      <c r="B118" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C118" s="16" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D118" s="16" t="inlineStr">
+        <is>
+          <t>Альтернатива: поезд</t>
+        </is>
+      </c>
+      <c r="E118" s="16" t="inlineStr">
+        <is>
+          <t>Поезд, купе</t>
+        </is>
+      </c>
+      <c r="F118" s="16" t="inlineStr">
+        <is>
+          <t>084С</t>
+        </is>
+      </c>
+      <c r="G118" s="16" t="inlineStr">
+        <is>
+          <t>27.10 23:37</t>
+        </is>
+      </c>
+      <c r="H118" s="16" t="inlineStr">
+        <is>
+          <t>28.10 08:40</t>
+        </is>
+      </c>
+      <c r="I118" s="16" t="inlineStr">
+        <is>
+          <t>Москва, Киевский</t>
+        </is>
+      </c>
+      <c r="J118" s="24" t="n">
+        <v>3655</v>
+      </c>
+      <c r="K118" s="24" t="n">
+        <v>3655</v>
+      </c>
+      <c r="L118" s="16" t="inlineStr">
+        <is>
+          <t>Киевский → метро до Комсомольской (~25 мин) → электричка + такси (09:48 → 11:36)</t>
+        </is>
+      </c>
+      <c r="M118" s="16" t="inlineStr">
+        <is>
+          <t>~12:00</t>
+        </is>
+      </c>
+      <c r="N118" s="16" t="inlineStr"/>
+      <c r="O118" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2000140&amp;nnst2=2000000</t>
+        </is>
+      </c>
+      <c r="P118" s="16" t="inlineStr">
+        <is>
+          <t>Основной вариант — машина вместе с Брянском</t>
+        </is>
+      </c>
+      <c r="Q118" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="15" t="inlineStr">
+        <is>
           <t>Брянск</t>
         </is>
       </c>
-      <c r="B114" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C114" s="16" t="inlineStr">
+      <c r="B119" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C119" s="16" t="inlineStr">
         <is>
           <t>В1: к 15:00 28.10</t>
         </is>
       </c>
-      <c r="D114" s="16" t="inlineStr">
+      <c r="D119" s="16" t="inlineStr">
         <is>
           <t>Альтернатива: поезд</t>
         </is>
       </c>
-      <c r="E114" s="16" t="inlineStr">
+      <c r="E119" s="16" t="inlineStr">
         <is>
           <t>Поезд, сидячий (купе 3 180)</t>
         </is>
       </c>
-      <c r="F114" s="16" t="inlineStr">
+      <c r="F119" s="16" t="inlineStr">
         <is>
           <t>086Щ</t>
         </is>
       </c>
-      <c r="G114" s="16" t="inlineStr">
+      <c r="G119" s="16" t="inlineStr">
         <is>
           <t>28.10 00:20</t>
         </is>
       </c>
-      <c r="H114" s="16" t="inlineStr">
+      <c r="H119" s="16" t="inlineStr">
         <is>
           <t>28.10 06:20</t>
         </is>
       </c>
-      <c r="I114" s="16" t="inlineStr">
+      <c r="I119" s="16" t="inlineStr">
         <is>
           <t>Москва, Киевский</t>
         </is>
       </c>
-      <c r="J114" s="24" t="n">
+      <c r="J119" s="24" t="n">
         <v>1749</v>
       </c>
-      <c r="K114" s="24" t="n">
+      <c r="K119" s="24" t="n">
         <v>1749</v>
       </c>
-      <c r="L114" s="16" t="inlineStr">
+      <c r="L119" s="16" t="inlineStr">
         <is>
           <t>Киевский → метро до Комсомольской (~25 мин) → электричка + такси (07:22 → 09:15)</t>
         </is>
       </c>
-      <c r="M114" s="16" t="inlineStr">
+      <c r="M119" s="16" t="inlineStr">
         <is>
           <t>~09:30</t>
         </is>
       </c>
-      <c r="N114" s="16" t="inlineStr">
+      <c r="N119" s="16" t="inlineStr">
         <is>
           <t>ранний заезд</t>
         </is>
       </c>
-      <c r="O114" s="19" t="inlineStr">
+      <c r="O119" s="19" t="inlineStr">
         <is>
           <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2000427&amp;nnst2=2000000</t>
         </is>
       </c>
-      <c r="P114" s="16" t="inlineStr">
+      <c r="P119" s="16" t="inlineStr">
         <is>
           <t>Время по расписанию 27.10. Основной вариант — машина</t>
         </is>
       </c>
-      <c r="Q114" s="16" t="inlineStr">
+      <c r="Q119" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q114"/>
+  <autoFilter ref="A1:Q119"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
@@ -11636,13 +12038,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O103" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O104" r:id="rId87"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O106" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O108" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O109" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O110" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O107" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O108" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O109" r:id="rId91"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O111" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O112" r:id="rId93"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O113" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O114" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O115" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O116" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O117" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O118" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O119" r:id="rId100"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13205,7 +13612,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Строки с пометкой «проверить» посчитаны по расписанию соседнего дня. Донецк — уточнить город и способ проезда.</t>
+          <t>Строки с пометкой «проверить» посчитаны по расписанию соседнего дня. Донецк: автобусы из ДНР продаются у перевозчиков, не на Туту; многие ходят через день — уточнить дату.</t>
         </is>
       </c>
     </row>

--- a/Коломна_маршруты_28-30.10.2026.xlsx
+++ b/Коломна_маршруты_28-30.10.2026.xlsx
@@ -15,8 +15,8 @@
     <sheet name="Правила и допущения" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Сводка по сотрудникам'!$A$4:$S$43</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Маршруты'!$A$1:$Q$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Сводка по сотрудникам'!$A$4:$S$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Маршруты'!$A$1:$Q$156</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -571,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S45"/>
+  <dimension ref="A1:S66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="S29" s="5" t="inlineStr">
         <is>
-          <t>Такси на 4 чел. из Домодедово</t>
+          <t>Едет вместе с отцом (Друсалевич В.А.). Такси на 4 чел. из Домодедово</t>
         </is>
       </c>
     </row>
@@ -3571,33 +3571,1545 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="12" t="inlineStr">
+      <c r="A44" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Друсалевич Владимир Анатольевич</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Иркутск</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>Самолёт</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>12305</v>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>15862</v>
+      </c>
+      <c r="H44" s="6" t="n">
+        <v>12308</v>
+      </c>
+      <c r="I44" s="6" t="n">
+        <v>15879</v>
+      </c>
+      <c r="J44" s="6" t="n">
+        <v>1800</v>
+      </c>
+      <c r="K44" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" s="8">
+        <f>F44+H44+J44+K44*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="M44" s="8">
+        <f>G44+I44+J44+K44*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="N44" s="9" t="n">
+        <v>22210</v>
+      </c>
+      <c r="O44" s="9" t="n">
+        <v>19332</v>
+      </c>
+      <c r="P44" s="9" t="n">
+        <v>1800</v>
+      </c>
+      <c r="Q44" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R44" s="11">
+        <f>N44+O44+P44+Q44*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="S44" s="5" t="inlineStr">
+        <is>
+          <t>Едет вместе с сыном (Друсалевич В.В.). Такси на 4 чел. из Домодедово</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Колчин Андрей Ильич</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>уточнить</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Электричка / авто</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>490</v>
+      </c>
+      <c r="G45" s="6" t="n">
+        <v>490</v>
+      </c>
+      <c r="H45" s="6" t="n">
+        <v>490</v>
+      </c>
+      <c r="I45" s="6" t="n">
+        <v>490</v>
+      </c>
+      <c r="J45" s="6" t="n">
+        <v>800</v>
+      </c>
+      <c r="K45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="8">
+        <f>F45+H45+J45+K45*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="M45" s="8">
+        <f>G45+I45+J45+K45*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="N45" s="9" t="n">
+        <v>750</v>
+      </c>
+      <c r="O45" s="9" t="n">
+        <v>750</v>
+      </c>
+      <c r="P45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" s="11">
+        <f>N45+O45+P45+Q45*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="S45" s="5" t="inlineStr">
+        <is>
+          <t>Удобный — своя машина</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Мордвинов Сергей Анатольевич</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>уточнить</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>Электричка / авто</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>490</v>
+      </c>
+      <c r="G46" s="6" t="n">
+        <v>490</v>
+      </c>
+      <c r="H46" s="6" t="n">
+        <v>490</v>
+      </c>
+      <c r="I46" s="6" t="n">
+        <v>490</v>
+      </c>
+      <c r="J46" s="6" t="n">
+        <v>800</v>
+      </c>
+      <c r="K46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="8">
+        <f>F46+H46+J46+K46*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="M46" s="8">
+        <f>G46+I46+J46+K46*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="N46" s="9" t="n">
+        <v>750</v>
+      </c>
+      <c r="O46" s="9" t="n">
+        <v>750</v>
+      </c>
+      <c r="P46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" s="11">
+        <f>N46+O46+P46+Q46*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="S46" s="5" t="inlineStr">
+        <is>
+          <t>Удобный — своя машина</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Бабкин Виктор Александрович</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>уточнить</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Нижний Новгород</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Поезд</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>2435</v>
+      </c>
+      <c r="G47" s="6" t="n">
+        <v>2435</v>
+      </c>
+      <c r="H47" s="6" t="n">
+        <v>2347</v>
+      </c>
+      <c r="I47" s="6" t="n">
+        <v>2347</v>
+      </c>
+      <c r="J47" s="6" t="n">
+        <v>1800</v>
+      </c>
+      <c r="K47" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="8">
+        <f>F47+H47+J47+K47*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="M47" s="8">
+        <f>G47+I47+J47+K47*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="N47" s="9" t="n">
+        <v>4460</v>
+      </c>
+      <c r="O47" s="9" t="n">
+        <v>5172</v>
+      </c>
+      <c r="P47" s="9" t="n">
+        <v>1800</v>
+      </c>
+      <c r="Q47" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" s="11">
+        <f>N47+O47+P47+Q47*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="S47" s="5" t="inlineStr">
+        <is>
+          <t>Ласточка / ночной поезд</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Полин Денис Валериевич</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>уточнить</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Рязань</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>Электричка / авто</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>306</v>
+      </c>
+      <c r="G48" s="6" t="n">
+        <v>306</v>
+      </c>
+      <c r="H48" s="6" t="n">
+        <v>306</v>
+      </c>
+      <c r="I48" s="6" t="n">
+        <v>306</v>
+      </c>
+      <c r="J48" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="K48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="8">
+        <f>F48+H48+J48+K48*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="M48" s="8">
+        <f>G48+I48+J48+K48*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="N48" s="9" t="n">
+        <v>650</v>
+      </c>
+      <c r="O48" s="9" t="n">
+        <v>650</v>
+      </c>
+      <c r="P48" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" s="11">
+        <f>N48+O48+P48+Q48*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="S48" s="5" t="inlineStr">
+        <is>
+          <t>Удобный — своя машина (~100 км)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Летягина Евгения Андреевна</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>СПб (юг)</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Поезд</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>3272</v>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>3272</v>
+      </c>
+      <c r="H49" s="6" t="n">
+        <v>2185</v>
+      </c>
+      <c r="I49" s="6" t="n">
+        <v>2185</v>
+      </c>
+      <c r="J49" s="6" t="n">
+        <v>1800</v>
+      </c>
+      <c r="K49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="8">
+        <f>F49+H49+J49+K49*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="M49" s="8">
+        <f>G49+I49+J49+K49*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="N49" s="9" t="n">
+        <v>3975</v>
+      </c>
+      <c r="O49" s="9" t="n">
+        <v>5093</v>
+      </c>
+      <c r="P49" s="9" t="n">
+        <v>1800</v>
+      </c>
+      <c r="Q49" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" s="11">
+        <f>N49+O49+P49+Q49*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="S49" s="5" t="inlineStr">
+        <is>
+          <t>Ночные поезда; Ленинградский рядом с Казанским</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Понамарёв Василий Васильевич</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Смоленск, В.Луки</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>Смоленск</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>Поезд</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>1832</v>
+      </c>
+      <c r="G50" s="6" t="n">
+        <v>1832</v>
+      </c>
+      <c r="H50" s="6" t="n">
+        <v>4022</v>
+      </c>
+      <c r="I50" s="6" t="n">
+        <v>4022</v>
+      </c>
+      <c r="J50" s="6" t="n">
+        <v>1800</v>
+      </c>
+      <c r="K50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="8">
+        <f>F50+H50+J50+K50*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="M50" s="8">
+        <f>G50+I50+J50+K50*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="N50" s="9" t="n">
+        <v>4656</v>
+      </c>
+      <c r="O50" s="9" t="n">
+        <v>4656</v>
+      </c>
+      <c r="P50" s="9" t="n">
+        <v>1800</v>
+      </c>
+      <c r="Q50" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" s="11">
+        <f>N50+O50+P50+Q50*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="S50" s="5" t="inlineStr">
+        <is>
+          <t>Ласточка туда, ночной поезд обратно</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Пирогов Игорь Владимирович</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>уточнить</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Тверь</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Поезд / авто</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>695</v>
+      </c>
+      <c r="G51" s="6" t="n">
+        <v>695</v>
+      </c>
+      <c r="H51" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I51" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J51" s="6" t="n">
+        <v>1800</v>
+      </c>
+      <c r="K51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="8">
+        <f>F51+H51+J51+K51*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="M51" s="8">
+        <f>G51+I51+J51+K51*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="N51" s="9" t="n">
+        <v>1885</v>
+      </c>
+      <c r="O51" s="9" t="n">
+        <v>1885</v>
+      </c>
+      <c r="P51" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" s="11">
+        <f>N51+O51+P51+Q51*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="S51" s="5" t="inlineStr">
+        <is>
+          <t>Удобный — своя машина</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Смирнов Игорь Алексеевич</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>Собственник</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>Самолёт</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="n">
+        <v>7811</v>
+      </c>
+      <c r="G52" s="6" t="n">
+        <v>10789</v>
+      </c>
+      <c r="H52" s="6" t="n">
+        <v>9104</v>
+      </c>
+      <c r="I52" s="6" t="n">
+        <v>12205</v>
+      </c>
+      <c r="J52" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="8">
+        <f>F52+H52+J52+K52*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="M52" s="8">
+        <f>G52+I52+J52+K52*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="N52" s="9" t="n">
+        <v>11932</v>
+      </c>
+      <c r="O52" s="9" t="n">
+        <v>13388</v>
+      </c>
+      <c r="P52" s="9" t="n">
+        <v>2200</v>
+      </c>
+      <c r="Q52" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" s="11">
+        <f>N52+O52+P52+Q52*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="S52" s="5" t="inlineStr">
+        <is>
+          <t>Едет вместе с дочерью (Смирнова Ю.И.). Группа 10 чел. одним рейсом; минивэны из Домодедово</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Догодаева Екатерина Николаевна</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>уточнить</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>Самолёт</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="n">
+        <v>7811</v>
+      </c>
+      <c r="G53" s="6" t="n">
+        <v>10789</v>
+      </c>
+      <c r="H53" s="6" t="n">
+        <v>9104</v>
+      </c>
+      <c r="I53" s="6" t="n">
+        <v>12205</v>
+      </c>
+      <c r="J53" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K53" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="8">
+        <f>F53+H53+J53+K53*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="M53" s="8">
+        <f>G53+I53+J53+K53*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="N53" s="9" t="n">
+        <v>11932</v>
+      </c>
+      <c r="O53" s="9" t="n">
+        <v>13388</v>
+      </c>
+      <c r="P53" s="9" t="n">
+        <v>2200</v>
+      </c>
+      <c r="Q53" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" s="11">
+        <f>N53+O53+P53+Q53*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="S53" s="5" t="inlineStr">
+        <is>
+          <t>Группа 10 чел. одним рейсом; минивэны из Домодедово</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>Дудник Светлана Васильевна</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>уточнить</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>Самолёт</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="n">
+        <v>7811</v>
+      </c>
+      <c r="G54" s="6" t="n">
+        <v>10789</v>
+      </c>
+      <c r="H54" s="6" t="n">
+        <v>9104</v>
+      </c>
+      <c r="I54" s="6" t="n">
+        <v>12205</v>
+      </c>
+      <c r="J54" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="8">
+        <f>F54+H54+J54+K54*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="M54" s="8">
+        <f>G54+I54+J54+K54*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="N54" s="9" t="n">
+        <v>11932</v>
+      </c>
+      <c r="O54" s="9" t="n">
+        <v>13388</v>
+      </c>
+      <c r="P54" s="9" t="n">
+        <v>2200</v>
+      </c>
+      <c r="Q54" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" s="11">
+        <f>N54+O54+P54+Q54*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="S54" s="5" t="inlineStr">
+        <is>
+          <t>Группа 10 чел. одним рейсом; минивэны из Домодедово</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Девлешова Татьяна Владимировна</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>уточнить</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>Самолёт</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>7811</v>
+      </c>
+      <c r="G55" s="6" t="n">
+        <v>10789</v>
+      </c>
+      <c r="H55" s="6" t="n">
+        <v>9104</v>
+      </c>
+      <c r="I55" s="6" t="n">
+        <v>12205</v>
+      </c>
+      <c r="J55" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="8">
+        <f>F55+H55+J55+K55*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="M55" s="8">
+        <f>G55+I55+J55+K55*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="N55" s="9" t="n">
+        <v>11932</v>
+      </c>
+      <c r="O55" s="9" t="n">
+        <v>13388</v>
+      </c>
+      <c r="P55" s="9" t="n">
+        <v>2200</v>
+      </c>
+      <c r="Q55" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" s="11">
+        <f>N55+O55+P55+Q55*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="S55" s="5" t="inlineStr">
+        <is>
+          <t>Группа 10 чел. одним рейсом; минивэны из Домодедово</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>Володина Людмила Эдуардовна</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>уточнить</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>Самолёт</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>7811</v>
+      </c>
+      <c r="G56" s="6" t="n">
+        <v>10789</v>
+      </c>
+      <c r="H56" s="6" t="n">
+        <v>9104</v>
+      </c>
+      <c r="I56" s="6" t="n">
+        <v>12205</v>
+      </c>
+      <c r="J56" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="8">
+        <f>F56+H56+J56+K56*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="M56" s="8">
+        <f>G56+I56+J56+K56*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="N56" s="9" t="n">
+        <v>11932</v>
+      </c>
+      <c r="O56" s="9" t="n">
+        <v>13388</v>
+      </c>
+      <c r="P56" s="9" t="n">
+        <v>2200</v>
+      </c>
+      <c r="Q56" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" s="11">
+        <f>N56+O56+P56+Q56*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="S56" s="5" t="inlineStr">
+        <is>
+          <t>Группа 10 чел. одним рейсом; минивэны из Домодедово</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Шакирзянова Надежда Александровна</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>уточнить</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>Самолёт</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>7811</v>
+      </c>
+      <c r="G57" s="6" t="n">
+        <v>10789</v>
+      </c>
+      <c r="H57" s="6" t="n">
+        <v>9104</v>
+      </c>
+      <c r="I57" s="6" t="n">
+        <v>12205</v>
+      </c>
+      <c r="J57" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K57" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="8">
+        <f>F57+H57+J57+K57*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="M57" s="8">
+        <f>G57+I57+J57+K57*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="N57" s="9" t="n">
+        <v>11932</v>
+      </c>
+      <c r="O57" s="9" t="n">
+        <v>13388</v>
+      </c>
+      <c r="P57" s="9" t="n">
+        <v>2200</v>
+      </c>
+      <c r="Q57" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" s="11">
+        <f>N57+O57+P57+Q57*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="S57" s="5" t="inlineStr">
+        <is>
+          <t>Группа 10 чел. одним рейсом; минивэны из Домодедово</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>Смирнова Юлия Игоревна</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>уточнить</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>Самолёт</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="n">
+        <v>7811</v>
+      </c>
+      <c r="G58" s="6" t="n">
+        <v>10789</v>
+      </c>
+      <c r="H58" s="6" t="n">
+        <v>9104</v>
+      </c>
+      <c r="I58" s="6" t="n">
+        <v>12205</v>
+      </c>
+      <c r="J58" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="8">
+        <f>F58+H58+J58+K58*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="M58" s="8">
+        <f>G58+I58+J58+K58*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="N58" s="9" t="n">
+        <v>11932</v>
+      </c>
+      <c r="O58" s="9" t="n">
+        <v>13388</v>
+      </c>
+      <c r="P58" s="9" t="n">
+        <v>2200</v>
+      </c>
+      <c r="Q58" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" s="11">
+        <f>N58+O58+P58+Q58*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="S58" s="5" t="inlineStr">
+        <is>
+          <t>Едет вместе с отцом (Смирнов И.А.). Группа 10 чел. одним рейсом; минивэны из Домодедово</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Микушин Евгений Геннадьевич</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>уточнить</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>Самолёт</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>7811</v>
+      </c>
+      <c r="G59" s="6" t="n">
+        <v>10789</v>
+      </c>
+      <c r="H59" s="6" t="n">
+        <v>9104</v>
+      </c>
+      <c r="I59" s="6" t="n">
+        <v>12205</v>
+      </c>
+      <c r="J59" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K59" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" s="8">
+        <f>F59+H59+J59+K59*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="M59" s="8">
+        <f>G59+I59+J59+K59*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="N59" s="9" t="n">
+        <v>11932</v>
+      </c>
+      <c r="O59" s="9" t="n">
+        <v>13388</v>
+      </c>
+      <c r="P59" s="9" t="n">
+        <v>2200</v>
+      </c>
+      <c r="Q59" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" s="11">
+        <f>N59+O59+P59+Q59*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="S59" s="5" t="inlineStr">
+        <is>
+          <t>Группа 10 чел. одним рейсом; минивэны из Домодедово</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>Устюгов Дмитрий Николаевич</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>уточнить</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>Самолёт</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>7811</v>
+      </c>
+      <c r="G60" s="6" t="n">
+        <v>10789</v>
+      </c>
+      <c r="H60" s="6" t="n">
+        <v>9104</v>
+      </c>
+      <c r="I60" s="6" t="n">
+        <v>12205</v>
+      </c>
+      <c r="J60" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K60" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="8">
+        <f>F60+H60+J60+K60*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="M60" s="8">
+        <f>G60+I60+J60+K60*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="N60" s="9" t="n">
+        <v>11932</v>
+      </c>
+      <c r="O60" s="9" t="n">
+        <v>13388</v>
+      </c>
+      <c r="P60" s="9" t="n">
+        <v>2200</v>
+      </c>
+      <c r="Q60" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" s="11">
+        <f>N60+O60+P60+Q60*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="S60" s="5" t="inlineStr">
+        <is>
+          <t>Группа 10 чел. одним рейсом; минивэны из Домодедово</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Мелентьев Евгений</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>Екатеринбург-север</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>Самолёт</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>7811</v>
+      </c>
+      <c r="G61" s="6" t="n">
+        <v>10789</v>
+      </c>
+      <c r="H61" s="6" t="n">
+        <v>9104</v>
+      </c>
+      <c r="I61" s="6" t="n">
+        <v>12205</v>
+      </c>
+      <c r="J61" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K61" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="8">
+        <f>F61+H61+J61+K61*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="M61" s="8">
+        <f>G61+I61+J61+K61*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="N61" s="9" t="n">
+        <v>11932</v>
+      </c>
+      <c r="O61" s="9" t="n">
+        <v>13388</v>
+      </c>
+      <c r="P61" s="9" t="n">
+        <v>2200</v>
+      </c>
+      <c r="Q61" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" s="11">
+        <f>N61+O61+P61+Q61*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="S61" s="5" t="inlineStr">
+        <is>
+          <t>Группа 10 чел. одним рейсом; минивэны из Домодедово</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>Фирстов Виктор Юрьевич</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>Златоуст, Челябинск</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>Челябинск</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>Самолёт</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="n">
+        <v>6196</v>
+      </c>
+      <c r="G62" s="6" t="n">
+        <v>8991</v>
+      </c>
+      <c r="H62" s="6" t="n">
+        <v>7789</v>
+      </c>
+      <c r="I62" s="6" t="n">
+        <v>10643</v>
+      </c>
+      <c r="J62" s="6" t="n">
+        <v>1800</v>
+      </c>
+      <c r="K62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="8">
+        <f>F62+H62+J62+K62*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="M62" s="8">
+        <f>G62+I62+J62+K62*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="N62" s="9" t="n">
+        <v>14081</v>
+      </c>
+      <c r="O62" s="9" t="n">
+        <v>10643</v>
+      </c>
+      <c r="P62" s="9" t="n">
+        <v>9800</v>
+      </c>
+      <c r="Q62" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" s="11">
+        <f>N62+O62+P62+Q62*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="S62" s="5" t="inlineStr">
+        <is>
+          <t>Если из Златоуста — +~150 км до аэропорта</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Бобошин Сергей Аркадьевич</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>Курган, Сургут, Тюмень</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Тюмень</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>Самолёт</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="n">
+        <v>5873</v>
+      </c>
+      <c r="G63" s="6" t="n">
+        <v>8712</v>
+      </c>
+      <c r="H63" s="6" t="n">
+        <v>8168</v>
+      </c>
+      <c r="I63" s="6" t="n">
+        <v>11154</v>
+      </c>
+      <c r="J63" s="6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K63" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" s="8">
+        <f>F63+H63+J63+K63*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="M63" s="8">
+        <f>G63+I63+J63+K63*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="N63" s="9" t="n">
+        <v>10125</v>
+      </c>
+      <c r="O63" s="9" t="n">
+        <v>11154</v>
+      </c>
+      <c r="P63" s="9" t="n">
+        <v>9800</v>
+      </c>
+      <c r="Q63" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" s="11">
+        <f>N63+O63+P63+Q63*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="S63" s="5" t="inlineStr">
+        <is>
+          <t>Уточнить, вылет из Тюмени или Сургута/Кургана</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>Федоров Константин Иванович</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>уточнить</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>Нижний Тагил</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>Самолёт</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="n">
+        <v>7811</v>
+      </c>
+      <c r="G64" s="6" t="n">
+        <v>10789</v>
+      </c>
+      <c r="H64" s="6" t="n">
+        <v>9104</v>
+      </c>
+      <c r="I64" s="6" t="n">
+        <v>12205</v>
+      </c>
+      <c r="J64" s="6" t="n">
+        <v>4400</v>
+      </c>
+      <c r="K64" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" s="8">
+        <f>F64+H64+J64+K64*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="M64" s="8">
+        <f>G64+I64+J64+K64*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="N64" s="9" t="n">
+        <v>11932</v>
+      </c>
+      <c r="O64" s="9" t="n">
+        <v>13388</v>
+      </c>
+      <c r="P64" s="9" t="n">
+        <v>10200</v>
+      </c>
+      <c r="Q64" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" s="11">
+        <f>N64+O64+P64+Q64*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="S64" s="5" t="inlineStr">
+        <is>
+          <t>С группой Екатеринбурга; вкл. подвоз до Кольцово и обратно</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="12" t="inlineStr">
         <is>
           <t>ИТОГО по списку</t>
         </is>
       </c>
-      <c r="L44" s="13">
-        <f>SUM(L5:L43)</f>
-        <v/>
-      </c>
-      <c r="M44" s="13">
-        <f>SUM(M5:M43)</f>
-        <v/>
-      </c>
-      <c r="R44" s="13">
-        <f>SUM(R5:R43)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="14" t="inlineStr">
-        <is>
-          <t>Сотрудников в списке: 39 . Ориентир на 65 человек — пропорционально.</t>
+      <c r="L65" s="13">
+        <f>SUM(L5:L64)</f>
+        <v/>
+      </c>
+      <c r="M65" s="13">
+        <f>SUM(M5:M64)</f>
+        <v/>
+      </c>
+      <c r="R65" s="13">
+        <f>SUM(R5:R64)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сотрудников в списке: 60 . </t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:S43"/>
+  <autoFilter ref="A4:S64"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3608,7 +5120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q119"/>
+  <dimension ref="A1:Q156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11403,72 +12915,72 @@
     <row r="113">
       <c r="A113" s="15" t="inlineStr">
         <is>
-          <t>Пенза</t>
+          <t>Екатеринбург (группа)</t>
         </is>
       </c>
       <c r="B113" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C113" s="16" t="inlineStr">
+        <v>11</v>
+      </c>
+      <c r="C113" s="17" t="inlineStr">
         <is>
           <t>В1: к 15:00 28.10</t>
         </is>
       </c>
-      <c r="D113" s="16" t="inlineStr">
-        <is>
-          <t>Альтернатива: поезд</t>
-        </is>
-      </c>
-      <c r="E113" s="16" t="inlineStr">
-        <is>
-          <t>Поезд «Сура», купе (сидячий 3 030)</t>
-        </is>
-      </c>
-      <c r="F113" s="16" t="inlineStr">
-        <is>
-          <t>052М</t>
+      <c r="D113" s="17" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E113" s="17" t="inlineStr">
+        <is>
+          <t>Самолёт, Уральские авиалинии</t>
+        </is>
+      </c>
+      <c r="F113" s="17" t="inlineStr">
+        <is>
+          <t>U6-264</t>
         </is>
       </c>
       <c r="G113" s="16" t="inlineStr">
         <is>
-          <t>27.10 21:35</t>
+          <t>28.10 06:50 (мест.)</t>
         </is>
       </c>
       <c r="H113" s="16" t="inlineStr">
         <is>
-          <t>28.10 07:59</t>
+          <t>28.10 07:25</t>
         </is>
       </c>
       <c r="I113" s="16" t="inlineStr">
         <is>
-          <t>Москва, Казанский</t>
-        </is>
-      </c>
-      <c r="J113" s="24" t="n">
-        <v>3967</v>
-      </c>
-      <c r="K113" s="24" t="n">
-        <v>3967</v>
+          <t>Домодедово</t>
+        </is>
+      </c>
+      <c r="J113" s="18" t="n">
+        <v>7811</v>
+      </c>
+      <c r="K113" s="18" t="n">
+        <v>10789</v>
       </c>
       <c r="L113" s="16" t="inlineStr">
         <is>
-          <t>Казанский вокзал → электричка до ст. Коломна (490–620 ₽) + такси 10 мин (~300 ₽) (09:48 → 11:36)</t>
+          <t>Домодедово: такси 1 ч 45 мин + 40 мин на выход (группа 2–4 чел.) — 2 минивэна на группу</t>
         </is>
       </c>
       <c r="M113" s="16" t="inlineStr">
         <is>
-          <t>~12:00</t>
+          <t>~09:50</t>
         </is>
       </c>
       <c r="N113" s="16" t="inlineStr"/>
       <c r="O113" s="19" t="inlineStr">
         <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2024120&amp;nnst2=2000000</t>
+          <t>https://avia.tutu.ru/f/Ekaterinburg/Moskva/?class=Y&amp;travelers=1&amp;route[0]=29-28102026-491</t>
         </is>
       </c>
       <c r="P113" s="16" t="inlineStr">
         <is>
-          <t>Основной вариант — машина (лист «Авто»)</t>
+          <t>Цена за 1 чел. при покупке 9 билетов сразу (места есть). На 10–11 чел. — запросить групповой тариф у авиакомпании</t>
         </is>
       </c>
       <c r="Q113" s="16" t="inlineStr">
@@ -11478,321 +12990,269 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="15" t="inlineStr">
-        <is>
-          <t>Саранск</t>
-        </is>
-      </c>
-      <c r="B114" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C114" s="16" t="inlineStr">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>Екатеринбург (группа)</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C114" s="10" t="inlineStr">
         <is>
           <t>В1: к 15:00 28.10</t>
         </is>
       </c>
-      <c r="D114" s="16" t="inlineStr">
-        <is>
-          <t>Альтернатива: поезд</t>
-        </is>
-      </c>
-      <c r="E114" s="16" t="inlineStr">
-        <is>
-          <t>Поезд, купе</t>
-        </is>
-      </c>
-      <c r="F114" s="16" t="inlineStr">
-        <is>
-          <t>041Й</t>
-        </is>
-      </c>
-      <c r="G114" s="16" t="inlineStr">
-        <is>
-          <t>27.10 20:40</t>
-        </is>
-      </c>
-      <c r="H114" s="16" t="inlineStr">
-        <is>
-          <t>28.10 05:50</t>
-        </is>
-      </c>
-      <c r="I114" s="16" t="inlineStr">
-        <is>
-          <t>Москва, Казанский</t>
-        </is>
-      </c>
-      <c r="J114" s="24" t="n">
-        <v>4394</v>
-      </c>
-      <c r="K114" s="24" t="n">
-        <v>4394</v>
-      </c>
-      <c r="L114" s="16" t="inlineStr">
-        <is>
-          <t>Казанский вокзал → электричка до ст. Коломна (490–620 ₽) + такси 10 мин (~300 ₽) (07:22 → 09:15)</t>
-        </is>
-      </c>
-      <c r="M114" s="16" t="inlineStr">
-        <is>
-          <t>~09:30</t>
-        </is>
-      </c>
-      <c r="N114" s="16" t="inlineStr">
-        <is>
-          <t>ранний заезд</t>
-        </is>
-      </c>
-      <c r="O114" s="19" t="inlineStr">
-        <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2024700&amp;nnst2=2000000</t>
-        </is>
-      </c>
-      <c r="P114" s="16" t="inlineStr">
-        <is>
-          <t>Основной вариант — машина</t>
-        </is>
-      </c>
-      <c r="Q114" s="16" t="inlineStr">
+      <c r="D114" s="10" t="inlineStr">
+        <is>
+          <t>Удобный</t>
+        </is>
+      </c>
+      <c r="E114" s="10" t="inlineStr">
+        <is>
+          <t>Самолёт, Уральские авиалинии</t>
+        </is>
+      </c>
+      <c r="F114" s="10" t="inlineStr">
+        <is>
+          <t>U6-262</t>
+        </is>
+      </c>
+      <c r="G114" s="5" t="inlineStr">
+        <is>
+          <t>28.10 08:15 (мест.)</t>
+        </is>
+      </c>
+      <c r="H114" s="5" t="inlineStr">
+        <is>
+          <t>28.10 08:55</t>
+        </is>
+      </c>
+      <c r="I114" s="5" t="inlineStr">
+        <is>
+          <t>Домодедово</t>
+        </is>
+      </c>
+      <c r="J114" s="9" t="n">
+        <v>8875</v>
+      </c>
+      <c r="K114" s="9" t="n">
+        <v>11932</v>
+      </c>
+      <c r="L114" s="5" t="inlineStr">
+        <is>
+          <t>Домодедово: такси 1 ч 45 мин + 40 мин на выход (группа 2–4 чел.) — 2 минивэна</t>
+        </is>
+      </c>
+      <c r="M114" s="5" t="inlineStr">
+        <is>
+          <t>~11:20</t>
+        </is>
+      </c>
+      <c r="N114" s="5" t="inlineStr"/>
+      <c r="O114" s="20" t="inlineStr">
+        <is>
+          <t>https://avia.tutu.ru/f/Ekaterinburg/Moskva/?class=Y&amp;travelers=1&amp;route[0]=29-28102026-491</t>
+        </is>
+      </c>
+      <c r="P114" s="5" t="inlineStr">
+        <is>
+          <t>Также DP-404 06:50→Внуково 07:30, 8 173 / 11 151</t>
+        </is>
+      </c>
+      <c r="Q114" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="15" t="inlineStr">
-        <is>
-          <t>Тамбов</t>
-        </is>
-      </c>
-      <c r="B115" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C115" s="16" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D115" s="16" t="inlineStr">
-        <is>
-          <t>Альтернатива: поезд</t>
-        </is>
-      </c>
-      <c r="E115" s="16" t="inlineStr">
-        <is>
-          <t>Поезд, сидячий (купе 2 868)</t>
-        </is>
-      </c>
-      <c r="F115" s="16" t="inlineStr">
-        <is>
-          <t>135Ж</t>
-        </is>
-      </c>
-      <c r="G115" s="16" t="inlineStr">
-        <is>
-          <t>27.10 21:56</t>
-        </is>
-      </c>
-      <c r="H115" s="16" t="inlineStr">
-        <is>
-          <t>28.10 07:22</t>
-        </is>
-      </c>
-      <c r="I115" s="16" t="inlineStr">
-        <is>
-          <t>Москва, Павелецкий</t>
-        </is>
-      </c>
-      <c r="J115" s="24" t="n">
-        <v>1979</v>
-      </c>
-      <c r="K115" s="24" t="n">
-        <v>1979</v>
-      </c>
-      <c r="L115" s="16" t="inlineStr">
-        <is>
-          <t>Павелецкий → метро до Комсомольской (~20 мин) → электричка от Казанского + такси (08:47 РЭКС → 10:28)</t>
-        </is>
-      </c>
-      <c r="M115" s="16" t="inlineStr">
-        <is>
-          <t>~10:45</t>
-        </is>
-      </c>
-      <c r="N115" s="16" t="inlineStr"/>
-      <c r="O115" s="19" t="inlineStr">
-        <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2014700&amp;nnst2=2000000</t>
-        </is>
-      </c>
-      <c r="P115" s="16" t="inlineStr">
-        <is>
-          <t>Основной вариант — машина. Купе осталось 1 место</t>
-        </is>
-      </c>
-      <c r="Q115" s="16" t="inlineStr">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>Екатеринбург (группа)</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>В2: после 15:00 28.10 / В3: к утру 29.10</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>не требуется</t>
+        </is>
+      </c>
+      <c r="F115" s="5" t="inlineStr"/>
+      <c r="G115" s="5" t="inlineStr"/>
+      <c r="H115" s="5" t="inlineStr"/>
+      <c r="I115" s="5" t="inlineStr"/>
+      <c r="J115" s="5" t="n"/>
+      <c r="K115" s="5" t="n"/>
+      <c r="L115" s="5" t="inlineStr"/>
+      <c r="M115" s="5" t="inlineStr"/>
+      <c r="N115" s="5" t="inlineStr"/>
+      <c r="O115" s="5" t="inlineStr"/>
+      <c r="P115" s="5" t="inlineStr">
+        <is>
+          <t>Подходит В1. Запасной: U6-300 12:00→DME 12:40, 10 289 / 13 395</t>
+        </is>
+      </c>
+      <c r="Q115" s="5" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>Екатеринбург (группа)</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C116" s="7" t="inlineStr">
+        <is>
+          <t>Обратно</t>
+        </is>
+      </c>
+      <c r="D116" s="7" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="inlineStr">
+        <is>
+          <t>Самолёт, Победа</t>
+        </is>
+      </c>
+      <c r="F116" s="7" t="inlineStr">
+        <is>
+          <t>DP-403</t>
+        </is>
+      </c>
+      <c r="G116" s="5" t="inlineStr">
+        <is>
+          <t>30.10 23:50</t>
+        </is>
+      </c>
+      <c r="H116" s="5" t="inlineStr">
+        <is>
+          <t>31.10 04:20 (мест.)</t>
+        </is>
+      </c>
+      <c r="I116" s="5" t="inlineStr">
+        <is>
+          <t>Внуково</t>
+        </is>
+      </c>
+      <c r="J116" s="6" t="n">
+        <v>9104</v>
+      </c>
+      <c r="K116" s="6" t="n">
+        <v>12205</v>
+      </c>
+      <c r="L116" s="5" t="inlineStr">
+        <is>
+          <t>Выезд из гостиницы 18:15; в аэропорту за 2 ч до вылета — минивэн до Внуково</t>
+        </is>
+      </c>
+      <c r="M116" s="5" t="inlineStr"/>
+      <c r="N116" s="5" t="inlineStr"/>
+      <c r="O116" s="20" t="inlineStr">
+        <is>
+          <t>https://avia.tutu.ru/f/Moskva/Ekaterinburg/?class=Y&amp;travelers=1&amp;route[0]=491-30102026-29</t>
+        </is>
+      </c>
+      <c r="P116" s="5" t="inlineStr">
+        <is>
+          <t>Проходит правило 2 ч (Внуково с 23:15)</t>
+        </is>
+      </c>
+      <c r="Q116" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="15" t="inlineStr">
-        <is>
-          <t>Липецк</t>
-        </is>
-      </c>
-      <c r="B116" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="C116" s="16" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D116" s="16" t="inlineStr">
-        <is>
-          <t>Альтернатива: поезд</t>
-        </is>
-      </c>
-      <c r="E116" s="16" t="inlineStr">
-        <is>
-          <t>Поезд, купе</t>
-        </is>
-      </c>
-      <c r="F116" s="16" t="inlineStr">
-        <is>
-          <t>033С</t>
-        </is>
-      </c>
-      <c r="G116" s="16" t="inlineStr">
-        <is>
-          <t>27.10 23:15</t>
-        </is>
-      </c>
-      <c r="H116" s="16" t="inlineStr">
-        <is>
-          <t>28.10 08:08</t>
-        </is>
-      </c>
-      <c r="I116" s="16" t="inlineStr">
-        <is>
-          <t>Москва, Павелецкий</t>
-        </is>
-      </c>
-      <c r="J116" s="24" t="n">
-        <v>4049</v>
-      </c>
-      <c r="K116" s="24" t="n">
-        <v>4049</v>
-      </c>
-      <c r="L116" s="16" t="inlineStr">
-        <is>
-          <t>Павелецкий → метро до Комсомольской (~20 мин) → электричка от Казанского + такси (09:48 → 11:36)</t>
-        </is>
-      </c>
-      <c r="M116" s="16" t="inlineStr">
-        <is>
-          <t>~12:00</t>
-        </is>
-      </c>
-      <c r="N116" s="16" t="inlineStr"/>
-      <c r="O116" s="19" t="inlineStr">
-        <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2014130&amp;nnst2=2000000</t>
-        </is>
-      </c>
-      <c r="P116" s="16" t="inlineStr">
-        <is>
-          <t>Основной вариант — одна машина на троих</t>
-        </is>
-      </c>
-      <c r="Q116" s="16" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
-      </c>
-    </row>
     <row r="117">
-      <c r="A117" s="15" t="inlineStr">
-        <is>
-          <t>Воронеж</t>
-        </is>
-      </c>
-      <c r="B117" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="C117" s="16" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D117" s="16" t="inlineStr">
-        <is>
-          <t>Альтернатива: поезд</t>
-        </is>
-      </c>
-      <c r="E117" s="16" t="inlineStr">
-        <is>
-          <t>Поезд «Ингушетия», купе</t>
-        </is>
-      </c>
-      <c r="F117" s="16" t="inlineStr">
-        <is>
-          <t>145С</t>
-        </is>
-      </c>
-      <c r="G117" s="16" t="inlineStr">
-        <is>
-          <t>27.10 23:17</t>
-        </is>
-      </c>
-      <c r="H117" s="16" t="inlineStr">
-        <is>
-          <t>28.10 07:24</t>
-        </is>
-      </c>
-      <c r="I117" s="16" t="inlineStr">
-        <is>
-          <t>Москва, Казанский</t>
-        </is>
-      </c>
-      <c r="J117" s="24" t="n">
-        <v>4045</v>
-      </c>
-      <c r="K117" s="24" t="n">
-        <v>4045</v>
-      </c>
-      <c r="L117" s="16" t="inlineStr">
-        <is>
-          <t>Казанский вокзал → электричка до ст. Коломна (490–620 ₽) + такси 10 мин (~300 ₽) (08:47 РЭКС → 10:28)</t>
-        </is>
-      </c>
-      <c r="M117" s="16" t="inlineStr">
-        <is>
-          <t>~10:45</t>
-        </is>
-      </c>
-      <c r="N117" s="16" t="inlineStr"/>
-      <c r="O117" s="19" t="inlineStr">
-        <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2014000&amp;nnst2=2000000</t>
-        </is>
-      </c>
-      <c r="P117" s="16" t="inlineStr">
-        <is>
-          <t>Или 213*С 21:09 — прямо до Голутвина (Коломна) в 04:50</t>
-        </is>
-      </c>
-      <c r="Q117" s="16" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
-      </c>
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>Екатеринбург (группа)</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C117" s="10" t="inlineStr">
+        <is>
+          <t>Обратно</t>
+        </is>
+      </c>
+      <c r="D117" s="10" t="inlineStr">
+        <is>
+          <t>Удобный</t>
+        </is>
+      </c>
+      <c r="E117" s="10" t="inlineStr">
+        <is>
+          <t>Самолёт, Уральские авиалинии</t>
+        </is>
+      </c>
+      <c r="F117" s="10" t="inlineStr">
+        <is>
+          <t>U6-271</t>
+        </is>
+      </c>
+      <c r="G117" s="5" t="inlineStr">
+        <is>
+          <t>30.10 23:45</t>
+        </is>
+      </c>
+      <c r="H117" s="5" t="inlineStr">
+        <is>
+          <t>31.10 04:15 (мест.)</t>
+        </is>
+      </c>
+      <c r="I117" s="5" t="inlineStr">
+        <is>
+          <t>Домодедово</t>
+        </is>
+      </c>
+      <c r="J117" s="9" t="n">
+        <v>10285</v>
+      </c>
+      <c r="K117" s="9" t="n">
+        <v>13388</v>
+      </c>
+      <c r="L117" s="5" t="inlineStr">
+        <is>
+          <t>Выезд из гостиницы 18:15; в аэропорту за 2 ч до вылета</t>
+        </is>
+      </c>
+      <c r="M117" s="5" t="inlineStr"/>
+      <c r="N117" s="5" t="inlineStr"/>
+      <c r="O117" s="20" t="inlineStr">
+        <is>
+          <t>https://avia.tutu.ru/f/Moskva/Ekaterinburg/?class=Y&amp;travelers=1&amp;route[0]=491-30102026-29</t>
+        </is>
+      </c>
+      <c r="P117" s="5" t="inlineStr">
+        <is>
+          <t>DP-6541 (SVO 23:25) не проходит правило 2 ч</t>
+        </is>
+      </c>
+      <c r="Q117" s="5" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="15" t="inlineStr">
         <is>
-          <t>Орёл</t>
+          <t>Нижний Тагил</t>
         </is>
       </c>
       <c r="B118" s="16" t="n">
@@ -11800,64 +13260,52 @@
       </c>
       <c r="C118" s="16" t="inlineStr">
         <is>
-          <t>В1: к 15:00 28.10</t>
+          <t>Подвоз к группе</t>
         </is>
       </c>
       <c r="D118" s="16" t="inlineStr">
         <is>
-          <t>Альтернатива: поезд</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E118" s="16" t="inlineStr">
         <is>
-          <t>Поезд, купе</t>
-        </is>
-      </c>
-      <c r="F118" s="16" t="inlineStr">
-        <is>
-          <t>084С</t>
-        </is>
-      </c>
+          <t>Электричка/такси до Кольцово</t>
+        </is>
+      </c>
+      <c r="F118" s="16" t="inlineStr"/>
       <c r="G118" s="16" t="inlineStr">
         <is>
-          <t>27.10 23:37</t>
+          <t>27.10 вечер или 28.10 ~03:30</t>
         </is>
       </c>
       <c r="H118" s="16" t="inlineStr">
         <is>
-          <t>28.10 08:40</t>
+          <t>до вылета 06:50</t>
         </is>
       </c>
       <c r="I118" s="16" t="inlineStr">
         <is>
-          <t>Москва, Киевский</t>
+          <t>Екатеринбург, Кольцово</t>
         </is>
       </c>
       <c r="J118" s="24" t="n">
-        <v>3655</v>
+        <v>1200</v>
       </c>
       <c r="K118" s="24" t="n">
-        <v>3655</v>
+        <v>4000</v>
       </c>
       <c r="L118" s="16" t="inlineStr">
         <is>
-          <t>Киевский → метро до Комсомольской (~25 мин) → электричка + такси (09:48 → 11:36)</t>
-        </is>
-      </c>
-      <c r="M118" s="16" t="inlineStr">
-        <is>
-          <t>~12:00</t>
-        </is>
-      </c>
+          <t>~150 км: электричка до Екатеринбурга + автобус (~1 200 ₽) или такси (~4 000 ₽)</t>
+        </is>
+      </c>
+      <c r="M118" s="16" t="inlineStr"/>
       <c r="N118" s="16" t="inlineStr"/>
-      <c r="O118" s="19" t="inlineStr">
-        <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2000140&amp;nnst2=2000000</t>
-        </is>
-      </c>
+      <c r="O118" s="16" t="inlineStr"/>
       <c r="P118" s="16" t="inlineStr">
         <is>
-          <t>Основной вариант — машина вместе с Брянском</t>
+          <t>Летит с группой Екатеринбурга. Удобнее приехать накануне и переночевать у аэропорта</t>
         </is>
       </c>
       <c r="Q118" s="16" t="inlineStr">
@@ -11869,86 +13317,2751 @@
     <row r="119">
       <c r="A119" s="15" t="inlineStr">
         <is>
+          <t>Челябинск (Златоуст)</t>
+        </is>
+      </c>
+      <c r="B119" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C119" s="17" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D119" s="17" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E119" s="17" t="inlineStr">
+        <is>
+          <t>Самолёт, Победа</t>
+        </is>
+      </c>
+      <c r="F119" s="17" t="inlineStr">
+        <is>
+          <t>DP-414</t>
+        </is>
+      </c>
+      <c r="G119" s="16" t="inlineStr">
+        <is>
+          <t>28.10 06:30 (мест.)</t>
+        </is>
+      </c>
+      <c r="H119" s="16" t="inlineStr">
+        <is>
+          <t>28.10 07:15</t>
+        </is>
+      </c>
+      <c r="I119" s="16" t="inlineStr">
+        <is>
+          <t>Внуково</t>
+        </is>
+      </c>
+      <c r="J119" s="18" t="n">
+        <v>6196</v>
+      </c>
+      <c r="K119" s="18" t="n">
+        <v>8991</v>
+      </c>
+      <c r="L119" s="16" t="inlineStr">
+        <is>
+          <t>Внуково: метро → Казанский вокзал + электричка, или такси ~2 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="M119" s="16" t="inlineStr">
+        <is>
+          <t>~10:40</t>
+        </is>
+      </c>
+      <c r="N119" s="16" t="inlineStr"/>
+      <c r="O119" s="19" t="inlineStr">
+        <is>
+          <t>https://avia.tutu.ru/f/Chelyabinsk/Moskva/?class=Y&amp;travelers=1&amp;route[0]=98-28102026-491</t>
+        </is>
+      </c>
+      <c r="P119" s="16" t="inlineStr">
+        <is>
+          <t>Также DP-6568 05:30→SVO 06:10, та же цена. Из Златоуста до аэропорта ~150 км</t>
+        </is>
+      </c>
+      <c r="Q119" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>Челябинск (Златоуст)</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C120" s="10" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D120" s="10" t="inlineStr">
+        <is>
+          <t>Удобный</t>
+        </is>
+      </c>
+      <c r="E120" s="10" t="inlineStr">
+        <is>
+          <t>Самолёт, Аэрофлот</t>
+        </is>
+      </c>
+      <c r="F120" s="10" t="inlineStr">
+        <is>
+          <t>SU-1093</t>
+        </is>
+      </c>
+      <c r="G120" s="5" t="inlineStr">
+        <is>
+          <t>28.10 06:05 (мест.)</t>
+        </is>
+      </c>
+      <c r="H120" s="5" t="inlineStr">
+        <is>
+          <t>28.10 06:45</t>
+        </is>
+      </c>
+      <c r="I120" s="5" t="inlineStr">
+        <is>
+          <t>Шереметьево</t>
+        </is>
+      </c>
+      <c r="J120" s="9" t="n">
+        <v>10408</v>
+      </c>
+      <c r="K120" s="9" t="n">
+        <v>14081</v>
+      </c>
+      <c r="L120" s="5" t="inlineStr">
+        <is>
+          <t>Шереметьево: такси ~3 ч или аэроэкспресс → Белорусский + метро → Казанский + электричка</t>
+        </is>
+      </c>
+      <c r="M120" s="5" t="inlineStr">
+        <is>
+          <t>~10:25</t>
+        </is>
+      </c>
+      <c r="N120" s="5" t="inlineStr"/>
+      <c r="O120" s="20" t="inlineStr">
+        <is>
+          <t>https://avia.tutu.ru/f/Chelyabinsk/Moskva/?class=Y&amp;travelers=1&amp;route[0]=98-28102026-491</t>
+        </is>
+      </c>
+      <c r="P120" s="5" t="inlineStr"/>
+      <c r="Q120" s="5" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>Челябинск (Златоуст)</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>В2: после 15:00 28.10 / В3: к утру 29.10</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>Самолёт, Аэрофлот</t>
+        </is>
+      </c>
+      <c r="F121" s="5" t="inlineStr">
+        <is>
+          <t>SU-1427</t>
+        </is>
+      </c>
+      <c r="G121" s="5" t="inlineStr">
+        <is>
+          <t>28.10 22:30 (мест.)</t>
+        </is>
+      </c>
+      <c r="H121" s="5" t="inlineStr">
+        <is>
+          <t>28.10 23:20</t>
+        </is>
+      </c>
+      <c r="I121" s="5" t="inlineStr">
+        <is>
+          <t>Шереметьево</t>
+        </is>
+      </c>
+      <c r="J121" s="21" t="n">
+        <v>8190</v>
+      </c>
+      <c r="K121" s="21" t="n">
+        <v>11788</v>
+      </c>
+      <c r="L121" s="5" t="inlineStr">
+        <is>
+          <t>Шереметьево: такси ~3 ч или аэроэкспресс → Белорусский + метро → Казанский + электричка</t>
+        </is>
+      </c>
+      <c r="M121" s="5" t="inlineStr">
+        <is>
+          <t>~02:30</t>
+        </is>
+      </c>
+      <c r="N121" s="5" t="inlineStr"/>
+      <c r="O121" s="20" t="inlineStr">
+        <is>
+          <t>https://avia.tutu.ru/f/Chelyabinsk/Moskva/?class=Y&amp;travelers=1&amp;route[0]=98-28102026-491</t>
+        </is>
+      </c>
+      <c r="P121" s="5" t="inlineStr">
+        <is>
+          <t>Поздно; лучше В1</t>
+        </is>
+      </c>
+      <c r="Q121" s="5" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>Челябинск (Златоуст)</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C122" s="7" t="inlineStr">
+        <is>
+          <t>Обратно</t>
+        </is>
+      </c>
+      <c r="D122" s="7" t="inlineStr">
+        <is>
+          <t>Самый дешёвый = Удобный</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="inlineStr">
+        <is>
+          <t>Самолёт, Победа</t>
+        </is>
+      </c>
+      <c r="F122" s="7" t="inlineStr">
+        <is>
+          <t>DP-413</t>
+        </is>
+      </c>
+      <c r="G122" s="5" t="inlineStr">
+        <is>
+          <t>30.10 23:45</t>
+        </is>
+      </c>
+      <c r="H122" s="5" t="inlineStr">
+        <is>
+          <t>31.10 04:25 (мест.)</t>
+        </is>
+      </c>
+      <c r="I122" s="5" t="inlineStr">
+        <is>
+          <t>Внуково</t>
+        </is>
+      </c>
+      <c r="J122" s="6" t="n">
+        <v>7789</v>
+      </c>
+      <c r="K122" s="6" t="n">
+        <v>10643</v>
+      </c>
+      <c r="L122" s="5" t="inlineStr">
+        <is>
+          <t>Выезд из гостиницы 18:15; в аэропорту за 2 ч до вылета</t>
+        </is>
+      </c>
+      <c r="M122" s="5" t="inlineStr"/>
+      <c r="N122" s="5" t="inlineStr"/>
+      <c r="O122" s="20" t="inlineStr">
+        <is>
+          <t>https://avia.tutu.ru/f/Moskva/Chelyabinsk/?class=Y&amp;travelers=1&amp;route[0]=491-30102026-98</t>
+        </is>
+      </c>
+      <c r="P122" s="5" t="inlineStr">
+        <is>
+          <t>Рейсы Победы из SVO в 23:00/23:30 не проходят правило 2 ч</t>
+        </is>
+      </c>
+      <c r="Q122" s="5" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="15" t="inlineStr">
+        <is>
+          <t>Тюмень</t>
+        </is>
+      </c>
+      <c r="B123" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C123" s="17" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D123" s="17" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E123" s="17" t="inlineStr">
+        <is>
+          <t>Самолёт, Победа</t>
+        </is>
+      </c>
+      <c r="F123" s="17" t="inlineStr">
+        <is>
+          <t>DP-6562</t>
+        </is>
+      </c>
+      <c r="G123" s="16" t="inlineStr">
+        <is>
+          <t>28.10 06:25 (мест.)</t>
+        </is>
+      </c>
+      <c r="H123" s="16" t="inlineStr">
+        <is>
+          <t>28.10 07:30</t>
+        </is>
+      </c>
+      <c r="I123" s="16" t="inlineStr">
+        <is>
+          <t>Шереметьево</t>
+        </is>
+      </c>
+      <c r="J123" s="18" t="n">
+        <v>5873</v>
+      </c>
+      <c r="K123" s="18" t="n">
+        <v>8712</v>
+      </c>
+      <c r="L123" s="16" t="inlineStr">
+        <is>
+          <t>Шереметьево: такси ~3 ч или аэроэкспресс → Белорусский + метро → Казанский + электричка</t>
+        </is>
+      </c>
+      <c r="M123" s="16" t="inlineStr">
+        <is>
+          <t>~11:10</t>
+        </is>
+      </c>
+      <c r="N123" s="16" t="inlineStr"/>
+      <c r="O123" s="19" t="inlineStr">
+        <is>
+          <t>https://avia.tutu.ru/f/Tyumen/Moskva/?class=Y&amp;travelers=1&amp;route[0]=86-28102026-491</t>
+        </is>
+      </c>
+      <c r="P123" s="16" t="inlineStr">
+        <is>
+          <t>Если сотрудник в Сургуте/Кургане — уточнить, откуда вылет</t>
+        </is>
+      </c>
+      <c r="Q123" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>Тюмень</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C124" s="10" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D124" s="10" t="inlineStr">
+        <is>
+          <t>Удобный</t>
+        </is>
+      </c>
+      <c r="E124" s="10" t="inlineStr">
+        <is>
+          <t>Самолёт, ЮТэйр</t>
+        </is>
+      </c>
+      <c r="F124" s="10" t="inlineStr">
+        <is>
+          <t>UT-454</t>
+        </is>
+      </c>
+      <c r="G124" s="5" t="inlineStr">
+        <is>
+          <t>28.10 07:15 (мест.)</t>
+        </is>
+      </c>
+      <c r="H124" s="5" t="inlineStr">
+        <is>
+          <t>28.10 08:10</t>
+        </is>
+      </c>
+      <c r="I124" s="5" t="inlineStr">
+        <is>
+          <t>Внуково</t>
+        </is>
+      </c>
+      <c r="J124" s="9" t="n">
+        <v>7065</v>
+      </c>
+      <c r="K124" s="9" t="n">
+        <v>10125</v>
+      </c>
+      <c r="L124" s="5" t="inlineStr">
+        <is>
+          <t>Внуково: метро → Казанский вокзал + электричка, или такси ~2 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="M124" s="5" t="inlineStr">
+        <is>
+          <t>~11:35</t>
+        </is>
+      </c>
+      <c r="N124" s="5" t="inlineStr"/>
+      <c r="O124" s="20" t="inlineStr">
+        <is>
+          <t>https://avia.tutu.ru/f/Tyumen/Moskva/?class=Y&amp;travelers=1&amp;route[0]=86-28102026-491</t>
+        </is>
+      </c>
+      <c r="P124" s="5" t="inlineStr"/>
+      <c r="Q124" s="5" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>Тюмень</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>В2: после 15:00 28.10 / В3: к утру 29.10</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E125" s="5" t="inlineStr">
+        <is>
+          <t>не требуется</t>
+        </is>
+      </c>
+      <c r="F125" s="5" t="inlineStr"/>
+      <c r="G125" s="5" t="inlineStr"/>
+      <c r="H125" s="5" t="inlineStr"/>
+      <c r="I125" s="5" t="inlineStr"/>
+      <c r="J125" s="5" t="n"/>
+      <c r="K125" s="5" t="n"/>
+      <c r="L125" s="5" t="inlineStr"/>
+      <c r="M125" s="5" t="inlineStr"/>
+      <c r="N125" s="5" t="inlineStr"/>
+      <c r="O125" s="5" t="inlineStr"/>
+      <c r="P125" s="5" t="inlineStr">
+        <is>
+          <t>Подходит В1</t>
+        </is>
+      </c>
+      <c r="Q125" s="5" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>Тюмень</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C126" s="7" t="inlineStr">
+        <is>
+          <t>Обратно</t>
+        </is>
+      </c>
+      <c r="D126" s="7" t="inlineStr">
+        <is>
+          <t>Самый дешёвый = Удобный</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="inlineStr">
+        <is>
+          <t>Самолёт, Победа</t>
+        </is>
+      </c>
+      <c r="F126" s="7" t="inlineStr">
+        <is>
+          <t>DP-6561</t>
+        </is>
+      </c>
+      <c r="G126" s="5" t="inlineStr">
+        <is>
+          <t>30.10 23:50</t>
+        </is>
+      </c>
+      <c r="H126" s="5" t="inlineStr">
+        <is>
+          <t>31.10 04:40 (мест.)</t>
+        </is>
+      </c>
+      <c r="I126" s="5" t="inlineStr">
+        <is>
+          <t>Шереметьево</t>
+        </is>
+      </c>
+      <c r="J126" s="6" t="n">
+        <v>8168</v>
+      </c>
+      <c r="K126" s="6" t="n">
+        <v>11154</v>
+      </c>
+      <c r="L126" s="5" t="inlineStr">
+        <is>
+          <t>Выезд из гостиницы 18:15; в аэропорту за 2 ч до вылета</t>
+        </is>
+      </c>
+      <c r="M126" s="5" t="inlineStr"/>
+      <c r="N126" s="5" t="inlineStr"/>
+      <c r="O126" s="20" t="inlineStr">
+        <is>
+          <t>https://avia.tutu.ru/f/Moskva/Tyumen/?class=Y&amp;travelers=1&amp;route[0]=491-30102026-86</t>
+        </is>
+      </c>
+      <c r="P126" s="5" t="inlineStr">
+        <is>
+          <t>Впритык по правилу 2 ч. UT-453 20:30 не успевает</t>
+        </is>
+      </c>
+      <c r="Q126" s="5" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="15" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="B127" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C127" s="17" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D127" s="17" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E127" s="17" t="inlineStr">
+        <is>
+          <t>Поезд, купе (сидячий 2 283)</t>
+        </is>
+      </c>
+      <c r="F127" s="17" t="inlineStr">
+        <is>
+          <t>081А</t>
+        </is>
+      </c>
+      <c r="G127" s="16" t="inlineStr">
+        <is>
+          <t>27.10 21:21</t>
+        </is>
+      </c>
+      <c r="H127" s="16" t="inlineStr">
+        <is>
+          <t>28.10 06:04</t>
+        </is>
+      </c>
+      <c r="I127" s="16" t="inlineStr">
+        <is>
+          <t>Москва, Восточный</t>
+        </is>
+      </c>
+      <c r="J127" s="18" t="n">
+        <v>3272</v>
+      </c>
+      <c r="K127" s="18" t="n">
+        <v>3272</v>
+      </c>
+      <c r="L127" s="16" t="inlineStr">
+        <is>
+          <t>Восточный вокзал → МЦД/метро до Казанского (~30 мин) → электричка + такси (07:22 → 09:15)</t>
+        </is>
+      </c>
+      <c r="M127" s="16" t="inlineStr">
+        <is>
+          <t>~09:30</t>
+        </is>
+      </c>
+      <c r="N127" s="16" t="inlineStr">
+        <is>
+          <t>ранний заезд</t>
+        </is>
+      </c>
+      <c r="O127" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2004000&amp;nnst2=2000000</t>
+        </is>
+      </c>
+      <c r="P127" s="16" t="inlineStr">
+        <is>
+          <t>Вечером сел — утром в Москве</t>
+        </is>
+      </c>
+      <c r="Q127" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C128" s="10" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D128" s="10" t="inlineStr">
+        <is>
+          <t>Удобный</t>
+        </is>
+      </c>
+      <c r="E128" s="10" t="inlineStr">
+        <is>
+          <t>Поезд «Смена — А. Бетанкур», купе</t>
+        </is>
+      </c>
+      <c r="F128" s="10" t="inlineStr">
+        <is>
+          <t>025А</t>
+        </is>
+      </c>
+      <c r="G128" s="5" t="inlineStr">
+        <is>
+          <t>27.10 23:40</t>
+        </is>
+      </c>
+      <c r="H128" s="5" t="inlineStr">
+        <is>
+          <t>28.10 07:45</t>
+        </is>
+      </c>
+      <c r="I128" s="5" t="inlineStr">
+        <is>
+          <t>Москва, Ленинградский</t>
+        </is>
+      </c>
+      <c r="J128" s="9" t="n">
+        <v>3975</v>
+      </c>
+      <c r="K128" s="9" t="n">
+        <v>3975</v>
+      </c>
+      <c r="L128" s="5" t="inlineStr">
+        <is>
+          <t>Ленинградский вокзал → через площадь на Казанский (5 мин) → электричка + такси (08:47 РЭКС → 10:28)</t>
+        </is>
+      </c>
+      <c r="M128" s="5" t="inlineStr">
+        <is>
+          <t>~10:45</t>
+        </is>
+      </c>
+      <c r="N128" s="5" t="inlineStr"/>
+      <c r="O128" s="20" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2004000&amp;nnst2=2000000</t>
+        </is>
+      </c>
+      <c r="P128" s="5" t="inlineStr">
+        <is>
+          <t>Ленинградский и Казанский — на одной площади. Также «Сапсан» 28.10 05:30→09:23, 3 830 ₽ (→ 09:48 → 11:36)</t>
+        </is>
+      </c>
+      <c r="Q128" s="5" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C129" s="7" t="inlineStr">
+        <is>
+          <t>В2: после 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D129" s="7" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E129" s="7" t="inlineStr">
+        <is>
+          <t>Ласточка, сидячий</t>
+        </is>
+      </c>
+      <c r="F129" s="7" t="inlineStr">
+        <is>
+          <t>723Р</t>
+        </is>
+      </c>
+      <c r="G129" s="5" t="inlineStr">
+        <is>
+          <t>28.10 05:35</t>
+        </is>
+      </c>
+      <c r="H129" s="5" t="inlineStr">
+        <is>
+          <t>28.10 11:13</t>
+        </is>
+      </c>
+      <c r="I129" s="5" t="inlineStr">
+        <is>
+          <t>Москва, Ленинградский</t>
+        </is>
+      </c>
+      <c r="J129" s="6" t="n">
+        <v>1121</v>
+      </c>
+      <c r="K129" s="6" t="n">
+        <v>1121</v>
+      </c>
+      <c r="L129" s="5" t="inlineStr">
+        <is>
+          <t>Ленинградский вокзал → через площадь на Казанский (5 мин) → электричка + такси (12:54 → 15:15)</t>
+        </is>
+      </c>
+      <c r="M129" s="5" t="inlineStr">
+        <is>
+          <t>~15:30</t>
+        </is>
+      </c>
+      <c r="N129" s="5" t="inlineStr"/>
+      <c r="O129" s="20" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2004000&amp;nnst2=2000000</t>
+        </is>
+      </c>
+      <c r="P129" s="5" t="inlineStr">
+        <is>
+          <t>Самый дешёвый; к экскурсии в 16:00 успевает</t>
+        </is>
+      </c>
+      <c r="Q129" s="5" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C130" s="7" t="inlineStr">
+        <is>
+          <t>Обратно</t>
+        </is>
+      </c>
+      <c r="D130" s="7" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E130" s="7" t="inlineStr">
+        <is>
+          <t>Поезд «Аврора», сидячий</t>
+        </is>
+      </c>
+      <c r="F130" s="7" t="inlineStr">
+        <is>
+          <t>750У</t>
+        </is>
+      </c>
+      <c r="G130" s="5" t="inlineStr">
+        <is>
+          <t>30.10 22:30</t>
+        </is>
+      </c>
+      <c r="H130" s="5" t="inlineStr">
+        <is>
+          <t>31.10 05:00</t>
+        </is>
+      </c>
+      <c r="I130" s="5" t="inlineStr">
+        <is>
+          <t>СПб, Московский вокзал</t>
+        </is>
+      </c>
+      <c r="J130" s="6" t="n">
+        <v>2185</v>
+      </c>
+      <c r="K130" s="6" t="n">
+        <v>2185</v>
+      </c>
+      <c r="L130" s="5" t="inlineStr">
+        <is>
+          <t>Электричка 18:43 → Казанский 20:47 → Ленинградский</t>
+        </is>
+      </c>
+      <c r="M130" s="5" t="inlineStr"/>
+      <c r="N130" s="5" t="inlineStr"/>
+      <c r="O130" s="20" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2004000</t>
+        </is>
+      </c>
+      <c r="P130" s="5" t="inlineStr"/>
+      <c r="Q130" s="5" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C131" s="10" t="inlineStr">
+        <is>
+          <t>Обратно</t>
+        </is>
+      </c>
+      <c r="D131" s="10" t="inlineStr">
+        <is>
+          <t>Удобный</t>
+        </is>
+      </c>
+      <c r="E131" s="10" t="inlineStr">
+        <is>
+          <t>Поезд «Смена — А. Бетанкур», купе</t>
+        </is>
+      </c>
+      <c r="F131" s="10" t="inlineStr">
+        <is>
+          <t>026А</t>
+        </is>
+      </c>
+      <c r="G131" s="5" t="inlineStr">
+        <is>
+          <t>30.10 23:10</t>
+        </is>
+      </c>
+      <c r="H131" s="5" t="inlineStr">
+        <is>
+          <t>31.10 07:07</t>
+        </is>
+      </c>
+      <c r="I131" s="5" t="inlineStr">
+        <is>
+          <t>СПб, Московский вокзал</t>
+        </is>
+      </c>
+      <c r="J131" s="9" t="n">
+        <v>5093</v>
+      </c>
+      <c r="K131" s="9" t="n">
+        <v>5093</v>
+      </c>
+      <c r="L131" s="5" t="inlineStr">
+        <is>
+          <t>Электричка 18:43 или 19:43 → Казанский → Ленинградский</t>
+        </is>
+      </c>
+      <c r="M131" s="5" t="inlineStr"/>
+      <c r="N131" s="5" t="inlineStr"/>
+      <c r="O131" s="20" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2004000</t>
+        </is>
+      </c>
+      <c r="P131" s="5" t="inlineStr">
+        <is>
+          <t>Ночь в купе. Также 028А 22:08, купе 4 256</t>
+        </is>
+      </c>
+      <c r="Q131" s="5" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="15" t="inlineStr">
+        <is>
+          <t>Нижний Новгород</t>
+        </is>
+      </c>
+      <c r="B132" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C132" s="17" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D132" s="17" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E132" s="17" t="inlineStr">
+        <is>
+          <t>Ласточка, сидячий</t>
+        </is>
+      </c>
+      <c r="F132" s="17" t="inlineStr">
+        <is>
+          <t>723А</t>
+        </is>
+      </c>
+      <c r="G132" s="16" t="inlineStr">
+        <is>
+          <t>28.10 04:51</t>
+        </is>
+      </c>
+      <c r="H132" s="16" t="inlineStr">
+        <is>
+          <t>28.10 09:09</t>
+        </is>
+      </c>
+      <c r="I132" s="16" t="inlineStr">
+        <is>
+          <t>Москва, Восточный</t>
+        </is>
+      </c>
+      <c r="J132" s="18" t="n">
+        <v>2435</v>
+      </c>
+      <c r="K132" s="18" t="n">
+        <v>2435</v>
+      </c>
+      <c r="L132" s="16" t="inlineStr">
+        <is>
+          <t>Восточный вокзал → МЦД/метро до Казанского (~30 мин) → электричка + такси (09:48 впритык, иначе 12:54 → 15:15)</t>
+        </is>
+      </c>
+      <c r="M132" s="16" t="inlineStr">
+        <is>
+          <t>~12:00 / ~15:30</t>
+        </is>
+      </c>
+      <c r="N132" s="16" t="inlineStr"/>
+      <c r="O132" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2060000&amp;nnst2=2000000</t>
+        </is>
+      </c>
+      <c r="P132" s="16" t="inlineStr">
+        <is>
+          <t>Или своя машина: ~430 км, ~6 ч</t>
+        </is>
+      </c>
+      <c r="Q132" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>Нижний Новгород</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C133" s="10" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D133" s="10" t="inlineStr">
+        <is>
+          <t>Удобный</t>
+        </is>
+      </c>
+      <c r="E133" s="10" t="inlineStr">
+        <is>
+          <t>Поезд «Вятка», купе</t>
+        </is>
+      </c>
+      <c r="F133" s="10" t="inlineStr">
+        <is>
+          <t>031Г</t>
+        </is>
+      </c>
+      <c r="G133" s="5" t="inlineStr">
+        <is>
+          <t>28.10 03:05</t>
+        </is>
+      </c>
+      <c r="H133" s="5" t="inlineStr">
+        <is>
+          <t>28.10 09:27</t>
+        </is>
+      </c>
+      <c r="I133" s="5" t="inlineStr">
+        <is>
+          <t>Москва, Ярославский</t>
+        </is>
+      </c>
+      <c r="J133" s="9" t="n">
+        <v>4460</v>
+      </c>
+      <c r="K133" s="9" t="n">
+        <v>4460</v>
+      </c>
+      <c r="L133" s="5" t="inlineStr">
+        <is>
+          <t>Ярославский вокзал → через площадь на Казанский (5 мин) → электричка + такси (09:48 → 11:36)</t>
+        </is>
+      </c>
+      <c r="M133" s="5" t="inlineStr">
+        <is>
+          <t>~12:00</t>
+        </is>
+      </c>
+      <c r="N133" s="5" t="inlineStr"/>
+      <c r="O133" s="20" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2060000&amp;nnst2=2000000</t>
+        </is>
+      </c>
+      <c r="P133" s="5" t="inlineStr">
+        <is>
+          <t>Ночной поезд, посадка в 03:05</t>
+        </is>
+      </c>
+      <c r="Q133" s="5" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>Нижний Новгород</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>В2: после 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t>Поезд «Буревестник», сидячий</t>
+        </is>
+      </c>
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>705Э</t>
+        </is>
+      </c>
+      <c r="G134" s="5" t="inlineStr">
+        <is>
+          <t>28.10 07:20</t>
+        </is>
+      </c>
+      <c r="H134" s="5" t="inlineStr">
+        <is>
+          <t>28.10 11:34</t>
+        </is>
+      </c>
+      <c r="I134" s="5" t="inlineStr">
+        <is>
+          <t>Москва, Восточный</t>
+        </is>
+      </c>
+      <c r="J134" s="21" t="n">
+        <v>2136</v>
+      </c>
+      <c r="K134" s="21" t="n">
+        <v>2136</v>
+      </c>
+      <c r="L134" s="5" t="inlineStr">
+        <is>
+          <t>Восточный вокзал → МЦД/метро до Казанского (~30 мин) → электричка + такси (12:54 → 15:15)</t>
+        </is>
+      </c>
+      <c r="M134" s="5" t="inlineStr">
+        <is>
+          <t>~15:30</t>
+        </is>
+      </c>
+      <c r="N134" s="5" t="inlineStr"/>
+      <c r="O134" s="20" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2060000&amp;nnst2=2000000</t>
+        </is>
+      </c>
+      <c r="P134" s="5" t="inlineStr"/>
+      <c r="Q134" s="5" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>Нижний Новгород</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C135" s="7" t="inlineStr">
+        <is>
+          <t>Обратно</t>
+        </is>
+      </c>
+      <c r="D135" s="7" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E135" s="7" t="inlineStr">
+        <is>
+          <t>Ласточка, сидячий</t>
+        </is>
+      </c>
+      <c r="F135" s="7" t="inlineStr">
+        <is>
+          <t>723Я</t>
+        </is>
+      </c>
+      <c r="G135" s="5" t="inlineStr">
+        <is>
+          <t>30.10 21:15</t>
+        </is>
+      </c>
+      <c r="H135" s="5" t="inlineStr">
+        <is>
+          <t>31.10 01:15</t>
+        </is>
+      </c>
+      <c r="I135" s="5" t="inlineStr">
+        <is>
+          <t>Нижний Новгород</t>
+        </is>
+      </c>
+      <c r="J135" s="6" t="n">
+        <v>2347</v>
+      </c>
+      <c r="K135" s="6" t="n">
+        <v>2347</v>
+      </c>
+      <c r="L135" s="5" t="inlineStr">
+        <is>
+          <t>Электричка 18:43 → Казанский 20:47 → Восточный</t>
+        </is>
+      </c>
+      <c r="M135" s="5" t="inlineStr"/>
+      <c r="N135" s="5" t="inlineStr"/>
+      <c r="O135" s="20" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2060000</t>
+        </is>
+      </c>
+      <c r="P135" s="5" t="inlineStr">
+        <is>
+          <t>Дома ночью</t>
+        </is>
+      </c>
+      <c r="Q135" s="5" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>Нижний Новгород</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C136" s="10" t="inlineStr">
+        <is>
+          <t>Обратно</t>
+        </is>
+      </c>
+      <c r="D136" s="10" t="inlineStr">
+        <is>
+          <t>Удобный</t>
+        </is>
+      </c>
+      <c r="E136" s="10" t="inlineStr">
+        <is>
+          <t>Поезд «Нижегородец», купе</t>
+        </is>
+      </c>
+      <c r="F136" s="10" t="inlineStr">
+        <is>
+          <t>036Щ</t>
+        </is>
+      </c>
+      <c r="G136" s="5" t="inlineStr">
+        <is>
+          <t>30.10 23:10</t>
+        </is>
+      </c>
+      <c r="H136" s="5" t="inlineStr">
+        <is>
+          <t>31.10 07:10</t>
+        </is>
+      </c>
+      <c r="I136" s="5" t="inlineStr">
+        <is>
+          <t>Нижний Новгород</t>
+        </is>
+      </c>
+      <c r="J136" s="9" t="n">
+        <v>5172</v>
+      </c>
+      <c r="K136" s="9" t="n">
+        <v>5172</v>
+      </c>
+      <c r="L136" s="5" t="inlineStr">
+        <is>
+          <t>Электричка → Казанский → Ярославский (через площадь)</t>
+        </is>
+      </c>
+      <c r="M136" s="5" t="inlineStr"/>
+      <c r="N136" s="5" t="inlineStr"/>
+      <c r="O136" s="20" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2060000</t>
+        </is>
+      </c>
+      <c r="P136" s="5" t="inlineStr">
+        <is>
+          <t>Ночь в купе. Также 010Н 22:30, купе 4 040</t>
+        </is>
+      </c>
+      <c r="Q136" s="5" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="15" t="inlineStr">
+        <is>
+          <t>Смоленск</t>
+        </is>
+      </c>
+      <c r="B137" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C137" s="17" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D137" s="17" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E137" s="17" t="inlineStr">
+        <is>
+          <t>Ласточка-премиум, сидячий</t>
+        </is>
+      </c>
+      <c r="F137" s="17" t="inlineStr">
+        <is>
+          <t>738М</t>
+        </is>
+      </c>
+      <c r="G137" s="16" t="inlineStr">
+        <is>
+          <t>28.10 07:29</t>
+        </is>
+      </c>
+      <c r="H137" s="16" t="inlineStr">
+        <is>
+          <t>28.10 11:53</t>
+        </is>
+      </c>
+      <c r="I137" s="16" t="inlineStr">
+        <is>
+          <t>Москва, Белорусский</t>
+        </is>
+      </c>
+      <c r="J137" s="18" t="n">
+        <v>1832</v>
+      </c>
+      <c r="K137" s="18" t="n">
+        <v>1832</v>
+      </c>
+      <c r="L137" s="16" t="inlineStr">
+        <is>
+          <t>Белорусский → метро до Комсомольской (~15 мин) → электричка + такси (12:54 → 15:15)</t>
+        </is>
+      </c>
+      <c r="M137" s="16" t="inlineStr">
+        <is>
+          <t>~15:30</t>
+        </is>
+      </c>
+      <c r="N137" s="16" t="inlineStr"/>
+      <c r="O137" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2000170&amp;nnst2=2000000</t>
+        </is>
+      </c>
+      <c r="P137" s="16" t="inlineStr">
+        <is>
+          <t>К экскурсии в 16:00 успевает</t>
+        </is>
+      </c>
+      <c r="Q137" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t>Смоленск</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C138" s="10" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D138" s="10" t="inlineStr">
+        <is>
+          <t>Удобный</t>
+        </is>
+      </c>
+      <c r="E138" s="10" t="inlineStr">
+        <is>
+          <t>Поезд, купе</t>
+        </is>
+      </c>
+      <c r="F138" s="10" t="inlineStr">
+        <is>
+          <t>008Б</t>
+        </is>
+      </c>
+      <c r="G138" s="5" t="inlineStr">
+        <is>
+          <t>28.10 01:35</t>
+        </is>
+      </c>
+      <c r="H138" s="5" t="inlineStr">
+        <is>
+          <t>28.10 06:56</t>
+        </is>
+      </c>
+      <c r="I138" s="5" t="inlineStr">
+        <is>
+          <t>Москва, Белорусский</t>
+        </is>
+      </c>
+      <c r="J138" s="9" t="n">
+        <v>4656</v>
+      </c>
+      <c r="K138" s="9" t="n">
+        <v>4656</v>
+      </c>
+      <c r="L138" s="5" t="inlineStr">
+        <is>
+          <t>Белорусский → метро до Комсомольской (~15 мин) → электричка + такси (08:47 РЭКС → 10:28)</t>
+        </is>
+      </c>
+      <c r="M138" s="5" t="inlineStr">
+        <is>
+          <t>~10:45</t>
+        </is>
+      </c>
+      <c r="N138" s="5" t="inlineStr"/>
+      <c r="O138" s="20" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2000170&amp;nnst2=2000000</t>
+        </is>
+      </c>
+      <c r="P138" s="5" t="inlineStr">
+        <is>
+          <t>Ночной поезд. Если сотрудник из Великих Лук — поезд до Москвы (Рижский вокзал), уточнить</t>
+        </is>
+      </c>
+      <c r="Q138" s="5" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>Смоленск</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C139" s="7" t="inlineStr">
+        <is>
+          <t>Обратно</t>
+        </is>
+      </c>
+      <c r="D139" s="7" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E139" s="7" t="inlineStr">
+        <is>
+          <t>Поезд, купе</t>
+        </is>
+      </c>
+      <c r="F139" s="7" t="inlineStr">
+        <is>
+          <t>027Б</t>
+        </is>
+      </c>
+      <c r="G139" s="5" t="inlineStr">
+        <is>
+          <t>30.10 23:30</t>
+        </is>
+      </c>
+      <c r="H139" s="5" t="inlineStr">
+        <is>
+          <t>31.10 04:39</t>
+        </is>
+      </c>
+      <c r="I139" s="5" t="inlineStr">
+        <is>
+          <t>Смоленск</t>
+        </is>
+      </c>
+      <c r="J139" s="6" t="n">
+        <v>4022</v>
+      </c>
+      <c r="K139" s="6" t="n">
+        <v>4022</v>
+      </c>
+      <c r="L139" s="5" t="inlineStr">
+        <is>
+          <t>Электричка 18:43 → Казанский → метро до Белорусской</t>
+        </is>
+      </c>
+      <c r="M139" s="5" t="inlineStr"/>
+      <c r="N139" s="5" t="inlineStr"/>
+      <c r="O139" s="20" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2000170</t>
+        </is>
+      </c>
+      <c r="P139" s="5" t="inlineStr"/>
+      <c r="Q139" s="5" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t>Смоленск</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C140" s="10" t="inlineStr">
+        <is>
+          <t>Обратно</t>
+        </is>
+      </c>
+      <c r="D140" s="10" t="inlineStr">
+        <is>
+          <t>Удобный</t>
+        </is>
+      </c>
+      <c r="E140" s="10" t="inlineStr">
+        <is>
+          <t>Поезд, купе</t>
+        </is>
+      </c>
+      <c r="F140" s="10" t="inlineStr">
+        <is>
+          <t>007М</t>
+        </is>
+      </c>
+      <c r="G140" s="5" t="inlineStr">
+        <is>
+          <t>30.10 22:12</t>
+        </is>
+      </c>
+      <c r="H140" s="5" t="inlineStr">
+        <is>
+          <t>31.10 02:39</t>
+        </is>
+      </c>
+      <c r="I140" s="5" t="inlineStr">
+        <is>
+          <t>Смоленск</t>
+        </is>
+      </c>
+      <c r="J140" s="9" t="n">
+        <v>4656</v>
+      </c>
+      <c r="K140" s="9" t="n">
+        <v>4656</v>
+      </c>
+      <c r="L140" s="5" t="inlineStr">
+        <is>
+          <t>Электричка 18:43 → Казанский → метро до Белорусской</t>
+        </is>
+      </c>
+      <c r="M140" s="5" t="inlineStr"/>
+      <c r="N140" s="5" t="inlineStr"/>
+      <c r="O140" s="20" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2000170</t>
+        </is>
+      </c>
+      <c r="P140" s="5" t="inlineStr">
+        <is>
+          <t>Или машина ~520 км, ~7 ч</t>
+        </is>
+      </c>
+      <c r="Q140" s="5" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="15" t="inlineStr">
+        <is>
+          <t>Тверь</t>
+        </is>
+      </c>
+      <c r="B141" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C141" s="17" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D141" s="17" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E141" s="17" t="inlineStr">
+        <is>
+          <t>Поезд «Аврора», сидячий</t>
+        </is>
+      </c>
+      <c r="F141" s="17" t="inlineStr">
+        <is>
+          <t>741У</t>
+        </is>
+      </c>
+      <c r="G141" s="16" t="inlineStr">
+        <is>
+          <t>28.10 10:16</t>
+        </is>
+      </c>
+      <c r="H141" s="16" t="inlineStr">
+        <is>
+          <t>28.10 11:55</t>
+        </is>
+      </c>
+      <c r="I141" s="16" t="inlineStr">
+        <is>
+          <t>Москва, Ленинградский</t>
+        </is>
+      </c>
+      <c r="J141" s="18" t="n">
+        <v>695</v>
+      </c>
+      <c r="K141" s="18" t="n">
+        <v>695</v>
+      </c>
+      <c r="L141" s="16" t="inlineStr">
+        <is>
+          <t>Ленинградский вокзал → через площадь на Казанский (5 мин) → электричка + такси (12:54 → 15:15)</t>
+        </is>
+      </c>
+      <c r="M141" s="16" t="inlineStr">
+        <is>
+          <t>~15:30</t>
+        </is>
+      </c>
+      <c r="N141" s="16" t="inlineStr"/>
+      <c r="O141" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2004600&amp;nnst2=2000000</t>
+        </is>
+      </c>
+      <c r="P141" s="16" t="inlineStr">
+        <is>
+          <t>Также Ласточка 723Р 09:19→11:13, 611 ₽</t>
+        </is>
+      </c>
+      <c r="Q141" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="5" t="inlineStr">
+        <is>
+          <t>Тверь</t>
+        </is>
+      </c>
+      <c r="B142" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C142" s="10" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D142" s="10" t="inlineStr">
+        <is>
+          <t>Удобный</t>
+        </is>
+      </c>
+      <c r="E142" s="10" t="inlineStr">
+        <is>
+          <t>Своя машина</t>
+        </is>
+      </c>
+      <c r="F142" s="10" t="inlineStr"/>
+      <c r="G142" s="5" t="inlineStr">
+        <is>
+          <t>28.10 ~09:30</t>
+        </is>
+      </c>
+      <c r="H142" s="5" t="inlineStr">
+        <is>
+          <t>28.10 ~13:30</t>
+        </is>
+      </c>
+      <c r="I142" s="5" t="inlineStr">
+        <is>
+          <t>Коломна</t>
+        </is>
+      </c>
+      <c r="J142" s="9" t="n">
+        <v>1885</v>
+      </c>
+      <c r="K142" s="9" t="n">
+        <v>1885</v>
+      </c>
+      <c r="L142" s="5" t="inlineStr">
+        <is>
+          <t>~290 км через ЦКАД, ~4 ч</t>
+        </is>
+      </c>
+      <c r="M142" s="5" t="inlineStr">
+        <is>
+          <t>~13:30</t>
+        </is>
+      </c>
+      <c r="N142" s="5" t="inlineStr"/>
+      <c r="O142" s="5" t="inlineStr"/>
+      <c r="P142" s="5" t="inlineStr">
+        <is>
+          <t>Топливо ~3 770 ₽ туда-обратно на машину</t>
+        </is>
+      </c>
+      <c r="Q142" s="5" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t>Тверь</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C143" s="7" t="inlineStr">
+        <is>
+          <t>Обратно</t>
+        </is>
+      </c>
+      <c r="D143" s="7" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E143" s="7" t="inlineStr">
+        <is>
+          <t>Поезд «Аврора», сидячий</t>
+        </is>
+      </c>
+      <c r="F143" s="7" t="inlineStr">
+        <is>
+          <t>750У</t>
+        </is>
+      </c>
+      <c r="G143" s="5" t="inlineStr">
+        <is>
+          <t>30.10 22:30</t>
+        </is>
+      </c>
+      <c r="H143" s="5" t="inlineStr">
+        <is>
+          <t>31.10 ~00:05</t>
+        </is>
+      </c>
+      <c r="I143" s="5" t="inlineStr">
+        <is>
+          <t>Тверь</t>
+        </is>
+      </c>
+      <c r="J143" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K143" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L143" s="5" t="inlineStr">
+        <is>
+          <t>Электричка 18:43 → Казанский 20:47 → Ленинградский</t>
+        </is>
+      </c>
+      <c r="M143" s="5" t="inlineStr"/>
+      <c r="N143" s="5" t="inlineStr"/>
+      <c r="O143" s="20" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2004600</t>
+        </is>
+      </c>
+      <c r="P143" s="5" t="inlineStr">
+        <is>
+          <t>Цена ориентировочная, проверить</t>
+        </is>
+      </c>
+      <c r="Q143" s="5" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="15" t="inlineStr">
+        <is>
+          <t>Рязань</t>
+        </is>
+      </c>
+      <c r="B144" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C144" s="17" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D144" s="17" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E144" s="17" t="inlineStr">
+        <is>
+          <t>Электричка «Стандарт плюс»</t>
+        </is>
+      </c>
+      <c r="F144" s="17" t="inlineStr">
+        <is>
+          <t>6993</t>
+        </is>
+      </c>
+      <c r="G144" s="16" t="inlineStr">
+        <is>
+          <t>28.10 05:18</t>
+        </is>
+      </c>
+      <c r="H144" s="16" t="inlineStr">
+        <is>
+          <t>28.10 06:54</t>
+        </is>
+      </c>
+      <c r="I144" s="16" t="inlineStr">
+        <is>
+          <t>Коломна</t>
+        </is>
+      </c>
+      <c r="J144" s="18" t="n">
+        <v>306</v>
+      </c>
+      <c r="K144" s="18" t="n">
+        <v>306</v>
+      </c>
+      <c r="L144" s="16" t="inlineStr">
+        <is>
+          <t>Ст. Коломна → такси 10 мин (~300 ₽)</t>
+        </is>
+      </c>
+      <c r="M144" s="16" t="inlineStr">
+        <is>
+          <t>~07:10</t>
+        </is>
+      </c>
+      <c r="N144" s="16" t="inlineStr">
+        <is>
+          <t>ранний заезд</t>
+        </is>
+      </c>
+      <c r="O144" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/rasp.php?st1=92502&amp;st2=11902&amp;date=28.10.2026</t>
+        </is>
+      </c>
+      <c r="P144" s="16" t="inlineStr">
+        <is>
+          <t>Следующая электричка только 14:36 (→16:17) — к экскурсии не успевает</t>
+        </is>
+      </c>
+      <c r="Q144" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="inlineStr">
+        <is>
+          <t>Рязань</t>
+        </is>
+      </c>
+      <c r="B145" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C145" s="10" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D145" s="10" t="inlineStr">
+        <is>
+          <t>Удобный</t>
+        </is>
+      </c>
+      <c r="E145" s="10" t="inlineStr">
+        <is>
+          <t>Своя машина</t>
+        </is>
+      </c>
+      <c r="F145" s="10" t="inlineStr"/>
+      <c r="G145" s="5" t="inlineStr">
+        <is>
+          <t>28.10 ~12:30</t>
+        </is>
+      </c>
+      <c r="H145" s="5" t="inlineStr">
+        <is>
+          <t>28.10 ~14:00</t>
+        </is>
+      </c>
+      <c r="I145" s="5" t="inlineStr">
+        <is>
+          <t>Коломна</t>
+        </is>
+      </c>
+      <c r="J145" s="9" t="n">
+        <v>650</v>
+      </c>
+      <c r="K145" s="9" t="n">
+        <v>650</v>
+      </c>
+      <c r="L145" s="5" t="inlineStr">
+        <is>
+          <t>~100 км, ~1 ч 30 мин</t>
+        </is>
+      </c>
+      <c r="M145" s="5" t="inlineStr">
+        <is>
+          <t>~14:00</t>
+        </is>
+      </c>
+      <c r="N145" s="5" t="inlineStr"/>
+      <c r="O145" s="5" t="inlineStr"/>
+      <c r="P145" s="5" t="inlineStr">
+        <is>
+          <t>Топливо ~1 300 ₽ туда-обратно</t>
+        </is>
+      </c>
+      <c r="Q145" s="5" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="5" t="inlineStr">
+        <is>
+          <t>Рязань</t>
+        </is>
+      </c>
+      <c r="B146" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C146" s="7" t="inlineStr">
+        <is>
+          <t>Обратно</t>
+        </is>
+      </c>
+      <c r="D146" s="7" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E146" s="7" t="inlineStr">
+        <is>
+          <t>Электричка «Стандарт плюс»</t>
+        </is>
+      </c>
+      <c r="F146" s="7" t="inlineStr">
+        <is>
+          <t>6996</t>
+        </is>
+      </c>
+      <c r="G146" s="5" t="inlineStr">
+        <is>
+          <t>30.10 21:16</t>
+        </is>
+      </c>
+      <c r="H146" s="5" t="inlineStr">
+        <is>
+          <t>30.10 22:49</t>
+        </is>
+      </c>
+      <c r="I146" s="5" t="inlineStr">
+        <is>
+          <t>Рязань-1</t>
+        </is>
+      </c>
+      <c r="J146" s="6" t="n">
+        <v>306</v>
+      </c>
+      <c r="K146" s="6" t="n">
+        <v>306</v>
+      </c>
+      <c r="L146" s="5" t="inlineStr">
+        <is>
+          <t>Такси до ст. Коломна (~300 ₽)</t>
+        </is>
+      </c>
+      <c r="M146" s="5" t="inlineStr"/>
+      <c r="N146" s="5" t="inlineStr"/>
+      <c r="O146" s="20" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/rasp.php?st1=11902&amp;st2=92502&amp;date=30.10.2026</t>
+        </is>
+      </c>
+      <c r="P146" s="5" t="inlineStr"/>
+      <c r="Q146" s="5" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="15" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="B147" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C147" s="17" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D147" s="17" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E147" s="17" t="inlineStr">
+        <is>
+          <t>Электричка / РЭКС</t>
+        </is>
+      </c>
+      <c r="F147" s="17" t="inlineStr"/>
+      <c r="G147" s="16" t="inlineStr">
+        <is>
+          <t>28.10 09:48 или 12:54</t>
+        </is>
+      </c>
+      <c r="H147" s="16" t="inlineStr">
+        <is>
+          <t>11:36 / 15:15</t>
+        </is>
+      </c>
+      <c r="I147" s="16" t="inlineStr">
+        <is>
+          <t>Коломна</t>
+        </is>
+      </c>
+      <c r="J147" s="18" t="n">
+        <v>490</v>
+      </c>
+      <c r="K147" s="18" t="n">
+        <v>490</v>
+      </c>
+      <c r="L147" s="16" t="inlineStr">
+        <is>
+          <t>Казанский вокзал → электричка до ст. Коломна (490–620 ₽) + такси 10 мин (~300 ₽)</t>
+        </is>
+      </c>
+      <c r="M147" s="16" t="inlineStr">
+        <is>
+          <t>~12:00 / ~15:30</t>
+        </is>
+      </c>
+      <c r="N147" s="16" t="inlineStr"/>
+      <c r="O147" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/prigorod/</t>
+        </is>
+      </c>
+      <c r="P147" s="16" t="inlineStr">
+        <is>
+          <t>РЭКС 620 ₽</t>
+        </is>
+      </c>
+      <c r="Q147" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="5" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="B148" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C148" s="10" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D148" s="10" t="inlineStr">
+        <is>
+          <t>Удобный</t>
+        </is>
+      </c>
+      <c r="E148" s="10" t="inlineStr">
+        <is>
+          <t>Своя машина</t>
+        </is>
+      </c>
+      <c r="F148" s="10" t="inlineStr"/>
+      <c r="G148" s="5" t="inlineStr">
+        <is>
+          <t>28.10 ~12:00</t>
+        </is>
+      </c>
+      <c r="H148" s="5" t="inlineStr">
+        <is>
+          <t>28.10 ~14:00</t>
+        </is>
+      </c>
+      <c r="I148" s="5" t="inlineStr">
+        <is>
+          <t>Коломна</t>
+        </is>
+      </c>
+      <c r="J148" s="9" t="n">
+        <v>750</v>
+      </c>
+      <c r="K148" s="9" t="n">
+        <v>750</v>
+      </c>
+      <c r="L148" s="5" t="inlineStr">
+        <is>
+          <t>~115 км по Новорязанскому ш., ~2 ч с пробками</t>
+        </is>
+      </c>
+      <c r="M148" s="5" t="inlineStr">
+        <is>
+          <t>~14:00</t>
+        </is>
+      </c>
+      <c r="N148" s="5" t="inlineStr"/>
+      <c r="O148" s="5" t="inlineStr"/>
+      <c r="P148" s="5" t="inlineStr">
+        <is>
+          <t>Топливо ~1 500 ₽ туда-обратно</t>
+        </is>
+      </c>
+      <c r="Q148" s="5" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="B149" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C149" s="7" t="inlineStr">
+        <is>
+          <t>Обратно</t>
+        </is>
+      </c>
+      <c r="D149" s="7" t="inlineStr">
+        <is>
+          <t>Самый дешёвый = Удобный</t>
+        </is>
+      </c>
+      <c r="E149" s="7" t="inlineStr">
+        <is>
+          <t>Электричка или машина</t>
+        </is>
+      </c>
+      <c r="F149" s="7" t="inlineStr"/>
+      <c r="G149" s="5" t="inlineStr">
+        <is>
+          <t>30.10 18:43</t>
+        </is>
+      </c>
+      <c r="H149" s="5" t="inlineStr">
+        <is>
+          <t>30.10 20:47</t>
+        </is>
+      </c>
+      <c r="I149" s="5" t="inlineStr">
+        <is>
+          <t>Москва, Казанский</t>
+        </is>
+      </c>
+      <c r="J149" s="6" t="n">
+        <v>490</v>
+      </c>
+      <c r="K149" s="6" t="n">
+        <v>490</v>
+      </c>
+      <c r="L149" s="5" t="inlineStr">
+        <is>
+          <t>Электричка 18:43 → 20:47</t>
+        </is>
+      </c>
+      <c r="M149" s="5" t="inlineStr"/>
+      <c r="N149" s="5" t="inlineStr"/>
+      <c r="O149" s="20" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/prigorod/</t>
+        </is>
+      </c>
+      <c r="P149" s="5" t="inlineStr"/>
+      <c r="Q149" s="5" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="15" t="inlineStr">
+        <is>
+          <t>Пенза</t>
+        </is>
+      </c>
+      <c r="B150" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C150" s="16" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D150" s="16" t="inlineStr">
+        <is>
+          <t>Альтернатива: поезд</t>
+        </is>
+      </c>
+      <c r="E150" s="16" t="inlineStr">
+        <is>
+          <t>Поезд «Сура», купе (сидячий 3 030)</t>
+        </is>
+      </c>
+      <c r="F150" s="16" t="inlineStr">
+        <is>
+          <t>052М</t>
+        </is>
+      </c>
+      <c r="G150" s="16" t="inlineStr">
+        <is>
+          <t>27.10 21:35</t>
+        </is>
+      </c>
+      <c r="H150" s="16" t="inlineStr">
+        <is>
+          <t>28.10 07:59</t>
+        </is>
+      </c>
+      <c r="I150" s="16" t="inlineStr">
+        <is>
+          <t>Москва, Казанский</t>
+        </is>
+      </c>
+      <c r="J150" s="24" t="n">
+        <v>3967</v>
+      </c>
+      <c r="K150" s="24" t="n">
+        <v>3967</v>
+      </c>
+      <c r="L150" s="16" t="inlineStr">
+        <is>
+          <t>Казанский вокзал → электричка до ст. Коломна (490–620 ₽) + такси 10 мин (~300 ₽) (09:48 → 11:36)</t>
+        </is>
+      </c>
+      <c r="M150" s="16" t="inlineStr">
+        <is>
+          <t>~12:00</t>
+        </is>
+      </c>
+      <c r="N150" s="16" t="inlineStr"/>
+      <c r="O150" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2024120&amp;nnst2=2000000</t>
+        </is>
+      </c>
+      <c r="P150" s="16" t="inlineStr">
+        <is>
+          <t>Основной вариант — машина (лист «Авто»)</t>
+        </is>
+      </c>
+      <c r="Q150" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="15" t="inlineStr">
+        <is>
+          <t>Саранск</t>
+        </is>
+      </c>
+      <c r="B151" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C151" s="16" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D151" s="16" t="inlineStr">
+        <is>
+          <t>Альтернатива: поезд</t>
+        </is>
+      </c>
+      <c r="E151" s="16" t="inlineStr">
+        <is>
+          <t>Поезд, купе</t>
+        </is>
+      </c>
+      <c r="F151" s="16" t="inlineStr">
+        <is>
+          <t>041Й</t>
+        </is>
+      </c>
+      <c r="G151" s="16" t="inlineStr">
+        <is>
+          <t>27.10 20:40</t>
+        </is>
+      </c>
+      <c r="H151" s="16" t="inlineStr">
+        <is>
+          <t>28.10 05:50</t>
+        </is>
+      </c>
+      <c r="I151" s="16" t="inlineStr">
+        <is>
+          <t>Москва, Казанский</t>
+        </is>
+      </c>
+      <c r="J151" s="24" t="n">
+        <v>4394</v>
+      </c>
+      <c r="K151" s="24" t="n">
+        <v>4394</v>
+      </c>
+      <c r="L151" s="16" t="inlineStr">
+        <is>
+          <t>Казанский вокзал → электричка до ст. Коломна (490–620 ₽) + такси 10 мин (~300 ₽) (07:22 → 09:15)</t>
+        </is>
+      </c>
+      <c r="M151" s="16" t="inlineStr">
+        <is>
+          <t>~09:30</t>
+        </is>
+      </c>
+      <c r="N151" s="16" t="inlineStr">
+        <is>
+          <t>ранний заезд</t>
+        </is>
+      </c>
+      <c r="O151" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2024700&amp;nnst2=2000000</t>
+        </is>
+      </c>
+      <c r="P151" s="16" t="inlineStr">
+        <is>
+          <t>Основной вариант — машина</t>
+        </is>
+      </c>
+      <c r="Q151" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="15" t="inlineStr">
+        <is>
+          <t>Тамбов</t>
+        </is>
+      </c>
+      <c r="B152" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C152" s="16" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D152" s="16" t="inlineStr">
+        <is>
+          <t>Альтернатива: поезд</t>
+        </is>
+      </c>
+      <c r="E152" s="16" t="inlineStr">
+        <is>
+          <t>Поезд, сидячий (купе 2 868)</t>
+        </is>
+      </c>
+      <c r="F152" s="16" t="inlineStr">
+        <is>
+          <t>135Ж</t>
+        </is>
+      </c>
+      <c r="G152" s="16" t="inlineStr">
+        <is>
+          <t>27.10 21:56</t>
+        </is>
+      </c>
+      <c r="H152" s="16" t="inlineStr">
+        <is>
+          <t>28.10 07:22</t>
+        </is>
+      </c>
+      <c r="I152" s="16" t="inlineStr">
+        <is>
+          <t>Москва, Павелецкий</t>
+        </is>
+      </c>
+      <c r="J152" s="24" t="n">
+        <v>1979</v>
+      </c>
+      <c r="K152" s="24" t="n">
+        <v>1979</v>
+      </c>
+      <c r="L152" s="16" t="inlineStr">
+        <is>
+          <t>Павелецкий → метро до Комсомольской (~20 мин) → электричка от Казанского + такси (08:47 РЭКС → 10:28)</t>
+        </is>
+      </c>
+      <c r="M152" s="16" t="inlineStr">
+        <is>
+          <t>~10:45</t>
+        </is>
+      </c>
+      <c r="N152" s="16" t="inlineStr"/>
+      <c r="O152" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2014700&amp;nnst2=2000000</t>
+        </is>
+      </c>
+      <c r="P152" s="16" t="inlineStr">
+        <is>
+          <t>Основной вариант — машина. Купе осталось 1 место</t>
+        </is>
+      </c>
+      <c r="Q152" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="15" t="inlineStr">
+        <is>
+          <t>Липецк</t>
+        </is>
+      </c>
+      <c r="B153" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C153" s="16" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D153" s="16" t="inlineStr">
+        <is>
+          <t>Альтернатива: поезд</t>
+        </is>
+      </c>
+      <c r="E153" s="16" t="inlineStr">
+        <is>
+          <t>Поезд, купе</t>
+        </is>
+      </c>
+      <c r="F153" s="16" t="inlineStr">
+        <is>
+          <t>033С</t>
+        </is>
+      </c>
+      <c r="G153" s="16" t="inlineStr">
+        <is>
+          <t>27.10 23:15</t>
+        </is>
+      </c>
+      <c r="H153" s="16" t="inlineStr">
+        <is>
+          <t>28.10 08:08</t>
+        </is>
+      </c>
+      <c r="I153" s="16" t="inlineStr">
+        <is>
+          <t>Москва, Павелецкий</t>
+        </is>
+      </c>
+      <c r="J153" s="24" t="n">
+        <v>4049</v>
+      </c>
+      <c r="K153" s="24" t="n">
+        <v>4049</v>
+      </c>
+      <c r="L153" s="16" t="inlineStr">
+        <is>
+          <t>Павелецкий → метро до Комсомольской (~20 мин) → электричка от Казанского + такси (09:48 → 11:36)</t>
+        </is>
+      </c>
+      <c r="M153" s="16" t="inlineStr">
+        <is>
+          <t>~12:00</t>
+        </is>
+      </c>
+      <c r="N153" s="16" t="inlineStr"/>
+      <c r="O153" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2014130&amp;nnst2=2000000</t>
+        </is>
+      </c>
+      <c r="P153" s="16" t="inlineStr">
+        <is>
+          <t>Основной вариант — одна машина на троих</t>
+        </is>
+      </c>
+      <c r="Q153" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="15" t="inlineStr">
+        <is>
+          <t>Воронеж</t>
+        </is>
+      </c>
+      <c r="B154" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C154" s="16" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D154" s="16" t="inlineStr">
+        <is>
+          <t>Альтернатива: поезд</t>
+        </is>
+      </c>
+      <c r="E154" s="16" t="inlineStr">
+        <is>
+          <t>Поезд «Ингушетия», купе</t>
+        </is>
+      </c>
+      <c r="F154" s="16" t="inlineStr">
+        <is>
+          <t>145С</t>
+        </is>
+      </c>
+      <c r="G154" s="16" t="inlineStr">
+        <is>
+          <t>27.10 23:17</t>
+        </is>
+      </c>
+      <c r="H154" s="16" t="inlineStr">
+        <is>
+          <t>28.10 07:24</t>
+        </is>
+      </c>
+      <c r="I154" s="16" t="inlineStr">
+        <is>
+          <t>Москва, Казанский</t>
+        </is>
+      </c>
+      <c r="J154" s="24" t="n">
+        <v>4045</v>
+      </c>
+      <c r="K154" s="24" t="n">
+        <v>4045</v>
+      </c>
+      <c r="L154" s="16" t="inlineStr">
+        <is>
+          <t>Казанский вокзал → электричка до ст. Коломна (490–620 ₽) + такси 10 мин (~300 ₽) (08:47 РЭКС → 10:28)</t>
+        </is>
+      </c>
+      <c r="M154" s="16" t="inlineStr">
+        <is>
+          <t>~10:45</t>
+        </is>
+      </c>
+      <c r="N154" s="16" t="inlineStr"/>
+      <c r="O154" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2014000&amp;nnst2=2000000</t>
+        </is>
+      </c>
+      <c r="P154" s="16" t="inlineStr">
+        <is>
+          <t>Или 213*С 21:09 — прямо до Голутвина (Коломна) в 04:50</t>
+        </is>
+      </c>
+      <c r="Q154" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="15" t="inlineStr">
+        <is>
+          <t>Орёл</t>
+        </is>
+      </c>
+      <c r="B155" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C155" s="16" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D155" s="16" t="inlineStr">
+        <is>
+          <t>Альтернатива: поезд</t>
+        </is>
+      </c>
+      <c r="E155" s="16" t="inlineStr">
+        <is>
+          <t>Поезд, купе</t>
+        </is>
+      </c>
+      <c r="F155" s="16" t="inlineStr">
+        <is>
+          <t>084С</t>
+        </is>
+      </c>
+      <c r="G155" s="16" t="inlineStr">
+        <is>
+          <t>27.10 23:37</t>
+        </is>
+      </c>
+      <c r="H155" s="16" t="inlineStr">
+        <is>
+          <t>28.10 08:40</t>
+        </is>
+      </c>
+      <c r="I155" s="16" t="inlineStr">
+        <is>
+          <t>Москва, Киевский</t>
+        </is>
+      </c>
+      <c r="J155" s="24" t="n">
+        <v>3655</v>
+      </c>
+      <c r="K155" s="24" t="n">
+        <v>3655</v>
+      </c>
+      <c r="L155" s="16" t="inlineStr">
+        <is>
+          <t>Киевский → метро до Комсомольской (~25 мин) → электричка + такси (09:48 → 11:36)</t>
+        </is>
+      </c>
+      <c r="M155" s="16" t="inlineStr">
+        <is>
+          <t>~12:00</t>
+        </is>
+      </c>
+      <c r="N155" s="16" t="inlineStr"/>
+      <c r="O155" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2000140&amp;nnst2=2000000</t>
+        </is>
+      </c>
+      <c r="P155" s="16" t="inlineStr">
+        <is>
+          <t>Основной вариант — машина вместе с Брянском</t>
+        </is>
+      </c>
+      <c r="Q155" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="15" t="inlineStr">
+        <is>
           <t>Брянск</t>
         </is>
       </c>
-      <c r="B119" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C119" s="16" t="inlineStr">
+      <c r="B156" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C156" s="16" t="inlineStr">
         <is>
           <t>В1: к 15:00 28.10</t>
         </is>
       </c>
-      <c r="D119" s="16" t="inlineStr">
+      <c r="D156" s="16" t="inlineStr">
         <is>
           <t>Альтернатива: поезд</t>
         </is>
       </c>
-      <c r="E119" s="16" t="inlineStr">
+      <c r="E156" s="16" t="inlineStr">
         <is>
           <t>Поезд, сидячий (купе 3 180)</t>
         </is>
       </c>
-      <c r="F119" s="16" t="inlineStr">
+      <c r="F156" s="16" t="inlineStr">
         <is>
           <t>086Щ</t>
         </is>
       </c>
-      <c r="G119" s="16" t="inlineStr">
+      <c r="G156" s="16" t="inlineStr">
         <is>
           <t>28.10 00:20</t>
         </is>
       </c>
-      <c r="H119" s="16" t="inlineStr">
+      <c r="H156" s="16" t="inlineStr">
         <is>
           <t>28.10 06:20</t>
         </is>
       </c>
-      <c r="I119" s="16" t="inlineStr">
+      <c r="I156" s="16" t="inlineStr">
         <is>
           <t>Москва, Киевский</t>
         </is>
       </c>
-      <c r="J119" s="24" t="n">
+      <c r="J156" s="24" t="n">
         <v>1749</v>
       </c>
-      <c r="K119" s="24" t="n">
+      <c r="K156" s="24" t="n">
         <v>1749</v>
       </c>
-      <c r="L119" s="16" t="inlineStr">
+      <c r="L156" s="16" t="inlineStr">
         <is>
           <t>Киевский → метро до Комсомольской (~25 мин) → электричка + такси (07:22 → 09:15)</t>
         </is>
       </c>
-      <c r="M119" s="16" t="inlineStr">
+      <c r="M156" s="16" t="inlineStr">
         <is>
           <t>~09:30</t>
         </is>
       </c>
-      <c r="N119" s="16" t="inlineStr">
+      <c r="N156" s="16" t="inlineStr">
         <is>
           <t>ранний заезд</t>
         </is>
       </c>
-      <c r="O119" s="19" t="inlineStr">
+      <c r="O156" s="19" t="inlineStr">
         <is>
           <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2000427&amp;nnst2=2000000</t>
         </is>
       </c>
-      <c r="P119" s="16" t="inlineStr">
+      <c r="P156" s="16" t="inlineStr">
         <is>
           <t>Время по расписанию 27.10. Основной вариант — машина</t>
         </is>
       </c>
-      <c r="Q119" s="16" t="inlineStr">
+      <c r="Q156" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q119"/>
+  <autoFilter ref="A1:Q156"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
@@ -12045,11 +16158,42 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O112" r:id="rId93"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O113" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O114" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O115" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O116" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O117" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O118" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O119" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O116" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O117" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O119" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O120" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O121" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O122" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O123" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O124" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O126" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O127" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O128" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O129" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O130" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O131" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O132" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O133" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O134" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O135" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O136" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O137" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O138" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O139" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O140" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O141" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O143" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O144" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O146" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O147" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O149" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O150" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O151" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O152" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O153" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O154" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O155" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O156" r:id="rId131"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12476,7 +16620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -12585,27 +16729,27 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Д-2</t>
+          <t>Д-0</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Улан-Удэ S7-3032 08:45; Ревда U6-262 08:55; Иркутск U6-106 09:10 (4 чел.)</t>
+          <t>Екатеринбург U6-264 07:25 — группа 10 чел. + Нижний Тагил</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>сбор ~09:40</t>
+          <t>сбор ~08:00</t>
         </is>
       </c>
       <c r="F3" s="5" t="n">
         <v>2</v>
       </c>
       <c r="G3" s="21" t="n">
-        <v>3500</v>
+        <v>6000</v>
       </c>
       <c r="H3" s="21">
         <f>G3*F3/D3</f>
@@ -12613,7 +16757,7 @@
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>Иркутск — отдельная машина на 4</t>
+          <t>2 минивэна (заказать заранее)</t>
         </is>
       </c>
     </row>
@@ -12625,24 +16769,24 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Д-3</t>
+          <t>Д-2</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Новокузнецк S7-2626 10:00; Чита S7-3018 10:55 (+ Иркутск, если выберет S7-3018)</t>
+          <t>Улан-Удэ S7-3032 08:45; Ревда U6-262 08:55; Иркутск U6-106 09:10 (5 чел., вкл. Друсалевича В.А.)</t>
         </is>
       </c>
       <c r="D4" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>сбор ~09:40</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="n">
         <v>2</v>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>сбор ~11:30</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>1</v>
       </c>
       <c r="G4" s="21" t="n">
         <v>3500</v>
@@ -12651,47 +16795,47 @@
         <f>G4*F4/D4</f>
         <v/>
       </c>
-      <c r="I4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Иркутск — минивэн или 2 машины</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>28.10 Шереметьево (эконом)</t>
+          <t>28.10 Домодедово</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Ш-1</t>
+          <t>Д-3</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Омск DP-6522 07:45; Новосибирск DP-6526 08:20 (3 чел.)</t>
+          <t>Новокузнецк S7-2626 10:00; Чита S7-3018 10:55 (+ Иркутск, если выберет S7-3018)</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>сбор ~09:00</t>
+          <t>сбор ~11:30</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="21" t="n">
-        <v>5000</v>
+        <v>3500</v>
       </c>
       <c r="H5" s="21">
         <f>G5*F5/D5</f>
         <v/>
       </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>Или аэроэкспресс «Вместе» на 4 чел. 2 400 ₽ + электричка</t>
-        </is>
-      </c>
+      <c r="I5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -12701,20 +16845,20 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Ш-2</t>
+          <t>Ш-1</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Красноярск DP-6548 09:25; Новокузнецк SU-1459 09:05 (удобный)</t>
+          <t>Омск DP-6522 07:45; Новосибирск DP-6526 08:20 (3 чел.)</t>
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>сбор ~10:00</t>
+          <t>сбор ~09:00</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
@@ -12727,30 +16871,34 @@
         <f>G6*F6/D6</f>
         <v/>
       </c>
-      <c r="I6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Или аэроэкспресс «Вместе» на 4 чел. 2 400 ₽ + электричка</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>28.10 Шереметьево</t>
+          <t>28.10 Шереметьево (эконом)</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Ш-3</t>
+          <t>Ш-2</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Ульяновск SU-6076 11:00 (2 чел.); Самара SU-1603 11:15</t>
+          <t>Красноярск DP-6548 09:25; Новокузнецк SU-1459 09:05 (удобный)</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>сбор ~11:45</t>
+          <t>сбор ~10:00</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
@@ -12763,26 +16911,22 @@
         <f>G7*F7/D7</f>
         <v/>
       </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>Успевают к ~15:00</t>
-        </is>
-      </c>
+      <c r="I7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>28.10 Внуково</t>
+          <t>28.10 Шереметьево</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>В-1</t>
+          <t>Ш-3</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Уфа DP-436 07:20; Ревда DP-404 07:30 (эконом); Красноярск UT-572 08:15 (удобный)</t>
+          <t>Ульяновск SU-6076 11:00 (2 чел.); Самара SU-1603 11:15</t>
         </is>
       </c>
       <c r="D8" s="5" t="n">
@@ -12790,14 +16934,14 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>сбор ~08:30</t>
+          <t>сбор ~11:45</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="21" t="n">
-        <v>4800</v>
+        <v>5000</v>
       </c>
       <c r="H8" s="21">
         <f>G8*F8/D8</f>
@@ -12805,39 +16949,39 @@
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>Или метро + электричка (~900 ₽/чел.)</t>
+          <t>Успевают к ~15:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>30.10 → Домодедово</t>
+          <t>28.10 Внуково</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>О-1</t>
+          <t>В-1</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Улан-Удэ S7-3033 22:20; Новосибирск S7-2513 23:00 (удобный, 3 чел.); Омск U6-387 23:05; Новокузнецк S7-2625 23:35; Ревда U6-271 23:45</t>
+          <t>Уфа DP-436 07:20; Ревда DP-404 07:30 (эконом); Красноярск UT-572 08:15 (удобный)</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>выезд из гостиницы 18:15</t>
+          <t>сбор ~08:30</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" s="21" t="n">
-        <v>3500</v>
+        <v>4800</v>
       </c>
       <c r="H9" s="21">
         <f>G9*F9/D9</f>
@@ -12845,39 +16989,39 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Минивэн на 7–8 мест выгоднее</t>
+          <t>Или метро + электричка (~900 ₽/чел.)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>30.10 → Шереметьево</t>
+          <t>30.10 → Домодедово</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>О-2</t>
+          <t>О-1</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Омск DP-6521 23:45 (эконом); Оренбург SU-6171 00:45 / 5N-231 02:40</t>
+          <t>Улан-Удэ S7-3033 22:20; Новосибирск S7-2513 23:00 (удобный, 3 чел.); Омск U6-387 23:05; Новокузнецк S7-2625 23:35; Ревда U6-271 23:45</t>
         </is>
       </c>
       <c r="D10" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>выезд из гостиницы 18:15</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>выезд 18:15–19:00</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="G10" s="21" t="n">
-        <v>5000</v>
+        <v>3500</v>
       </c>
       <c r="H10" s="21">
         <f>G10*F10/D10</f>
@@ -12885,39 +17029,39 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>Или электричка + аэроэкспресс</t>
+          <t>Минивэн на 7–8 мест выгоднее</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>30.10 → Внуково</t>
+          <t>30.10 → Шереметьево</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>О-3</t>
+          <t>О-2</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Уфа DP-435 23:40</t>
+          <t>Омск DP-6521 23:45 (эконом); Оренбург SU-6171 00:45 / 5N-231 02:40</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>выезд 18:15</t>
+          <t>выезд 18:15–19:00</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="21" t="n">
-        <v>4800</v>
+        <v>5000</v>
       </c>
       <c r="H11" s="21">
         <f>G11*F11/D11</f>
@@ -12925,39 +17069,39 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>Или электричка + метро</t>
+          <t>Или электричка + аэроэкспресс</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>31.10 → Домодедово</t>
+          <t>30.10 → Внуково</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>О-4</t>
+          <t>О-3</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Иркутск (4 чел.) S7-3021 12:05 или U6-105 19:25; Чита U6-93 19:40; Ижевск S7-1165 15:10; Волгоград S7-2143 11:05</t>
+          <t>Уфа DP-435 23:40; Екатеринбург DP-403 23:50 (11 чел.); Челябинск DP-413 23:45</t>
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>по времени рейсов</t>
+          <t>выезд 18:15</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
         <v>2</v>
       </c>
       <c r="G12" s="21" t="n">
-        <v>3500</v>
+        <v>6000</v>
       </c>
       <c r="H12" s="21">
         <f>G12*F12/D12</f>
@@ -12965,39 +17109,39 @@
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>Иркутск + Чита вечером — одна машина</t>
+          <t>2 минивэна</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>31.10 → Шереметьево</t>
+          <t>31.10 → Домодедово</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>О-5</t>
+          <t>О-4</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Набережные Челны DP-6845 14:10; Астрахань DP-6963 13:50; Саратов DP-6861 14:40 (2 чел.); Красноярск / Абакан / Новосибирск вечером</t>
+          <t>Иркутск (4 чел.) S7-3021 12:05 или U6-105 19:25; Чита U6-93 19:40; Ижевск S7-1165 15:10; Волгоград S7-2143 11:05</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>выезд ~10:00</t>
+          <t>по времени рейсов</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G13" s="21" t="n">
-        <v>5000</v>
+        <v>3500</v>
       </c>
       <c r="H13" s="21">
         <f>G13*F13/D13</f>
@@ -13005,45 +17149,85 @@
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>Утренняя группа</t>
+          <t>Иркутск + Чита вечером — одна машина</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>31.10 → Внуково</t>
+          <t>31.10 → Шереметьево</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>О-6</t>
+          <t>О-5</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Ульяновск DP-485 19:35 (2 чел.); Саратов DP-475 17:55 (удобный)</t>
+          <t>Набережные Челны DP-6845 14:10; Астрахань DP-6963 13:50; Саратов DP-6861 14:40 (2 чел.); Красноярск / Абакан / Новосибирск вечером</t>
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>выезд ~14:30</t>
+          <t>выезд ~10:00</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="21" t="n">
-        <v>4800</v>
+        <v>5000</v>
       </c>
       <c r="H14" s="21">
         <f>G14*F14/D14</f>
         <v/>
       </c>
-      <c r="I14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Утренняя группа</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>31.10 → Внуково</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>О-6</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Ульяновск DP-485 19:35 (2 чел.); Саратов DP-475 17:55 (удобный)</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>выезд ~14:30</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="21" t="n">
+        <v>4800</v>
+      </c>
+      <c r="H15" s="21">
+        <f>G15*F15/D15</f>
+        <v/>
+      </c>
+      <c r="I15" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Коломна_маршруты_28-30.10.2026.xlsx
+++ b/Коломна_маршруты_28-30.10.2026.xlsx
@@ -2366,7 +2366,7 @@
       </c>
       <c r="S27" s="5" t="inlineStr">
         <is>
-          <t>Такси на 4 чел. из Домодедово</t>
+          <t>Группа 5 чел.: минивэн из Домодедово</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="S28" s="5" t="inlineStr">
         <is>
-          <t>Такси на 4 чел. из Домодедово</t>
+          <t>Группа 5 чел.: минивэн из Домодедово</t>
         </is>
       </c>
     </row>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="S29" s="5" t="inlineStr">
         <is>
-          <t>Едет вместе с отцом (Друсалевич В.А.). Такси на 4 чел. из Домодедово</t>
+          <t>Едет вместе с отцом (Друсалевич В.А.). Группа 5 чел.: минивэн из Домодедово</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="S31" s="5" t="inlineStr">
         <is>
-          <t>Такси на 4 чел. из Домодедово</t>
+          <t>Группа 5 чел.: минивэн из Домодедово</t>
         </is>
       </c>
     </row>
@@ -3638,7 +3638,7 @@
       </c>
       <c r="S44" s="5" t="inlineStr">
         <is>
-          <t>Едет вместе с сыном (Друсалевич В.В.). Такси на 4 чел. из Домодедово</t>
+          <t>Едет вместе с сыном (Друсалевич В.В.). Группа 5 чел.: минивэн из Домодедово</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
         </is>
       </c>
       <c r="B35" s="16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C35" s="17" t="inlineStr">
         <is>
@@ -7496,7 +7496,7 @@
       </c>
       <c r="L35" s="16" t="inlineStr">
         <is>
-          <t>Домодедово: такси 1 ч 45 мин + 40 мин на выход (группа 2–4 чел.) — одно такси на 4 чел.</t>
+          <t>Домодедово: такси 1 ч 45 мин + 40 мин на выход (группа 2–4 чел.) — минивэн на 5 чел.</t>
         </is>
       </c>
       <c r="M35" s="16" t="inlineStr">
@@ -7528,7 +7528,7 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
@@ -7605,7 +7605,7 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
@@ -7759,7 +7759,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>

--- a/Коломна_маршруты_28-30.10.2026.xlsx
+++ b/Коломна_маршруты_28-30.10.2026.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Сводка по сотрудникам'!$A$4:$S$64</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Маршруты'!$A$1:$Q$156</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Маршруты'!$A$1:$Q$160</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="S52" s="5" t="inlineStr">
         <is>
-          <t>Едет вместе с дочерью (Смирнова Ю.И.). Группа 10 чел. одним рейсом; минивэны из Домодедово</t>
+          <t>Едет вместе с дочерью (Смирнова Ю.И.). Группа 9 чел. одним рейсом; минивэны из Домодедово</t>
         </is>
       </c>
     </row>
@@ -4286,7 +4286,7 @@
       </c>
       <c r="S53" s="5" t="inlineStr">
         <is>
-          <t>Группа 10 чел. одним рейсом; минивэны из Домодедово</t>
+          <t>Группа 9 чел. одним рейсом; минивэны из Домодедово</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="S54" s="5" t="inlineStr">
         <is>
-          <t>Группа 10 чел. одним рейсом; минивэны из Домодедово</t>
+          <t>Группа 9 чел. одним рейсом; минивэны из Домодедово</t>
         </is>
       </c>
     </row>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="S55" s="5" t="inlineStr">
         <is>
-          <t>Группа 10 чел. одним рейсом; минивэны из Домодедово</t>
+          <t>Группа 9 чел. одним рейсом; минивэны из Домодедово</t>
         </is>
       </c>
     </row>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="S56" s="5" t="inlineStr">
         <is>
-          <t>Группа 10 чел. одним рейсом; минивэны из Домодедово</t>
+          <t>Группа 9 чел. одним рейсом; минивэны из Домодедово</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="S57" s="5" t="inlineStr">
         <is>
-          <t>Группа 10 чел. одним рейсом; минивэны из Домодедово</t>
+          <t>Группа 9 чел. одним рейсом; минивэны из Домодедово</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S58" s="5" t="inlineStr">
         <is>
-          <t>Едет вместе с отцом (Смирнов И.А.). Группа 10 чел. одним рейсом; минивэны из Домодедово</t>
+          <t>Едет вместе с отцом (Смирнов И.А.). Группа 9 чел. одним рейсом; минивэны из Домодедово</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="S59" s="5" t="inlineStr">
         <is>
-          <t>Группа 10 чел. одним рейсом; минивэны из Домодедово</t>
+          <t>Группа 9 чел. одним рейсом; минивэны из Домодедово</t>
         </is>
       </c>
     </row>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="S60" s="5" t="inlineStr">
         <is>
-          <t>Группа 10 чел. одним рейсом; минивэны из Домодедово</t>
+          <t>Группа 9 чел. одним рейсом; минивэны из Домодедово</t>
         </is>
       </c>
     </row>
@@ -4805,12 +4805,12 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Екатеринбург-север</t>
+          <t>уточнить</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Екатеринбург</t>
+          <t>Магнитогорск</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -4819,19 +4819,19 @@
         </is>
       </c>
       <c r="F61" s="6" t="n">
-        <v>7811</v>
+        <v>12962</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>10789</v>
+        <v>16375</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>9104</v>
+        <v>11097</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>12205</v>
+        <v>14765</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>2000</v>
+        <v>2400</v>
       </c>
       <c r="K61" s="7" t="n">
         <v>0</v>
@@ -4845,13 +4845,13 @@
         <v/>
       </c>
       <c r="N61" s="9" t="n">
-        <v>11932</v>
+        <v>17111</v>
       </c>
       <c r="O61" s="9" t="n">
-        <v>13388</v>
+        <v>14765</v>
       </c>
       <c r="P61" s="9" t="n">
-        <v>2200</v>
+        <v>10000</v>
       </c>
       <c r="Q61" s="10" t="n">
         <v>0</v>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="S61" s="5" t="inlineStr">
         <is>
-          <t>Группа 10 чел. одним рейсом; минивэны из Домодедово</t>
+          <t>Обратно ночным рейсом 31.10 в 00:40, без доп. ночи</t>
         </is>
       </c>
     </row>
@@ -4932,11 +4932,7 @@
         <f>N62+O62+P62+Q62*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S62" s="5" t="inlineStr">
-        <is>
-          <t>Если из Златоуста — +~150 км до аэропорта</t>
-        </is>
-      </c>
+      <c r="S62" s="5" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n">
@@ -5004,11 +5000,7 @@
         <f>N63+O63+P63+Q63*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S63" s="5" t="inlineStr">
-        <is>
-          <t>Уточнить, вылет из Тюмени или Сургута/Кургана</t>
-        </is>
-      </c>
+      <c r="S63" s="5" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="n">
@@ -5120,7 +5112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q156"/>
+  <dimension ref="A1:Q160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12919,7 +12911,7 @@
         </is>
       </c>
       <c r="B113" s="16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C113" s="17" t="inlineStr">
         <is>
@@ -13317,72 +13309,72 @@
     <row r="119">
       <c r="A119" s="15" t="inlineStr">
         <is>
-          <t>Челябинск (Златоуст)</t>
+          <t>Магнитогорск</t>
         </is>
       </c>
       <c r="B119" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="C119" s="17" t="inlineStr">
+      <c r="C119" s="22" t="inlineStr">
         <is>
           <t>В1: к 15:00 28.10</t>
         </is>
       </c>
-      <c r="D119" s="17" t="inlineStr">
-        <is>
-          <t>Самый дешёвый</t>
-        </is>
-      </c>
-      <c r="E119" s="17" t="inlineStr">
-        <is>
-          <t>Самолёт, Победа</t>
-        </is>
-      </c>
-      <c r="F119" s="17" t="inlineStr">
-        <is>
-          <t>DP-414</t>
+      <c r="D119" s="22" t="inlineStr">
+        <is>
+          <t>Удобный</t>
+        </is>
+      </c>
+      <c r="E119" s="22" t="inlineStr">
+        <is>
+          <t>Самолёт, Аэрофлот</t>
+        </is>
+      </c>
+      <c r="F119" s="22" t="inlineStr">
+        <is>
+          <t>SU-1429</t>
         </is>
       </c>
       <c r="G119" s="16" t="inlineStr">
         <is>
-          <t>28.10 06:30 (мест.)</t>
+          <t>28.10 06:15 (мест.)</t>
         </is>
       </c>
       <c r="H119" s="16" t="inlineStr">
         <is>
-          <t>28.10 07:15</t>
+          <t>28.10 06:40</t>
         </is>
       </c>
       <c r="I119" s="16" t="inlineStr">
         <is>
-          <t>Внуково</t>
-        </is>
-      </c>
-      <c r="J119" s="18" t="n">
-        <v>6196</v>
-      </c>
-      <c r="K119" s="18" t="n">
-        <v>8991</v>
+          <t>Шереметьево</t>
+        </is>
+      </c>
+      <c r="J119" s="23" t="n">
+        <v>13489</v>
+      </c>
+      <c r="K119" s="23" t="n">
+        <v>17111</v>
       </c>
       <c r="L119" s="16" t="inlineStr">
         <is>
-          <t>Внуково: метро → Казанский вокзал + электричка, или такси ~2 ч 45 мин</t>
+          <t>Шереметьево: такси ~3 ч или аэроэкспресс → Белорусский + метро → Казанский + электричка</t>
         </is>
       </c>
       <c r="M119" s="16" t="inlineStr">
         <is>
-          <t>~10:40</t>
+          <t>~10:20</t>
         </is>
       </c>
       <c r="N119" s="16" t="inlineStr"/>
       <c r="O119" s="19" t="inlineStr">
         <is>
-          <t>https://avia.tutu.ru/f/Chelyabinsk/Moskva/?class=Y&amp;travelers=1&amp;route[0]=98-28102026-491</t>
+          <t>https://avia.tutu.ru/f/Magnitogorsk/Moskva/?class=Y&amp;travelers=1&amp;route[0]=45-28102026-491</t>
         </is>
       </c>
       <c r="P119" s="16" t="inlineStr">
         <is>
-          <t>Также DP-6568 05:30→SVO 06:10, та же цена. Из Златоуста до аэропорта ~150 км</t>
+          <t>Единственный утренний прямой рейс</t>
         </is>
       </c>
       <c r="Q119" s="16" t="inlineStr">
@@ -13394,70 +13386,74 @@
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>Челябинск (Златоуст)</t>
+          <t>Магнитогорск</t>
         </is>
       </c>
       <c r="B120" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C120" s="10" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D120" s="10" t="inlineStr">
-        <is>
-          <t>Удобный</t>
-        </is>
-      </c>
-      <c r="E120" s="10" t="inlineStr">
-        <is>
-          <t>Самолёт, Аэрофлот</t>
-        </is>
-      </c>
-      <c r="F120" s="10" t="inlineStr">
-        <is>
-          <t>SU-1093</t>
+      <c r="C120" s="7" t="inlineStr">
+        <is>
+          <t>В2: после 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D120" s="7" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="inlineStr">
+        <is>
+          <t>Самолёт, Азимут</t>
+        </is>
+      </c>
+      <c r="F120" s="7" t="inlineStr">
+        <is>
+          <t>A4-7062</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
         <is>
-          <t>28.10 06:05 (мест.)</t>
+          <t>28.10 12:20 (мест.)</t>
         </is>
       </c>
       <c r="H120" s="5" t="inlineStr">
         <is>
-          <t>28.10 06:45</t>
+          <t>28.10 13:00</t>
         </is>
       </c>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>Шереметьево</t>
-        </is>
-      </c>
-      <c r="J120" s="9" t="n">
-        <v>10408</v>
-      </c>
-      <c r="K120" s="9" t="n">
-        <v>14081</v>
+          <t>Внуково</t>
+        </is>
+      </c>
+      <c r="J120" s="6" t="n">
+        <v>12962</v>
+      </c>
+      <c r="K120" s="6" t="n">
+        <v>16375</v>
       </c>
       <c r="L120" s="5" t="inlineStr">
         <is>
-          <t>Шереметьево: такси ~3 ч или аэроэкспресс → Белорусский + метро → Казанский + электричка</t>
+          <t>Внуково: метро → Казанский вокзал + электричка, или такси ~2 ч 45 мин</t>
         </is>
       </c>
       <c r="M120" s="5" t="inlineStr">
         <is>
-          <t>~10:25</t>
+          <t>~16:25</t>
         </is>
       </c>
       <c r="N120" s="5" t="inlineStr"/>
       <c r="O120" s="20" t="inlineStr">
         <is>
-          <t>https://avia.tutu.ru/f/Chelyabinsk/Moskva/?class=Y&amp;travelers=1&amp;route[0]=98-28102026-491</t>
-        </is>
-      </c>
-      <c r="P120" s="5" t="inlineStr"/>
+          <t>https://avia.tutu.ru/f/Magnitogorsk/Moskva/?class=Y&amp;travelers=1&amp;route[0]=45-28102026-491</t>
+        </is>
+      </c>
+      <c r="P120" s="5" t="inlineStr">
+        <is>
+          <t>Чуть дешевле, но экскурсия в 16:00 не успевает</t>
+        </is>
+      </c>
       <c r="Q120" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
@@ -13467,7 +13463,7 @@
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>Челябинск (Златоуст)</t>
+          <t>Магнитогорск</t>
         </is>
       </c>
       <c r="B121" s="5" t="n">
@@ -13475,7 +13471,7 @@
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>В2: после 15:00 28.10 / В3: к утру 29.10</t>
+          <t>В3: к утру 29.10</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
@@ -13485,66 +13481,30 @@
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>Самолёт, Аэрофлот</t>
+          <t>как В2</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>SU-1427</t>
-        </is>
-      </c>
-      <c r="G121" s="5" t="inlineStr">
-        <is>
-          <t>28.10 22:30 (мест.)</t>
-        </is>
-      </c>
-      <c r="H121" s="5" t="inlineStr">
-        <is>
-          <t>28.10 23:20</t>
-        </is>
-      </c>
-      <c r="I121" s="5" t="inlineStr">
-        <is>
-          <t>Шереметьево</t>
-        </is>
-      </c>
-      <c r="J121" s="21" t="n">
-        <v>8190</v>
-      </c>
-      <c r="K121" s="21" t="n">
-        <v>11788</v>
-      </c>
-      <c r="L121" s="5" t="inlineStr">
-        <is>
-          <t>Шереметьево: такси ~3 ч или аэроэкспресс → Белорусский + метро → Казанский + электричка</t>
-        </is>
-      </c>
-      <c r="M121" s="5" t="inlineStr">
-        <is>
-          <t>~02:30</t>
-        </is>
-      </c>
+          <t>A4-7062</t>
+        </is>
+      </c>
+      <c r="G121" s="5" t="inlineStr"/>
+      <c r="H121" s="5" t="inlineStr"/>
+      <c r="I121" s="5" t="inlineStr"/>
+      <c r="J121" s="5" t="n"/>
+      <c r="K121" s="5" t="n"/>
+      <c r="L121" s="5" t="inlineStr"/>
+      <c r="M121" s="5" t="inlineStr"/>
       <c r="N121" s="5" t="inlineStr"/>
-      <c r="O121" s="20" t="inlineStr">
-        <is>
-          <t>https://avia.tutu.ru/f/Chelyabinsk/Moskva/?class=Y&amp;travelers=1&amp;route[0]=98-28102026-491</t>
-        </is>
-      </c>
-      <c r="P121" s="5" t="inlineStr">
-        <is>
-          <t>Поздно; лучше В1</t>
-        </is>
-      </c>
-      <c r="Q121" s="5" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
-      </c>
+      <c r="O121" s="5" t="inlineStr"/>
+      <c r="P121" s="5" t="inlineStr"/>
+      <c r="Q121" s="5" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>Челябинск (Златоуст)</t>
+          <t>Магнитогорск</t>
         </is>
       </c>
       <c r="B122" s="5" t="n">
@@ -13562,34 +13522,34 @@
       </c>
       <c r="E122" s="7" t="inlineStr">
         <is>
-          <t>Самолёт, Победа</t>
+          <t>Самолёт, Аэрофлот</t>
         </is>
       </c>
       <c r="F122" s="7" t="inlineStr">
         <is>
-          <t>DP-413</t>
+          <t>SU-1428</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
-          <t>30.10 23:45</t>
+          <t>31.10 00:40</t>
         </is>
       </c>
       <c r="H122" s="5" t="inlineStr">
         <is>
-          <t>31.10 04:25 (мест.)</t>
+          <t>31.10 05:05 (мест.)</t>
         </is>
       </c>
       <c r="I122" s="5" t="inlineStr">
         <is>
-          <t>Внуково</t>
+          <t>Шереметьево</t>
         </is>
       </c>
       <c r="J122" s="6" t="n">
-        <v>7789</v>
+        <v>11097</v>
       </c>
       <c r="K122" s="6" t="n">
-        <v>10643</v>
+        <v>14765</v>
       </c>
       <c r="L122" s="5" t="inlineStr">
         <is>
@@ -13600,12 +13560,12 @@
       <c r="N122" s="5" t="inlineStr"/>
       <c r="O122" s="20" t="inlineStr">
         <is>
-          <t>https://avia.tutu.ru/f/Moskva/Chelyabinsk/?class=Y&amp;travelers=1&amp;route[0]=491-30102026-98</t>
+          <t>https://avia.tutu.ru/f/Moskva/Magnitogorsk/?class=Y&amp;travelers=1&amp;route[0]=491-30102026-45</t>
         </is>
       </c>
       <c r="P122" s="5" t="inlineStr">
         <is>
-          <t>Рейсы Победы из SVO в 23:00/23:30 не проходят правило 2 ч</t>
+          <t>Ночной рейс сразу после конференции, гостиница не нужна. Время по расписанию 30.10 — проверить на 31.10</t>
         </is>
       </c>
       <c r="Q122" s="5" t="inlineStr"/>
@@ -13613,7 +13573,7 @@
     <row r="123">
       <c r="A123" s="15" t="inlineStr">
         <is>
-          <t>Тюмень</t>
+          <t>Челябинск</t>
         </is>
       </c>
       <c r="B123" s="16" t="n">
@@ -13636,49 +13596,49 @@
       </c>
       <c r="F123" s="17" t="inlineStr">
         <is>
-          <t>DP-6562</t>
+          <t>DP-414</t>
         </is>
       </c>
       <c r="G123" s="16" t="inlineStr">
         <is>
-          <t>28.10 06:25 (мест.)</t>
+          <t>28.10 06:30 (мест.)</t>
         </is>
       </c>
       <c r="H123" s="16" t="inlineStr">
         <is>
-          <t>28.10 07:30</t>
+          <t>28.10 07:15</t>
         </is>
       </c>
       <c r="I123" s="16" t="inlineStr">
         <is>
-          <t>Шереметьево</t>
+          <t>Внуково</t>
         </is>
       </c>
       <c r="J123" s="18" t="n">
-        <v>5873</v>
+        <v>6196</v>
       </c>
       <c r="K123" s="18" t="n">
-        <v>8712</v>
+        <v>8991</v>
       </c>
       <c r="L123" s="16" t="inlineStr">
         <is>
-          <t>Шереметьево: такси ~3 ч или аэроэкспресс → Белорусский + метро → Казанский + электричка</t>
+          <t>Внуково: метро → Казанский вокзал + электричка, или такси ~2 ч 45 мин</t>
         </is>
       </c>
       <c r="M123" s="16" t="inlineStr">
         <is>
-          <t>~11:10</t>
+          <t>~10:40</t>
         </is>
       </c>
       <c r="N123" s="16" t="inlineStr"/>
       <c r="O123" s="19" t="inlineStr">
         <is>
-          <t>https://avia.tutu.ru/f/Tyumen/Moskva/?class=Y&amp;travelers=1&amp;route[0]=86-28102026-491</t>
+          <t>https://avia.tutu.ru/f/Chelyabinsk/Moskva/?class=Y&amp;travelers=1&amp;route[0]=98-28102026-491</t>
         </is>
       </c>
       <c r="P123" s="16" t="inlineStr">
         <is>
-          <t>Если сотрудник в Сургуте/Кургане — уточнить, откуда вылет</t>
+          <t>Также DP-6568 05:30→SVO 06:10, та же цена</t>
         </is>
       </c>
       <c r="Q123" s="16" t="inlineStr">
@@ -13690,7 +13650,7 @@
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>Тюмень</t>
+          <t>Челябинск</t>
         </is>
       </c>
       <c r="B124" s="5" t="n">
@@ -13708,49 +13668,49 @@
       </c>
       <c r="E124" s="10" t="inlineStr">
         <is>
-          <t>Самолёт, ЮТэйр</t>
+          <t>Самолёт, Аэрофлот</t>
         </is>
       </c>
       <c r="F124" s="10" t="inlineStr">
         <is>
-          <t>UT-454</t>
+          <t>SU-1093</t>
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr">
         <is>
-          <t>28.10 07:15 (мест.)</t>
+          <t>28.10 06:05 (мест.)</t>
         </is>
       </c>
       <c r="H124" s="5" t="inlineStr">
         <is>
-          <t>28.10 08:10</t>
+          <t>28.10 06:45</t>
         </is>
       </c>
       <c r="I124" s="5" t="inlineStr">
         <is>
-          <t>Внуково</t>
+          <t>Шереметьево</t>
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>7065</v>
+        <v>10408</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>10125</v>
+        <v>14081</v>
       </c>
       <c r="L124" s="5" t="inlineStr">
         <is>
-          <t>Внуково: метро → Казанский вокзал + электричка, или такси ~2 ч 45 мин</t>
+          <t>Шереметьево: такси ~3 ч или аэроэкспресс → Белорусский + метро → Казанский + электричка</t>
         </is>
       </c>
       <c r="M124" s="5" t="inlineStr">
         <is>
-          <t>~11:35</t>
+          <t>~10:25</t>
         </is>
       </c>
       <c r="N124" s="5" t="inlineStr"/>
       <c r="O124" s="20" t="inlineStr">
         <is>
-          <t>https://avia.tutu.ru/f/Tyumen/Moskva/?class=Y&amp;travelers=1&amp;route[0]=86-28102026-491</t>
+          <t>https://avia.tutu.ru/f/Chelyabinsk/Moskva/?class=Y&amp;travelers=1&amp;route[0]=98-28102026-491</t>
         </is>
       </c>
       <c r="P124" s="5" t="inlineStr"/>
@@ -13763,7 +13723,7 @@
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>Тюмень</t>
+          <t>Челябинск</t>
         </is>
       </c>
       <c r="B125" s="5" t="n">
@@ -13781,30 +13741,66 @@
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>не требуется</t>
-        </is>
-      </c>
-      <c r="F125" s="5" t="inlineStr"/>
-      <c r="G125" s="5" t="inlineStr"/>
-      <c r="H125" s="5" t="inlineStr"/>
-      <c r="I125" s="5" t="inlineStr"/>
-      <c r="J125" s="5" t="n"/>
-      <c r="K125" s="5" t="n"/>
-      <c r="L125" s="5" t="inlineStr"/>
-      <c r="M125" s="5" t="inlineStr"/>
+          <t>Самолёт, Аэрофлот</t>
+        </is>
+      </c>
+      <c r="F125" s="5" t="inlineStr">
+        <is>
+          <t>SU-1427</t>
+        </is>
+      </c>
+      <c r="G125" s="5" t="inlineStr">
+        <is>
+          <t>28.10 22:30 (мест.)</t>
+        </is>
+      </c>
+      <c r="H125" s="5" t="inlineStr">
+        <is>
+          <t>28.10 23:20</t>
+        </is>
+      </c>
+      <c r="I125" s="5" t="inlineStr">
+        <is>
+          <t>Шереметьево</t>
+        </is>
+      </c>
+      <c r="J125" s="21" t="n">
+        <v>8190</v>
+      </c>
+      <c r="K125" s="21" t="n">
+        <v>11788</v>
+      </c>
+      <c r="L125" s="5" t="inlineStr">
+        <is>
+          <t>Шереметьево: такси ~3 ч или аэроэкспресс → Белорусский + метро → Казанский + электричка</t>
+        </is>
+      </c>
+      <c r="M125" s="5" t="inlineStr">
+        <is>
+          <t>~02:30</t>
+        </is>
+      </c>
       <c r="N125" s="5" t="inlineStr"/>
-      <c r="O125" s="5" t="inlineStr"/>
+      <c r="O125" s="20" t="inlineStr">
+        <is>
+          <t>https://avia.tutu.ru/f/Chelyabinsk/Moskva/?class=Y&amp;travelers=1&amp;route[0]=98-28102026-491</t>
+        </is>
+      </c>
       <c r="P125" s="5" t="inlineStr">
         <is>
-          <t>Подходит В1</t>
-        </is>
-      </c>
-      <c r="Q125" s="5" t="inlineStr"/>
+          <t>Поздно; лучше В1</t>
+        </is>
+      </c>
+      <c r="Q125" s="5" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>Тюмень</t>
+          <t>Челябинск</t>
         </is>
       </c>
       <c r="B126" s="5" t="n">
@@ -13827,29 +13823,29 @@
       </c>
       <c r="F126" s="7" t="inlineStr">
         <is>
-          <t>DP-6561</t>
+          <t>DP-413</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr">
         <is>
-          <t>30.10 23:50</t>
+          <t>30.10 23:45</t>
         </is>
       </c>
       <c r="H126" s="5" t="inlineStr">
         <is>
-          <t>31.10 04:40 (мест.)</t>
+          <t>31.10 04:25 (мест.)</t>
         </is>
       </c>
       <c r="I126" s="5" t="inlineStr">
         <is>
-          <t>Шереметьево</t>
+          <t>Внуково</t>
         </is>
       </c>
       <c r="J126" s="6" t="n">
-        <v>8168</v>
+        <v>7789</v>
       </c>
       <c r="K126" s="6" t="n">
-        <v>11154</v>
+        <v>10643</v>
       </c>
       <c r="L126" s="5" t="inlineStr">
         <is>
@@ -13860,12 +13856,12 @@
       <c r="N126" s="5" t="inlineStr"/>
       <c r="O126" s="20" t="inlineStr">
         <is>
-          <t>https://avia.tutu.ru/f/Moskva/Tyumen/?class=Y&amp;travelers=1&amp;route[0]=491-30102026-86</t>
+          <t>https://avia.tutu.ru/f/Moskva/Chelyabinsk/?class=Y&amp;travelers=1&amp;route[0]=491-30102026-98</t>
         </is>
       </c>
       <c r="P126" s="5" t="inlineStr">
         <is>
-          <t>Впритык по правилу 2 ч. UT-453 20:30 не успевает</t>
+          <t>Рейсы Победы из SVO в 23:00/23:30 не проходят правило 2 ч</t>
         </is>
       </c>
       <c r="Q126" s="5" t="inlineStr"/>
@@ -13873,7 +13869,7 @@
     <row r="127">
       <c r="A127" s="15" t="inlineStr">
         <is>
-          <t>Санкт-Петербург</t>
+          <t>Тюмень</t>
         </is>
       </c>
       <c r="B127" s="16" t="n">
@@ -13891,60 +13887,52 @@
       </c>
       <c r="E127" s="17" t="inlineStr">
         <is>
-          <t>Поезд, купе (сидячий 2 283)</t>
+          <t>Самолёт, Победа</t>
         </is>
       </c>
       <c r="F127" s="17" t="inlineStr">
         <is>
-          <t>081А</t>
+          <t>DP-6562</t>
         </is>
       </c>
       <c r="G127" s="16" t="inlineStr">
         <is>
-          <t>27.10 21:21</t>
+          <t>28.10 06:25 (мест.)</t>
         </is>
       </c>
       <c r="H127" s="16" t="inlineStr">
         <is>
-          <t>28.10 06:04</t>
+          <t>28.10 07:30</t>
         </is>
       </c>
       <c r="I127" s="16" t="inlineStr">
         <is>
-          <t>Москва, Восточный</t>
+          <t>Шереметьево</t>
         </is>
       </c>
       <c r="J127" s="18" t="n">
-        <v>3272</v>
+        <v>5873</v>
       </c>
       <c r="K127" s="18" t="n">
-        <v>3272</v>
+        <v>8712</v>
       </c>
       <c r="L127" s="16" t="inlineStr">
         <is>
-          <t>Восточный вокзал → МЦД/метро до Казанского (~30 мин) → электричка + такси (07:22 → 09:15)</t>
+          <t>Шереметьево: такси ~3 ч или аэроэкспресс → Белорусский + метро → Казанский + электричка</t>
         </is>
       </c>
       <c r="M127" s="16" t="inlineStr">
         <is>
-          <t>~09:30</t>
-        </is>
-      </c>
-      <c r="N127" s="16" t="inlineStr">
-        <is>
-          <t>ранний заезд</t>
-        </is>
-      </c>
+          <t>~11:10</t>
+        </is>
+      </c>
+      <c r="N127" s="16" t="inlineStr"/>
       <c r="O127" s="19" t="inlineStr">
         <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2004000&amp;nnst2=2000000</t>
-        </is>
-      </c>
-      <c r="P127" s="16" t="inlineStr">
-        <is>
-          <t>Вечером сел — утром в Москве</t>
-        </is>
-      </c>
+          <t>https://avia.tutu.ru/f/Tyumen/Moskva/?class=Y&amp;travelers=1&amp;route[0]=86-28102026-491</t>
+        </is>
+      </c>
+      <c r="P127" s="16" t="inlineStr"/>
       <c r="Q127" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
@@ -13954,7 +13942,7 @@
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>Санкт-Петербург</t>
+          <t>Тюмень</t>
         </is>
       </c>
       <c r="B128" s="5" t="n">
@@ -13972,56 +13960,52 @@
       </c>
       <c r="E128" s="10" t="inlineStr">
         <is>
-          <t>Поезд «Смена — А. Бетанкур», купе</t>
+          <t>Самолёт, ЮТэйр</t>
         </is>
       </c>
       <c r="F128" s="10" t="inlineStr">
         <is>
-          <t>025А</t>
+          <t>UT-454</t>
         </is>
       </c>
       <c r="G128" s="5" t="inlineStr">
         <is>
-          <t>27.10 23:40</t>
+          <t>28.10 07:15 (мест.)</t>
         </is>
       </c>
       <c r="H128" s="5" t="inlineStr">
         <is>
-          <t>28.10 07:45</t>
+          <t>28.10 08:10</t>
         </is>
       </c>
       <c r="I128" s="5" t="inlineStr">
         <is>
-          <t>Москва, Ленинградский</t>
+          <t>Внуково</t>
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>3975</v>
+        <v>7065</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>3975</v>
+        <v>10125</v>
       </c>
       <c r="L128" s="5" t="inlineStr">
         <is>
-          <t>Ленинградский вокзал → через площадь на Казанский (5 мин) → электричка + такси (08:47 РЭКС → 10:28)</t>
+          <t>Внуково: метро → Казанский вокзал + электричка, или такси ~2 ч 45 мин</t>
         </is>
       </c>
       <c r="M128" s="5" t="inlineStr">
         <is>
-          <t>~10:45</t>
+          <t>~11:35</t>
         </is>
       </c>
       <c r="N128" s="5" t="inlineStr"/>
       <c r="O128" s="20" t="inlineStr">
         <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2004000&amp;nnst2=2000000</t>
-        </is>
-      </c>
-      <c r="P128" s="5" t="inlineStr">
-        <is>
-          <t>Ленинградский и Казанский — на одной площади. Также «Сапсан» 28.10 05:30→09:23, 3 830 ₽ (→ 09:48 → 11:36)</t>
-        </is>
-      </c>
+          <t>https://avia.tutu.ru/f/Tyumen/Moskva/?class=Y&amp;travelers=1&amp;route[0]=86-28102026-491</t>
+        </is>
+      </c>
+      <c r="P128" s="5" t="inlineStr"/>
       <c r="Q128" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
@@ -14031,84 +14015,48 @@
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>Санкт-Петербург</t>
+          <t>Тюмень</t>
         </is>
       </c>
       <c r="B129" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C129" s="7" t="inlineStr">
-        <is>
-          <t>В2: после 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D129" s="7" t="inlineStr">
-        <is>
-          <t>Самый дешёвый</t>
-        </is>
-      </c>
-      <c r="E129" s="7" t="inlineStr">
-        <is>
-          <t>Ласточка, сидячий</t>
-        </is>
-      </c>
-      <c r="F129" s="7" t="inlineStr">
-        <is>
-          <t>723Р</t>
-        </is>
-      </c>
-      <c r="G129" s="5" t="inlineStr">
-        <is>
-          <t>28.10 05:35</t>
-        </is>
-      </c>
-      <c r="H129" s="5" t="inlineStr">
-        <is>
-          <t>28.10 11:13</t>
-        </is>
-      </c>
-      <c r="I129" s="5" t="inlineStr">
-        <is>
-          <t>Москва, Ленинградский</t>
-        </is>
-      </c>
-      <c r="J129" s="6" t="n">
-        <v>1121</v>
-      </c>
-      <c r="K129" s="6" t="n">
-        <v>1121</v>
-      </c>
-      <c r="L129" s="5" t="inlineStr">
-        <is>
-          <t>Ленинградский вокзал → через площадь на Казанский (5 мин) → электричка + такси (12:54 → 15:15)</t>
-        </is>
-      </c>
-      <c r="M129" s="5" t="inlineStr">
-        <is>
-          <t>~15:30</t>
-        </is>
-      </c>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>В2: после 15:00 28.10 / В3: к утру 29.10</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E129" s="5" t="inlineStr">
+        <is>
+          <t>не требуется</t>
+        </is>
+      </c>
+      <c r="F129" s="5" t="inlineStr"/>
+      <c r="G129" s="5" t="inlineStr"/>
+      <c r="H129" s="5" t="inlineStr"/>
+      <c r="I129" s="5" t="inlineStr"/>
+      <c r="J129" s="5" t="n"/>
+      <c r="K129" s="5" t="n"/>
+      <c r="L129" s="5" t="inlineStr"/>
+      <c r="M129" s="5" t="inlineStr"/>
       <c r="N129" s="5" t="inlineStr"/>
-      <c r="O129" s="20" t="inlineStr">
-        <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2004000&amp;nnst2=2000000</t>
-        </is>
-      </c>
+      <c r="O129" s="5" t="inlineStr"/>
       <c r="P129" s="5" t="inlineStr">
         <is>
-          <t>Самый дешёвый; к экскурсии в 16:00 успевает</t>
-        </is>
-      </c>
-      <c r="Q129" s="5" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
-      </c>
+          <t>Подходит В1</t>
+        </is>
+      </c>
+      <c r="Q129" s="5" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>Санкт-Петербург</t>
+          <t>Тюмень</t>
         </is>
       </c>
       <c r="B130" s="5" t="n">
@@ -14121,196 +14069,212 @@
       </c>
       <c r="D130" s="7" t="inlineStr">
         <is>
-          <t>Самый дешёвый</t>
+          <t>Самый дешёвый = Удобный</t>
         </is>
       </c>
       <c r="E130" s="7" t="inlineStr">
         <is>
-          <t>Поезд «Аврора», сидячий</t>
+          <t>Самолёт, Победа</t>
         </is>
       </c>
       <c r="F130" s="7" t="inlineStr">
         <is>
-          <t>750У</t>
+          <t>DP-6561</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>30.10 22:30</t>
+          <t>30.10 23:50</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
         <is>
-          <t>31.10 05:00</t>
+          <t>31.10 04:40 (мест.)</t>
         </is>
       </c>
       <c r="I130" s="5" t="inlineStr">
         <is>
-          <t>СПб, Московский вокзал</t>
+          <t>Шереметьево</t>
         </is>
       </c>
       <c r="J130" s="6" t="n">
-        <v>2185</v>
+        <v>8168</v>
       </c>
       <c r="K130" s="6" t="n">
-        <v>2185</v>
+        <v>11154</v>
       </c>
       <c r="L130" s="5" t="inlineStr">
         <is>
-          <t>Электричка 18:43 → Казанский 20:47 → Ленинградский</t>
+          <t>Выезд из гостиницы 18:15; в аэропорту за 2 ч до вылета</t>
         </is>
       </c>
       <c r="M130" s="5" t="inlineStr"/>
       <c r="N130" s="5" t="inlineStr"/>
       <c r="O130" s="20" t="inlineStr">
         <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2004000</t>
-        </is>
-      </c>
-      <c r="P130" s="5" t="inlineStr"/>
+          <t>https://avia.tutu.ru/f/Moskva/Tyumen/?class=Y&amp;travelers=1&amp;route[0]=491-30102026-86</t>
+        </is>
+      </c>
+      <c r="P130" s="5" t="inlineStr">
+        <is>
+          <t>Впритык по правилу 2 ч. UT-453 20:30 не успевает</t>
+        </is>
+      </c>
       <c r="Q130" s="5" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="5" t="inlineStr">
+      <c r="A131" s="15" t="inlineStr">
         <is>
           <t>Санкт-Петербург</t>
         </is>
       </c>
-      <c r="B131" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C131" s="10" t="inlineStr">
-        <is>
-          <t>Обратно</t>
-        </is>
-      </c>
-      <c r="D131" s="10" t="inlineStr">
+      <c r="B131" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C131" s="17" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D131" s="17" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E131" s="17" t="inlineStr">
+        <is>
+          <t>Поезд, купе (сидячий 2 283)</t>
+        </is>
+      </c>
+      <c r="F131" s="17" t="inlineStr">
+        <is>
+          <t>081А</t>
+        </is>
+      </c>
+      <c r="G131" s="16" t="inlineStr">
+        <is>
+          <t>27.10 21:21</t>
+        </is>
+      </c>
+      <c r="H131" s="16" t="inlineStr">
+        <is>
+          <t>28.10 06:04</t>
+        </is>
+      </c>
+      <c r="I131" s="16" t="inlineStr">
+        <is>
+          <t>Москва, Восточный</t>
+        </is>
+      </c>
+      <c r="J131" s="18" t="n">
+        <v>3272</v>
+      </c>
+      <c r="K131" s="18" t="n">
+        <v>3272</v>
+      </c>
+      <c r="L131" s="16" t="inlineStr">
+        <is>
+          <t>Восточный вокзал → МЦД/метро до Казанского (~30 мин) → электричка + такси (07:22 → 09:15)</t>
+        </is>
+      </c>
+      <c r="M131" s="16" t="inlineStr">
+        <is>
+          <t>~09:30</t>
+        </is>
+      </c>
+      <c r="N131" s="16" t="inlineStr">
+        <is>
+          <t>ранний заезд</t>
+        </is>
+      </c>
+      <c r="O131" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2004000&amp;nnst2=2000000</t>
+        </is>
+      </c>
+      <c r="P131" s="16" t="inlineStr">
+        <is>
+          <t>Вечером сел — утром в Москве</t>
+        </is>
+      </c>
+      <c r="Q131" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C132" s="10" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D132" s="10" t="inlineStr">
         <is>
           <t>Удобный</t>
         </is>
       </c>
-      <c r="E131" s="10" t="inlineStr">
+      <c r="E132" s="10" t="inlineStr">
         <is>
           <t>Поезд «Смена — А. Бетанкур», купе</t>
         </is>
       </c>
-      <c r="F131" s="10" t="inlineStr">
-        <is>
-          <t>026А</t>
-        </is>
-      </c>
-      <c r="G131" s="5" t="inlineStr">
-        <is>
-          <t>30.10 23:10</t>
-        </is>
-      </c>
-      <c r="H131" s="5" t="inlineStr">
-        <is>
-          <t>31.10 07:07</t>
-        </is>
-      </c>
-      <c r="I131" s="5" t="inlineStr">
-        <is>
-          <t>СПб, Московский вокзал</t>
-        </is>
-      </c>
-      <c r="J131" s="9" t="n">
-        <v>5093</v>
-      </c>
-      <c r="K131" s="9" t="n">
-        <v>5093</v>
-      </c>
-      <c r="L131" s="5" t="inlineStr">
-        <is>
-          <t>Электричка 18:43 или 19:43 → Казанский → Ленинградский</t>
-        </is>
-      </c>
-      <c r="M131" s="5" t="inlineStr"/>
-      <c r="N131" s="5" t="inlineStr"/>
-      <c r="O131" s="20" t="inlineStr">
-        <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2004000</t>
-        </is>
-      </c>
-      <c r="P131" s="5" t="inlineStr">
-        <is>
-          <t>Ночь в купе. Также 028А 22:08, купе 4 256</t>
-        </is>
-      </c>
-      <c r="Q131" s="5" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="15" t="inlineStr">
-        <is>
-          <t>Нижний Новгород</t>
-        </is>
-      </c>
-      <c r="B132" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C132" s="17" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D132" s="17" t="inlineStr">
-        <is>
-          <t>Самый дешёвый</t>
-        </is>
-      </c>
-      <c r="E132" s="17" t="inlineStr">
-        <is>
-          <t>Ласточка, сидячий</t>
-        </is>
-      </c>
-      <c r="F132" s="17" t="inlineStr">
-        <is>
-          <t>723А</t>
-        </is>
-      </c>
-      <c r="G132" s="16" t="inlineStr">
-        <is>
-          <t>28.10 04:51</t>
-        </is>
-      </c>
-      <c r="H132" s="16" t="inlineStr">
-        <is>
-          <t>28.10 09:09</t>
-        </is>
-      </c>
-      <c r="I132" s="16" t="inlineStr">
-        <is>
-          <t>Москва, Восточный</t>
-        </is>
-      </c>
-      <c r="J132" s="18" t="n">
-        <v>2435</v>
-      </c>
-      <c r="K132" s="18" t="n">
-        <v>2435</v>
-      </c>
-      <c r="L132" s="16" t="inlineStr">
-        <is>
-          <t>Восточный вокзал → МЦД/метро до Казанского (~30 мин) → электричка + такси (09:48 впритык, иначе 12:54 → 15:15)</t>
-        </is>
-      </c>
-      <c r="M132" s="16" t="inlineStr">
-        <is>
-          <t>~12:00 / ~15:30</t>
-        </is>
-      </c>
-      <c r="N132" s="16" t="inlineStr"/>
-      <c r="O132" s="19" t="inlineStr">
-        <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2060000&amp;nnst2=2000000</t>
-        </is>
-      </c>
-      <c r="P132" s="16" t="inlineStr">
-        <is>
-          <t>Или своя машина: ~430 км, ~6 ч</t>
-        </is>
-      </c>
-      <c r="Q132" s="16" t="inlineStr">
+      <c r="F132" s="10" t="inlineStr">
+        <is>
+          <t>025А</t>
+        </is>
+      </c>
+      <c r="G132" s="5" t="inlineStr">
+        <is>
+          <t>27.10 23:40</t>
+        </is>
+      </c>
+      <c r="H132" s="5" t="inlineStr">
+        <is>
+          <t>28.10 07:45</t>
+        </is>
+      </c>
+      <c r="I132" s="5" t="inlineStr">
+        <is>
+          <t>Москва, Ленинградский</t>
+        </is>
+      </c>
+      <c r="J132" s="9" t="n">
+        <v>3975</v>
+      </c>
+      <c r="K132" s="9" t="n">
+        <v>3975</v>
+      </c>
+      <c r="L132" s="5" t="inlineStr">
+        <is>
+          <t>Ленинградский вокзал → через площадь на Казанский (5 мин) → электричка + такси (08:47 РЭКС → 10:28)</t>
+        </is>
+      </c>
+      <c r="M132" s="5" t="inlineStr">
+        <is>
+          <t>~10:45</t>
+        </is>
+      </c>
+      <c r="N132" s="5" t="inlineStr"/>
+      <c r="O132" s="20" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2004000&amp;nnst2=2000000</t>
+        </is>
+      </c>
+      <c r="P132" s="5" t="inlineStr">
+        <is>
+          <t>Ленинградский и Казанский — на одной площади. Также «Сапсан» 28.10 05:30→09:23, 3 830 ₽ (→ 09:48 → 11:36)</t>
+        </is>
+      </c>
+      <c r="Q132" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -14319,72 +14283,72 @@
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>Нижний Новгород</t>
+          <t>Санкт-Петербург</t>
         </is>
       </c>
       <c r="B133" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C133" s="10" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D133" s="10" t="inlineStr">
-        <is>
-          <t>Удобный</t>
-        </is>
-      </c>
-      <c r="E133" s="10" t="inlineStr">
-        <is>
-          <t>Поезд «Вятка», купе</t>
-        </is>
-      </c>
-      <c r="F133" s="10" t="inlineStr">
-        <is>
-          <t>031Г</t>
+      <c r="C133" s="7" t="inlineStr">
+        <is>
+          <t>В2: после 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D133" s="7" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E133" s="7" t="inlineStr">
+        <is>
+          <t>Ласточка, сидячий</t>
+        </is>
+      </c>
+      <c r="F133" s="7" t="inlineStr">
+        <is>
+          <t>723Р</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>28.10 03:05</t>
+          <t>28.10 05:35</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
         <is>
-          <t>28.10 09:27</t>
+          <t>28.10 11:13</t>
         </is>
       </c>
       <c r="I133" s="5" t="inlineStr">
         <is>
-          <t>Москва, Ярославский</t>
-        </is>
-      </c>
-      <c r="J133" s="9" t="n">
-        <v>4460</v>
-      </c>
-      <c r="K133" s="9" t="n">
-        <v>4460</v>
+          <t>Москва, Ленинградский</t>
+        </is>
+      </c>
+      <c r="J133" s="6" t="n">
+        <v>1121</v>
+      </c>
+      <c r="K133" s="6" t="n">
+        <v>1121</v>
       </c>
       <c r="L133" s="5" t="inlineStr">
         <is>
-          <t>Ярославский вокзал → через площадь на Казанский (5 мин) → электричка + такси (09:48 → 11:36)</t>
+          <t>Ленинградский вокзал → через площадь на Казанский (5 мин) → электричка + такси (12:54 → 15:15)</t>
         </is>
       </c>
       <c r="M133" s="5" t="inlineStr">
         <is>
-          <t>~12:00</t>
+          <t>~15:30</t>
         </is>
       </c>
       <c r="N133" s="5" t="inlineStr"/>
       <c r="O133" s="20" t="inlineStr">
         <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2060000&amp;nnst2=2000000</t>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2004000&amp;nnst2=2000000</t>
         </is>
       </c>
       <c r="P133" s="5" t="inlineStr">
         <is>
-          <t>Ночной поезд, посадка в 03:05</t>
+          <t>Самый дешёвый; к экскурсии в 16:00 успевает</t>
         </is>
       </c>
       <c r="Q133" s="5" t="inlineStr">
@@ -14396,286 +14360,286 @@
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>Нижний Новгород</t>
+          <t>Санкт-Петербург</t>
         </is>
       </c>
       <c r="B134" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C134" s="5" t="inlineStr">
-        <is>
-          <t>В2: после 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D134" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E134" s="5" t="inlineStr">
-        <is>
-          <t>Поезд «Буревестник», сидячий</t>
-        </is>
-      </c>
-      <c r="F134" s="5" t="inlineStr">
-        <is>
-          <t>705Э</t>
+      <c r="C134" s="7" t="inlineStr">
+        <is>
+          <t>Обратно</t>
+        </is>
+      </c>
+      <c r="D134" s="7" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E134" s="7" t="inlineStr">
+        <is>
+          <t>Поезд «Аврора», сидячий</t>
+        </is>
+      </c>
+      <c r="F134" s="7" t="inlineStr">
+        <is>
+          <t>750У</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>28.10 07:20</t>
+          <t>30.10 22:30</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
         <is>
-          <t>28.10 11:34</t>
+          <t>31.10 05:00</t>
         </is>
       </c>
       <c r="I134" s="5" t="inlineStr">
         <is>
-          <t>Москва, Восточный</t>
-        </is>
-      </c>
-      <c r="J134" s="21" t="n">
-        <v>2136</v>
-      </c>
-      <c r="K134" s="21" t="n">
-        <v>2136</v>
+          <t>СПб, Московский вокзал</t>
+        </is>
+      </c>
+      <c r="J134" s="6" t="n">
+        <v>2185</v>
+      </c>
+      <c r="K134" s="6" t="n">
+        <v>2185</v>
       </c>
       <c r="L134" s="5" t="inlineStr">
         <is>
-          <t>Восточный вокзал → МЦД/метро до Казанского (~30 мин) → электричка + такси (12:54 → 15:15)</t>
-        </is>
-      </c>
-      <c r="M134" s="5" t="inlineStr">
-        <is>
-          <t>~15:30</t>
-        </is>
-      </c>
+          <t>Электричка 18:43 → Казанский 20:47 → Ленинградский</t>
+        </is>
+      </c>
+      <c r="M134" s="5" t="inlineStr"/>
       <c r="N134" s="5" t="inlineStr"/>
       <c r="O134" s="20" t="inlineStr">
         <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2060000&amp;nnst2=2000000</t>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2004000</t>
         </is>
       </c>
       <c r="P134" s="5" t="inlineStr"/>
-      <c r="Q134" s="5" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
-      </c>
+      <c r="Q134" s="5" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>Нижний Новгород</t>
+          <t>Санкт-Петербург</t>
         </is>
       </c>
       <c r="B135" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C135" s="7" t="inlineStr">
+      <c r="C135" s="10" t="inlineStr">
         <is>
           <t>Обратно</t>
         </is>
       </c>
-      <c r="D135" s="7" t="inlineStr">
-        <is>
-          <t>Самый дешёвый</t>
-        </is>
-      </c>
-      <c r="E135" s="7" t="inlineStr">
-        <is>
-          <t>Ласточка, сидячий</t>
-        </is>
-      </c>
-      <c r="F135" s="7" t="inlineStr">
-        <is>
-          <t>723Я</t>
+      <c r="D135" s="10" t="inlineStr">
+        <is>
+          <t>Удобный</t>
+        </is>
+      </c>
+      <c r="E135" s="10" t="inlineStr">
+        <is>
+          <t>Поезд «Смена — А. Бетанкур», купе</t>
+        </is>
+      </c>
+      <c r="F135" s="10" t="inlineStr">
+        <is>
+          <t>026А</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>30.10 21:15</t>
+          <t>30.10 23:10</t>
         </is>
       </c>
       <c r="H135" s="5" t="inlineStr">
         <is>
-          <t>31.10 01:15</t>
+          <t>31.10 07:07</t>
         </is>
       </c>
       <c r="I135" s="5" t="inlineStr">
         <is>
-          <t>Нижний Новгород</t>
-        </is>
-      </c>
-      <c r="J135" s="6" t="n">
-        <v>2347</v>
-      </c>
-      <c r="K135" s="6" t="n">
-        <v>2347</v>
+          <t>СПб, Московский вокзал</t>
+        </is>
+      </c>
+      <c r="J135" s="9" t="n">
+        <v>5093</v>
+      </c>
+      <c r="K135" s="9" t="n">
+        <v>5093</v>
       </c>
       <c r="L135" s="5" t="inlineStr">
         <is>
-          <t>Электричка 18:43 → Казанский 20:47 → Восточный</t>
+          <t>Электричка 18:43 или 19:43 → Казанский → Ленинградский</t>
         </is>
       </c>
       <c r="M135" s="5" t="inlineStr"/>
       <c r="N135" s="5" t="inlineStr"/>
       <c r="O135" s="20" t="inlineStr">
         <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2060000</t>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2004000</t>
         </is>
       </c>
       <c r="P135" s="5" t="inlineStr">
         <is>
-          <t>Дома ночью</t>
+          <t>Ночь в купе. Также 028А 22:08, купе 4 256</t>
         </is>
       </c>
       <c r="Q135" s="5" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="5" t="inlineStr">
+      <c r="A136" s="15" t="inlineStr">
         <is>
           <t>Нижний Новгород</t>
         </is>
       </c>
-      <c r="B136" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C136" s="10" t="inlineStr">
-        <is>
-          <t>Обратно</t>
-        </is>
-      </c>
-      <c r="D136" s="10" t="inlineStr">
+      <c r="B136" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C136" s="17" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D136" s="17" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E136" s="17" t="inlineStr">
+        <is>
+          <t>Ласточка, сидячий</t>
+        </is>
+      </c>
+      <c r="F136" s="17" t="inlineStr">
+        <is>
+          <t>723А</t>
+        </is>
+      </c>
+      <c r="G136" s="16" t="inlineStr">
+        <is>
+          <t>28.10 04:51</t>
+        </is>
+      </c>
+      <c r="H136" s="16" t="inlineStr">
+        <is>
+          <t>28.10 09:09</t>
+        </is>
+      </c>
+      <c r="I136" s="16" t="inlineStr">
+        <is>
+          <t>Москва, Восточный</t>
+        </is>
+      </c>
+      <c r="J136" s="18" t="n">
+        <v>2435</v>
+      </c>
+      <c r="K136" s="18" t="n">
+        <v>2435</v>
+      </c>
+      <c r="L136" s="16" t="inlineStr">
+        <is>
+          <t>Восточный вокзал → МЦД/метро до Казанского (~30 мин) → электричка + такси (09:48 впритык, иначе 12:54 → 15:15)</t>
+        </is>
+      </c>
+      <c r="M136" s="16" t="inlineStr">
+        <is>
+          <t>~12:00 / ~15:30</t>
+        </is>
+      </c>
+      <c r="N136" s="16" t="inlineStr"/>
+      <c r="O136" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2060000&amp;nnst2=2000000</t>
+        </is>
+      </c>
+      <c r="P136" s="16" t="inlineStr">
+        <is>
+          <t>Или своя машина: ~430 км, ~6 ч</t>
+        </is>
+      </c>
+      <c r="Q136" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>Нижний Новгород</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C137" s="10" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D137" s="10" t="inlineStr">
         <is>
           <t>Удобный</t>
         </is>
       </c>
-      <c r="E136" s="10" t="inlineStr">
-        <is>
-          <t>Поезд «Нижегородец», купе</t>
-        </is>
-      </c>
-      <c r="F136" s="10" t="inlineStr">
-        <is>
-          <t>036Щ</t>
-        </is>
-      </c>
-      <c r="G136" s="5" t="inlineStr">
-        <is>
-          <t>30.10 23:10</t>
-        </is>
-      </c>
-      <c r="H136" s="5" t="inlineStr">
-        <is>
-          <t>31.10 07:10</t>
-        </is>
-      </c>
-      <c r="I136" s="5" t="inlineStr">
-        <is>
-          <t>Нижний Новгород</t>
-        </is>
-      </c>
-      <c r="J136" s="9" t="n">
-        <v>5172</v>
-      </c>
-      <c r="K136" s="9" t="n">
-        <v>5172</v>
-      </c>
-      <c r="L136" s="5" t="inlineStr">
-        <is>
-          <t>Электричка → Казанский → Ярославский (через площадь)</t>
-        </is>
-      </c>
-      <c r="M136" s="5" t="inlineStr"/>
-      <c r="N136" s="5" t="inlineStr"/>
-      <c r="O136" s="20" t="inlineStr">
-        <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2060000</t>
-        </is>
-      </c>
-      <c r="P136" s="5" t="inlineStr">
-        <is>
-          <t>Ночь в купе. Также 010Н 22:30, купе 4 040</t>
-        </is>
-      </c>
-      <c r="Q136" s="5" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="15" t="inlineStr">
-        <is>
-          <t>Смоленск</t>
-        </is>
-      </c>
-      <c r="B137" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C137" s="17" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D137" s="17" t="inlineStr">
-        <is>
-          <t>Самый дешёвый</t>
-        </is>
-      </c>
-      <c r="E137" s="17" t="inlineStr">
-        <is>
-          <t>Ласточка-премиум, сидячий</t>
-        </is>
-      </c>
-      <c r="F137" s="17" t="inlineStr">
-        <is>
-          <t>738М</t>
-        </is>
-      </c>
-      <c r="G137" s="16" t="inlineStr">
-        <is>
-          <t>28.10 07:29</t>
-        </is>
-      </c>
-      <c r="H137" s="16" t="inlineStr">
-        <is>
-          <t>28.10 11:53</t>
-        </is>
-      </c>
-      <c r="I137" s="16" t="inlineStr">
-        <is>
-          <t>Москва, Белорусский</t>
-        </is>
-      </c>
-      <c r="J137" s="18" t="n">
-        <v>1832</v>
-      </c>
-      <c r="K137" s="18" t="n">
-        <v>1832</v>
-      </c>
-      <c r="L137" s="16" t="inlineStr">
-        <is>
-          <t>Белорусский → метро до Комсомольской (~15 мин) → электричка + такси (12:54 → 15:15)</t>
-        </is>
-      </c>
-      <c r="M137" s="16" t="inlineStr">
-        <is>
-          <t>~15:30</t>
-        </is>
-      </c>
-      <c r="N137" s="16" t="inlineStr"/>
-      <c r="O137" s="19" t="inlineStr">
-        <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2000170&amp;nnst2=2000000</t>
-        </is>
-      </c>
-      <c r="P137" s="16" t="inlineStr">
-        <is>
-          <t>К экскурсии в 16:00 успевает</t>
-        </is>
-      </c>
-      <c r="Q137" s="16" t="inlineStr">
+      <c r="E137" s="10" t="inlineStr">
+        <is>
+          <t>Поезд «Вятка», купе</t>
+        </is>
+      </c>
+      <c r="F137" s="10" t="inlineStr">
+        <is>
+          <t>031Г</t>
+        </is>
+      </c>
+      <c r="G137" s="5" t="inlineStr">
+        <is>
+          <t>28.10 03:05</t>
+        </is>
+      </c>
+      <c r="H137" s="5" t="inlineStr">
+        <is>
+          <t>28.10 09:27</t>
+        </is>
+      </c>
+      <c r="I137" s="5" t="inlineStr">
+        <is>
+          <t>Москва, Ярославский</t>
+        </is>
+      </c>
+      <c r="J137" s="9" t="n">
+        <v>4460</v>
+      </c>
+      <c r="K137" s="9" t="n">
+        <v>4460</v>
+      </c>
+      <c r="L137" s="5" t="inlineStr">
+        <is>
+          <t>Ярославский вокзал → через площадь на Казанский (5 мин) → электричка + такси (09:48 → 11:36)</t>
+        </is>
+      </c>
+      <c r="M137" s="5" t="inlineStr">
+        <is>
+          <t>~12:00</t>
+        </is>
+      </c>
+      <c r="N137" s="5" t="inlineStr"/>
+      <c r="O137" s="20" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2060000&amp;nnst2=2000000</t>
+        </is>
+      </c>
+      <c r="P137" s="5" t="inlineStr">
+        <is>
+          <t>Ночной поезд, посадка в 03:05</t>
+        </is>
+      </c>
+      <c r="Q137" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -14684,74 +14648,70 @@
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>Смоленск</t>
+          <t>Нижний Новгород</t>
         </is>
       </c>
       <c r="B138" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C138" s="10" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D138" s="10" t="inlineStr">
-        <is>
-          <t>Удобный</t>
-        </is>
-      </c>
-      <c r="E138" s="10" t="inlineStr">
-        <is>
-          <t>Поезд, купе</t>
-        </is>
-      </c>
-      <c r="F138" s="10" t="inlineStr">
-        <is>
-          <t>008Б</t>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>В2: после 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="inlineStr">
+        <is>
+          <t>Поезд «Буревестник», сидячий</t>
+        </is>
+      </c>
+      <c r="F138" s="5" t="inlineStr">
+        <is>
+          <t>705Э</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>28.10 01:35</t>
+          <t>28.10 07:20</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
         <is>
-          <t>28.10 06:56</t>
+          <t>28.10 11:34</t>
         </is>
       </c>
       <c r="I138" s="5" t="inlineStr">
         <is>
-          <t>Москва, Белорусский</t>
-        </is>
-      </c>
-      <c r="J138" s="9" t="n">
-        <v>4656</v>
-      </c>
-      <c r="K138" s="9" t="n">
-        <v>4656</v>
+          <t>Москва, Восточный</t>
+        </is>
+      </c>
+      <c r="J138" s="21" t="n">
+        <v>2136</v>
+      </c>
+      <c r="K138" s="21" t="n">
+        <v>2136</v>
       </c>
       <c r="L138" s="5" t="inlineStr">
         <is>
-          <t>Белорусский → метро до Комсомольской (~15 мин) → электричка + такси (08:47 РЭКС → 10:28)</t>
+          <t>Восточный вокзал → МЦД/метро до Казанского (~30 мин) → электричка + такси (12:54 → 15:15)</t>
         </is>
       </c>
       <c r="M138" s="5" t="inlineStr">
         <is>
-          <t>~10:45</t>
+          <t>~15:30</t>
         </is>
       </c>
       <c r="N138" s="5" t="inlineStr"/>
       <c r="O138" s="20" t="inlineStr">
         <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2000170&amp;nnst2=2000000</t>
-        </is>
-      </c>
-      <c r="P138" s="5" t="inlineStr">
-        <is>
-          <t>Ночной поезд. Если сотрудник из Великих Лук — поезд до Москвы (Рижский вокзал), уточнить</t>
-        </is>
-      </c>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2060000&amp;nnst2=2000000</t>
+        </is>
+      </c>
+      <c r="P138" s="5" t="inlineStr"/>
       <c r="Q138" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
@@ -14761,7 +14721,7 @@
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>Смоленск</t>
+          <t>Нижний Новгород</t>
         </is>
       </c>
       <c r="B139" s="5" t="n">
@@ -14779,54 +14739,58 @@
       </c>
       <c r="E139" s="7" t="inlineStr">
         <is>
-          <t>Поезд, купе</t>
+          <t>Ласточка, сидячий</t>
         </is>
       </c>
       <c r="F139" s="7" t="inlineStr">
         <is>
-          <t>027Б</t>
+          <t>723Я</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>30.10 23:30</t>
+          <t>30.10 21:15</t>
         </is>
       </c>
       <c r="H139" s="5" t="inlineStr">
         <is>
-          <t>31.10 04:39</t>
+          <t>31.10 01:15</t>
         </is>
       </c>
       <c r="I139" s="5" t="inlineStr">
         <is>
-          <t>Смоленск</t>
+          <t>Нижний Новгород</t>
         </is>
       </c>
       <c r="J139" s="6" t="n">
-        <v>4022</v>
+        <v>2347</v>
       </c>
       <c r="K139" s="6" t="n">
-        <v>4022</v>
+        <v>2347</v>
       </c>
       <c r="L139" s="5" t="inlineStr">
         <is>
-          <t>Электричка 18:43 → Казанский → метро до Белорусской</t>
+          <t>Электричка 18:43 → Казанский 20:47 → Восточный</t>
         </is>
       </c>
       <c r="M139" s="5" t="inlineStr"/>
       <c r="N139" s="5" t="inlineStr"/>
       <c r="O139" s="20" t="inlineStr">
         <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2000170</t>
-        </is>
-      </c>
-      <c r="P139" s="5" t="inlineStr"/>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2060000</t>
+        </is>
+      </c>
+      <c r="P139" s="5" t="inlineStr">
+        <is>
+          <t>Дома ночью</t>
+        </is>
+      </c>
       <c r="Q139" s="5" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>Смоленск</t>
+          <t>Нижний Новгород</t>
         </is>
       </c>
       <c r="B140" s="5" t="n">
@@ -14844,50 +14808,50 @@
       </c>
       <c r="E140" s="10" t="inlineStr">
         <is>
-          <t>Поезд, купе</t>
+          <t>Поезд «Нижегородец», купе</t>
         </is>
       </c>
       <c r="F140" s="10" t="inlineStr">
         <is>
-          <t>007М</t>
+          <t>036Щ</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>30.10 22:12</t>
+          <t>30.10 23:10</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr">
         <is>
-          <t>31.10 02:39</t>
+          <t>31.10 07:10</t>
         </is>
       </c>
       <c r="I140" s="5" t="inlineStr">
         <is>
-          <t>Смоленск</t>
+          <t>Нижний Новгород</t>
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>4656</v>
+        <v>5172</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>4656</v>
+        <v>5172</v>
       </c>
       <c r="L140" s="5" t="inlineStr">
         <is>
-          <t>Электричка 18:43 → Казанский → метро до Белорусской</t>
+          <t>Электричка → Казанский → Ярославский (через площадь)</t>
         </is>
       </c>
       <c r="M140" s="5" t="inlineStr"/>
       <c r="N140" s="5" t="inlineStr"/>
       <c r="O140" s="20" t="inlineStr">
         <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2000170</t>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2060000</t>
         </is>
       </c>
       <c r="P140" s="5" t="inlineStr">
         <is>
-          <t>Или машина ~520 км, ~7 ч</t>
+          <t>Ночь в купе. Также 010Н 22:30, купе 4 040</t>
         </is>
       </c>
       <c r="Q140" s="5" t="inlineStr"/>
@@ -14895,7 +14859,7 @@
     <row r="141">
       <c r="A141" s="15" t="inlineStr">
         <is>
-          <t>Тверь</t>
+          <t>Смоленск</t>
         </is>
       </c>
       <c r="B141" s="16" t="n">
@@ -14913,38 +14877,38 @@
       </c>
       <c r="E141" s="17" t="inlineStr">
         <is>
-          <t>Поезд «Аврора», сидячий</t>
+          <t>Ласточка-премиум, сидячий</t>
         </is>
       </c>
       <c r="F141" s="17" t="inlineStr">
         <is>
-          <t>741У</t>
+          <t>738М</t>
         </is>
       </c>
       <c r="G141" s="16" t="inlineStr">
         <is>
-          <t>28.10 10:16</t>
+          <t>28.10 07:29</t>
         </is>
       </c>
       <c r="H141" s="16" t="inlineStr">
         <is>
-          <t>28.10 11:55</t>
+          <t>28.10 11:53</t>
         </is>
       </c>
       <c r="I141" s="16" t="inlineStr">
         <is>
-          <t>Москва, Ленинградский</t>
+          <t>Москва, Белорусский</t>
         </is>
       </c>
       <c r="J141" s="18" t="n">
-        <v>695</v>
+        <v>1832</v>
       </c>
       <c r="K141" s="18" t="n">
-        <v>695</v>
+        <v>1832</v>
       </c>
       <c r="L141" s="16" t="inlineStr">
         <is>
-          <t>Ленинградский вокзал → через площадь на Казанский (5 мин) → электричка + такси (12:54 → 15:15)</t>
+          <t>Белорусский → метро до Комсомольской (~15 мин) → электричка + такси (12:54 → 15:15)</t>
         </is>
       </c>
       <c r="M141" s="16" t="inlineStr">
@@ -14955,12 +14919,12 @@
       <c r="N141" s="16" t="inlineStr"/>
       <c r="O141" s="19" t="inlineStr">
         <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2004600&amp;nnst2=2000000</t>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2000170&amp;nnst2=2000000</t>
         </is>
       </c>
       <c r="P141" s="16" t="inlineStr">
         <is>
-          <t>Также Ласточка 723Р 09:19→11:13, 611 ₽</t>
+          <t>К экскурсии в 16:00 успевает</t>
         </is>
       </c>
       <c r="Q141" s="16" t="inlineStr">
@@ -14972,7 +14936,7 @@
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>Тверь</t>
+          <t>Смоленск</t>
         </is>
       </c>
       <c r="B142" s="5" t="n">
@@ -14990,54 +14954,66 @@
       </c>
       <c r="E142" s="10" t="inlineStr">
         <is>
-          <t>Своя машина</t>
-        </is>
-      </c>
-      <c r="F142" s="10" t="inlineStr"/>
+          <t>Поезд, купе</t>
+        </is>
+      </c>
+      <c r="F142" s="10" t="inlineStr">
+        <is>
+          <t>008Б</t>
+        </is>
+      </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>28.10 ~09:30</t>
+          <t>28.10 01:35</t>
         </is>
       </c>
       <c r="H142" s="5" t="inlineStr">
         <is>
-          <t>28.10 ~13:30</t>
+          <t>28.10 06:56</t>
         </is>
       </c>
       <c r="I142" s="5" t="inlineStr">
         <is>
-          <t>Коломна</t>
+          <t>Москва, Белорусский</t>
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>1885</v>
+        <v>4656</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>1885</v>
+        <v>4656</v>
       </c>
       <c r="L142" s="5" t="inlineStr">
         <is>
-          <t>~290 км через ЦКАД, ~4 ч</t>
+          <t>Белорусский → метро до Комсомольской (~15 мин) → электричка + такси (08:47 РЭКС → 10:28)</t>
         </is>
       </c>
       <c r="M142" s="5" t="inlineStr">
         <is>
-          <t>~13:30</t>
+          <t>~10:45</t>
         </is>
       </c>
       <c r="N142" s="5" t="inlineStr"/>
-      <c r="O142" s="5" t="inlineStr"/>
+      <c r="O142" s="20" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2000170&amp;nnst2=2000000</t>
+        </is>
+      </c>
       <c r="P142" s="5" t="inlineStr">
         <is>
-          <t>Топливо ~3 770 ₽ туда-обратно на машину</t>
-        </is>
-      </c>
-      <c r="Q142" s="5" t="inlineStr"/>
+          <t>Ночной поезд</t>
+        </is>
+      </c>
+      <c r="Q142" s="5" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>Тверь</t>
+          <t>Смоленск</t>
         </is>
       </c>
       <c r="B143" s="5" t="n">
@@ -15055,784 +15031,748 @@
       </c>
       <c r="E143" s="7" t="inlineStr">
         <is>
-          <t>Поезд «Аврора», сидячий</t>
+          <t>Поезд, купе</t>
         </is>
       </c>
       <c r="F143" s="7" t="inlineStr">
         <is>
-          <t>750У</t>
+          <t>027Б</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>30.10 22:30</t>
+          <t>30.10 23:30</t>
         </is>
       </c>
       <c r="H143" s="5" t="inlineStr">
         <is>
-          <t>31.10 ~00:05</t>
+          <t>31.10 04:39</t>
         </is>
       </c>
       <c r="I143" s="5" t="inlineStr">
         <is>
-          <t>Тверь</t>
+          <t>Смоленск</t>
         </is>
       </c>
       <c r="J143" s="6" t="n">
-        <v>1000</v>
+        <v>4022</v>
       </c>
       <c r="K143" s="6" t="n">
-        <v>1000</v>
+        <v>4022</v>
       </c>
       <c r="L143" s="5" t="inlineStr">
         <is>
-          <t>Электричка 18:43 → Казанский 20:47 → Ленинградский</t>
+          <t>Электричка 18:43 → Казанский → метро до Белорусской</t>
         </is>
       </c>
       <c r="M143" s="5" t="inlineStr"/>
       <c r="N143" s="5" t="inlineStr"/>
       <c r="O143" s="20" t="inlineStr">
         <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2004600</t>
-        </is>
-      </c>
-      <c r="P143" s="5" t="inlineStr">
-        <is>
-          <t>Цена ориентировочная, проверить</t>
-        </is>
-      </c>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2000170</t>
+        </is>
+      </c>
+      <c r="P143" s="5" t="inlineStr"/>
       <c r="Q143" s="5" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="15" t="inlineStr">
-        <is>
-          <t>Рязань</t>
-        </is>
-      </c>
-      <c r="B144" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C144" s="17" t="inlineStr">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t>Смоленск</t>
+        </is>
+      </c>
+      <c r="B144" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C144" s="10" t="inlineStr">
+        <is>
+          <t>Обратно</t>
+        </is>
+      </c>
+      <c r="D144" s="10" t="inlineStr">
+        <is>
+          <t>Удобный</t>
+        </is>
+      </c>
+      <c r="E144" s="10" t="inlineStr">
+        <is>
+          <t>Поезд, купе</t>
+        </is>
+      </c>
+      <c r="F144" s="10" t="inlineStr">
+        <is>
+          <t>007М</t>
+        </is>
+      </c>
+      <c r="G144" s="5" t="inlineStr">
+        <is>
+          <t>30.10 22:12</t>
+        </is>
+      </c>
+      <c r="H144" s="5" t="inlineStr">
+        <is>
+          <t>31.10 02:39</t>
+        </is>
+      </c>
+      <c r="I144" s="5" t="inlineStr">
+        <is>
+          <t>Смоленск</t>
+        </is>
+      </c>
+      <c r="J144" s="9" t="n">
+        <v>4656</v>
+      </c>
+      <c r="K144" s="9" t="n">
+        <v>4656</v>
+      </c>
+      <c r="L144" s="5" t="inlineStr">
+        <is>
+          <t>Электричка 18:43 → Казанский → метро до Белорусской</t>
+        </is>
+      </c>
+      <c r="M144" s="5" t="inlineStr"/>
+      <c r="N144" s="5" t="inlineStr"/>
+      <c r="O144" s="20" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2000170</t>
+        </is>
+      </c>
+      <c r="P144" s="5" t="inlineStr">
+        <is>
+          <t>Или машина ~520 км, ~7 ч</t>
+        </is>
+      </c>
+      <c r="Q144" s="5" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="15" t="inlineStr">
+        <is>
+          <t>Тверь</t>
+        </is>
+      </c>
+      <c r="B145" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C145" s="17" t="inlineStr">
         <is>
           <t>В1: к 15:00 28.10</t>
         </is>
       </c>
-      <c r="D144" s="17" t="inlineStr">
+      <c r="D145" s="17" t="inlineStr">
         <is>
           <t>Самый дешёвый</t>
         </is>
       </c>
-      <c r="E144" s="17" t="inlineStr">
-        <is>
-          <t>Электричка «Стандарт плюс»</t>
-        </is>
-      </c>
-      <c r="F144" s="17" t="inlineStr">
-        <is>
-          <t>6993</t>
-        </is>
-      </c>
-      <c r="G144" s="16" t="inlineStr">
-        <is>
-          <t>28.10 05:18</t>
-        </is>
-      </c>
-      <c r="H144" s="16" t="inlineStr">
-        <is>
-          <t>28.10 06:54</t>
-        </is>
-      </c>
-      <c r="I144" s="16" t="inlineStr">
-        <is>
-          <t>Коломна</t>
-        </is>
-      </c>
-      <c r="J144" s="18" t="n">
-        <v>306</v>
-      </c>
-      <c r="K144" s="18" t="n">
-        <v>306</v>
-      </c>
-      <c r="L144" s="16" t="inlineStr">
-        <is>
-          <t>Ст. Коломна → такси 10 мин (~300 ₽)</t>
-        </is>
-      </c>
-      <c r="M144" s="16" t="inlineStr">
-        <is>
-          <t>~07:10</t>
-        </is>
-      </c>
-      <c r="N144" s="16" t="inlineStr">
-        <is>
-          <t>ранний заезд</t>
-        </is>
-      </c>
-      <c r="O144" s="19" t="inlineStr">
-        <is>
-          <t>https://www.tutu.ru/rasp.php?st1=92502&amp;st2=11902&amp;date=28.10.2026</t>
-        </is>
-      </c>
-      <c r="P144" s="16" t="inlineStr">
-        <is>
-          <t>Следующая электричка только 14:36 (→16:17) — к экскурсии не успевает</t>
-        </is>
-      </c>
-      <c r="Q144" s="16" t="inlineStr">
+      <c r="E145" s="17" t="inlineStr">
+        <is>
+          <t>Поезд «Аврора», сидячий</t>
+        </is>
+      </c>
+      <c r="F145" s="17" t="inlineStr">
+        <is>
+          <t>741У</t>
+        </is>
+      </c>
+      <c r="G145" s="16" t="inlineStr">
+        <is>
+          <t>28.10 10:16</t>
+        </is>
+      </c>
+      <c r="H145" s="16" t="inlineStr">
+        <is>
+          <t>28.10 11:55</t>
+        </is>
+      </c>
+      <c r="I145" s="16" t="inlineStr">
+        <is>
+          <t>Москва, Ленинградский</t>
+        </is>
+      </c>
+      <c r="J145" s="18" t="n">
+        <v>695</v>
+      </c>
+      <c r="K145" s="18" t="n">
+        <v>695</v>
+      </c>
+      <c r="L145" s="16" t="inlineStr">
+        <is>
+          <t>Ленинградский вокзал → через площадь на Казанский (5 мин) → электричка + такси (12:54 → 15:15)</t>
+        </is>
+      </c>
+      <c r="M145" s="16" t="inlineStr">
+        <is>
+          <t>~15:30</t>
+        </is>
+      </c>
+      <c r="N145" s="16" t="inlineStr"/>
+      <c r="O145" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2004600&amp;nnst2=2000000</t>
+        </is>
+      </c>
+      <c r="P145" s="16" t="inlineStr">
+        <is>
+          <t>Также Ласточка 723Р 09:19→11:13, 611 ₽</t>
+        </is>
+      </c>
+      <c r="Q145" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
       </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="5" t="inlineStr">
-        <is>
-          <t>Рязань</t>
-        </is>
-      </c>
-      <c r="B145" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C145" s="10" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D145" s="10" t="inlineStr">
-        <is>
-          <t>Удобный</t>
-        </is>
-      </c>
-      <c r="E145" s="10" t="inlineStr">
-        <is>
-          <t>Своя машина</t>
-        </is>
-      </c>
-      <c r="F145" s="10" t="inlineStr"/>
-      <c r="G145" s="5" t="inlineStr">
-        <is>
-          <t>28.10 ~12:30</t>
-        </is>
-      </c>
-      <c r="H145" s="5" t="inlineStr">
-        <is>
-          <t>28.10 ~14:00</t>
-        </is>
-      </c>
-      <c r="I145" s="5" t="inlineStr">
-        <is>
-          <t>Коломна</t>
-        </is>
-      </c>
-      <c r="J145" s="9" t="n">
-        <v>650</v>
-      </c>
-      <c r="K145" s="9" t="n">
-        <v>650</v>
-      </c>
-      <c r="L145" s="5" t="inlineStr">
-        <is>
-          <t>~100 км, ~1 ч 30 мин</t>
-        </is>
-      </c>
-      <c r="M145" s="5" t="inlineStr">
-        <is>
-          <t>~14:00</t>
-        </is>
-      </c>
-      <c r="N145" s="5" t="inlineStr"/>
-      <c r="O145" s="5" t="inlineStr"/>
-      <c r="P145" s="5" t="inlineStr">
-        <is>
-          <t>Топливо ~1 300 ₽ туда-обратно</t>
-        </is>
-      </c>
-      <c r="Q145" s="5" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
         <is>
+          <t>Тверь</t>
+        </is>
+      </c>
+      <c r="B146" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C146" s="10" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D146" s="10" t="inlineStr">
+        <is>
+          <t>Удобный</t>
+        </is>
+      </c>
+      <c r="E146" s="10" t="inlineStr">
+        <is>
+          <t>Своя машина</t>
+        </is>
+      </c>
+      <c r="F146" s="10" t="inlineStr"/>
+      <c r="G146" s="5" t="inlineStr">
+        <is>
+          <t>28.10 ~09:30</t>
+        </is>
+      </c>
+      <c r="H146" s="5" t="inlineStr">
+        <is>
+          <t>28.10 ~13:30</t>
+        </is>
+      </c>
+      <c r="I146" s="5" t="inlineStr">
+        <is>
+          <t>Коломна</t>
+        </is>
+      </c>
+      <c r="J146" s="9" t="n">
+        <v>1885</v>
+      </c>
+      <c r="K146" s="9" t="n">
+        <v>1885</v>
+      </c>
+      <c r="L146" s="5" t="inlineStr">
+        <is>
+          <t>~290 км через ЦКАД, ~4 ч</t>
+        </is>
+      </c>
+      <c r="M146" s="5" t="inlineStr">
+        <is>
+          <t>~13:30</t>
+        </is>
+      </c>
+      <c r="N146" s="5" t="inlineStr"/>
+      <c r="O146" s="5" t="inlineStr"/>
+      <c r="P146" s="5" t="inlineStr">
+        <is>
+          <t>Топливо ~3 770 ₽ туда-обратно на машину</t>
+        </is>
+      </c>
+      <c r="Q146" s="5" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="5" t="inlineStr">
+        <is>
+          <t>Тверь</t>
+        </is>
+      </c>
+      <c r="B147" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C147" s="7" t="inlineStr">
+        <is>
+          <t>Обратно</t>
+        </is>
+      </c>
+      <c r="D147" s="7" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E147" s="7" t="inlineStr">
+        <is>
+          <t>Поезд «Аврора», сидячий</t>
+        </is>
+      </c>
+      <c r="F147" s="7" t="inlineStr">
+        <is>
+          <t>750У</t>
+        </is>
+      </c>
+      <c r="G147" s="5" t="inlineStr">
+        <is>
+          <t>30.10 22:30</t>
+        </is>
+      </c>
+      <c r="H147" s="5" t="inlineStr">
+        <is>
+          <t>31.10 ~00:05</t>
+        </is>
+      </c>
+      <c r="I147" s="5" t="inlineStr">
+        <is>
+          <t>Тверь</t>
+        </is>
+      </c>
+      <c r="J147" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K147" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L147" s="5" t="inlineStr">
+        <is>
+          <t>Электричка 18:43 → Казанский 20:47 → Ленинградский</t>
+        </is>
+      </c>
+      <c r="M147" s="5" t="inlineStr"/>
+      <c r="N147" s="5" t="inlineStr"/>
+      <c r="O147" s="20" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2004600</t>
+        </is>
+      </c>
+      <c r="P147" s="5" t="inlineStr">
+        <is>
+          <t>Цена ориентировочная, проверить</t>
+        </is>
+      </c>
+      <c r="Q147" s="5" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="15" t="inlineStr">
+        <is>
           <t>Рязань</t>
         </is>
       </c>
-      <c r="B146" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C146" s="7" t="inlineStr">
-        <is>
-          <t>Обратно</t>
-        </is>
-      </c>
-      <c r="D146" s="7" t="inlineStr">
+      <c r="B148" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C148" s="17" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D148" s="17" t="inlineStr">
         <is>
           <t>Самый дешёвый</t>
         </is>
       </c>
-      <c r="E146" s="7" t="inlineStr">
+      <c r="E148" s="17" t="inlineStr">
         <is>
           <t>Электричка «Стандарт плюс»</t>
         </is>
       </c>
-      <c r="F146" s="7" t="inlineStr">
-        <is>
-          <t>6996</t>
-        </is>
-      </c>
-      <c r="G146" s="5" t="inlineStr">
-        <is>
-          <t>30.10 21:16</t>
-        </is>
-      </c>
-      <c r="H146" s="5" t="inlineStr">
-        <is>
-          <t>30.10 22:49</t>
-        </is>
-      </c>
-      <c r="I146" s="5" t="inlineStr">
-        <is>
-          <t>Рязань-1</t>
-        </is>
-      </c>
-      <c r="J146" s="6" t="n">
+      <c r="F148" s="17" t="inlineStr">
+        <is>
+          <t>6993</t>
+        </is>
+      </c>
+      <c r="G148" s="16" t="inlineStr">
+        <is>
+          <t>28.10 05:18</t>
+        </is>
+      </c>
+      <c r="H148" s="16" t="inlineStr">
+        <is>
+          <t>28.10 06:54</t>
+        </is>
+      </c>
+      <c r="I148" s="16" t="inlineStr">
+        <is>
+          <t>Коломна</t>
+        </is>
+      </c>
+      <c r="J148" s="18" t="n">
         <v>306</v>
       </c>
-      <c r="K146" s="6" t="n">
+      <c r="K148" s="18" t="n">
         <v>306</v>
       </c>
-      <c r="L146" s="5" t="inlineStr">
-        <is>
-          <t>Такси до ст. Коломна (~300 ₽)</t>
-        </is>
-      </c>
-      <c r="M146" s="5" t="inlineStr"/>
-      <c r="N146" s="5" t="inlineStr"/>
-      <c r="O146" s="20" t="inlineStr">
-        <is>
-          <t>https://www.tutu.ru/rasp.php?st1=11902&amp;st2=92502&amp;date=30.10.2026</t>
-        </is>
-      </c>
-      <c r="P146" s="5" t="inlineStr"/>
-      <c r="Q146" s="5" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="15" t="inlineStr">
-        <is>
-          <t>Москва</t>
-        </is>
-      </c>
-      <c r="B147" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="C147" s="17" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D147" s="17" t="inlineStr">
-        <is>
-          <t>Самый дешёвый</t>
-        </is>
-      </c>
-      <c r="E147" s="17" t="inlineStr">
-        <is>
-          <t>Электричка / РЭКС</t>
-        </is>
-      </c>
-      <c r="F147" s="17" t="inlineStr"/>
-      <c r="G147" s="16" t="inlineStr">
-        <is>
-          <t>28.10 09:48 или 12:54</t>
-        </is>
-      </c>
-      <c r="H147" s="16" t="inlineStr">
-        <is>
-          <t>11:36 / 15:15</t>
-        </is>
-      </c>
-      <c r="I147" s="16" t="inlineStr">
-        <is>
-          <t>Коломна</t>
-        </is>
-      </c>
-      <c r="J147" s="18" t="n">
-        <v>490</v>
-      </c>
-      <c r="K147" s="18" t="n">
-        <v>490</v>
-      </c>
-      <c r="L147" s="16" t="inlineStr">
-        <is>
-          <t>Казанский вокзал → электричка до ст. Коломна (490–620 ₽) + такси 10 мин (~300 ₽)</t>
-        </is>
-      </c>
-      <c r="M147" s="16" t="inlineStr">
-        <is>
-          <t>~12:00 / ~15:30</t>
-        </is>
-      </c>
-      <c r="N147" s="16" t="inlineStr"/>
-      <c r="O147" s="19" t="inlineStr">
-        <is>
-          <t>https://www.tutu.ru/prigorod/</t>
-        </is>
-      </c>
-      <c r="P147" s="16" t="inlineStr">
-        <is>
-          <t>РЭКС 620 ₽</t>
-        </is>
-      </c>
-      <c r="Q147" s="16" t="inlineStr">
+      <c r="L148" s="16" t="inlineStr">
+        <is>
+          <t>Ст. Коломна → такси 10 мин (~300 ₽)</t>
+        </is>
+      </c>
+      <c r="M148" s="16" t="inlineStr">
+        <is>
+          <t>~07:10</t>
+        </is>
+      </c>
+      <c r="N148" s="16" t="inlineStr">
+        <is>
+          <t>ранний заезд</t>
+        </is>
+      </c>
+      <c r="O148" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/rasp.php?st1=92502&amp;st2=11902&amp;date=28.10.2026</t>
+        </is>
+      </c>
+      <c r="P148" s="16" t="inlineStr">
+        <is>
+          <t>Следующая электричка только 14:36 (→16:17) — к экскурсии не успевает</t>
+        </is>
+      </c>
+      <c r="Q148" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
       </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="5" t="inlineStr">
-        <is>
-          <t>Москва</t>
-        </is>
-      </c>
-      <c r="B148" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C148" s="10" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D148" s="10" t="inlineStr">
-        <is>
-          <t>Удобный</t>
-        </is>
-      </c>
-      <c r="E148" s="10" t="inlineStr">
-        <is>
-          <t>Своя машина</t>
-        </is>
-      </c>
-      <c r="F148" s="10" t="inlineStr"/>
-      <c r="G148" s="5" t="inlineStr">
-        <is>
-          <t>28.10 ~12:00</t>
-        </is>
-      </c>
-      <c r="H148" s="5" t="inlineStr">
-        <is>
-          <t>28.10 ~14:00</t>
-        </is>
-      </c>
-      <c r="I148" s="5" t="inlineStr">
-        <is>
-          <t>Коломна</t>
-        </is>
-      </c>
-      <c r="J148" s="9" t="n">
-        <v>750</v>
-      </c>
-      <c r="K148" s="9" t="n">
-        <v>750</v>
-      </c>
-      <c r="L148" s="5" t="inlineStr">
-        <is>
-          <t>~115 км по Новорязанскому ш., ~2 ч с пробками</t>
-        </is>
-      </c>
-      <c r="M148" s="5" t="inlineStr">
-        <is>
-          <t>~14:00</t>
-        </is>
-      </c>
-      <c r="N148" s="5" t="inlineStr"/>
-      <c r="O148" s="5" t="inlineStr"/>
-      <c r="P148" s="5" t="inlineStr">
-        <is>
-          <t>Топливо ~1 500 ₽ туда-обратно</t>
-        </is>
-      </c>
-      <c r="Q148" s="5" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>Москва</t>
+          <t>Рязань</t>
         </is>
       </c>
       <c r="B149" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C149" s="7" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="C149" s="10" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D149" s="10" t="inlineStr">
+        <is>
+          <t>Удобный</t>
+        </is>
+      </c>
+      <c r="E149" s="10" t="inlineStr">
+        <is>
+          <t>Своя машина</t>
+        </is>
+      </c>
+      <c r="F149" s="10" t="inlineStr"/>
+      <c r="G149" s="5" t="inlineStr">
+        <is>
+          <t>28.10 ~12:30</t>
+        </is>
+      </c>
+      <c r="H149" s="5" t="inlineStr">
+        <is>
+          <t>28.10 ~14:00</t>
+        </is>
+      </c>
+      <c r="I149" s="5" t="inlineStr">
+        <is>
+          <t>Коломна</t>
+        </is>
+      </c>
+      <c r="J149" s="9" t="n">
+        <v>650</v>
+      </c>
+      <c r="K149" s="9" t="n">
+        <v>650</v>
+      </c>
+      <c r="L149" s="5" t="inlineStr">
+        <is>
+          <t>~100 км, ~1 ч 30 мин</t>
+        </is>
+      </c>
+      <c r="M149" s="5" t="inlineStr">
+        <is>
+          <t>~14:00</t>
+        </is>
+      </c>
+      <c r="N149" s="5" t="inlineStr"/>
+      <c r="O149" s="5" t="inlineStr"/>
+      <c r="P149" s="5" t="inlineStr">
+        <is>
+          <t>Топливо ~1 300 ₽ туда-обратно</t>
+        </is>
+      </c>
+      <c r="Q149" s="5" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="5" t="inlineStr">
+        <is>
+          <t>Рязань</t>
+        </is>
+      </c>
+      <c r="B150" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C150" s="7" t="inlineStr">
         <is>
           <t>Обратно</t>
         </is>
       </c>
-      <c r="D149" s="7" t="inlineStr">
-        <is>
-          <t>Самый дешёвый = Удобный</t>
-        </is>
-      </c>
-      <c r="E149" s="7" t="inlineStr">
-        <is>
-          <t>Электричка или машина</t>
-        </is>
-      </c>
-      <c r="F149" s="7" t="inlineStr"/>
-      <c r="G149" s="5" t="inlineStr">
-        <is>
-          <t>30.10 18:43</t>
-        </is>
-      </c>
-      <c r="H149" s="5" t="inlineStr">
-        <is>
-          <t>30.10 20:47</t>
-        </is>
-      </c>
-      <c r="I149" s="5" t="inlineStr">
-        <is>
-          <t>Москва, Казанский</t>
-        </is>
-      </c>
-      <c r="J149" s="6" t="n">
-        <v>490</v>
-      </c>
-      <c r="K149" s="6" t="n">
-        <v>490</v>
-      </c>
-      <c r="L149" s="5" t="inlineStr">
-        <is>
-          <t>Электричка 18:43 → 20:47</t>
-        </is>
-      </c>
-      <c r="M149" s="5" t="inlineStr"/>
-      <c r="N149" s="5" t="inlineStr"/>
-      <c r="O149" s="20" t="inlineStr">
-        <is>
-          <t>https://www.tutu.ru/prigorod/</t>
-        </is>
-      </c>
-      <c r="P149" s="5" t="inlineStr"/>
-      <c r="Q149" s="5" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="15" t="inlineStr">
-        <is>
-          <t>Пенза</t>
-        </is>
-      </c>
-      <c r="B150" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C150" s="16" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D150" s="16" t="inlineStr">
-        <is>
-          <t>Альтернатива: поезд</t>
-        </is>
-      </c>
-      <c r="E150" s="16" t="inlineStr">
-        <is>
-          <t>Поезд «Сура», купе (сидячий 3 030)</t>
-        </is>
-      </c>
-      <c r="F150" s="16" t="inlineStr">
-        <is>
-          <t>052М</t>
-        </is>
-      </c>
-      <c r="G150" s="16" t="inlineStr">
-        <is>
-          <t>27.10 21:35</t>
-        </is>
-      </c>
-      <c r="H150" s="16" t="inlineStr">
-        <is>
-          <t>28.10 07:59</t>
-        </is>
-      </c>
-      <c r="I150" s="16" t="inlineStr">
-        <is>
-          <t>Москва, Казанский</t>
-        </is>
-      </c>
-      <c r="J150" s="24" t="n">
-        <v>3967</v>
-      </c>
-      <c r="K150" s="24" t="n">
-        <v>3967</v>
-      </c>
-      <c r="L150" s="16" t="inlineStr">
-        <is>
-          <t>Казанский вокзал → электричка до ст. Коломна (490–620 ₽) + такси 10 мин (~300 ₽) (09:48 → 11:36)</t>
-        </is>
-      </c>
-      <c r="M150" s="16" t="inlineStr">
-        <is>
-          <t>~12:00</t>
-        </is>
-      </c>
-      <c r="N150" s="16" t="inlineStr"/>
-      <c r="O150" s="19" t="inlineStr">
-        <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2024120&amp;nnst2=2000000</t>
-        </is>
-      </c>
-      <c r="P150" s="16" t="inlineStr">
-        <is>
-          <t>Основной вариант — машина (лист «Авто»)</t>
-        </is>
-      </c>
-      <c r="Q150" s="16" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
-      </c>
+      <c r="D150" s="7" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E150" s="7" t="inlineStr">
+        <is>
+          <t>Электричка «Стандарт плюс»</t>
+        </is>
+      </c>
+      <c r="F150" s="7" t="inlineStr">
+        <is>
+          <t>6996</t>
+        </is>
+      </c>
+      <c r="G150" s="5" t="inlineStr">
+        <is>
+          <t>30.10 21:16</t>
+        </is>
+      </c>
+      <c r="H150" s="5" t="inlineStr">
+        <is>
+          <t>30.10 22:49</t>
+        </is>
+      </c>
+      <c r="I150" s="5" t="inlineStr">
+        <is>
+          <t>Рязань-1</t>
+        </is>
+      </c>
+      <c r="J150" s="6" t="n">
+        <v>306</v>
+      </c>
+      <c r="K150" s="6" t="n">
+        <v>306</v>
+      </c>
+      <c r="L150" s="5" t="inlineStr">
+        <is>
+          <t>Такси до ст. Коломна (~300 ₽)</t>
+        </is>
+      </c>
+      <c r="M150" s="5" t="inlineStr"/>
+      <c r="N150" s="5" t="inlineStr"/>
+      <c r="O150" s="20" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/rasp.php?st1=11902&amp;st2=92502&amp;date=30.10.2026</t>
+        </is>
+      </c>
+      <c r="P150" s="5" t="inlineStr"/>
+      <c r="Q150" s="5" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="15" t="inlineStr">
         <is>
-          <t>Саранск</t>
+          <t>Москва</t>
         </is>
       </c>
       <c r="B151" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C151" s="16" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="C151" s="17" t="inlineStr">
         <is>
           <t>В1: к 15:00 28.10</t>
         </is>
       </c>
-      <c r="D151" s="16" t="inlineStr">
-        <is>
-          <t>Альтернатива: поезд</t>
-        </is>
-      </c>
-      <c r="E151" s="16" t="inlineStr">
-        <is>
-          <t>Поезд, купе</t>
-        </is>
-      </c>
-      <c r="F151" s="16" t="inlineStr">
-        <is>
-          <t>041Й</t>
-        </is>
-      </c>
+      <c r="D151" s="17" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E151" s="17" t="inlineStr">
+        <is>
+          <t>Электричка / РЭКС</t>
+        </is>
+      </c>
+      <c r="F151" s="17" t="inlineStr"/>
       <c r="G151" s="16" t="inlineStr">
         <is>
-          <t>27.10 20:40</t>
+          <t>28.10 09:48 или 12:54</t>
         </is>
       </c>
       <c r="H151" s="16" t="inlineStr">
         <is>
-          <t>28.10 05:50</t>
+          <t>11:36 / 15:15</t>
         </is>
       </c>
       <c r="I151" s="16" t="inlineStr">
         <is>
+          <t>Коломна</t>
+        </is>
+      </c>
+      <c r="J151" s="18" t="n">
+        <v>490</v>
+      </c>
+      <c r="K151" s="18" t="n">
+        <v>490</v>
+      </c>
+      <c r="L151" s="16" t="inlineStr">
+        <is>
+          <t>Казанский вокзал → электричка до ст. Коломна (490–620 ₽) + такси 10 мин (~300 ₽)</t>
+        </is>
+      </c>
+      <c r="M151" s="16" t="inlineStr">
+        <is>
+          <t>~12:00 / ~15:30</t>
+        </is>
+      </c>
+      <c r="N151" s="16" t="inlineStr"/>
+      <c r="O151" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/prigorod/</t>
+        </is>
+      </c>
+      <c r="P151" s="16" t="inlineStr">
+        <is>
+          <t>РЭКС 620 ₽</t>
+        </is>
+      </c>
+      <c r="Q151" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="5" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="B152" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C152" s="10" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D152" s="10" t="inlineStr">
+        <is>
+          <t>Удобный</t>
+        </is>
+      </c>
+      <c r="E152" s="10" t="inlineStr">
+        <is>
+          <t>Своя машина</t>
+        </is>
+      </c>
+      <c r="F152" s="10" t="inlineStr"/>
+      <c r="G152" s="5" t="inlineStr">
+        <is>
+          <t>28.10 ~12:00</t>
+        </is>
+      </c>
+      <c r="H152" s="5" t="inlineStr">
+        <is>
+          <t>28.10 ~14:00</t>
+        </is>
+      </c>
+      <c r="I152" s="5" t="inlineStr">
+        <is>
+          <t>Коломна</t>
+        </is>
+      </c>
+      <c r="J152" s="9" t="n">
+        <v>750</v>
+      </c>
+      <c r="K152" s="9" t="n">
+        <v>750</v>
+      </c>
+      <c r="L152" s="5" t="inlineStr">
+        <is>
+          <t>~115 км по Новорязанскому ш., ~2 ч с пробками</t>
+        </is>
+      </c>
+      <c r="M152" s="5" t="inlineStr">
+        <is>
+          <t>~14:00</t>
+        </is>
+      </c>
+      <c r="N152" s="5" t="inlineStr"/>
+      <c r="O152" s="5" t="inlineStr"/>
+      <c r="P152" s="5" t="inlineStr">
+        <is>
+          <t>Топливо ~1 500 ₽ туда-обратно</t>
+        </is>
+      </c>
+      <c r="Q152" s="5" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="5" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="B153" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C153" s="7" t="inlineStr">
+        <is>
+          <t>Обратно</t>
+        </is>
+      </c>
+      <c r="D153" s="7" t="inlineStr">
+        <is>
+          <t>Самый дешёвый = Удобный</t>
+        </is>
+      </c>
+      <c r="E153" s="7" t="inlineStr">
+        <is>
+          <t>Электричка или машина</t>
+        </is>
+      </c>
+      <c r="F153" s="7" t="inlineStr"/>
+      <c r="G153" s="5" t="inlineStr">
+        <is>
+          <t>30.10 18:43</t>
+        </is>
+      </c>
+      <c r="H153" s="5" t="inlineStr">
+        <is>
+          <t>30.10 20:47</t>
+        </is>
+      </c>
+      <c r="I153" s="5" t="inlineStr">
+        <is>
           <t>Москва, Казанский</t>
         </is>
       </c>
-      <c r="J151" s="24" t="n">
-        <v>4394</v>
-      </c>
-      <c r="K151" s="24" t="n">
-        <v>4394</v>
-      </c>
-      <c r="L151" s="16" t="inlineStr">
-        <is>
-          <t>Казанский вокзал → электричка до ст. Коломна (490–620 ₽) + такси 10 мин (~300 ₽) (07:22 → 09:15)</t>
-        </is>
-      </c>
-      <c r="M151" s="16" t="inlineStr">
-        <is>
-          <t>~09:30</t>
-        </is>
-      </c>
-      <c r="N151" s="16" t="inlineStr">
-        <is>
-          <t>ранний заезд</t>
-        </is>
-      </c>
-      <c r="O151" s="19" t="inlineStr">
-        <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2024700&amp;nnst2=2000000</t>
-        </is>
-      </c>
-      <c r="P151" s="16" t="inlineStr">
-        <is>
-          <t>Основной вариант — машина</t>
-        </is>
-      </c>
-      <c r="Q151" s="16" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="15" t="inlineStr">
-        <is>
-          <t>Тамбов</t>
-        </is>
-      </c>
-      <c r="B152" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C152" s="16" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D152" s="16" t="inlineStr">
-        <is>
-          <t>Альтернатива: поезд</t>
-        </is>
-      </c>
-      <c r="E152" s="16" t="inlineStr">
-        <is>
-          <t>Поезд, сидячий (купе 2 868)</t>
-        </is>
-      </c>
-      <c r="F152" s="16" t="inlineStr">
-        <is>
-          <t>135Ж</t>
-        </is>
-      </c>
-      <c r="G152" s="16" t="inlineStr">
-        <is>
-          <t>27.10 21:56</t>
-        </is>
-      </c>
-      <c r="H152" s="16" t="inlineStr">
-        <is>
-          <t>28.10 07:22</t>
-        </is>
-      </c>
-      <c r="I152" s="16" t="inlineStr">
-        <is>
-          <t>Москва, Павелецкий</t>
-        </is>
-      </c>
-      <c r="J152" s="24" t="n">
-        <v>1979</v>
-      </c>
-      <c r="K152" s="24" t="n">
-        <v>1979</v>
-      </c>
-      <c r="L152" s="16" t="inlineStr">
-        <is>
-          <t>Павелецкий → метро до Комсомольской (~20 мин) → электричка от Казанского + такси (08:47 РЭКС → 10:28)</t>
-        </is>
-      </c>
-      <c r="M152" s="16" t="inlineStr">
-        <is>
-          <t>~10:45</t>
-        </is>
-      </c>
-      <c r="N152" s="16" t="inlineStr"/>
-      <c r="O152" s="19" t="inlineStr">
-        <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2014700&amp;nnst2=2000000</t>
-        </is>
-      </c>
-      <c r="P152" s="16" t="inlineStr">
-        <is>
-          <t>Основной вариант — машина. Купе осталось 1 место</t>
-        </is>
-      </c>
-      <c r="Q152" s="16" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="15" t="inlineStr">
-        <is>
-          <t>Липецк</t>
-        </is>
-      </c>
-      <c r="B153" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="C153" s="16" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D153" s="16" t="inlineStr">
-        <is>
-          <t>Альтернатива: поезд</t>
-        </is>
-      </c>
-      <c r="E153" s="16" t="inlineStr">
-        <is>
-          <t>Поезд, купе</t>
-        </is>
-      </c>
-      <c r="F153" s="16" t="inlineStr">
-        <is>
-          <t>033С</t>
-        </is>
-      </c>
-      <c r="G153" s="16" t="inlineStr">
-        <is>
-          <t>27.10 23:15</t>
-        </is>
-      </c>
-      <c r="H153" s="16" t="inlineStr">
-        <is>
-          <t>28.10 08:08</t>
-        </is>
-      </c>
-      <c r="I153" s="16" t="inlineStr">
-        <is>
-          <t>Москва, Павелецкий</t>
-        </is>
-      </c>
-      <c r="J153" s="24" t="n">
-        <v>4049</v>
-      </c>
-      <c r="K153" s="24" t="n">
-        <v>4049</v>
-      </c>
-      <c r="L153" s="16" t="inlineStr">
-        <is>
-          <t>Павелецкий → метро до Комсомольской (~20 мин) → электричка от Казанского + такси (09:48 → 11:36)</t>
-        </is>
-      </c>
-      <c r="M153" s="16" t="inlineStr">
-        <is>
-          <t>~12:00</t>
-        </is>
-      </c>
-      <c r="N153" s="16" t="inlineStr"/>
-      <c r="O153" s="19" t="inlineStr">
-        <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2014130&amp;nnst2=2000000</t>
-        </is>
-      </c>
-      <c r="P153" s="16" t="inlineStr">
-        <is>
-          <t>Основной вариант — одна машина на троих</t>
-        </is>
-      </c>
-      <c r="Q153" s="16" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
-      </c>
+      <c r="J153" s="6" t="n">
+        <v>490</v>
+      </c>
+      <c r="K153" s="6" t="n">
+        <v>490</v>
+      </c>
+      <c r="L153" s="5" t="inlineStr">
+        <is>
+          <t>Электричка 18:43 → 20:47</t>
+        </is>
+      </c>
+      <c r="M153" s="5" t="inlineStr"/>
+      <c r="N153" s="5" t="inlineStr"/>
+      <c r="O153" s="20" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/prigorod/</t>
+        </is>
+      </c>
+      <c r="P153" s="5" t="inlineStr"/>
+      <c r="Q153" s="5" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="15" t="inlineStr">
         <is>
-          <t>Воронеж</t>
+          <t>Пенза</t>
         </is>
       </c>
       <c r="B154" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C154" s="16" t="inlineStr">
         <is>
@@ -15846,22 +15786,22 @@
       </c>
       <c r="E154" s="16" t="inlineStr">
         <is>
-          <t>Поезд «Ингушетия», купе</t>
+          <t>Поезд «Сура», купе (сидячий 3 030)</t>
         </is>
       </c>
       <c r="F154" s="16" t="inlineStr">
         <is>
-          <t>145С</t>
+          <t>052М</t>
         </is>
       </c>
       <c r="G154" s="16" t="inlineStr">
         <is>
-          <t>27.10 23:17</t>
+          <t>27.10 21:35</t>
         </is>
       </c>
       <c r="H154" s="16" t="inlineStr">
         <is>
-          <t>28.10 07:24</t>
+          <t>28.10 07:59</t>
         </is>
       </c>
       <c r="I154" s="16" t="inlineStr">
@@ -15870,30 +15810,30 @@
         </is>
       </c>
       <c r="J154" s="24" t="n">
-        <v>4045</v>
+        <v>3967</v>
       </c>
       <c r="K154" s="24" t="n">
-        <v>4045</v>
+        <v>3967</v>
       </c>
       <c r="L154" s="16" t="inlineStr">
         <is>
-          <t>Казанский вокзал → электричка до ст. Коломна (490–620 ₽) + такси 10 мин (~300 ₽) (08:47 РЭКС → 10:28)</t>
+          <t>Казанский вокзал → электричка до ст. Коломна (490–620 ₽) + такси 10 мин (~300 ₽) (09:48 → 11:36)</t>
         </is>
       </c>
       <c r="M154" s="16" t="inlineStr">
         <is>
-          <t>~10:45</t>
+          <t>~12:00</t>
         </is>
       </c>
       <c r="N154" s="16" t="inlineStr"/>
       <c r="O154" s="19" t="inlineStr">
         <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2014000&amp;nnst2=2000000</t>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2024120&amp;nnst2=2000000</t>
         </is>
       </c>
       <c r="P154" s="16" t="inlineStr">
         <is>
-          <t>Или 213*С 21:09 — прямо до Голутвина (Коломна) в 04:50</t>
+          <t>Основной вариант — машина (лист «Авто»)</t>
         </is>
       </c>
       <c r="Q154" s="16" t="inlineStr">
@@ -15905,7 +15845,7 @@
     <row r="155">
       <c r="A155" s="15" t="inlineStr">
         <is>
-          <t>Орёл</t>
+          <t>Саранск</t>
         </is>
       </c>
       <c r="B155" s="16" t="n">
@@ -15928,49 +15868,53 @@
       </c>
       <c r="F155" s="16" t="inlineStr">
         <is>
-          <t>084С</t>
+          <t>041Й</t>
         </is>
       </c>
       <c r="G155" s="16" t="inlineStr">
         <is>
-          <t>27.10 23:37</t>
+          <t>27.10 20:40</t>
         </is>
       </c>
       <c r="H155" s="16" t="inlineStr">
         <is>
-          <t>28.10 08:40</t>
+          <t>28.10 05:50</t>
         </is>
       </c>
       <c r="I155" s="16" t="inlineStr">
         <is>
-          <t>Москва, Киевский</t>
+          <t>Москва, Казанский</t>
         </is>
       </c>
       <c r="J155" s="24" t="n">
-        <v>3655</v>
+        <v>4394</v>
       </c>
       <c r="K155" s="24" t="n">
-        <v>3655</v>
+        <v>4394</v>
       </c>
       <c r="L155" s="16" t="inlineStr">
         <is>
-          <t>Киевский → метро до Комсомольской (~25 мин) → электричка + такси (09:48 → 11:36)</t>
+          <t>Казанский вокзал → электричка до ст. Коломна (490–620 ₽) + такси 10 мин (~300 ₽) (07:22 → 09:15)</t>
         </is>
       </c>
       <c r="M155" s="16" t="inlineStr">
         <is>
-          <t>~12:00</t>
-        </is>
-      </c>
-      <c r="N155" s="16" t="inlineStr"/>
+          <t>~09:30</t>
+        </is>
+      </c>
+      <c r="N155" s="16" t="inlineStr">
+        <is>
+          <t>ранний заезд</t>
+        </is>
+      </c>
       <c r="O155" s="19" t="inlineStr">
         <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2000140&amp;nnst2=2000000</t>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2024700&amp;nnst2=2000000</t>
         </is>
       </c>
       <c r="P155" s="16" t="inlineStr">
         <is>
-          <t>Основной вариант — машина вместе с Брянском</t>
+          <t>Основной вариант — машина</t>
         </is>
       </c>
       <c r="Q155" s="16" t="inlineStr">
@@ -15982,86 +15926,394 @@
     <row r="156">
       <c r="A156" s="15" t="inlineStr">
         <is>
+          <t>Тамбов</t>
+        </is>
+      </c>
+      <c r="B156" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C156" s="16" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D156" s="16" t="inlineStr">
+        <is>
+          <t>Альтернатива: поезд</t>
+        </is>
+      </c>
+      <c r="E156" s="16" t="inlineStr">
+        <is>
+          <t>Поезд, сидячий (купе 2 868)</t>
+        </is>
+      </c>
+      <c r="F156" s="16" t="inlineStr">
+        <is>
+          <t>135Ж</t>
+        </is>
+      </c>
+      <c r="G156" s="16" t="inlineStr">
+        <is>
+          <t>27.10 21:56</t>
+        </is>
+      </c>
+      <c r="H156" s="16" t="inlineStr">
+        <is>
+          <t>28.10 07:22</t>
+        </is>
+      </c>
+      <c r="I156" s="16" t="inlineStr">
+        <is>
+          <t>Москва, Павелецкий</t>
+        </is>
+      </c>
+      <c r="J156" s="24" t="n">
+        <v>1979</v>
+      </c>
+      <c r="K156" s="24" t="n">
+        <v>1979</v>
+      </c>
+      <c r="L156" s="16" t="inlineStr">
+        <is>
+          <t>Павелецкий → метро до Комсомольской (~20 мин) → электричка от Казанского + такси (08:47 РЭКС → 10:28)</t>
+        </is>
+      </c>
+      <c r="M156" s="16" t="inlineStr">
+        <is>
+          <t>~10:45</t>
+        </is>
+      </c>
+      <c r="N156" s="16" t="inlineStr"/>
+      <c r="O156" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2014700&amp;nnst2=2000000</t>
+        </is>
+      </c>
+      <c r="P156" s="16" t="inlineStr">
+        <is>
+          <t>Основной вариант — машина. Купе осталось 1 место</t>
+        </is>
+      </c>
+      <c r="Q156" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="15" t="inlineStr">
+        <is>
+          <t>Липецк</t>
+        </is>
+      </c>
+      <c r="B157" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C157" s="16" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D157" s="16" t="inlineStr">
+        <is>
+          <t>Альтернатива: поезд</t>
+        </is>
+      </c>
+      <c r="E157" s="16" t="inlineStr">
+        <is>
+          <t>Поезд, купе</t>
+        </is>
+      </c>
+      <c r="F157" s="16" t="inlineStr">
+        <is>
+          <t>033С</t>
+        </is>
+      </c>
+      <c r="G157" s="16" t="inlineStr">
+        <is>
+          <t>27.10 23:15</t>
+        </is>
+      </c>
+      <c r="H157" s="16" t="inlineStr">
+        <is>
+          <t>28.10 08:08</t>
+        </is>
+      </c>
+      <c r="I157" s="16" t="inlineStr">
+        <is>
+          <t>Москва, Павелецкий</t>
+        </is>
+      </c>
+      <c r="J157" s="24" t="n">
+        <v>4049</v>
+      </c>
+      <c r="K157" s="24" t="n">
+        <v>4049</v>
+      </c>
+      <c r="L157" s="16" t="inlineStr">
+        <is>
+          <t>Павелецкий → метро до Комсомольской (~20 мин) → электричка от Казанского + такси (09:48 → 11:36)</t>
+        </is>
+      </c>
+      <c r="M157" s="16" t="inlineStr">
+        <is>
+          <t>~12:00</t>
+        </is>
+      </c>
+      <c r="N157" s="16" t="inlineStr"/>
+      <c r="O157" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2014130&amp;nnst2=2000000</t>
+        </is>
+      </c>
+      <c r="P157" s="16" t="inlineStr">
+        <is>
+          <t>Основной вариант — одна машина на троих</t>
+        </is>
+      </c>
+      <c r="Q157" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="15" t="inlineStr">
+        <is>
+          <t>Воронеж</t>
+        </is>
+      </c>
+      <c r="B158" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C158" s="16" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D158" s="16" t="inlineStr">
+        <is>
+          <t>Альтернатива: поезд</t>
+        </is>
+      </c>
+      <c r="E158" s="16" t="inlineStr">
+        <is>
+          <t>Поезд «Ингушетия», купе</t>
+        </is>
+      </c>
+      <c r="F158" s="16" t="inlineStr">
+        <is>
+          <t>145С</t>
+        </is>
+      </c>
+      <c r="G158" s="16" t="inlineStr">
+        <is>
+          <t>27.10 23:17</t>
+        </is>
+      </c>
+      <c r="H158" s="16" t="inlineStr">
+        <is>
+          <t>28.10 07:24</t>
+        </is>
+      </c>
+      <c r="I158" s="16" t="inlineStr">
+        <is>
+          <t>Москва, Казанский</t>
+        </is>
+      </c>
+      <c r="J158" s="24" t="n">
+        <v>4045</v>
+      </c>
+      <c r="K158" s="24" t="n">
+        <v>4045</v>
+      </c>
+      <c r="L158" s="16" t="inlineStr">
+        <is>
+          <t>Казанский вокзал → электричка до ст. Коломна (490–620 ₽) + такси 10 мин (~300 ₽) (08:47 РЭКС → 10:28)</t>
+        </is>
+      </c>
+      <c r="M158" s="16" t="inlineStr">
+        <is>
+          <t>~10:45</t>
+        </is>
+      </c>
+      <c r="N158" s="16" t="inlineStr"/>
+      <c r="O158" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2014000&amp;nnst2=2000000</t>
+        </is>
+      </c>
+      <c r="P158" s="16" t="inlineStr">
+        <is>
+          <t>Или 213*С 21:09 — прямо до Голутвина (Коломна) в 04:50</t>
+        </is>
+      </c>
+      <c r="Q158" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="15" t="inlineStr">
+        <is>
+          <t>Орёл</t>
+        </is>
+      </c>
+      <c r="B159" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C159" s="16" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D159" s="16" t="inlineStr">
+        <is>
+          <t>Альтернатива: поезд</t>
+        </is>
+      </c>
+      <c r="E159" s="16" t="inlineStr">
+        <is>
+          <t>Поезд, купе</t>
+        </is>
+      </c>
+      <c r="F159" s="16" t="inlineStr">
+        <is>
+          <t>084С</t>
+        </is>
+      </c>
+      <c r="G159" s="16" t="inlineStr">
+        <is>
+          <t>27.10 23:37</t>
+        </is>
+      </c>
+      <c r="H159" s="16" t="inlineStr">
+        <is>
+          <t>28.10 08:40</t>
+        </is>
+      </c>
+      <c r="I159" s="16" t="inlineStr">
+        <is>
+          <t>Москва, Киевский</t>
+        </is>
+      </c>
+      <c r="J159" s="24" t="n">
+        <v>3655</v>
+      </c>
+      <c r="K159" s="24" t="n">
+        <v>3655</v>
+      </c>
+      <c r="L159" s="16" t="inlineStr">
+        <is>
+          <t>Киевский → метро до Комсомольской (~25 мин) → электричка + такси (09:48 → 11:36)</t>
+        </is>
+      </c>
+      <c r="M159" s="16" t="inlineStr">
+        <is>
+          <t>~12:00</t>
+        </is>
+      </c>
+      <c r="N159" s="16" t="inlineStr"/>
+      <c r="O159" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2000140&amp;nnst2=2000000</t>
+        </is>
+      </c>
+      <c r="P159" s="16" t="inlineStr">
+        <is>
+          <t>Основной вариант — машина вместе с Брянском</t>
+        </is>
+      </c>
+      <c r="Q159" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="15" t="inlineStr">
+        <is>
           <t>Брянск</t>
         </is>
       </c>
-      <c r="B156" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C156" s="16" t="inlineStr">
+      <c r="B160" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C160" s="16" t="inlineStr">
         <is>
           <t>В1: к 15:00 28.10</t>
         </is>
       </c>
-      <c r="D156" s="16" t="inlineStr">
+      <c r="D160" s="16" t="inlineStr">
         <is>
           <t>Альтернатива: поезд</t>
         </is>
       </c>
-      <c r="E156" s="16" t="inlineStr">
+      <c r="E160" s="16" t="inlineStr">
         <is>
           <t>Поезд, сидячий (купе 3 180)</t>
         </is>
       </c>
-      <c r="F156" s="16" t="inlineStr">
+      <c r="F160" s="16" t="inlineStr">
         <is>
           <t>086Щ</t>
         </is>
       </c>
-      <c r="G156" s="16" t="inlineStr">
+      <c r="G160" s="16" t="inlineStr">
         <is>
           <t>28.10 00:20</t>
         </is>
       </c>
-      <c r="H156" s="16" t="inlineStr">
+      <c r="H160" s="16" t="inlineStr">
         <is>
           <t>28.10 06:20</t>
         </is>
       </c>
-      <c r="I156" s="16" t="inlineStr">
+      <c r="I160" s="16" t="inlineStr">
         <is>
           <t>Москва, Киевский</t>
         </is>
       </c>
-      <c r="J156" s="24" t="n">
+      <c r="J160" s="24" t="n">
         <v>1749</v>
       </c>
-      <c r="K156" s="24" t="n">
+      <c r="K160" s="24" t="n">
         <v>1749</v>
       </c>
-      <c r="L156" s="16" t="inlineStr">
+      <c r="L160" s="16" t="inlineStr">
         <is>
           <t>Киевский → метро до Комсомольской (~25 мин) → электричка + такси (07:22 → 09:15)</t>
         </is>
       </c>
-      <c r="M156" s="16" t="inlineStr">
+      <c r="M160" s="16" t="inlineStr">
         <is>
           <t>~09:30</t>
         </is>
       </c>
-      <c r="N156" s="16" t="inlineStr">
+      <c r="N160" s="16" t="inlineStr">
         <is>
           <t>ранний заезд</t>
         </is>
       </c>
-      <c r="O156" s="19" t="inlineStr">
+      <c r="O160" s="19" t="inlineStr">
         <is>
           <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2000427&amp;nnst2=2000000</t>
         </is>
       </c>
-      <c r="P156" s="16" t="inlineStr">
+      <c r="P160" s="16" t="inlineStr">
         <is>
           <t>Время по расписанию 27.10. Основной вариант — машина</t>
         </is>
       </c>
-      <c r="Q156" s="16" t="inlineStr">
+      <c r="Q160" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q156"/>
+  <autoFilter ref="A1:Q160"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
@@ -16162,38 +16414,41 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O117" r:id="rId97"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O119" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O120" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O121" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O122" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O123" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O124" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O122" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O123" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O124" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O125" r:id="rId103"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O126" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O127" r:id="rId105"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O128" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O129" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O130" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O131" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O132" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O133" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O134" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O135" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O136" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O137" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O138" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O139" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O140" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O141" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O130" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O131" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O132" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O133" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O134" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O135" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O136" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O137" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O138" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O139" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O140" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O141" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O142" r:id="rId119"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O143" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O144" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O146" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O145" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O147" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O149" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O148" r:id="rId124"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O150" r:id="rId125"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O151" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O152" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O153" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O154" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O155" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O156" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O153" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O154" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O155" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O156" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O157" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O158" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O159" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O160" r:id="rId134"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16734,11 +16989,11 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Екатеринбург U6-264 07:25 — группа 10 чел. + Нижний Тагил</t>
+          <t>Екатеринбург U6-264 07:25 — группа 9 чел. + Нижний Тагил</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
@@ -17086,11 +17341,11 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Уфа DP-435 23:40; Екатеринбург DP-403 23:50 (11 чел.); Челябинск DP-413 23:45</t>
+          <t>Уфа DP-435 23:40; Екатеринбург DP-403 23:50 (10 чел.); Челябинск DP-413 23:45</t>
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>

--- a/Коломна_маршруты_28-30.10.2026.xlsx
+++ b/Коломна_маршруты_28-30.10.2026.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Сводка по сотрудникам'!$A$4:$S$64</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Маршруты'!$A$1:$Q$160</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Маршруты'!$A$1:$Q$159</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -4845,13 +4845,13 @@
         <v/>
       </c>
       <c r="N61" s="9" t="n">
-        <v>17111</v>
+        <v>16375</v>
       </c>
       <c r="O61" s="9" t="n">
         <v>14765</v>
       </c>
       <c r="P61" s="9" t="n">
-        <v>10000</v>
+        <v>9800</v>
       </c>
       <c r="Q61" s="10" t="n">
         <v>0</v>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="S61" s="5" t="inlineStr">
         <is>
-          <t>Обратно ночным рейсом 31.10 в 00:40, без доп. ночи</t>
+          <t>Туда A4-7062 в 12:20 (утренний в 06:15 — слишком ранний подъём). Обратно ночным рейсом 31.10 в 00:40</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q160"/>
+  <dimension ref="A1:Q159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13315,22 +13315,22 @@
       <c r="B119" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="C119" s="22" t="inlineStr">
+      <c r="C119" s="16" t="inlineStr">
         <is>
           <t>В1: к 15:00 28.10</t>
         </is>
       </c>
-      <c r="D119" s="22" t="inlineStr">
-        <is>
-          <t>Удобный</t>
-        </is>
-      </c>
-      <c r="E119" s="22" t="inlineStr">
+      <c r="D119" s="16" t="inlineStr">
+        <is>
+          <t>Только если обязательна экскурсия</t>
+        </is>
+      </c>
+      <c r="E119" s="16" t="inlineStr">
         <is>
           <t>Самолёт, Аэрофлот</t>
         </is>
       </c>
-      <c r="F119" s="22" t="inlineStr">
+      <c r="F119" s="16" t="inlineStr">
         <is>
           <t>SU-1429</t>
         </is>
@@ -13350,10 +13350,10 @@
           <t>Шереметьево</t>
         </is>
       </c>
-      <c r="J119" s="23" t="n">
+      <c r="J119" s="24" t="n">
         <v>13489</v>
       </c>
-      <c r="K119" s="23" t="n">
+      <c r="K119" s="24" t="n">
         <v>17111</v>
       </c>
       <c r="L119" s="16" t="inlineStr">
@@ -13374,7 +13374,7 @@
       </c>
       <c r="P119" s="16" t="inlineStr">
         <is>
-          <t>Единственный утренний прямой рейс</t>
+          <t>Неудобно: в аэропорту к 04:45, выезд из дома ~04:15, подъём ~03:30. Рейс ежедневный — вылет 27.10 такой же ранний</t>
         </is>
       </c>
       <c r="Q119" s="16" t="inlineStr">
@@ -13394,12 +13394,12 @@
       </c>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>В2: после 15:00 28.10</t>
+          <t>В2: после 15:00 28.10 / В3: к утру 29.10</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>Самый дешёвый</t>
+          <t>Самый дешёвый = Удобный</t>
         </is>
       </c>
       <c r="E120" s="7" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="P120" s="5" t="inlineStr">
         <is>
-          <t>Чуть дешевле, но экскурсия в 16:00 не успевает</t>
+          <t>Рекомендуем: выезд из дома ~10:00, в аэропорту за 1,5 ч. Дешевле утреннего. К началу экскурсии не успевает — можно присоединиться позже. Рейс через Казань в 01:10 ночью — ещё хуже</t>
         </is>
       </c>
       <c r="Q120" s="5" t="inlineStr">
@@ -13469,179 +13469,211 @@
       <c r="B121" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C121" s="5" t="inlineStr">
-        <is>
-          <t>В3: к утру 29.10</t>
-        </is>
-      </c>
-      <c r="D121" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E121" s="5" t="inlineStr">
-        <is>
-          <t>как В2</t>
-        </is>
-      </c>
-      <c r="F121" s="5" t="inlineStr">
-        <is>
-          <t>A4-7062</t>
-        </is>
-      </c>
-      <c r="G121" s="5" t="inlineStr"/>
-      <c r="H121" s="5" t="inlineStr"/>
-      <c r="I121" s="5" t="inlineStr"/>
-      <c r="J121" s="5" t="n"/>
-      <c r="K121" s="5" t="n"/>
-      <c r="L121" s="5" t="inlineStr"/>
+      <c r="C121" s="7" t="inlineStr">
+        <is>
+          <t>Обратно</t>
+        </is>
+      </c>
+      <c r="D121" s="7" t="inlineStr">
+        <is>
+          <t>Самый дешёвый = Удобный</t>
+        </is>
+      </c>
+      <c r="E121" s="7" t="inlineStr">
+        <is>
+          <t>Самолёт, Аэрофлот</t>
+        </is>
+      </c>
+      <c r="F121" s="7" t="inlineStr">
+        <is>
+          <t>SU-1428</t>
+        </is>
+      </c>
+      <c r="G121" s="5" t="inlineStr">
+        <is>
+          <t>31.10 00:40</t>
+        </is>
+      </c>
+      <c r="H121" s="5" t="inlineStr">
+        <is>
+          <t>31.10 05:05 (мест.)</t>
+        </is>
+      </c>
+      <c r="I121" s="5" t="inlineStr">
+        <is>
+          <t>Шереметьево</t>
+        </is>
+      </c>
+      <c r="J121" s="6" t="n">
+        <v>11097</v>
+      </c>
+      <c r="K121" s="6" t="n">
+        <v>14765</v>
+      </c>
+      <c r="L121" s="5" t="inlineStr">
+        <is>
+          <t>Выезд из гостиницы 18:15; в аэропорту за 2 ч до вылета</t>
+        </is>
+      </c>
       <c r="M121" s="5" t="inlineStr"/>
       <c r="N121" s="5" t="inlineStr"/>
-      <c r="O121" s="5" t="inlineStr"/>
-      <c r="P121" s="5" t="inlineStr"/>
+      <c r="O121" s="20" t="inlineStr">
+        <is>
+          <t>https://avia.tutu.ru/f/Moskva/Magnitogorsk/?class=Y&amp;travelers=1&amp;route[0]=491-30102026-45</t>
+        </is>
+      </c>
+      <c r="P121" s="5" t="inlineStr">
+        <is>
+          <t>Ночной рейс сразу после конференции, гостиница не нужна. Время по расписанию 30.10 — проверить на 31.10. Альтернатива: SU-1434 31.10 07:40 + ночь</t>
+        </is>
+      </c>
       <c r="Q121" s="5" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="5" t="inlineStr">
-        <is>
-          <t>Магнитогорск</t>
-        </is>
-      </c>
-      <c r="B122" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C122" s="7" t="inlineStr">
-        <is>
-          <t>Обратно</t>
-        </is>
-      </c>
-      <c r="D122" s="7" t="inlineStr">
-        <is>
-          <t>Самый дешёвый = Удобный</t>
-        </is>
-      </c>
-      <c r="E122" s="7" t="inlineStr">
+      <c r="A122" s="15" t="inlineStr">
+        <is>
+          <t>Челябинск</t>
+        </is>
+      </c>
+      <c r="B122" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C122" s="17" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D122" s="17" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E122" s="17" t="inlineStr">
+        <is>
+          <t>Самолёт, Победа</t>
+        </is>
+      </c>
+      <c r="F122" s="17" t="inlineStr">
+        <is>
+          <t>DP-414</t>
+        </is>
+      </c>
+      <c r="G122" s="16" t="inlineStr">
+        <is>
+          <t>28.10 06:30 (мест.)</t>
+        </is>
+      </c>
+      <c r="H122" s="16" t="inlineStr">
+        <is>
+          <t>28.10 07:15</t>
+        </is>
+      </c>
+      <c r="I122" s="16" t="inlineStr">
+        <is>
+          <t>Внуково</t>
+        </is>
+      </c>
+      <c r="J122" s="18" t="n">
+        <v>6196</v>
+      </c>
+      <c r="K122" s="18" t="n">
+        <v>8991</v>
+      </c>
+      <c r="L122" s="16" t="inlineStr">
+        <is>
+          <t>Внуково: метро → Казанский вокзал + электричка, или такси ~2 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="M122" s="16" t="inlineStr">
+        <is>
+          <t>~10:40</t>
+        </is>
+      </c>
+      <c r="N122" s="16" t="inlineStr"/>
+      <c r="O122" s="19" t="inlineStr">
+        <is>
+          <t>https://avia.tutu.ru/f/Chelyabinsk/Moskva/?class=Y&amp;travelers=1&amp;route[0]=98-28102026-491</t>
+        </is>
+      </c>
+      <c r="P122" s="16" t="inlineStr">
+        <is>
+          <t>Также DP-6568 05:30→SVO 06:10, та же цена</t>
+        </is>
+      </c>
+      <c r="Q122" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>Челябинск</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C123" s="10" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D123" s="10" t="inlineStr">
+        <is>
+          <t>Удобный</t>
+        </is>
+      </c>
+      <c r="E123" s="10" t="inlineStr">
         <is>
           <t>Самолёт, Аэрофлот</t>
         </is>
       </c>
-      <c r="F122" s="7" t="inlineStr">
-        <is>
-          <t>SU-1428</t>
-        </is>
-      </c>
-      <c r="G122" s="5" t="inlineStr">
-        <is>
-          <t>31.10 00:40</t>
-        </is>
-      </c>
-      <c r="H122" s="5" t="inlineStr">
-        <is>
-          <t>31.10 05:05 (мест.)</t>
-        </is>
-      </c>
-      <c r="I122" s="5" t="inlineStr">
+      <c r="F123" s="10" t="inlineStr">
+        <is>
+          <t>SU-1093</t>
+        </is>
+      </c>
+      <c r="G123" s="5" t="inlineStr">
+        <is>
+          <t>28.10 06:05 (мест.)</t>
+        </is>
+      </c>
+      <c r="H123" s="5" t="inlineStr">
+        <is>
+          <t>28.10 06:45</t>
+        </is>
+      </c>
+      <c r="I123" s="5" t="inlineStr">
         <is>
           <t>Шереметьево</t>
         </is>
       </c>
-      <c r="J122" s="6" t="n">
-        <v>11097</v>
-      </c>
-      <c r="K122" s="6" t="n">
-        <v>14765</v>
-      </c>
-      <c r="L122" s="5" t="inlineStr">
-        <is>
-          <t>Выезд из гостиницы 18:15; в аэропорту за 2 ч до вылета</t>
-        </is>
-      </c>
-      <c r="M122" s="5" t="inlineStr"/>
-      <c r="N122" s="5" t="inlineStr"/>
-      <c r="O122" s="20" t="inlineStr">
-        <is>
-          <t>https://avia.tutu.ru/f/Moskva/Magnitogorsk/?class=Y&amp;travelers=1&amp;route[0]=491-30102026-45</t>
-        </is>
-      </c>
-      <c r="P122" s="5" t="inlineStr">
-        <is>
-          <t>Ночной рейс сразу после конференции, гостиница не нужна. Время по расписанию 30.10 — проверить на 31.10</t>
-        </is>
-      </c>
-      <c r="Q122" s="5" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="15" t="inlineStr">
-        <is>
-          <t>Челябинск</t>
-        </is>
-      </c>
-      <c r="B123" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C123" s="17" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D123" s="17" t="inlineStr">
-        <is>
-          <t>Самый дешёвый</t>
-        </is>
-      </c>
-      <c r="E123" s="17" t="inlineStr">
-        <is>
-          <t>Самолёт, Победа</t>
-        </is>
-      </c>
-      <c r="F123" s="17" t="inlineStr">
-        <is>
-          <t>DP-414</t>
-        </is>
-      </c>
-      <c r="G123" s="16" t="inlineStr">
-        <is>
-          <t>28.10 06:30 (мест.)</t>
-        </is>
-      </c>
-      <c r="H123" s="16" t="inlineStr">
-        <is>
-          <t>28.10 07:15</t>
-        </is>
-      </c>
-      <c r="I123" s="16" t="inlineStr">
-        <is>
-          <t>Внуково</t>
-        </is>
-      </c>
-      <c r="J123" s="18" t="n">
-        <v>6196</v>
-      </c>
-      <c r="K123" s="18" t="n">
-        <v>8991</v>
-      </c>
-      <c r="L123" s="16" t="inlineStr">
-        <is>
-          <t>Внуково: метро → Казанский вокзал + электричка, или такси ~2 ч 45 мин</t>
-        </is>
-      </c>
-      <c r="M123" s="16" t="inlineStr">
-        <is>
-          <t>~10:40</t>
-        </is>
-      </c>
-      <c r="N123" s="16" t="inlineStr"/>
-      <c r="O123" s="19" t="inlineStr">
+      <c r="J123" s="9" t="n">
+        <v>10408</v>
+      </c>
+      <c r="K123" s="9" t="n">
+        <v>14081</v>
+      </c>
+      <c r="L123" s="5" t="inlineStr">
+        <is>
+          <t>Шереметьево: такси ~3 ч или аэроэкспресс → Белорусский + метро → Казанский + электричка</t>
+        </is>
+      </c>
+      <c r="M123" s="5" t="inlineStr">
+        <is>
+          <t>~10:25</t>
+        </is>
+      </c>
+      <c r="N123" s="5" t="inlineStr"/>
+      <c r="O123" s="20" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/f/Chelyabinsk/Moskva/?class=Y&amp;travelers=1&amp;route[0]=98-28102026-491</t>
         </is>
       </c>
-      <c r="P123" s="16" t="inlineStr">
-        <is>
-          <t>Также DP-6568 05:30→SVO 06:10, та же цена</t>
-        </is>
-      </c>
-      <c r="Q123" s="16" t="inlineStr">
+      <c r="P123" s="5" t="inlineStr"/>
+      <c r="Q123" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -13656,34 +13688,34 @@
       <c r="B124" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C124" s="10" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D124" s="10" t="inlineStr">
-        <is>
-          <t>Удобный</t>
-        </is>
-      </c>
-      <c r="E124" s="10" t="inlineStr">
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>В2: после 15:00 28.10 / В3: к утру 29.10</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="inlineStr">
         <is>
           <t>Самолёт, Аэрофлот</t>
         </is>
       </c>
-      <c r="F124" s="10" t="inlineStr">
-        <is>
-          <t>SU-1093</t>
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t>SU-1427</t>
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr">
         <is>
-          <t>28.10 06:05 (мест.)</t>
+          <t>28.10 22:30 (мест.)</t>
         </is>
       </c>
       <c r="H124" s="5" t="inlineStr">
         <is>
-          <t>28.10 06:45</t>
+          <t>28.10 23:20</t>
         </is>
       </c>
       <c r="I124" s="5" t="inlineStr">
@@ -13691,11 +13723,11 @@
           <t>Шереметьево</t>
         </is>
       </c>
-      <c r="J124" s="9" t="n">
-        <v>10408</v>
-      </c>
-      <c r="K124" s="9" t="n">
-        <v>14081</v>
+      <c r="J124" s="21" t="n">
+        <v>8190</v>
+      </c>
+      <c r="K124" s="21" t="n">
+        <v>11788</v>
       </c>
       <c r="L124" s="5" t="inlineStr">
         <is>
@@ -13704,7 +13736,7 @@
       </c>
       <c r="M124" s="5" t="inlineStr">
         <is>
-          <t>~10:25</t>
+          <t>~02:30</t>
         </is>
       </c>
       <c r="N124" s="5" t="inlineStr"/>
@@ -13713,7 +13745,11 @@
           <t>https://avia.tutu.ru/f/Chelyabinsk/Moskva/?class=Y&amp;travelers=1&amp;route[0]=98-28102026-491</t>
         </is>
       </c>
-      <c r="P124" s="5" t="inlineStr"/>
+      <c r="P124" s="5" t="inlineStr">
+        <is>
+          <t>Поздно; лучше В1</t>
+        </is>
+      </c>
       <c r="Q124" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
@@ -13729,211 +13765,207 @@
       <c r="B125" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C125" s="5" t="inlineStr">
-        <is>
-          <t>В2: после 15:00 28.10 / В3: к утру 29.10</t>
-        </is>
-      </c>
-      <c r="D125" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E125" s="5" t="inlineStr">
-        <is>
-          <t>Самолёт, Аэрофлот</t>
-        </is>
-      </c>
-      <c r="F125" s="5" t="inlineStr">
-        <is>
-          <t>SU-1427</t>
+      <c r="C125" s="7" t="inlineStr">
+        <is>
+          <t>Обратно</t>
+        </is>
+      </c>
+      <c r="D125" s="7" t="inlineStr">
+        <is>
+          <t>Самый дешёвый = Удобный</t>
+        </is>
+      </c>
+      <c r="E125" s="7" t="inlineStr">
+        <is>
+          <t>Самолёт, Победа</t>
+        </is>
+      </c>
+      <c r="F125" s="7" t="inlineStr">
+        <is>
+          <t>DP-413</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>28.10 22:30 (мест.)</t>
+          <t>30.10 23:45</t>
         </is>
       </c>
       <c r="H125" s="5" t="inlineStr">
         <is>
-          <t>28.10 23:20</t>
+          <t>31.10 04:25 (мест.)</t>
         </is>
       </c>
       <c r="I125" s="5" t="inlineStr">
         <is>
-          <t>Шереметьево</t>
-        </is>
-      </c>
-      <c r="J125" s="21" t="n">
-        <v>8190</v>
-      </c>
-      <c r="K125" s="21" t="n">
-        <v>11788</v>
+          <t>Внуково</t>
+        </is>
+      </c>
+      <c r="J125" s="6" t="n">
+        <v>7789</v>
+      </c>
+      <c r="K125" s="6" t="n">
+        <v>10643</v>
       </c>
       <c r="L125" s="5" t="inlineStr">
         <is>
-          <t>Шереметьево: такси ~3 ч или аэроэкспресс → Белорусский + метро → Казанский + электричка</t>
-        </is>
-      </c>
-      <c r="M125" s="5" t="inlineStr">
-        <is>
-          <t>~02:30</t>
-        </is>
-      </c>
+          <t>Выезд из гостиницы 18:15; в аэропорту за 2 ч до вылета</t>
+        </is>
+      </c>
+      <c r="M125" s="5" t="inlineStr"/>
       <c r="N125" s="5" t="inlineStr"/>
       <c r="O125" s="20" t="inlineStr">
         <is>
-          <t>https://avia.tutu.ru/f/Chelyabinsk/Moskva/?class=Y&amp;travelers=1&amp;route[0]=98-28102026-491</t>
+          <t>https://avia.tutu.ru/f/Moskva/Chelyabinsk/?class=Y&amp;travelers=1&amp;route[0]=491-30102026-98</t>
         </is>
       </c>
       <c r="P125" s="5" t="inlineStr">
         <is>
-          <t>Поздно; лучше В1</t>
-        </is>
-      </c>
-      <c r="Q125" s="5" t="inlineStr">
+          <t>Рейсы Победы из SVO в 23:00/23:30 не проходят правило 2 ч</t>
+        </is>
+      </c>
+      <c r="Q125" s="5" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="15" t="inlineStr">
+        <is>
+          <t>Тюмень</t>
+        </is>
+      </c>
+      <c r="B126" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C126" s="17" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D126" s="17" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E126" s="17" t="inlineStr">
+        <is>
+          <t>Самолёт, Победа</t>
+        </is>
+      </c>
+      <c r="F126" s="17" t="inlineStr">
+        <is>
+          <t>DP-6562</t>
+        </is>
+      </c>
+      <c r="G126" s="16" t="inlineStr">
+        <is>
+          <t>28.10 06:25 (мест.)</t>
+        </is>
+      </c>
+      <c r="H126" s="16" t="inlineStr">
+        <is>
+          <t>28.10 07:30</t>
+        </is>
+      </c>
+      <c r="I126" s="16" t="inlineStr">
+        <is>
+          <t>Шереметьево</t>
+        </is>
+      </c>
+      <c r="J126" s="18" t="n">
+        <v>5873</v>
+      </c>
+      <c r="K126" s="18" t="n">
+        <v>8712</v>
+      </c>
+      <c r="L126" s="16" t="inlineStr">
+        <is>
+          <t>Шереметьево: такси ~3 ч или аэроэкспресс → Белорусский + метро → Казанский + электричка</t>
+        </is>
+      </c>
+      <c r="M126" s="16" t="inlineStr">
+        <is>
+          <t>~11:10</t>
+        </is>
+      </c>
+      <c r="N126" s="16" t="inlineStr"/>
+      <c r="O126" s="19" t="inlineStr">
+        <is>
+          <t>https://avia.tutu.ru/f/Tyumen/Moskva/?class=Y&amp;travelers=1&amp;route[0]=86-28102026-491</t>
+        </is>
+      </c>
+      <c r="P126" s="16" t="inlineStr"/>
+      <c r="Q126" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="5" t="inlineStr">
-        <is>
-          <t>Челябинск</t>
-        </is>
-      </c>
-      <c r="B126" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C126" s="7" t="inlineStr">
-        <is>
-          <t>Обратно</t>
-        </is>
-      </c>
-      <c r="D126" s="7" t="inlineStr">
-        <is>
-          <t>Самый дешёвый = Удобный</t>
-        </is>
-      </c>
-      <c r="E126" s="7" t="inlineStr">
-        <is>
-          <t>Самолёт, Победа</t>
-        </is>
-      </c>
-      <c r="F126" s="7" t="inlineStr">
-        <is>
-          <t>DP-413</t>
-        </is>
-      </c>
-      <c r="G126" s="5" t="inlineStr">
-        <is>
-          <t>30.10 23:45</t>
-        </is>
-      </c>
-      <c r="H126" s="5" t="inlineStr">
-        <is>
-          <t>31.10 04:25 (мест.)</t>
-        </is>
-      </c>
-      <c r="I126" s="5" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>Тюмень</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C127" s="10" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D127" s="10" t="inlineStr">
+        <is>
+          <t>Удобный</t>
+        </is>
+      </c>
+      <c r="E127" s="10" t="inlineStr">
+        <is>
+          <t>Самолёт, ЮТэйр</t>
+        </is>
+      </c>
+      <c r="F127" s="10" t="inlineStr">
+        <is>
+          <t>UT-454</t>
+        </is>
+      </c>
+      <c r="G127" s="5" t="inlineStr">
+        <is>
+          <t>28.10 07:15 (мест.)</t>
+        </is>
+      </c>
+      <c r="H127" s="5" t="inlineStr">
+        <is>
+          <t>28.10 08:10</t>
+        </is>
+      </c>
+      <c r="I127" s="5" t="inlineStr">
         <is>
           <t>Внуково</t>
         </is>
       </c>
-      <c r="J126" s="6" t="n">
-        <v>7789</v>
-      </c>
-      <c r="K126" s="6" t="n">
-        <v>10643</v>
-      </c>
-      <c r="L126" s="5" t="inlineStr">
-        <is>
-          <t>Выезд из гостиницы 18:15; в аэропорту за 2 ч до вылета</t>
-        </is>
-      </c>
-      <c r="M126" s="5" t="inlineStr"/>
-      <c r="N126" s="5" t="inlineStr"/>
-      <c r="O126" s="20" t="inlineStr">
-        <is>
-          <t>https://avia.tutu.ru/f/Moskva/Chelyabinsk/?class=Y&amp;travelers=1&amp;route[0]=491-30102026-98</t>
-        </is>
-      </c>
-      <c r="P126" s="5" t="inlineStr">
-        <is>
-          <t>Рейсы Победы из SVO в 23:00/23:30 не проходят правило 2 ч</t>
-        </is>
-      </c>
-      <c r="Q126" s="5" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="15" t="inlineStr">
-        <is>
-          <t>Тюмень</t>
-        </is>
-      </c>
-      <c r="B127" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C127" s="17" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D127" s="17" t="inlineStr">
-        <is>
-          <t>Самый дешёвый</t>
-        </is>
-      </c>
-      <c r="E127" s="17" t="inlineStr">
-        <is>
-          <t>Самолёт, Победа</t>
-        </is>
-      </c>
-      <c r="F127" s="17" t="inlineStr">
-        <is>
-          <t>DP-6562</t>
-        </is>
-      </c>
-      <c r="G127" s="16" t="inlineStr">
-        <is>
-          <t>28.10 06:25 (мест.)</t>
-        </is>
-      </c>
-      <c r="H127" s="16" t="inlineStr">
-        <is>
-          <t>28.10 07:30</t>
-        </is>
-      </c>
-      <c r="I127" s="16" t="inlineStr">
-        <is>
-          <t>Шереметьево</t>
-        </is>
-      </c>
-      <c r="J127" s="18" t="n">
-        <v>5873</v>
-      </c>
-      <c r="K127" s="18" t="n">
-        <v>8712</v>
-      </c>
-      <c r="L127" s="16" t="inlineStr">
-        <is>
-          <t>Шереметьево: такси ~3 ч или аэроэкспресс → Белорусский + метро → Казанский + электричка</t>
-        </is>
-      </c>
-      <c r="M127" s="16" t="inlineStr">
-        <is>
-          <t>~11:10</t>
-        </is>
-      </c>
-      <c r="N127" s="16" t="inlineStr"/>
-      <c r="O127" s="19" t="inlineStr">
+      <c r="J127" s="9" t="n">
+        <v>7065</v>
+      </c>
+      <c r="K127" s="9" t="n">
+        <v>10125</v>
+      </c>
+      <c r="L127" s="5" t="inlineStr">
+        <is>
+          <t>Внуково: метро → Казанский вокзал + электричка, или такси ~2 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="M127" s="5" t="inlineStr">
+        <is>
+          <t>~11:35</t>
+        </is>
+      </c>
+      <c r="N127" s="5" t="inlineStr"/>
+      <c r="O127" s="20" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/f/Tyumen/Moskva/?class=Y&amp;travelers=1&amp;route[0]=86-28102026-491</t>
         </is>
       </c>
-      <c r="P127" s="16" t="inlineStr"/>
-      <c r="Q127" s="16" t="inlineStr">
+      <c r="P127" s="5" t="inlineStr"/>
+      <c r="Q127" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -13948,69 +13980,37 @@
       <c r="B128" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C128" s="10" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D128" s="10" t="inlineStr">
-        <is>
-          <t>Удобный</t>
-        </is>
-      </c>
-      <c r="E128" s="10" t="inlineStr">
-        <is>
-          <t>Самолёт, ЮТэйр</t>
-        </is>
-      </c>
-      <c r="F128" s="10" t="inlineStr">
-        <is>
-          <t>UT-454</t>
-        </is>
-      </c>
-      <c r="G128" s="5" t="inlineStr">
-        <is>
-          <t>28.10 07:15 (мест.)</t>
-        </is>
-      </c>
-      <c r="H128" s="5" t="inlineStr">
-        <is>
-          <t>28.10 08:10</t>
-        </is>
-      </c>
-      <c r="I128" s="5" t="inlineStr">
-        <is>
-          <t>Внуково</t>
-        </is>
-      </c>
-      <c r="J128" s="9" t="n">
-        <v>7065</v>
-      </c>
-      <c r="K128" s="9" t="n">
-        <v>10125</v>
-      </c>
-      <c r="L128" s="5" t="inlineStr">
-        <is>
-          <t>Внуково: метро → Казанский вокзал + электричка, или такси ~2 ч 45 мин</t>
-        </is>
-      </c>
-      <c r="M128" s="5" t="inlineStr">
-        <is>
-          <t>~11:35</t>
-        </is>
-      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>В2: после 15:00 28.10 / В3: к утру 29.10</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="inlineStr">
+        <is>
+          <t>не требуется</t>
+        </is>
+      </c>
+      <c r="F128" s="5" t="inlineStr"/>
+      <c r="G128" s="5" t="inlineStr"/>
+      <c r="H128" s="5" t="inlineStr"/>
+      <c r="I128" s="5" t="inlineStr"/>
+      <c r="J128" s="5" t="n"/>
+      <c r="K128" s="5" t="n"/>
+      <c r="L128" s="5" t="inlineStr"/>
+      <c r="M128" s="5" t="inlineStr"/>
       <c r="N128" s="5" t="inlineStr"/>
-      <c r="O128" s="20" t="inlineStr">
-        <is>
-          <t>https://avia.tutu.ru/f/Tyumen/Moskva/?class=Y&amp;travelers=1&amp;route[0]=86-28102026-491</t>
-        </is>
-      </c>
-      <c r="P128" s="5" t="inlineStr"/>
-      <c r="Q128" s="5" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
-      </c>
+      <c r="O128" s="5" t="inlineStr"/>
+      <c r="P128" s="5" t="inlineStr">
+        <is>
+          <t>Подходит В1</t>
+        </is>
+      </c>
+      <c r="Q128" s="5" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
@@ -14021,183 +14021,219 @@
       <c r="B129" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C129" s="5" t="inlineStr">
-        <is>
-          <t>В2: после 15:00 28.10 / В3: к утру 29.10</t>
-        </is>
-      </c>
-      <c r="D129" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E129" s="5" t="inlineStr">
-        <is>
-          <t>не требуется</t>
-        </is>
-      </c>
-      <c r="F129" s="5" t="inlineStr"/>
-      <c r="G129" s="5" t="inlineStr"/>
-      <c r="H129" s="5" t="inlineStr"/>
-      <c r="I129" s="5" t="inlineStr"/>
-      <c r="J129" s="5" t="n"/>
-      <c r="K129" s="5" t="n"/>
-      <c r="L129" s="5" t="inlineStr"/>
+      <c r="C129" s="7" t="inlineStr">
+        <is>
+          <t>Обратно</t>
+        </is>
+      </c>
+      <c r="D129" s="7" t="inlineStr">
+        <is>
+          <t>Самый дешёвый = Удобный</t>
+        </is>
+      </c>
+      <c r="E129" s="7" t="inlineStr">
+        <is>
+          <t>Самолёт, Победа</t>
+        </is>
+      </c>
+      <c r="F129" s="7" t="inlineStr">
+        <is>
+          <t>DP-6561</t>
+        </is>
+      </c>
+      <c r="G129" s="5" t="inlineStr">
+        <is>
+          <t>30.10 23:50</t>
+        </is>
+      </c>
+      <c r="H129" s="5" t="inlineStr">
+        <is>
+          <t>31.10 04:40 (мест.)</t>
+        </is>
+      </c>
+      <c r="I129" s="5" t="inlineStr">
+        <is>
+          <t>Шереметьево</t>
+        </is>
+      </c>
+      <c r="J129" s="6" t="n">
+        <v>8168</v>
+      </c>
+      <c r="K129" s="6" t="n">
+        <v>11154</v>
+      </c>
+      <c r="L129" s="5" t="inlineStr">
+        <is>
+          <t>Выезд из гостиницы 18:15; в аэропорту за 2 ч до вылета</t>
+        </is>
+      </c>
       <c r="M129" s="5" t="inlineStr"/>
       <c r="N129" s="5" t="inlineStr"/>
-      <c r="O129" s="5" t="inlineStr"/>
+      <c r="O129" s="20" t="inlineStr">
+        <is>
+          <t>https://avia.tutu.ru/f/Moskva/Tyumen/?class=Y&amp;travelers=1&amp;route[0]=491-30102026-86</t>
+        </is>
+      </c>
       <c r="P129" s="5" t="inlineStr">
         <is>
-          <t>Подходит В1</t>
+          <t>Впритык по правилу 2 ч. UT-453 20:30 не успевает</t>
         </is>
       </c>
       <c r="Q129" s="5" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="5" t="inlineStr">
-        <is>
-          <t>Тюмень</t>
-        </is>
-      </c>
-      <c r="B130" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C130" s="7" t="inlineStr">
-        <is>
-          <t>Обратно</t>
-        </is>
-      </c>
-      <c r="D130" s="7" t="inlineStr">
-        <is>
-          <t>Самый дешёвый = Удобный</t>
-        </is>
-      </c>
-      <c r="E130" s="7" t="inlineStr">
-        <is>
-          <t>Самолёт, Победа</t>
-        </is>
-      </c>
-      <c r="F130" s="7" t="inlineStr">
-        <is>
-          <t>DP-6561</t>
-        </is>
-      </c>
-      <c r="G130" s="5" t="inlineStr">
-        <is>
-          <t>30.10 23:50</t>
-        </is>
-      </c>
-      <c r="H130" s="5" t="inlineStr">
-        <is>
-          <t>31.10 04:40 (мест.)</t>
-        </is>
-      </c>
-      <c r="I130" s="5" t="inlineStr">
-        <is>
-          <t>Шереметьево</t>
-        </is>
-      </c>
-      <c r="J130" s="6" t="n">
-        <v>8168</v>
-      </c>
-      <c r="K130" s="6" t="n">
-        <v>11154</v>
-      </c>
-      <c r="L130" s="5" t="inlineStr">
-        <is>
-          <t>Выезд из гостиницы 18:15; в аэропорту за 2 ч до вылета</t>
-        </is>
-      </c>
-      <c r="M130" s="5" t="inlineStr"/>
-      <c r="N130" s="5" t="inlineStr"/>
-      <c r="O130" s="20" t="inlineStr">
-        <is>
-          <t>https://avia.tutu.ru/f/Moskva/Tyumen/?class=Y&amp;travelers=1&amp;route[0]=491-30102026-86</t>
-        </is>
-      </c>
-      <c r="P130" s="5" t="inlineStr">
-        <is>
-          <t>Впритык по правилу 2 ч. UT-453 20:30 не успевает</t>
-        </is>
-      </c>
-      <c r="Q130" s="5" t="inlineStr"/>
+      <c r="A130" s="15" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="B130" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C130" s="17" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D130" s="17" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E130" s="17" t="inlineStr">
+        <is>
+          <t>Поезд, купе (сидячий 2 283)</t>
+        </is>
+      </c>
+      <c r="F130" s="17" t="inlineStr">
+        <is>
+          <t>081А</t>
+        </is>
+      </c>
+      <c r="G130" s="16" t="inlineStr">
+        <is>
+          <t>27.10 21:21</t>
+        </is>
+      </c>
+      <c r="H130" s="16" t="inlineStr">
+        <is>
+          <t>28.10 06:04</t>
+        </is>
+      </c>
+      <c r="I130" s="16" t="inlineStr">
+        <is>
+          <t>Москва, Восточный</t>
+        </is>
+      </c>
+      <c r="J130" s="18" t="n">
+        <v>3272</v>
+      </c>
+      <c r="K130" s="18" t="n">
+        <v>3272</v>
+      </c>
+      <c r="L130" s="16" t="inlineStr">
+        <is>
+          <t>Восточный вокзал → МЦД/метро до Казанского (~30 мин) → электричка + такси (07:22 → 09:15)</t>
+        </is>
+      </c>
+      <c r="M130" s="16" t="inlineStr">
+        <is>
+          <t>~09:30</t>
+        </is>
+      </c>
+      <c r="N130" s="16" t="inlineStr">
+        <is>
+          <t>ранний заезд</t>
+        </is>
+      </c>
+      <c r="O130" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2004000&amp;nnst2=2000000</t>
+        </is>
+      </c>
+      <c r="P130" s="16" t="inlineStr">
+        <is>
+          <t>Вечером сел — утром в Москве</t>
+        </is>
+      </c>
+      <c r="Q130" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
     </row>
     <row r="131">
-      <c r="A131" s="15" t="inlineStr">
+      <c r="A131" s="5" t="inlineStr">
         <is>
           <t>Санкт-Петербург</t>
         </is>
       </c>
-      <c r="B131" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C131" s="17" t="inlineStr">
+      <c r="B131" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C131" s="10" t="inlineStr">
         <is>
           <t>В1: к 15:00 28.10</t>
         </is>
       </c>
-      <c r="D131" s="17" t="inlineStr">
-        <is>
-          <t>Самый дешёвый</t>
-        </is>
-      </c>
-      <c r="E131" s="17" t="inlineStr">
-        <is>
-          <t>Поезд, купе (сидячий 2 283)</t>
-        </is>
-      </c>
-      <c r="F131" s="17" t="inlineStr">
-        <is>
-          <t>081А</t>
-        </is>
-      </c>
-      <c r="G131" s="16" t="inlineStr">
-        <is>
-          <t>27.10 21:21</t>
-        </is>
-      </c>
-      <c r="H131" s="16" t="inlineStr">
-        <is>
-          <t>28.10 06:04</t>
-        </is>
-      </c>
-      <c r="I131" s="16" t="inlineStr">
-        <is>
-          <t>Москва, Восточный</t>
-        </is>
-      </c>
-      <c r="J131" s="18" t="n">
-        <v>3272</v>
-      </c>
-      <c r="K131" s="18" t="n">
-        <v>3272</v>
-      </c>
-      <c r="L131" s="16" t="inlineStr">
-        <is>
-          <t>Восточный вокзал → МЦД/метро до Казанского (~30 мин) → электричка + такси (07:22 → 09:15)</t>
-        </is>
-      </c>
-      <c r="M131" s="16" t="inlineStr">
-        <is>
-          <t>~09:30</t>
-        </is>
-      </c>
-      <c r="N131" s="16" t="inlineStr">
-        <is>
-          <t>ранний заезд</t>
-        </is>
-      </c>
-      <c r="O131" s="19" t="inlineStr">
+      <c r="D131" s="10" t="inlineStr">
+        <is>
+          <t>Удобный</t>
+        </is>
+      </c>
+      <c r="E131" s="10" t="inlineStr">
+        <is>
+          <t>Поезд «Смена — А. Бетанкур», купе</t>
+        </is>
+      </c>
+      <c r="F131" s="10" t="inlineStr">
+        <is>
+          <t>025А</t>
+        </is>
+      </c>
+      <c r="G131" s="5" t="inlineStr">
+        <is>
+          <t>27.10 23:40</t>
+        </is>
+      </c>
+      <c r="H131" s="5" t="inlineStr">
+        <is>
+          <t>28.10 07:45</t>
+        </is>
+      </c>
+      <c r="I131" s="5" t="inlineStr">
+        <is>
+          <t>Москва, Ленинградский</t>
+        </is>
+      </c>
+      <c r="J131" s="9" t="n">
+        <v>3975</v>
+      </c>
+      <c r="K131" s="9" t="n">
+        <v>3975</v>
+      </c>
+      <c r="L131" s="5" t="inlineStr">
+        <is>
+          <t>Ленинградский вокзал → через площадь на Казанский (5 мин) → электричка + такси (08:47 РЭКС → 10:28)</t>
+        </is>
+      </c>
+      <c r="M131" s="5" t="inlineStr">
+        <is>
+          <t>~10:45</t>
+        </is>
+      </c>
+      <c r="N131" s="5" t="inlineStr"/>
+      <c r="O131" s="20" t="inlineStr">
         <is>
           <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2004000&amp;nnst2=2000000</t>
         </is>
       </c>
-      <c r="P131" s="16" t="inlineStr">
-        <is>
-          <t>Вечером сел — утром в Москве</t>
-        </is>
-      </c>
-      <c r="Q131" s="16" t="inlineStr">
+      <c r="P131" s="5" t="inlineStr">
+        <is>
+          <t>Ленинградский и Казанский — на одной площади. Также «Сапсан» 28.10 05:30→09:23, 3 830 ₽ (→ 09:48 → 11:36)</t>
+        </is>
+      </c>
+      <c r="Q131" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -14212,34 +14248,34 @@
       <c r="B132" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C132" s="10" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D132" s="10" t="inlineStr">
-        <is>
-          <t>Удобный</t>
-        </is>
-      </c>
-      <c r="E132" s="10" t="inlineStr">
-        <is>
-          <t>Поезд «Смена — А. Бетанкур», купе</t>
-        </is>
-      </c>
-      <c r="F132" s="10" t="inlineStr">
-        <is>
-          <t>025А</t>
+      <c r="C132" s="7" t="inlineStr">
+        <is>
+          <t>В2: после 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D132" s="7" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E132" s="7" t="inlineStr">
+        <is>
+          <t>Ласточка, сидячий</t>
+        </is>
+      </c>
+      <c r="F132" s="7" t="inlineStr">
+        <is>
+          <t>723Р</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
-          <t>27.10 23:40</t>
+          <t>28.10 05:35</t>
         </is>
       </c>
       <c r="H132" s="5" t="inlineStr">
         <is>
-          <t>28.10 07:45</t>
+          <t>28.10 11:13</t>
         </is>
       </c>
       <c r="I132" s="5" t="inlineStr">
@@ -14247,31 +14283,31 @@
           <t>Москва, Ленинградский</t>
         </is>
       </c>
-      <c r="J132" s="9" t="n">
-        <v>3975</v>
-      </c>
-      <c r="K132" s="9" t="n">
-        <v>3975</v>
+      <c r="J132" s="6" t="n">
+        <v>1121</v>
+      </c>
+      <c r="K132" s="6" t="n">
+        <v>1121</v>
       </c>
       <c r="L132" s="5" t="inlineStr">
         <is>
-          <t>Ленинградский вокзал → через площадь на Казанский (5 мин) → электричка + такси (08:47 РЭКС → 10:28)</t>
+          <t>Ленинградский вокзал → через площадь на Казанский (5 мин) → электричка + такси (12:54 → 15:15)</t>
         </is>
       </c>
       <c r="M132" s="5" t="inlineStr">
         <is>
-          <t>~10:45</t>
+          <t>~15:30</t>
         </is>
       </c>
       <c r="N132" s="5" t="inlineStr"/>
       <c r="O132" s="20" t="inlineStr">
         <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2004000&amp;nnst2=2000000</t>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2004000&amp;nnst2=2000000</t>
         </is>
       </c>
       <c r="P132" s="5" t="inlineStr">
         <is>
-          <t>Ленинградский и Казанский — на одной площади. Также «Сапсан» 28.10 05:30→09:23, 3 830 ₽ (→ 09:48 → 11:36)</t>
+          <t>Самый дешёвый; к экскурсии в 16:00 успевает</t>
         </is>
       </c>
       <c r="Q132" s="5" t="inlineStr">
@@ -14291,7 +14327,7 @@
       </c>
       <c r="C133" s="7" t="inlineStr">
         <is>
-          <t>В2: после 15:00 28.10</t>
+          <t>Обратно</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
@@ -14301,61 +14337,49 @@
       </c>
       <c r="E133" s="7" t="inlineStr">
         <is>
-          <t>Ласточка, сидячий</t>
+          <t>Поезд «Аврора», сидячий</t>
         </is>
       </c>
       <c r="F133" s="7" t="inlineStr">
         <is>
-          <t>723Р</t>
+          <t>750У</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>28.10 05:35</t>
+          <t>30.10 22:30</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
         <is>
-          <t>28.10 11:13</t>
+          <t>31.10 05:00</t>
         </is>
       </c>
       <c r="I133" s="5" t="inlineStr">
         <is>
-          <t>Москва, Ленинградский</t>
+          <t>СПб, Московский вокзал</t>
         </is>
       </c>
       <c r="J133" s="6" t="n">
-        <v>1121</v>
+        <v>2185</v>
       </c>
       <c r="K133" s="6" t="n">
-        <v>1121</v>
+        <v>2185</v>
       </c>
       <c r="L133" s="5" t="inlineStr">
         <is>
-          <t>Ленинградский вокзал → через площадь на Казанский (5 мин) → электричка + такси (12:54 → 15:15)</t>
-        </is>
-      </c>
-      <c r="M133" s="5" t="inlineStr">
-        <is>
-          <t>~15:30</t>
-        </is>
-      </c>
+          <t>Электричка 18:43 → Казанский 20:47 → Ленинградский</t>
+        </is>
+      </c>
+      <c r="M133" s="5" t="inlineStr"/>
       <c r="N133" s="5" t="inlineStr"/>
       <c r="O133" s="20" t="inlineStr">
         <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2004000&amp;nnst2=2000000</t>
-        </is>
-      </c>
-      <c r="P133" s="5" t="inlineStr">
-        <is>
-          <t>Самый дешёвый; к экскурсии в 16:00 успевает</t>
-        </is>
-      </c>
-      <c r="Q133" s="5" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
-      </c>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2004000</t>
+        </is>
+      </c>
+      <c r="P133" s="5" t="inlineStr"/>
+      <c r="Q133" s="5" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
@@ -14366,34 +14390,34 @@
       <c r="B134" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C134" s="7" t="inlineStr">
+      <c r="C134" s="10" t="inlineStr">
         <is>
           <t>Обратно</t>
         </is>
       </c>
-      <c r="D134" s="7" t="inlineStr">
-        <is>
-          <t>Самый дешёвый</t>
-        </is>
-      </c>
-      <c r="E134" s="7" t="inlineStr">
-        <is>
-          <t>Поезд «Аврора», сидячий</t>
-        </is>
-      </c>
-      <c r="F134" s="7" t="inlineStr">
-        <is>
-          <t>750У</t>
+      <c r="D134" s="10" t="inlineStr">
+        <is>
+          <t>Удобный</t>
+        </is>
+      </c>
+      <c r="E134" s="10" t="inlineStr">
+        <is>
+          <t>Поезд «Смена — А. Бетанкур», купе</t>
+        </is>
+      </c>
+      <c r="F134" s="10" t="inlineStr">
+        <is>
+          <t>026А</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>30.10 22:30</t>
+          <t>30.10 23:10</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
         <is>
-          <t>31.10 05:00</t>
+          <t>31.10 07:07</t>
         </is>
       </c>
       <c r="I134" s="5" t="inlineStr">
@@ -14401,15 +14425,15 @@
           <t>СПб, Московский вокзал</t>
         </is>
       </c>
-      <c r="J134" s="6" t="n">
-        <v>2185</v>
-      </c>
-      <c r="K134" s="6" t="n">
-        <v>2185</v>
+      <c r="J134" s="9" t="n">
+        <v>5093</v>
+      </c>
+      <c r="K134" s="9" t="n">
+        <v>5093</v>
       </c>
       <c r="L134" s="5" t="inlineStr">
         <is>
-          <t>Электричка 18:43 → Казанский 20:47 → Ленинградский</t>
+          <t>Электричка 18:43 или 19:43 → Казанский → Ленинградский</t>
         </is>
       </c>
       <c r="M134" s="5" t="inlineStr"/>
@@ -14419,150 +14443,162 @@
           <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2004000</t>
         </is>
       </c>
-      <c r="P134" s="5" t="inlineStr"/>
+      <c r="P134" s="5" t="inlineStr">
+        <is>
+          <t>Ночь в купе. Также 028А 22:08, купе 4 256</t>
+        </is>
+      </c>
       <c r="Q134" s="5" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="5" t="inlineStr">
-        <is>
-          <t>Санкт-Петербург</t>
-        </is>
-      </c>
-      <c r="B135" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C135" s="10" t="inlineStr">
-        <is>
-          <t>Обратно</t>
-        </is>
-      </c>
-      <c r="D135" s="10" t="inlineStr">
+      <c r="A135" s="15" t="inlineStr">
+        <is>
+          <t>Нижний Новгород</t>
+        </is>
+      </c>
+      <c r="B135" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C135" s="17" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D135" s="17" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E135" s="17" t="inlineStr">
+        <is>
+          <t>Ласточка, сидячий</t>
+        </is>
+      </c>
+      <c r="F135" s="17" t="inlineStr">
+        <is>
+          <t>723А</t>
+        </is>
+      </c>
+      <c r="G135" s="16" t="inlineStr">
+        <is>
+          <t>28.10 04:51</t>
+        </is>
+      </c>
+      <c r="H135" s="16" t="inlineStr">
+        <is>
+          <t>28.10 09:09</t>
+        </is>
+      </c>
+      <c r="I135" s="16" t="inlineStr">
+        <is>
+          <t>Москва, Восточный</t>
+        </is>
+      </c>
+      <c r="J135" s="18" t="n">
+        <v>2435</v>
+      </c>
+      <c r="K135" s="18" t="n">
+        <v>2435</v>
+      </c>
+      <c r="L135" s="16" t="inlineStr">
+        <is>
+          <t>Восточный вокзал → МЦД/метро до Казанского (~30 мин) → электричка + такси (09:48 впритык, иначе 12:54 → 15:15)</t>
+        </is>
+      </c>
+      <c r="M135" s="16" t="inlineStr">
+        <is>
+          <t>~12:00 / ~15:30</t>
+        </is>
+      </c>
+      <c r="N135" s="16" t="inlineStr"/>
+      <c r="O135" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2060000&amp;nnst2=2000000</t>
+        </is>
+      </c>
+      <c r="P135" s="16" t="inlineStr">
+        <is>
+          <t>Или своя машина: ~430 км, ~6 ч</t>
+        </is>
+      </c>
+      <c r="Q135" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>Нижний Новгород</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C136" s="10" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D136" s="10" t="inlineStr">
         <is>
           <t>Удобный</t>
         </is>
       </c>
-      <c r="E135" s="10" t="inlineStr">
-        <is>
-          <t>Поезд «Смена — А. Бетанкур», купе</t>
-        </is>
-      </c>
-      <c r="F135" s="10" t="inlineStr">
-        <is>
-          <t>026А</t>
-        </is>
-      </c>
-      <c r="G135" s="5" t="inlineStr">
-        <is>
-          <t>30.10 23:10</t>
-        </is>
-      </c>
-      <c r="H135" s="5" t="inlineStr">
-        <is>
-          <t>31.10 07:07</t>
-        </is>
-      </c>
-      <c r="I135" s="5" t="inlineStr">
-        <is>
-          <t>СПб, Московский вокзал</t>
-        </is>
-      </c>
-      <c r="J135" s="9" t="n">
-        <v>5093</v>
-      </c>
-      <c r="K135" s="9" t="n">
-        <v>5093</v>
-      </c>
-      <c r="L135" s="5" t="inlineStr">
-        <is>
-          <t>Электричка 18:43 или 19:43 → Казанский → Ленинградский</t>
-        </is>
-      </c>
-      <c r="M135" s="5" t="inlineStr"/>
-      <c r="N135" s="5" t="inlineStr"/>
-      <c r="O135" s="20" t="inlineStr">
-        <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2004000</t>
-        </is>
-      </c>
-      <c r="P135" s="5" t="inlineStr">
-        <is>
-          <t>Ночь в купе. Также 028А 22:08, купе 4 256</t>
-        </is>
-      </c>
-      <c r="Q135" s="5" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="15" t="inlineStr">
-        <is>
-          <t>Нижний Новгород</t>
-        </is>
-      </c>
-      <c r="B136" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C136" s="17" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D136" s="17" t="inlineStr">
-        <is>
-          <t>Самый дешёвый</t>
-        </is>
-      </c>
-      <c r="E136" s="17" t="inlineStr">
-        <is>
-          <t>Ласточка, сидячий</t>
-        </is>
-      </c>
-      <c r="F136" s="17" t="inlineStr">
-        <is>
-          <t>723А</t>
-        </is>
-      </c>
-      <c r="G136" s="16" t="inlineStr">
-        <is>
-          <t>28.10 04:51</t>
-        </is>
-      </c>
-      <c r="H136" s="16" t="inlineStr">
-        <is>
-          <t>28.10 09:09</t>
-        </is>
-      </c>
-      <c r="I136" s="16" t="inlineStr">
-        <is>
-          <t>Москва, Восточный</t>
-        </is>
-      </c>
-      <c r="J136" s="18" t="n">
-        <v>2435</v>
-      </c>
-      <c r="K136" s="18" t="n">
-        <v>2435</v>
-      </c>
-      <c r="L136" s="16" t="inlineStr">
-        <is>
-          <t>Восточный вокзал → МЦД/метро до Казанского (~30 мин) → электричка + такси (09:48 впритык, иначе 12:54 → 15:15)</t>
-        </is>
-      </c>
-      <c r="M136" s="16" t="inlineStr">
-        <is>
-          <t>~12:00 / ~15:30</t>
-        </is>
-      </c>
-      <c r="N136" s="16" t="inlineStr"/>
-      <c r="O136" s="19" t="inlineStr">
+      <c r="E136" s="10" t="inlineStr">
+        <is>
+          <t>Поезд «Вятка», купе</t>
+        </is>
+      </c>
+      <c r="F136" s="10" t="inlineStr">
+        <is>
+          <t>031Г</t>
+        </is>
+      </c>
+      <c r="G136" s="5" t="inlineStr">
+        <is>
+          <t>28.10 03:05</t>
+        </is>
+      </c>
+      <c r="H136" s="5" t="inlineStr">
+        <is>
+          <t>28.10 09:27</t>
+        </is>
+      </c>
+      <c r="I136" s="5" t="inlineStr">
+        <is>
+          <t>Москва, Ярославский</t>
+        </is>
+      </c>
+      <c r="J136" s="9" t="n">
+        <v>4460</v>
+      </c>
+      <c r="K136" s="9" t="n">
+        <v>4460</v>
+      </c>
+      <c r="L136" s="5" t="inlineStr">
+        <is>
+          <t>Ярославский вокзал → через площадь на Казанский (5 мин) → электричка + такси (09:48 → 11:36)</t>
+        </is>
+      </c>
+      <c r="M136" s="5" t="inlineStr">
+        <is>
+          <t>~12:00</t>
+        </is>
+      </c>
+      <c r="N136" s="5" t="inlineStr"/>
+      <c r="O136" s="20" t="inlineStr">
         <is>
           <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2060000&amp;nnst2=2000000</t>
         </is>
       </c>
-      <c r="P136" s="16" t="inlineStr">
-        <is>
-          <t>Или своя машина: ~430 км, ~6 ч</t>
-        </is>
-      </c>
-      <c r="Q136" s="16" t="inlineStr">
+      <c r="P136" s="5" t="inlineStr">
+        <is>
+          <t>Ночной поезд, посадка в 03:05</t>
+        </is>
+      </c>
+      <c r="Q136" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -14577,55 +14613,55 @@
       <c r="B137" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C137" s="10" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D137" s="10" t="inlineStr">
-        <is>
-          <t>Удобный</t>
-        </is>
-      </c>
-      <c r="E137" s="10" t="inlineStr">
-        <is>
-          <t>Поезд «Вятка», купе</t>
-        </is>
-      </c>
-      <c r="F137" s="10" t="inlineStr">
-        <is>
-          <t>031Г</t>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>В2: после 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="inlineStr">
+        <is>
+          <t>Поезд «Буревестник», сидячий</t>
+        </is>
+      </c>
+      <c r="F137" s="5" t="inlineStr">
+        <is>
+          <t>705Э</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>28.10 03:05</t>
+          <t>28.10 07:20</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
         <is>
-          <t>28.10 09:27</t>
+          <t>28.10 11:34</t>
         </is>
       </c>
       <c r="I137" s="5" t="inlineStr">
         <is>
-          <t>Москва, Ярославский</t>
-        </is>
-      </c>
-      <c r="J137" s="9" t="n">
-        <v>4460</v>
-      </c>
-      <c r="K137" s="9" t="n">
-        <v>4460</v>
+          <t>Москва, Восточный</t>
+        </is>
+      </c>
+      <c r="J137" s="21" t="n">
+        <v>2136</v>
+      </c>
+      <c r="K137" s="21" t="n">
+        <v>2136</v>
       </c>
       <c r="L137" s="5" t="inlineStr">
         <is>
-          <t>Ярославский вокзал → через площадь на Казанский (5 мин) → электричка + такси (09:48 → 11:36)</t>
+          <t>Восточный вокзал → МЦД/метро до Казанского (~30 мин) → электричка + такси (12:54 → 15:15)</t>
         </is>
       </c>
       <c r="M137" s="5" t="inlineStr">
         <is>
-          <t>~12:00</t>
+          <t>~15:30</t>
         </is>
       </c>
       <c r="N137" s="5" t="inlineStr"/>
@@ -14634,11 +14670,7 @@
           <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2060000&amp;nnst2=2000000</t>
         </is>
       </c>
-      <c r="P137" s="5" t="inlineStr">
-        <is>
-          <t>Ночной поезд, посадка в 03:05</t>
-        </is>
-      </c>
+      <c r="P137" s="5" t="inlineStr"/>
       <c r="Q137" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
@@ -14654,69 +14686,65 @@
       <c r="B138" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C138" s="5" t="inlineStr">
-        <is>
-          <t>В2: после 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D138" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E138" s="5" t="inlineStr">
-        <is>
-          <t>Поезд «Буревестник», сидячий</t>
-        </is>
-      </c>
-      <c r="F138" s="5" t="inlineStr">
-        <is>
-          <t>705Э</t>
+      <c r="C138" s="7" t="inlineStr">
+        <is>
+          <t>Обратно</t>
+        </is>
+      </c>
+      <c r="D138" s="7" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E138" s="7" t="inlineStr">
+        <is>
+          <t>Ласточка, сидячий</t>
+        </is>
+      </c>
+      <c r="F138" s="7" t="inlineStr">
+        <is>
+          <t>723Я</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>28.10 07:20</t>
+          <t>30.10 21:15</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
         <is>
-          <t>28.10 11:34</t>
+          <t>31.10 01:15</t>
         </is>
       </c>
       <c r="I138" s="5" t="inlineStr">
         <is>
-          <t>Москва, Восточный</t>
-        </is>
-      </c>
-      <c r="J138" s="21" t="n">
-        <v>2136</v>
-      </c>
-      <c r="K138" s="21" t="n">
-        <v>2136</v>
+          <t>Нижний Новгород</t>
+        </is>
+      </c>
+      <c r="J138" s="6" t="n">
+        <v>2347</v>
+      </c>
+      <c r="K138" s="6" t="n">
+        <v>2347</v>
       </c>
       <c r="L138" s="5" t="inlineStr">
         <is>
-          <t>Восточный вокзал → МЦД/метро до Казанского (~30 мин) → электричка + такси (12:54 → 15:15)</t>
-        </is>
-      </c>
-      <c r="M138" s="5" t="inlineStr">
-        <is>
-          <t>~15:30</t>
-        </is>
-      </c>
+          <t>Электричка 18:43 → Казанский 20:47 → Восточный</t>
+        </is>
+      </c>
+      <c r="M138" s="5" t="inlineStr"/>
       <c r="N138" s="5" t="inlineStr"/>
       <c r="O138" s="20" t="inlineStr">
         <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2060000&amp;nnst2=2000000</t>
-        </is>
-      </c>
-      <c r="P138" s="5" t="inlineStr"/>
-      <c r="Q138" s="5" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
-      </c>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2060000</t>
+        </is>
+      </c>
+      <c r="P138" s="5" t="inlineStr">
+        <is>
+          <t>Дома ночью</t>
+        </is>
+      </c>
+      <c r="Q138" s="5" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
@@ -14727,34 +14755,34 @@
       <c r="B139" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C139" s="7" t="inlineStr">
+      <c r="C139" s="10" t="inlineStr">
         <is>
           <t>Обратно</t>
         </is>
       </c>
-      <c r="D139" s="7" t="inlineStr">
-        <is>
-          <t>Самый дешёвый</t>
-        </is>
-      </c>
-      <c r="E139" s="7" t="inlineStr">
-        <is>
-          <t>Ласточка, сидячий</t>
-        </is>
-      </c>
-      <c r="F139" s="7" t="inlineStr">
-        <is>
-          <t>723Я</t>
+      <c r="D139" s="10" t="inlineStr">
+        <is>
+          <t>Удобный</t>
+        </is>
+      </c>
+      <c r="E139" s="10" t="inlineStr">
+        <is>
+          <t>Поезд «Нижегородец», купе</t>
+        </is>
+      </c>
+      <c r="F139" s="10" t="inlineStr">
+        <is>
+          <t>036Щ</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>30.10 21:15</t>
+          <t>30.10 23:10</t>
         </is>
       </c>
       <c r="H139" s="5" t="inlineStr">
         <is>
-          <t>31.10 01:15</t>
+          <t>31.10 07:10</t>
         </is>
       </c>
       <c r="I139" s="5" t="inlineStr">
@@ -14762,15 +14790,15 @@
           <t>Нижний Новгород</t>
         </is>
       </c>
-      <c r="J139" s="6" t="n">
-        <v>2347</v>
-      </c>
-      <c r="K139" s="6" t="n">
-        <v>2347</v>
+      <c r="J139" s="9" t="n">
+        <v>5172</v>
+      </c>
+      <c r="K139" s="9" t="n">
+        <v>5172</v>
       </c>
       <c r="L139" s="5" t="inlineStr">
         <is>
-          <t>Электричка 18:43 → Казанский 20:47 → Восточный</t>
+          <t>Электричка → Казанский → Ярославский (через площадь)</t>
         </is>
       </c>
       <c r="M139" s="5" t="inlineStr"/>
@@ -14782,152 +14810,160 @@
       </c>
       <c r="P139" s="5" t="inlineStr">
         <is>
-          <t>Дома ночью</t>
+          <t>Ночь в купе. Также 010Н 22:30, купе 4 040</t>
         </is>
       </c>
       <c r="Q139" s="5" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="5" t="inlineStr">
-        <is>
-          <t>Нижний Новгород</t>
-        </is>
-      </c>
-      <c r="B140" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C140" s="10" t="inlineStr">
-        <is>
-          <t>Обратно</t>
-        </is>
-      </c>
-      <c r="D140" s="10" t="inlineStr">
+      <c r="A140" s="15" t="inlineStr">
+        <is>
+          <t>Смоленск</t>
+        </is>
+      </c>
+      <c r="B140" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C140" s="17" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D140" s="17" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E140" s="17" t="inlineStr">
+        <is>
+          <t>Ласточка-премиум, сидячий</t>
+        </is>
+      </c>
+      <c r="F140" s="17" t="inlineStr">
+        <is>
+          <t>738М</t>
+        </is>
+      </c>
+      <c r="G140" s="16" t="inlineStr">
+        <is>
+          <t>28.10 07:29</t>
+        </is>
+      </c>
+      <c r="H140" s="16" t="inlineStr">
+        <is>
+          <t>28.10 11:53</t>
+        </is>
+      </c>
+      <c r="I140" s="16" t="inlineStr">
+        <is>
+          <t>Москва, Белорусский</t>
+        </is>
+      </c>
+      <c r="J140" s="18" t="n">
+        <v>1832</v>
+      </c>
+      <c r="K140" s="18" t="n">
+        <v>1832</v>
+      </c>
+      <c r="L140" s="16" t="inlineStr">
+        <is>
+          <t>Белорусский → метро до Комсомольской (~15 мин) → электричка + такси (12:54 → 15:15)</t>
+        </is>
+      </c>
+      <c r="M140" s="16" t="inlineStr">
+        <is>
+          <t>~15:30</t>
+        </is>
+      </c>
+      <c r="N140" s="16" t="inlineStr"/>
+      <c r="O140" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2000170&amp;nnst2=2000000</t>
+        </is>
+      </c>
+      <c r="P140" s="16" t="inlineStr">
+        <is>
+          <t>К экскурсии в 16:00 успевает</t>
+        </is>
+      </c>
+      <c r="Q140" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>Смоленск</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C141" s="10" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D141" s="10" t="inlineStr">
         <is>
           <t>Удобный</t>
         </is>
       </c>
-      <c r="E140" s="10" t="inlineStr">
-        <is>
-          <t>Поезд «Нижегородец», купе</t>
-        </is>
-      </c>
-      <c r="F140" s="10" t="inlineStr">
-        <is>
-          <t>036Щ</t>
-        </is>
-      </c>
-      <c r="G140" s="5" t="inlineStr">
-        <is>
-          <t>30.10 23:10</t>
-        </is>
-      </c>
-      <c r="H140" s="5" t="inlineStr">
-        <is>
-          <t>31.10 07:10</t>
-        </is>
-      </c>
-      <c r="I140" s="5" t="inlineStr">
-        <is>
-          <t>Нижний Новгород</t>
-        </is>
-      </c>
-      <c r="J140" s="9" t="n">
-        <v>5172</v>
-      </c>
-      <c r="K140" s="9" t="n">
-        <v>5172</v>
-      </c>
-      <c r="L140" s="5" t="inlineStr">
-        <is>
-          <t>Электричка → Казанский → Ярославский (через площадь)</t>
-        </is>
-      </c>
-      <c r="M140" s="5" t="inlineStr"/>
-      <c r="N140" s="5" t="inlineStr"/>
-      <c r="O140" s="20" t="inlineStr">
-        <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2060000</t>
-        </is>
-      </c>
-      <c r="P140" s="5" t="inlineStr">
-        <is>
-          <t>Ночь в купе. Также 010Н 22:30, купе 4 040</t>
-        </is>
-      </c>
-      <c r="Q140" s="5" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="15" t="inlineStr">
-        <is>
-          <t>Смоленск</t>
-        </is>
-      </c>
-      <c r="B141" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C141" s="17" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D141" s="17" t="inlineStr">
-        <is>
-          <t>Самый дешёвый</t>
-        </is>
-      </c>
-      <c r="E141" s="17" t="inlineStr">
-        <is>
-          <t>Ласточка-премиум, сидячий</t>
-        </is>
-      </c>
-      <c r="F141" s="17" t="inlineStr">
-        <is>
-          <t>738М</t>
-        </is>
-      </c>
-      <c r="G141" s="16" t="inlineStr">
-        <is>
-          <t>28.10 07:29</t>
-        </is>
-      </c>
-      <c r="H141" s="16" t="inlineStr">
-        <is>
-          <t>28.10 11:53</t>
-        </is>
-      </c>
-      <c r="I141" s="16" t="inlineStr">
+      <c r="E141" s="10" t="inlineStr">
+        <is>
+          <t>Поезд, купе</t>
+        </is>
+      </c>
+      <c r="F141" s="10" t="inlineStr">
+        <is>
+          <t>008Б</t>
+        </is>
+      </c>
+      <c r="G141" s="5" t="inlineStr">
+        <is>
+          <t>28.10 01:35</t>
+        </is>
+      </c>
+      <c r="H141" s="5" t="inlineStr">
+        <is>
+          <t>28.10 06:56</t>
+        </is>
+      </c>
+      <c r="I141" s="5" t="inlineStr">
         <is>
           <t>Москва, Белорусский</t>
         </is>
       </c>
-      <c r="J141" s="18" t="n">
-        <v>1832</v>
-      </c>
-      <c r="K141" s="18" t="n">
-        <v>1832</v>
-      </c>
-      <c r="L141" s="16" t="inlineStr">
-        <is>
-          <t>Белорусский → метро до Комсомольской (~15 мин) → электричка + такси (12:54 → 15:15)</t>
-        </is>
-      </c>
-      <c r="M141" s="16" t="inlineStr">
-        <is>
-          <t>~15:30</t>
-        </is>
-      </c>
-      <c r="N141" s="16" t="inlineStr"/>
-      <c r="O141" s="19" t="inlineStr">
+      <c r="J141" s="9" t="n">
+        <v>4656</v>
+      </c>
+      <c r="K141" s="9" t="n">
+        <v>4656</v>
+      </c>
+      <c r="L141" s="5" t="inlineStr">
+        <is>
+          <t>Белорусский → метро до Комсомольской (~15 мин) → электричка + такси (08:47 РЭКС → 10:28)</t>
+        </is>
+      </c>
+      <c r="M141" s="5" t="inlineStr">
+        <is>
+          <t>~10:45</t>
+        </is>
+      </c>
+      <c r="N141" s="5" t="inlineStr"/>
+      <c r="O141" s="20" t="inlineStr">
         <is>
           <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2000170&amp;nnst2=2000000</t>
         </is>
       </c>
-      <c r="P141" s="16" t="inlineStr">
-        <is>
-          <t>К экскурсии в 16:00 успевает</t>
-        </is>
-      </c>
-      <c r="Q141" s="16" t="inlineStr">
+      <c r="P141" s="5" t="inlineStr">
+        <is>
+          <t>Ночной поезд</t>
+        </is>
+      </c>
+      <c r="Q141" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -14942,73 +14978,61 @@
       <c r="B142" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C142" s="10" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D142" s="10" t="inlineStr">
-        <is>
-          <t>Удобный</t>
-        </is>
-      </c>
-      <c r="E142" s="10" t="inlineStr">
+      <c r="C142" s="7" t="inlineStr">
+        <is>
+          <t>Обратно</t>
+        </is>
+      </c>
+      <c r="D142" s="7" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E142" s="7" t="inlineStr">
         <is>
           <t>Поезд, купе</t>
         </is>
       </c>
-      <c r="F142" s="10" t="inlineStr">
-        <is>
-          <t>008Б</t>
+      <c r="F142" s="7" t="inlineStr">
+        <is>
+          <t>027Б</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>28.10 01:35</t>
+          <t>30.10 23:30</t>
         </is>
       </c>
       <c r="H142" s="5" t="inlineStr">
         <is>
-          <t>28.10 06:56</t>
+          <t>31.10 04:39</t>
         </is>
       </c>
       <c r="I142" s="5" t="inlineStr">
         <is>
-          <t>Москва, Белорусский</t>
-        </is>
-      </c>
-      <c r="J142" s="9" t="n">
-        <v>4656</v>
-      </c>
-      <c r="K142" s="9" t="n">
-        <v>4656</v>
+          <t>Смоленск</t>
+        </is>
+      </c>
+      <c r="J142" s="6" t="n">
+        <v>4022</v>
+      </c>
+      <c r="K142" s="6" t="n">
+        <v>4022</v>
       </c>
       <c r="L142" s="5" t="inlineStr">
         <is>
-          <t>Белорусский → метро до Комсомольской (~15 мин) → электричка + такси (08:47 РЭКС → 10:28)</t>
-        </is>
-      </c>
-      <c r="M142" s="5" t="inlineStr">
-        <is>
-          <t>~10:45</t>
-        </is>
-      </c>
+          <t>Электричка 18:43 → Казанский → метро до Белорусской</t>
+        </is>
+      </c>
+      <c r="M142" s="5" t="inlineStr"/>
       <c r="N142" s="5" t="inlineStr"/>
       <c r="O142" s="20" t="inlineStr">
         <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2000170&amp;nnst2=2000000</t>
-        </is>
-      </c>
-      <c r="P142" s="5" t="inlineStr">
-        <is>
-          <t>Ночной поезд</t>
-        </is>
-      </c>
-      <c r="Q142" s="5" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
-      </c>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2000170</t>
+        </is>
+      </c>
+      <c r="P142" s="5" t="inlineStr"/>
+      <c r="Q142" s="5" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
@@ -15019,34 +15043,34 @@
       <c r="B143" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C143" s="7" t="inlineStr">
+      <c r="C143" s="10" t="inlineStr">
         <is>
           <t>Обратно</t>
         </is>
       </c>
-      <c r="D143" s="7" t="inlineStr">
-        <is>
-          <t>Самый дешёвый</t>
-        </is>
-      </c>
-      <c r="E143" s="7" t="inlineStr">
+      <c r="D143" s="10" t="inlineStr">
+        <is>
+          <t>Удобный</t>
+        </is>
+      </c>
+      <c r="E143" s="10" t="inlineStr">
         <is>
           <t>Поезд, купе</t>
         </is>
       </c>
-      <c r="F143" s="7" t="inlineStr">
-        <is>
-          <t>027Б</t>
+      <c r="F143" s="10" t="inlineStr">
+        <is>
+          <t>007М</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>30.10 23:30</t>
+          <t>30.10 22:12</t>
         </is>
       </c>
       <c r="H143" s="5" t="inlineStr">
         <is>
-          <t>31.10 04:39</t>
+          <t>31.10 02:39</t>
         </is>
       </c>
       <c r="I143" s="5" t="inlineStr">
@@ -15054,11 +15078,11 @@
           <t>Смоленск</t>
         </is>
       </c>
-      <c r="J143" s="6" t="n">
-        <v>4022</v>
-      </c>
-      <c r="K143" s="6" t="n">
-        <v>4022</v>
+      <c r="J143" s="9" t="n">
+        <v>4656</v>
+      </c>
+      <c r="K143" s="9" t="n">
+        <v>4656</v>
       </c>
       <c r="L143" s="5" t="inlineStr">
         <is>
@@ -15072,154 +15096,154 @@
           <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2000170</t>
         </is>
       </c>
-      <c r="P143" s="5" t="inlineStr"/>
+      <c r="P143" s="5" t="inlineStr">
+        <is>
+          <t>Или машина ~520 км, ~7 ч</t>
+        </is>
+      </c>
       <c r="Q143" s="5" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="5" t="inlineStr">
-        <is>
-          <t>Смоленск</t>
-        </is>
-      </c>
-      <c r="B144" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C144" s="10" t="inlineStr">
-        <is>
-          <t>Обратно</t>
-        </is>
-      </c>
-      <c r="D144" s="10" t="inlineStr">
+      <c r="A144" s="15" t="inlineStr">
+        <is>
+          <t>Тверь</t>
+        </is>
+      </c>
+      <c r="B144" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C144" s="17" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D144" s="17" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E144" s="17" t="inlineStr">
+        <is>
+          <t>Поезд «Аврора», сидячий</t>
+        </is>
+      </c>
+      <c r="F144" s="17" t="inlineStr">
+        <is>
+          <t>741У</t>
+        </is>
+      </c>
+      <c r="G144" s="16" t="inlineStr">
+        <is>
+          <t>28.10 10:16</t>
+        </is>
+      </c>
+      <c r="H144" s="16" t="inlineStr">
+        <is>
+          <t>28.10 11:55</t>
+        </is>
+      </c>
+      <c r="I144" s="16" t="inlineStr">
+        <is>
+          <t>Москва, Ленинградский</t>
+        </is>
+      </c>
+      <c r="J144" s="18" t="n">
+        <v>695</v>
+      </c>
+      <c r="K144" s="18" t="n">
+        <v>695</v>
+      </c>
+      <c r="L144" s="16" t="inlineStr">
+        <is>
+          <t>Ленинградский вокзал → через площадь на Казанский (5 мин) → электричка + такси (12:54 → 15:15)</t>
+        </is>
+      </c>
+      <c r="M144" s="16" t="inlineStr">
+        <is>
+          <t>~15:30</t>
+        </is>
+      </c>
+      <c r="N144" s="16" t="inlineStr"/>
+      <c r="O144" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2004600&amp;nnst2=2000000</t>
+        </is>
+      </c>
+      <c r="P144" s="16" t="inlineStr">
+        <is>
+          <t>Также Ласточка 723Р 09:19→11:13, 611 ₽</t>
+        </is>
+      </c>
+      <c r="Q144" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="inlineStr">
+        <is>
+          <t>Тверь</t>
+        </is>
+      </c>
+      <c r="B145" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C145" s="10" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D145" s="10" t="inlineStr">
         <is>
           <t>Удобный</t>
         </is>
       </c>
-      <c r="E144" s="10" t="inlineStr">
-        <is>
-          <t>Поезд, купе</t>
-        </is>
-      </c>
-      <c r="F144" s="10" t="inlineStr">
-        <is>
-          <t>007М</t>
-        </is>
-      </c>
-      <c r="G144" s="5" t="inlineStr">
-        <is>
-          <t>30.10 22:12</t>
-        </is>
-      </c>
-      <c r="H144" s="5" t="inlineStr">
-        <is>
-          <t>31.10 02:39</t>
-        </is>
-      </c>
-      <c r="I144" s="5" t="inlineStr">
-        <is>
-          <t>Смоленск</t>
-        </is>
-      </c>
-      <c r="J144" s="9" t="n">
-        <v>4656</v>
-      </c>
-      <c r="K144" s="9" t="n">
-        <v>4656</v>
-      </c>
-      <c r="L144" s="5" t="inlineStr">
-        <is>
-          <t>Электричка 18:43 → Казанский → метро до Белорусской</t>
-        </is>
-      </c>
-      <c r="M144" s="5" t="inlineStr"/>
-      <c r="N144" s="5" t="inlineStr"/>
-      <c r="O144" s="20" t="inlineStr">
-        <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2000170</t>
-        </is>
-      </c>
-      <c r="P144" s="5" t="inlineStr">
-        <is>
-          <t>Или машина ~520 км, ~7 ч</t>
-        </is>
-      </c>
-      <c r="Q144" s="5" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="15" t="inlineStr">
-        <is>
-          <t>Тверь</t>
-        </is>
-      </c>
-      <c r="B145" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C145" s="17" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D145" s="17" t="inlineStr">
-        <is>
-          <t>Самый дешёвый</t>
-        </is>
-      </c>
-      <c r="E145" s="17" t="inlineStr">
-        <is>
-          <t>Поезд «Аврора», сидячий</t>
-        </is>
-      </c>
-      <c r="F145" s="17" t="inlineStr">
-        <is>
-          <t>741У</t>
-        </is>
-      </c>
-      <c r="G145" s="16" t="inlineStr">
-        <is>
-          <t>28.10 10:16</t>
-        </is>
-      </c>
-      <c r="H145" s="16" t="inlineStr">
-        <is>
-          <t>28.10 11:55</t>
-        </is>
-      </c>
-      <c r="I145" s="16" t="inlineStr">
-        <is>
-          <t>Москва, Ленинградский</t>
-        </is>
-      </c>
-      <c r="J145" s="18" t="n">
-        <v>695</v>
-      </c>
-      <c r="K145" s="18" t="n">
-        <v>695</v>
-      </c>
-      <c r="L145" s="16" t="inlineStr">
-        <is>
-          <t>Ленинградский вокзал → через площадь на Казанский (5 мин) → электричка + такси (12:54 → 15:15)</t>
-        </is>
-      </c>
-      <c r="M145" s="16" t="inlineStr">
-        <is>
-          <t>~15:30</t>
-        </is>
-      </c>
-      <c r="N145" s="16" t="inlineStr"/>
-      <c r="O145" s="19" t="inlineStr">
-        <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2004600&amp;nnst2=2000000</t>
-        </is>
-      </c>
-      <c r="P145" s="16" t="inlineStr">
-        <is>
-          <t>Также Ласточка 723Р 09:19→11:13, 611 ₽</t>
-        </is>
-      </c>
-      <c r="Q145" s="16" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
-      </c>
+      <c r="E145" s="10" t="inlineStr">
+        <is>
+          <t>Своя машина</t>
+        </is>
+      </c>
+      <c r="F145" s="10" t="inlineStr"/>
+      <c r="G145" s="5" t="inlineStr">
+        <is>
+          <t>28.10 ~09:30</t>
+        </is>
+      </c>
+      <c r="H145" s="5" t="inlineStr">
+        <is>
+          <t>28.10 ~13:30</t>
+        </is>
+      </c>
+      <c r="I145" s="5" t="inlineStr">
+        <is>
+          <t>Коломна</t>
+        </is>
+      </c>
+      <c r="J145" s="9" t="n">
+        <v>1885</v>
+      </c>
+      <c r="K145" s="9" t="n">
+        <v>1885</v>
+      </c>
+      <c r="L145" s="5" t="inlineStr">
+        <is>
+          <t>~290 км через ЦКАД, ~4 ч</t>
+        </is>
+      </c>
+      <c r="M145" s="5" t="inlineStr">
+        <is>
+          <t>~13:30</t>
+        </is>
+      </c>
+      <c r="N145" s="5" t="inlineStr"/>
+      <c r="O145" s="5" t="inlineStr"/>
+      <c r="P145" s="5" t="inlineStr">
+        <is>
+          <t>Топливо ~3 770 ₽ туда-обратно на машину</t>
+        </is>
+      </c>
+      <c r="Q145" s="5" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
@@ -15230,211 +15254,211 @@
       <c r="B146" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C146" s="10" t="inlineStr">
+      <c r="C146" s="7" t="inlineStr">
+        <is>
+          <t>Обратно</t>
+        </is>
+      </c>
+      <c r="D146" s="7" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E146" s="7" t="inlineStr">
+        <is>
+          <t>Поезд «Аврора», сидячий</t>
+        </is>
+      </c>
+      <c r="F146" s="7" t="inlineStr">
+        <is>
+          <t>750У</t>
+        </is>
+      </c>
+      <c r="G146" s="5" t="inlineStr">
+        <is>
+          <t>30.10 22:30</t>
+        </is>
+      </c>
+      <c r="H146" s="5" t="inlineStr">
+        <is>
+          <t>31.10 ~00:05</t>
+        </is>
+      </c>
+      <c r="I146" s="5" t="inlineStr">
+        <is>
+          <t>Тверь</t>
+        </is>
+      </c>
+      <c r="J146" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K146" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L146" s="5" t="inlineStr">
+        <is>
+          <t>Электричка 18:43 → Казанский 20:47 → Ленинградский</t>
+        </is>
+      </c>
+      <c r="M146" s="5" t="inlineStr"/>
+      <c r="N146" s="5" t="inlineStr"/>
+      <c r="O146" s="20" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2004600</t>
+        </is>
+      </c>
+      <c r="P146" s="5" t="inlineStr">
+        <is>
+          <t>Цена ориентировочная, проверить</t>
+        </is>
+      </c>
+      <c r="Q146" s="5" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="15" t="inlineStr">
+        <is>
+          <t>Рязань</t>
+        </is>
+      </c>
+      <c r="B147" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C147" s="17" t="inlineStr">
         <is>
           <t>В1: к 15:00 28.10</t>
         </is>
       </c>
-      <c r="D146" s="10" t="inlineStr">
+      <c r="D147" s="17" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E147" s="17" t="inlineStr">
+        <is>
+          <t>Электричка «Стандарт плюс»</t>
+        </is>
+      </c>
+      <c r="F147" s="17" t="inlineStr">
+        <is>
+          <t>6993</t>
+        </is>
+      </c>
+      <c r="G147" s="16" t="inlineStr">
+        <is>
+          <t>28.10 05:18</t>
+        </is>
+      </c>
+      <c r="H147" s="16" t="inlineStr">
+        <is>
+          <t>28.10 06:54</t>
+        </is>
+      </c>
+      <c r="I147" s="16" t="inlineStr">
+        <is>
+          <t>Коломна</t>
+        </is>
+      </c>
+      <c r="J147" s="18" t="n">
+        <v>306</v>
+      </c>
+      <c r="K147" s="18" t="n">
+        <v>306</v>
+      </c>
+      <c r="L147" s="16" t="inlineStr">
+        <is>
+          <t>Ст. Коломна → такси 10 мин (~300 ₽)</t>
+        </is>
+      </c>
+      <c r="M147" s="16" t="inlineStr">
+        <is>
+          <t>~07:10</t>
+        </is>
+      </c>
+      <c r="N147" s="16" t="inlineStr">
+        <is>
+          <t>ранний заезд</t>
+        </is>
+      </c>
+      <c r="O147" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/rasp.php?st1=92502&amp;st2=11902&amp;date=28.10.2026</t>
+        </is>
+      </c>
+      <c r="P147" s="16" t="inlineStr">
+        <is>
+          <t>Следующая электричка только 14:36 (→16:17) — к экскурсии не успевает</t>
+        </is>
+      </c>
+      <c r="Q147" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="5" t="inlineStr">
+        <is>
+          <t>Рязань</t>
+        </is>
+      </c>
+      <c r="B148" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C148" s="10" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D148" s="10" t="inlineStr">
         <is>
           <t>Удобный</t>
         </is>
       </c>
-      <c r="E146" s="10" t="inlineStr">
+      <c r="E148" s="10" t="inlineStr">
         <is>
           <t>Своя машина</t>
         </is>
       </c>
-      <c r="F146" s="10" t="inlineStr"/>
-      <c r="G146" s="5" t="inlineStr">
-        <is>
-          <t>28.10 ~09:30</t>
-        </is>
-      </c>
-      <c r="H146" s="5" t="inlineStr">
-        <is>
-          <t>28.10 ~13:30</t>
-        </is>
-      </c>
-      <c r="I146" s="5" t="inlineStr">
+      <c r="F148" s="10" t="inlineStr"/>
+      <c r="G148" s="5" t="inlineStr">
+        <is>
+          <t>28.10 ~12:30</t>
+        </is>
+      </c>
+      <c r="H148" s="5" t="inlineStr">
+        <is>
+          <t>28.10 ~14:00</t>
+        </is>
+      </c>
+      <c r="I148" s="5" t="inlineStr">
         <is>
           <t>Коломна</t>
         </is>
       </c>
-      <c r="J146" s="9" t="n">
-        <v>1885</v>
-      </c>
-      <c r="K146" s="9" t="n">
-        <v>1885</v>
-      </c>
-      <c r="L146" s="5" t="inlineStr">
-        <is>
-          <t>~290 км через ЦКАД, ~4 ч</t>
-        </is>
-      </c>
-      <c r="M146" s="5" t="inlineStr">
-        <is>
-          <t>~13:30</t>
-        </is>
-      </c>
-      <c r="N146" s="5" t="inlineStr"/>
-      <c r="O146" s="5" t="inlineStr"/>
-      <c r="P146" s="5" t="inlineStr">
-        <is>
-          <t>Топливо ~3 770 ₽ туда-обратно на машину</t>
-        </is>
-      </c>
-      <c r="Q146" s="5" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="5" t="inlineStr">
-        <is>
-          <t>Тверь</t>
-        </is>
-      </c>
-      <c r="B147" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C147" s="7" t="inlineStr">
-        <is>
-          <t>Обратно</t>
-        </is>
-      </c>
-      <c r="D147" s="7" t="inlineStr">
-        <is>
-          <t>Самый дешёвый</t>
-        </is>
-      </c>
-      <c r="E147" s="7" t="inlineStr">
-        <is>
-          <t>Поезд «Аврора», сидячий</t>
-        </is>
-      </c>
-      <c r="F147" s="7" t="inlineStr">
-        <is>
-          <t>750У</t>
-        </is>
-      </c>
-      <c r="G147" s="5" t="inlineStr">
-        <is>
-          <t>30.10 22:30</t>
-        </is>
-      </c>
-      <c r="H147" s="5" t="inlineStr">
-        <is>
-          <t>31.10 ~00:05</t>
-        </is>
-      </c>
-      <c r="I147" s="5" t="inlineStr">
-        <is>
-          <t>Тверь</t>
-        </is>
-      </c>
-      <c r="J147" s="6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K147" s="6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L147" s="5" t="inlineStr">
-        <is>
-          <t>Электричка 18:43 → Казанский 20:47 → Ленинградский</t>
-        </is>
-      </c>
-      <c r="M147" s="5" t="inlineStr"/>
-      <c r="N147" s="5" t="inlineStr"/>
-      <c r="O147" s="20" t="inlineStr">
-        <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2004600</t>
-        </is>
-      </c>
-      <c r="P147" s="5" t="inlineStr">
-        <is>
-          <t>Цена ориентировочная, проверить</t>
-        </is>
-      </c>
-      <c r="Q147" s="5" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="15" t="inlineStr">
-        <is>
-          <t>Рязань</t>
-        </is>
-      </c>
-      <c r="B148" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C148" s="17" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D148" s="17" t="inlineStr">
-        <is>
-          <t>Самый дешёвый</t>
-        </is>
-      </c>
-      <c r="E148" s="17" t="inlineStr">
-        <is>
-          <t>Электричка «Стандарт плюс»</t>
-        </is>
-      </c>
-      <c r="F148" s="17" t="inlineStr">
-        <is>
-          <t>6993</t>
-        </is>
-      </c>
-      <c r="G148" s="16" t="inlineStr">
-        <is>
-          <t>28.10 05:18</t>
-        </is>
-      </c>
-      <c r="H148" s="16" t="inlineStr">
-        <is>
-          <t>28.10 06:54</t>
-        </is>
-      </c>
-      <c r="I148" s="16" t="inlineStr">
-        <is>
-          <t>Коломна</t>
-        </is>
-      </c>
-      <c r="J148" s="18" t="n">
-        <v>306</v>
-      </c>
-      <c r="K148" s="18" t="n">
-        <v>306</v>
-      </c>
-      <c r="L148" s="16" t="inlineStr">
-        <is>
-          <t>Ст. Коломна → такси 10 мин (~300 ₽)</t>
-        </is>
-      </c>
-      <c r="M148" s="16" t="inlineStr">
-        <is>
-          <t>~07:10</t>
-        </is>
-      </c>
-      <c r="N148" s="16" t="inlineStr">
-        <is>
-          <t>ранний заезд</t>
-        </is>
-      </c>
-      <c r="O148" s="19" t="inlineStr">
-        <is>
-          <t>https://www.tutu.ru/rasp.php?st1=92502&amp;st2=11902&amp;date=28.10.2026</t>
-        </is>
-      </c>
-      <c r="P148" s="16" t="inlineStr">
-        <is>
-          <t>Следующая электричка только 14:36 (→16:17) — к экскурсии не успевает</t>
-        </is>
-      </c>
-      <c r="Q148" s="16" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
-      </c>
+      <c r="J148" s="9" t="n">
+        <v>650</v>
+      </c>
+      <c r="K148" s="9" t="n">
+        <v>650</v>
+      </c>
+      <c r="L148" s="5" t="inlineStr">
+        <is>
+          <t>~100 км, ~1 ч 30 мин</t>
+        </is>
+      </c>
+      <c r="M148" s="5" t="inlineStr">
+        <is>
+          <t>~14:00</t>
+        </is>
+      </c>
+      <c r="N148" s="5" t="inlineStr"/>
+      <c r="O148" s="5" t="inlineStr"/>
+      <c r="P148" s="5" t="inlineStr">
+        <is>
+          <t>Топливо ~1 300 ₽ туда-обратно</t>
+        </is>
+      </c>
+      <c r="Q148" s="5" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
@@ -15445,199 +15469,199 @@
       <c r="B149" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C149" s="10" t="inlineStr">
+      <c r="C149" s="7" t="inlineStr">
+        <is>
+          <t>Обратно</t>
+        </is>
+      </c>
+      <c r="D149" s="7" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E149" s="7" t="inlineStr">
+        <is>
+          <t>Электричка «Стандарт плюс»</t>
+        </is>
+      </c>
+      <c r="F149" s="7" t="inlineStr">
+        <is>
+          <t>6996</t>
+        </is>
+      </c>
+      <c r="G149" s="5" t="inlineStr">
+        <is>
+          <t>30.10 21:16</t>
+        </is>
+      </c>
+      <c r="H149" s="5" t="inlineStr">
+        <is>
+          <t>30.10 22:49</t>
+        </is>
+      </c>
+      <c r="I149" s="5" t="inlineStr">
+        <is>
+          <t>Рязань-1</t>
+        </is>
+      </c>
+      <c r="J149" s="6" t="n">
+        <v>306</v>
+      </c>
+      <c r="K149" s="6" t="n">
+        <v>306</v>
+      </c>
+      <c r="L149" s="5" t="inlineStr">
+        <is>
+          <t>Такси до ст. Коломна (~300 ₽)</t>
+        </is>
+      </c>
+      <c r="M149" s="5" t="inlineStr"/>
+      <c r="N149" s="5" t="inlineStr"/>
+      <c r="O149" s="20" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/rasp.php?st1=11902&amp;st2=92502&amp;date=30.10.2026</t>
+        </is>
+      </c>
+      <c r="P149" s="5" t="inlineStr"/>
+      <c r="Q149" s="5" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="15" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="B150" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C150" s="17" t="inlineStr">
         <is>
           <t>В1: к 15:00 28.10</t>
         </is>
       </c>
-      <c r="D149" s="10" t="inlineStr">
+      <c r="D150" s="17" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E150" s="17" t="inlineStr">
+        <is>
+          <t>Электричка / РЭКС</t>
+        </is>
+      </c>
+      <c r="F150" s="17" t="inlineStr"/>
+      <c r="G150" s="16" t="inlineStr">
+        <is>
+          <t>28.10 09:48 или 12:54</t>
+        </is>
+      </c>
+      <c r="H150" s="16" t="inlineStr">
+        <is>
+          <t>11:36 / 15:15</t>
+        </is>
+      </c>
+      <c r="I150" s="16" t="inlineStr">
+        <is>
+          <t>Коломна</t>
+        </is>
+      </c>
+      <c r="J150" s="18" t="n">
+        <v>490</v>
+      </c>
+      <c r="K150" s="18" t="n">
+        <v>490</v>
+      </c>
+      <c r="L150" s="16" t="inlineStr">
+        <is>
+          <t>Казанский вокзал → электричка до ст. Коломна (490–620 ₽) + такси 10 мин (~300 ₽)</t>
+        </is>
+      </c>
+      <c r="M150" s="16" t="inlineStr">
+        <is>
+          <t>~12:00 / ~15:30</t>
+        </is>
+      </c>
+      <c r="N150" s="16" t="inlineStr"/>
+      <c r="O150" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/prigorod/</t>
+        </is>
+      </c>
+      <c r="P150" s="16" t="inlineStr">
+        <is>
+          <t>РЭКС 620 ₽</t>
+        </is>
+      </c>
+      <c r="Q150" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="5" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="B151" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C151" s="10" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D151" s="10" t="inlineStr">
         <is>
           <t>Удобный</t>
         </is>
       </c>
-      <c r="E149" s="10" t="inlineStr">
+      <c r="E151" s="10" t="inlineStr">
         <is>
           <t>Своя машина</t>
         </is>
       </c>
-      <c r="F149" s="10" t="inlineStr"/>
-      <c r="G149" s="5" t="inlineStr">
-        <is>
-          <t>28.10 ~12:30</t>
-        </is>
-      </c>
-      <c r="H149" s="5" t="inlineStr">
+      <c r="F151" s="10" t="inlineStr"/>
+      <c r="G151" s="5" t="inlineStr">
+        <is>
+          <t>28.10 ~12:00</t>
+        </is>
+      </c>
+      <c r="H151" s="5" t="inlineStr">
         <is>
           <t>28.10 ~14:00</t>
         </is>
       </c>
-      <c r="I149" s="5" t="inlineStr">
+      <c r="I151" s="5" t="inlineStr">
         <is>
           <t>Коломна</t>
         </is>
       </c>
-      <c r="J149" s="9" t="n">
-        <v>650</v>
-      </c>
-      <c r="K149" s="9" t="n">
-        <v>650</v>
-      </c>
-      <c r="L149" s="5" t="inlineStr">
-        <is>
-          <t>~100 км, ~1 ч 30 мин</t>
-        </is>
-      </c>
-      <c r="M149" s="5" t="inlineStr">
+      <c r="J151" s="9" t="n">
+        <v>750</v>
+      </c>
+      <c r="K151" s="9" t="n">
+        <v>750</v>
+      </c>
+      <c r="L151" s="5" t="inlineStr">
+        <is>
+          <t>~115 км по Новорязанскому ш., ~2 ч с пробками</t>
+        </is>
+      </c>
+      <c r="M151" s="5" t="inlineStr">
         <is>
           <t>~14:00</t>
         </is>
       </c>
-      <c r="N149" s="5" t="inlineStr"/>
-      <c r="O149" s="5" t="inlineStr"/>
-      <c r="P149" s="5" t="inlineStr">
-        <is>
-          <t>Топливо ~1 300 ₽ туда-обратно</t>
-        </is>
-      </c>
-      <c r="Q149" s="5" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="5" t="inlineStr">
-        <is>
-          <t>Рязань</t>
-        </is>
-      </c>
-      <c r="B150" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C150" s="7" t="inlineStr">
-        <is>
-          <t>Обратно</t>
-        </is>
-      </c>
-      <c r="D150" s="7" t="inlineStr">
-        <is>
-          <t>Самый дешёвый</t>
-        </is>
-      </c>
-      <c r="E150" s="7" t="inlineStr">
-        <is>
-          <t>Электричка «Стандарт плюс»</t>
-        </is>
-      </c>
-      <c r="F150" s="7" t="inlineStr">
-        <is>
-          <t>6996</t>
-        </is>
-      </c>
-      <c r="G150" s="5" t="inlineStr">
-        <is>
-          <t>30.10 21:16</t>
-        </is>
-      </c>
-      <c r="H150" s="5" t="inlineStr">
-        <is>
-          <t>30.10 22:49</t>
-        </is>
-      </c>
-      <c r="I150" s="5" t="inlineStr">
-        <is>
-          <t>Рязань-1</t>
-        </is>
-      </c>
-      <c r="J150" s="6" t="n">
-        <v>306</v>
-      </c>
-      <c r="K150" s="6" t="n">
-        <v>306</v>
-      </c>
-      <c r="L150" s="5" t="inlineStr">
-        <is>
-          <t>Такси до ст. Коломна (~300 ₽)</t>
-        </is>
-      </c>
-      <c r="M150" s="5" t="inlineStr"/>
-      <c r="N150" s="5" t="inlineStr"/>
-      <c r="O150" s="20" t="inlineStr">
-        <is>
-          <t>https://www.tutu.ru/rasp.php?st1=11902&amp;st2=92502&amp;date=30.10.2026</t>
-        </is>
-      </c>
-      <c r="P150" s="5" t="inlineStr"/>
-      <c r="Q150" s="5" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="15" t="inlineStr">
-        <is>
-          <t>Москва</t>
-        </is>
-      </c>
-      <c r="B151" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="C151" s="17" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D151" s="17" t="inlineStr">
-        <is>
-          <t>Самый дешёвый</t>
-        </is>
-      </c>
-      <c r="E151" s="17" t="inlineStr">
-        <is>
-          <t>Электричка / РЭКС</t>
-        </is>
-      </c>
-      <c r="F151" s="17" t="inlineStr"/>
-      <c r="G151" s="16" t="inlineStr">
-        <is>
-          <t>28.10 09:48 или 12:54</t>
-        </is>
-      </c>
-      <c r="H151" s="16" t="inlineStr">
-        <is>
-          <t>11:36 / 15:15</t>
-        </is>
-      </c>
-      <c r="I151" s="16" t="inlineStr">
-        <is>
-          <t>Коломна</t>
-        </is>
-      </c>
-      <c r="J151" s="18" t="n">
-        <v>490</v>
-      </c>
-      <c r="K151" s="18" t="n">
-        <v>490</v>
-      </c>
-      <c r="L151" s="16" t="inlineStr">
-        <is>
-          <t>Казанский вокзал → электричка до ст. Коломна (490–620 ₽) + такси 10 мин (~300 ₽)</t>
-        </is>
-      </c>
-      <c r="M151" s="16" t="inlineStr">
-        <is>
-          <t>~12:00 / ~15:30</t>
-        </is>
-      </c>
-      <c r="N151" s="16" t="inlineStr"/>
-      <c r="O151" s="19" t="inlineStr">
-        <is>
-          <t>https://www.tutu.ru/prigorod/</t>
-        </is>
-      </c>
-      <c r="P151" s="16" t="inlineStr">
-        <is>
-          <t>РЭКС 620 ₽</t>
-        </is>
-      </c>
-      <c r="Q151" s="16" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
-      </c>
+      <c r="N151" s="5" t="inlineStr"/>
+      <c r="O151" s="5" t="inlineStr"/>
+      <c r="P151" s="5" t="inlineStr">
+        <is>
+          <t>Топливо ~1 500 ₽ туда-обратно</t>
+        </is>
+      </c>
+      <c r="Q151" s="5" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
@@ -15648,127 +15672,139 @@
       <c r="B152" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C152" s="10" t="inlineStr">
+      <c r="C152" s="7" t="inlineStr">
+        <is>
+          <t>Обратно</t>
+        </is>
+      </c>
+      <c r="D152" s="7" t="inlineStr">
+        <is>
+          <t>Самый дешёвый = Удобный</t>
+        </is>
+      </c>
+      <c r="E152" s="7" t="inlineStr">
+        <is>
+          <t>Электричка или машина</t>
+        </is>
+      </c>
+      <c r="F152" s="7" t="inlineStr"/>
+      <c r="G152" s="5" t="inlineStr">
+        <is>
+          <t>30.10 18:43</t>
+        </is>
+      </c>
+      <c r="H152" s="5" t="inlineStr">
+        <is>
+          <t>30.10 20:47</t>
+        </is>
+      </c>
+      <c r="I152" s="5" t="inlineStr">
+        <is>
+          <t>Москва, Казанский</t>
+        </is>
+      </c>
+      <c r="J152" s="6" t="n">
+        <v>490</v>
+      </c>
+      <c r="K152" s="6" t="n">
+        <v>490</v>
+      </c>
+      <c r="L152" s="5" t="inlineStr">
+        <is>
+          <t>Электричка 18:43 → 20:47</t>
+        </is>
+      </c>
+      <c r="M152" s="5" t="inlineStr"/>
+      <c r="N152" s="5" t="inlineStr"/>
+      <c r="O152" s="20" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/prigorod/</t>
+        </is>
+      </c>
+      <c r="P152" s="5" t="inlineStr"/>
+      <c r="Q152" s="5" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="15" t="inlineStr">
+        <is>
+          <t>Пенза</t>
+        </is>
+      </c>
+      <c r="B153" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C153" s="16" t="inlineStr">
         <is>
           <t>В1: к 15:00 28.10</t>
         </is>
       </c>
-      <c r="D152" s="10" t="inlineStr">
-        <is>
-          <t>Удобный</t>
-        </is>
-      </c>
-      <c r="E152" s="10" t="inlineStr">
-        <is>
-          <t>Своя машина</t>
-        </is>
-      </c>
-      <c r="F152" s="10" t="inlineStr"/>
-      <c r="G152" s="5" t="inlineStr">
-        <is>
-          <t>28.10 ~12:00</t>
-        </is>
-      </c>
-      <c r="H152" s="5" t="inlineStr">
-        <is>
-          <t>28.10 ~14:00</t>
-        </is>
-      </c>
-      <c r="I152" s="5" t="inlineStr">
-        <is>
-          <t>Коломна</t>
-        </is>
-      </c>
-      <c r="J152" s="9" t="n">
-        <v>750</v>
-      </c>
-      <c r="K152" s="9" t="n">
-        <v>750</v>
-      </c>
-      <c r="L152" s="5" t="inlineStr">
-        <is>
-          <t>~115 км по Новорязанскому ш., ~2 ч с пробками</t>
-        </is>
-      </c>
-      <c r="M152" s="5" t="inlineStr">
-        <is>
-          <t>~14:00</t>
-        </is>
-      </c>
-      <c r="N152" s="5" t="inlineStr"/>
-      <c r="O152" s="5" t="inlineStr"/>
-      <c r="P152" s="5" t="inlineStr">
-        <is>
-          <t>Топливо ~1 500 ₽ туда-обратно</t>
-        </is>
-      </c>
-      <c r="Q152" s="5" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="5" t="inlineStr">
-        <is>
-          <t>Москва</t>
-        </is>
-      </c>
-      <c r="B153" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C153" s="7" t="inlineStr">
-        <is>
-          <t>Обратно</t>
-        </is>
-      </c>
-      <c r="D153" s="7" t="inlineStr">
-        <is>
-          <t>Самый дешёвый = Удобный</t>
-        </is>
-      </c>
-      <c r="E153" s="7" t="inlineStr">
-        <is>
-          <t>Электричка или машина</t>
-        </is>
-      </c>
-      <c r="F153" s="7" t="inlineStr"/>
-      <c r="G153" s="5" t="inlineStr">
-        <is>
-          <t>30.10 18:43</t>
-        </is>
-      </c>
-      <c r="H153" s="5" t="inlineStr">
-        <is>
-          <t>30.10 20:47</t>
-        </is>
-      </c>
-      <c r="I153" s="5" t="inlineStr">
+      <c r="D153" s="16" t="inlineStr">
+        <is>
+          <t>Альтернатива: поезд</t>
+        </is>
+      </c>
+      <c r="E153" s="16" t="inlineStr">
+        <is>
+          <t>Поезд «Сура», купе (сидячий 3 030)</t>
+        </is>
+      </c>
+      <c r="F153" s="16" t="inlineStr">
+        <is>
+          <t>052М</t>
+        </is>
+      </c>
+      <c r="G153" s="16" t="inlineStr">
+        <is>
+          <t>27.10 21:35</t>
+        </is>
+      </c>
+      <c r="H153" s="16" t="inlineStr">
+        <is>
+          <t>28.10 07:59</t>
+        </is>
+      </c>
+      <c r="I153" s="16" t="inlineStr">
         <is>
           <t>Москва, Казанский</t>
         </is>
       </c>
-      <c r="J153" s="6" t="n">
-        <v>490</v>
-      </c>
-      <c r="K153" s="6" t="n">
-        <v>490</v>
-      </c>
-      <c r="L153" s="5" t="inlineStr">
-        <is>
-          <t>Электричка 18:43 → 20:47</t>
-        </is>
-      </c>
-      <c r="M153" s="5" t="inlineStr"/>
-      <c r="N153" s="5" t="inlineStr"/>
-      <c r="O153" s="20" t="inlineStr">
-        <is>
-          <t>https://www.tutu.ru/prigorod/</t>
-        </is>
-      </c>
-      <c r="P153" s="5" t="inlineStr"/>
-      <c r="Q153" s="5" t="inlineStr"/>
+      <c r="J153" s="24" t="n">
+        <v>3967</v>
+      </c>
+      <c r="K153" s="24" t="n">
+        <v>3967</v>
+      </c>
+      <c r="L153" s="16" t="inlineStr">
+        <is>
+          <t>Казанский вокзал → электричка до ст. Коломна (490–620 ₽) + такси 10 мин (~300 ₽) (09:48 → 11:36)</t>
+        </is>
+      </c>
+      <c r="M153" s="16" t="inlineStr">
+        <is>
+          <t>~12:00</t>
+        </is>
+      </c>
+      <c r="N153" s="16" t="inlineStr"/>
+      <c r="O153" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2024120&amp;nnst2=2000000</t>
+        </is>
+      </c>
+      <c r="P153" s="16" t="inlineStr">
+        <is>
+          <t>Основной вариант — машина (лист «Авто»)</t>
+        </is>
+      </c>
+      <c r="Q153" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="15" t="inlineStr">
         <is>
-          <t>Пенза</t>
+          <t>Саранск</t>
         </is>
       </c>
       <c r="B154" s="16" t="n">
@@ -15786,22 +15822,22 @@
       </c>
       <c r="E154" s="16" t="inlineStr">
         <is>
-          <t>Поезд «Сура», купе (сидячий 3 030)</t>
+          <t>Поезд, купе</t>
         </is>
       </c>
       <c r="F154" s="16" t="inlineStr">
         <is>
-          <t>052М</t>
+          <t>041Й</t>
         </is>
       </c>
       <c r="G154" s="16" t="inlineStr">
         <is>
-          <t>27.10 21:35</t>
+          <t>27.10 20:40</t>
         </is>
       </c>
       <c r="H154" s="16" t="inlineStr">
         <is>
-          <t>28.10 07:59</t>
+          <t>28.10 05:50</t>
         </is>
       </c>
       <c r="I154" s="16" t="inlineStr">
@@ -15810,30 +15846,34 @@
         </is>
       </c>
       <c r="J154" s="24" t="n">
-        <v>3967</v>
+        <v>4394</v>
       </c>
       <c r="K154" s="24" t="n">
-        <v>3967</v>
+        <v>4394</v>
       </c>
       <c r="L154" s="16" t="inlineStr">
         <is>
-          <t>Казанский вокзал → электричка до ст. Коломна (490–620 ₽) + такси 10 мин (~300 ₽) (09:48 → 11:36)</t>
+          <t>Казанский вокзал → электричка до ст. Коломна (490–620 ₽) + такси 10 мин (~300 ₽) (07:22 → 09:15)</t>
         </is>
       </c>
       <c r="M154" s="16" t="inlineStr">
         <is>
-          <t>~12:00</t>
-        </is>
-      </c>
-      <c r="N154" s="16" t="inlineStr"/>
+          <t>~09:30</t>
+        </is>
+      </c>
+      <c r="N154" s="16" t="inlineStr">
+        <is>
+          <t>ранний заезд</t>
+        </is>
+      </c>
       <c r="O154" s="19" t="inlineStr">
         <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2024120&amp;nnst2=2000000</t>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2024700&amp;nnst2=2000000</t>
         </is>
       </c>
       <c r="P154" s="16" t="inlineStr">
         <is>
-          <t>Основной вариант — машина (лист «Авто»)</t>
+          <t>Основной вариант — машина</t>
         </is>
       </c>
       <c r="Q154" s="16" t="inlineStr">
@@ -15845,7 +15885,7 @@
     <row r="155">
       <c r="A155" s="15" t="inlineStr">
         <is>
-          <t>Саранск</t>
+          <t>Тамбов</t>
         </is>
       </c>
       <c r="B155" s="16" t="n">
@@ -15863,58 +15903,54 @@
       </c>
       <c r="E155" s="16" t="inlineStr">
         <is>
-          <t>Поезд, купе</t>
+          <t>Поезд, сидячий (купе 2 868)</t>
         </is>
       </c>
       <c r="F155" s="16" t="inlineStr">
         <is>
-          <t>041Й</t>
+          <t>135Ж</t>
         </is>
       </c>
       <c r="G155" s="16" t="inlineStr">
         <is>
-          <t>27.10 20:40</t>
+          <t>27.10 21:56</t>
         </is>
       </c>
       <c r="H155" s="16" t="inlineStr">
         <is>
-          <t>28.10 05:50</t>
+          <t>28.10 07:22</t>
         </is>
       </c>
       <c r="I155" s="16" t="inlineStr">
         <is>
-          <t>Москва, Казанский</t>
+          <t>Москва, Павелецкий</t>
         </is>
       </c>
       <c r="J155" s="24" t="n">
-        <v>4394</v>
+        <v>1979</v>
       </c>
       <c r="K155" s="24" t="n">
-        <v>4394</v>
+        <v>1979</v>
       </c>
       <c r="L155" s="16" t="inlineStr">
         <is>
-          <t>Казанский вокзал → электричка до ст. Коломна (490–620 ₽) + такси 10 мин (~300 ₽) (07:22 → 09:15)</t>
+          <t>Павелецкий → метро до Комсомольской (~20 мин) → электричка от Казанского + такси (08:47 РЭКС → 10:28)</t>
         </is>
       </c>
       <c r="M155" s="16" t="inlineStr">
         <is>
-          <t>~09:30</t>
-        </is>
-      </c>
-      <c r="N155" s="16" t="inlineStr">
-        <is>
-          <t>ранний заезд</t>
-        </is>
-      </c>
+          <t>~10:45</t>
+        </is>
+      </c>
+      <c r="N155" s="16" t="inlineStr"/>
       <c r="O155" s="19" t="inlineStr">
         <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2024700&amp;nnst2=2000000</t>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2014700&amp;nnst2=2000000</t>
         </is>
       </c>
       <c r="P155" s="16" t="inlineStr">
         <is>
-          <t>Основной вариант — машина</t>
+          <t>Основной вариант — машина. Купе осталось 1 место</t>
         </is>
       </c>
       <c r="Q155" s="16" t="inlineStr">
@@ -15926,11 +15962,11 @@
     <row r="156">
       <c r="A156" s="15" t="inlineStr">
         <is>
-          <t>Тамбов</t>
+          <t>Липецк</t>
         </is>
       </c>
       <c r="B156" s="16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C156" s="16" t="inlineStr">
         <is>
@@ -15944,22 +15980,22 @@
       </c>
       <c r="E156" s="16" t="inlineStr">
         <is>
-          <t>Поезд, сидячий (купе 2 868)</t>
+          <t>Поезд, купе</t>
         </is>
       </c>
       <c r="F156" s="16" t="inlineStr">
         <is>
-          <t>135Ж</t>
+          <t>033С</t>
         </is>
       </c>
       <c r="G156" s="16" t="inlineStr">
         <is>
-          <t>27.10 21:56</t>
+          <t>27.10 23:15</t>
         </is>
       </c>
       <c r="H156" s="16" t="inlineStr">
         <is>
-          <t>28.10 07:22</t>
+          <t>28.10 08:08</t>
         </is>
       </c>
       <c r="I156" s="16" t="inlineStr">
@@ -15968,30 +16004,30 @@
         </is>
       </c>
       <c r="J156" s="24" t="n">
-        <v>1979</v>
+        <v>4049</v>
       </c>
       <c r="K156" s="24" t="n">
-        <v>1979</v>
+        <v>4049</v>
       </c>
       <c r="L156" s="16" t="inlineStr">
         <is>
-          <t>Павелецкий → метро до Комсомольской (~20 мин) → электричка от Казанского + такси (08:47 РЭКС → 10:28)</t>
+          <t>Павелецкий → метро до Комсомольской (~20 мин) → электричка от Казанского + такси (09:48 → 11:36)</t>
         </is>
       </c>
       <c r="M156" s="16" t="inlineStr">
         <is>
-          <t>~10:45</t>
+          <t>~12:00</t>
         </is>
       </c>
       <c r="N156" s="16" t="inlineStr"/>
       <c r="O156" s="19" t="inlineStr">
         <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2014700&amp;nnst2=2000000</t>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2014130&amp;nnst2=2000000</t>
         </is>
       </c>
       <c r="P156" s="16" t="inlineStr">
         <is>
-          <t>Основной вариант — машина. Купе осталось 1 место</t>
+          <t>Основной вариант — одна машина на троих</t>
         </is>
       </c>
       <c r="Q156" s="16" t="inlineStr">
@@ -16003,11 +16039,11 @@
     <row r="157">
       <c r="A157" s="15" t="inlineStr">
         <is>
-          <t>Липецк</t>
+          <t>Воронеж</t>
         </is>
       </c>
       <c r="B157" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C157" s="16" t="inlineStr">
         <is>
@@ -16021,54 +16057,54 @@
       </c>
       <c r="E157" s="16" t="inlineStr">
         <is>
-          <t>Поезд, купе</t>
+          <t>Поезд «Ингушетия», купе</t>
         </is>
       </c>
       <c r="F157" s="16" t="inlineStr">
         <is>
-          <t>033С</t>
+          <t>145С</t>
         </is>
       </c>
       <c r="G157" s="16" t="inlineStr">
         <is>
-          <t>27.10 23:15</t>
+          <t>27.10 23:17</t>
         </is>
       </c>
       <c r="H157" s="16" t="inlineStr">
         <is>
-          <t>28.10 08:08</t>
+          <t>28.10 07:24</t>
         </is>
       </c>
       <c r="I157" s="16" t="inlineStr">
         <is>
-          <t>Москва, Павелецкий</t>
+          <t>Москва, Казанский</t>
         </is>
       </c>
       <c r="J157" s="24" t="n">
-        <v>4049</v>
+        <v>4045</v>
       </c>
       <c r="K157" s="24" t="n">
-        <v>4049</v>
+        <v>4045</v>
       </c>
       <c r="L157" s="16" t="inlineStr">
         <is>
-          <t>Павелецкий → метро до Комсомольской (~20 мин) → электричка от Казанского + такси (09:48 → 11:36)</t>
+          <t>Казанский вокзал → электричка до ст. Коломна (490–620 ₽) + такси 10 мин (~300 ₽) (08:47 РЭКС → 10:28)</t>
         </is>
       </c>
       <c r="M157" s="16" t="inlineStr">
         <is>
-          <t>~12:00</t>
+          <t>~10:45</t>
         </is>
       </c>
       <c r="N157" s="16" t="inlineStr"/>
       <c r="O157" s="19" t="inlineStr">
         <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2014130&amp;nnst2=2000000</t>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2014000&amp;nnst2=2000000</t>
         </is>
       </c>
       <c r="P157" s="16" t="inlineStr">
         <is>
-          <t>Основной вариант — одна машина на троих</t>
+          <t>Или 213*С 21:09 — прямо до Голутвина (Коломна) в 04:50</t>
         </is>
       </c>
       <c r="Q157" s="16" t="inlineStr">
@@ -16080,11 +16116,11 @@
     <row r="158">
       <c r="A158" s="15" t="inlineStr">
         <is>
-          <t>Воронеж</t>
+          <t>Орёл</t>
         </is>
       </c>
       <c r="B158" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C158" s="16" t="inlineStr">
         <is>
@@ -16098,54 +16134,54 @@
       </c>
       <c r="E158" s="16" t="inlineStr">
         <is>
-          <t>Поезд «Ингушетия», купе</t>
+          <t>Поезд, купе</t>
         </is>
       </c>
       <c r="F158" s="16" t="inlineStr">
         <is>
-          <t>145С</t>
+          <t>084С</t>
         </is>
       </c>
       <c r="G158" s="16" t="inlineStr">
         <is>
-          <t>27.10 23:17</t>
+          <t>27.10 23:37</t>
         </is>
       </c>
       <c r="H158" s="16" t="inlineStr">
         <is>
-          <t>28.10 07:24</t>
+          <t>28.10 08:40</t>
         </is>
       </c>
       <c r="I158" s="16" t="inlineStr">
         <is>
-          <t>Москва, Казанский</t>
+          <t>Москва, Киевский</t>
         </is>
       </c>
       <c r="J158" s="24" t="n">
-        <v>4045</v>
+        <v>3655</v>
       </c>
       <c r="K158" s="24" t="n">
-        <v>4045</v>
+        <v>3655</v>
       </c>
       <c r="L158" s="16" t="inlineStr">
         <is>
-          <t>Казанский вокзал → электричка до ст. Коломна (490–620 ₽) + такси 10 мин (~300 ₽) (08:47 РЭКС → 10:28)</t>
+          <t>Киевский → метро до Комсомольской (~25 мин) → электричка + такси (09:48 → 11:36)</t>
         </is>
       </c>
       <c r="M158" s="16" t="inlineStr">
         <is>
-          <t>~10:45</t>
+          <t>~12:00</t>
         </is>
       </c>
       <c r="N158" s="16" t="inlineStr"/>
       <c r="O158" s="19" t="inlineStr">
         <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2014000&amp;nnst2=2000000</t>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2000140&amp;nnst2=2000000</t>
         </is>
       </c>
       <c r="P158" s="16" t="inlineStr">
         <is>
-          <t>Или 213*С 21:09 — прямо до Голутвина (Коломна) в 04:50</t>
+          <t>Основной вариант — машина вместе с Брянском</t>
         </is>
       </c>
       <c r="Q158" s="16" t="inlineStr">
@@ -16157,7 +16193,7 @@
     <row r="159">
       <c r="A159" s="15" t="inlineStr">
         <is>
-          <t>Орёл</t>
+          <t>Брянск</t>
         </is>
       </c>
       <c r="B159" s="16" t="n">
@@ -16175,22 +16211,22 @@
       </c>
       <c r="E159" s="16" t="inlineStr">
         <is>
-          <t>Поезд, купе</t>
+          <t>Поезд, сидячий (купе 3 180)</t>
         </is>
       </c>
       <c r="F159" s="16" t="inlineStr">
         <is>
-          <t>084С</t>
+          <t>086Щ</t>
         </is>
       </c>
       <c r="G159" s="16" t="inlineStr">
         <is>
-          <t>27.10 23:37</t>
+          <t>28.10 00:20</t>
         </is>
       </c>
       <c r="H159" s="16" t="inlineStr">
         <is>
-          <t>28.10 08:40</t>
+          <t>28.10 06:20</t>
         </is>
       </c>
       <c r="I159" s="16" t="inlineStr">
@@ -16199,30 +16235,34 @@
         </is>
       </c>
       <c r="J159" s="24" t="n">
-        <v>3655</v>
+        <v>1749</v>
       </c>
       <c r="K159" s="24" t="n">
-        <v>3655</v>
+        <v>1749</v>
       </c>
       <c r="L159" s="16" t="inlineStr">
         <is>
-          <t>Киевский → метро до Комсомольской (~25 мин) → электричка + такси (09:48 → 11:36)</t>
+          <t>Киевский → метро до Комсомольской (~25 мин) → электричка + такси (07:22 → 09:15)</t>
         </is>
       </c>
       <c r="M159" s="16" t="inlineStr">
         <is>
-          <t>~12:00</t>
-        </is>
-      </c>
-      <c r="N159" s="16" t="inlineStr"/>
+          <t>~09:30</t>
+        </is>
+      </c>
+      <c r="N159" s="16" t="inlineStr">
+        <is>
+          <t>ранний заезд</t>
+        </is>
+      </c>
       <c r="O159" s="19" t="inlineStr">
         <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2000140&amp;nnst2=2000000</t>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2000427&amp;nnst2=2000000</t>
         </is>
       </c>
       <c r="P159" s="16" t="inlineStr">
         <is>
-          <t>Основной вариант — машина вместе с Брянском</t>
+          <t>Время по расписанию 27.10. Основной вариант — машина</t>
         </is>
       </c>
       <c r="Q159" s="16" t="inlineStr">
@@ -16231,89 +16271,8 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="15" t="inlineStr">
-        <is>
-          <t>Брянск</t>
-        </is>
-      </c>
-      <c r="B160" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C160" s="16" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D160" s="16" t="inlineStr">
-        <is>
-          <t>Альтернатива: поезд</t>
-        </is>
-      </c>
-      <c r="E160" s="16" t="inlineStr">
-        <is>
-          <t>Поезд, сидячий (купе 3 180)</t>
-        </is>
-      </c>
-      <c r="F160" s="16" t="inlineStr">
-        <is>
-          <t>086Щ</t>
-        </is>
-      </c>
-      <c r="G160" s="16" t="inlineStr">
-        <is>
-          <t>28.10 00:20</t>
-        </is>
-      </c>
-      <c r="H160" s="16" t="inlineStr">
-        <is>
-          <t>28.10 06:20</t>
-        </is>
-      </c>
-      <c r="I160" s="16" t="inlineStr">
-        <is>
-          <t>Москва, Киевский</t>
-        </is>
-      </c>
-      <c r="J160" s="24" t="n">
-        <v>1749</v>
-      </c>
-      <c r="K160" s="24" t="n">
-        <v>1749</v>
-      </c>
-      <c r="L160" s="16" t="inlineStr">
-        <is>
-          <t>Киевский → метро до Комсомольской (~25 мин) → электричка + такси (07:22 → 09:15)</t>
-        </is>
-      </c>
-      <c r="M160" s="16" t="inlineStr">
-        <is>
-          <t>~09:30</t>
-        </is>
-      </c>
-      <c r="N160" s="16" t="inlineStr">
-        <is>
-          <t>ранний заезд</t>
-        </is>
-      </c>
-      <c r="O160" s="19" t="inlineStr">
-        <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2000427&amp;nnst2=2000000</t>
-        </is>
-      </c>
-      <c r="P160" s="16" t="inlineStr">
-        <is>
-          <t>Время по расписанию 27.10. Основной вариант — машина</t>
-        </is>
-      </c>
-      <c r="Q160" s="16" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:Q160"/>
+  <autoFilter ref="A1:Q159"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
@@ -16414,41 +16373,41 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O117" r:id="rId97"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O119" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O120" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O122" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O123" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O124" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O125" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O126" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O127" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O128" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O130" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O131" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O132" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O133" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O134" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O135" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O136" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O137" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O138" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O139" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O140" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O141" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O142" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O143" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O144" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O145" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O147" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O148" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O150" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O151" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O153" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O154" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O155" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O156" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O157" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O158" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O159" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O160" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O121" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O122" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O123" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O124" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O125" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O126" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O127" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O129" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O130" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O131" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O132" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O133" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O134" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O135" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O136" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O137" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O138" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O139" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O140" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O141" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O142" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O143" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O144" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O146" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O147" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O149" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O150" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O152" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O153" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O154" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O155" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O156" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O157" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O158" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O159" r:id="rId134"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17967,7 +17926,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>В аэропорту минимум за 2 часа до вылета.</t>
+          <t>В аэропорту минимум за 2 часа до вылета (Москва и крупные города); в небольших городах — за 1,5 часа. Учитывать время подъёма и дорогу до аэропорта: рейсы с вылетом до ~07:00 означают подъём среди ночи.</t>
         </is>
       </c>
     </row>

--- a/Коломна_маршруты_28-30.10.2026.xlsx
+++ b/Коломна_маршруты_28-30.10.2026.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Сводка по сотрудникам'!$A$4:$S$64</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Маршруты'!$A$1:$Q$159</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Маршруты'!$A$1:$Q$158</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -5112,7 +5112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q159"/>
+  <dimension ref="A1:Q158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13315,55 +13315,55 @@
       <c r="B119" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="C119" s="16" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D119" s="16" t="inlineStr">
-        <is>
-          <t>Только если обязательна экскурсия</t>
-        </is>
-      </c>
-      <c r="E119" s="16" t="inlineStr">
-        <is>
-          <t>Самолёт, Аэрофлот</t>
-        </is>
-      </c>
-      <c r="F119" s="16" t="inlineStr">
-        <is>
-          <t>SU-1429</t>
+      <c r="C119" s="17" t="inlineStr">
+        <is>
+          <t>В2: после 15:00 28.10 / В3: к утру 29.10</t>
+        </is>
+      </c>
+      <c r="D119" s="17" t="inlineStr">
+        <is>
+          <t>Самый дешёвый = Удобный</t>
+        </is>
+      </c>
+      <c r="E119" s="17" t="inlineStr">
+        <is>
+          <t>Самолёт, Азимут</t>
+        </is>
+      </c>
+      <c r="F119" s="17" t="inlineStr">
+        <is>
+          <t>A4-7062</t>
         </is>
       </c>
       <c r="G119" s="16" t="inlineStr">
         <is>
-          <t>28.10 06:15 (мест.)</t>
+          <t>28.10 12:20 (мест.)</t>
         </is>
       </c>
       <c r="H119" s="16" t="inlineStr">
         <is>
-          <t>28.10 06:40</t>
+          <t>28.10 13:00</t>
         </is>
       </c>
       <c r="I119" s="16" t="inlineStr">
         <is>
-          <t>Шереметьево</t>
-        </is>
-      </c>
-      <c r="J119" s="24" t="n">
-        <v>13489</v>
-      </c>
-      <c r="K119" s="24" t="n">
-        <v>17111</v>
+          <t>Внуково</t>
+        </is>
+      </c>
+      <c r="J119" s="18" t="n">
+        <v>12962</v>
+      </c>
+      <c r="K119" s="18" t="n">
+        <v>16375</v>
       </c>
       <c r="L119" s="16" t="inlineStr">
         <is>
-          <t>Шереметьево: такси ~3 ч или аэроэкспресс → Белорусский + метро → Казанский + электричка</t>
+          <t>Внуково: метро → Казанский вокзал + электричка, или такси ~2 ч 45 мин</t>
         </is>
       </c>
       <c r="M119" s="16" t="inlineStr">
         <is>
-          <t>~10:20</t>
+          <t>~16:25</t>
         </is>
       </c>
       <c r="N119" s="16" t="inlineStr"/>
@@ -13374,7 +13374,7 @@
       </c>
       <c r="P119" s="16" t="inlineStr">
         <is>
-          <t>Неудобно: в аэропорту к 04:45, выезд из дома ~04:15, подъём ~03:30. Рейс ежедневный — вылет 27.10 такой же ранний</t>
+          <t>Выезд из дома ~10:00, в аэропорту за 1,5 ч. К началу экскурсии не успевает — можно присоединиться позже. Другие рейсы неудобны: SU-1429 в 06:15 (подъём ~03:30), через Казань в 01:10</t>
         </is>
       </c>
       <c r="Q119" s="16" t="inlineStr">
@@ -13394,7 +13394,7 @@
       </c>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>В2: после 15:00 28.10 / В3: к утру 29.10</t>
+          <t>Обратно</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
@@ -13404,203 +13404,199 @@
       </c>
       <c r="E120" s="7" t="inlineStr">
         <is>
-          <t>Самолёт, Азимут</t>
+          <t>Самолёт, Аэрофлот</t>
         </is>
       </c>
       <c r="F120" s="7" t="inlineStr">
         <is>
-          <t>A4-7062</t>
+          <t>SU-1428</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
         <is>
-          <t>28.10 12:20 (мест.)</t>
+          <t>31.10 00:40</t>
         </is>
       </c>
       <c r="H120" s="5" t="inlineStr">
         <is>
-          <t>28.10 13:00</t>
+          <t>31.10 05:05 (мест.)</t>
         </is>
       </c>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>Внуково</t>
+          <t>Шереметьево</t>
         </is>
       </c>
       <c r="J120" s="6" t="n">
-        <v>12962</v>
+        <v>11097</v>
       </c>
       <c r="K120" s="6" t="n">
-        <v>16375</v>
+        <v>14765</v>
       </c>
       <c r="L120" s="5" t="inlineStr">
         <is>
-          <t>Внуково: метро → Казанский вокзал + электричка, или такси ~2 ч 45 мин</t>
-        </is>
-      </c>
-      <c r="M120" s="5" t="inlineStr">
-        <is>
-          <t>~16:25</t>
-        </is>
-      </c>
+          <t>Выезд из гостиницы 18:15; в аэропорту за 2 ч до вылета</t>
+        </is>
+      </c>
+      <c r="M120" s="5" t="inlineStr"/>
       <c r="N120" s="5" t="inlineStr"/>
       <c r="O120" s="20" t="inlineStr">
         <is>
-          <t>https://avia.tutu.ru/f/Magnitogorsk/Moskva/?class=Y&amp;travelers=1&amp;route[0]=45-28102026-491</t>
+          <t>https://avia.tutu.ru/f/Moskva/Magnitogorsk/?class=Y&amp;travelers=1&amp;route[0]=491-30102026-45</t>
         </is>
       </c>
       <c r="P120" s="5" t="inlineStr">
         <is>
-          <t>Рекомендуем: выезд из дома ~10:00, в аэропорту за 1,5 ч. Дешевле утреннего. К началу экскурсии не успевает — можно присоединиться позже. Рейс через Казань в 01:10 ночью — ещё хуже</t>
-        </is>
-      </c>
-      <c r="Q120" s="5" t="inlineStr">
+          <t>Ночной рейс сразу после конференции, гостиница не нужна. Время по расписанию 30.10 — проверить на 31.10. Альтернатива: SU-1434 31.10 07:40 + ночь</t>
+        </is>
+      </c>
+      <c r="Q120" s="5" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="15" t="inlineStr">
+        <is>
+          <t>Челябинск</t>
+        </is>
+      </c>
+      <c r="B121" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C121" s="17" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D121" s="17" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E121" s="17" t="inlineStr">
+        <is>
+          <t>Самолёт, Победа</t>
+        </is>
+      </c>
+      <c r="F121" s="17" t="inlineStr">
+        <is>
+          <t>DP-414</t>
+        </is>
+      </c>
+      <c r="G121" s="16" t="inlineStr">
+        <is>
+          <t>28.10 06:30 (мест.)</t>
+        </is>
+      </c>
+      <c r="H121" s="16" t="inlineStr">
+        <is>
+          <t>28.10 07:15</t>
+        </is>
+      </c>
+      <c r="I121" s="16" t="inlineStr">
+        <is>
+          <t>Внуково</t>
+        </is>
+      </c>
+      <c r="J121" s="18" t="n">
+        <v>6196</v>
+      </c>
+      <c r="K121" s="18" t="n">
+        <v>8991</v>
+      </c>
+      <c r="L121" s="16" t="inlineStr">
+        <is>
+          <t>Внуково: метро → Казанский вокзал + электричка, или такси ~2 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="M121" s="16" t="inlineStr">
+        <is>
+          <t>~10:40</t>
+        </is>
+      </c>
+      <c r="N121" s="16" t="inlineStr"/>
+      <c r="O121" s="19" t="inlineStr">
+        <is>
+          <t>https://avia.tutu.ru/f/Chelyabinsk/Moskva/?class=Y&amp;travelers=1&amp;route[0]=98-28102026-491</t>
+        </is>
+      </c>
+      <c r="P121" s="16" t="inlineStr">
+        <is>
+          <t>Также DP-6568 05:30→SVO 06:10, та же цена</t>
+        </is>
+      </c>
+      <c r="Q121" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="5" t="inlineStr">
-        <is>
-          <t>Магнитогорск</t>
-        </is>
-      </c>
-      <c r="B121" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C121" s="7" t="inlineStr">
-        <is>
-          <t>Обратно</t>
-        </is>
-      </c>
-      <c r="D121" s="7" t="inlineStr">
-        <is>
-          <t>Самый дешёвый = Удобный</t>
-        </is>
-      </c>
-      <c r="E121" s="7" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>Челябинск</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C122" s="10" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D122" s="10" t="inlineStr">
+        <is>
+          <t>Удобный</t>
+        </is>
+      </c>
+      <c r="E122" s="10" t="inlineStr">
         <is>
           <t>Самолёт, Аэрофлот</t>
         </is>
       </c>
-      <c r="F121" s="7" t="inlineStr">
-        <is>
-          <t>SU-1428</t>
-        </is>
-      </c>
-      <c r="G121" s="5" t="inlineStr">
-        <is>
-          <t>31.10 00:40</t>
-        </is>
-      </c>
-      <c r="H121" s="5" t="inlineStr">
-        <is>
-          <t>31.10 05:05 (мест.)</t>
-        </is>
-      </c>
-      <c r="I121" s="5" t="inlineStr">
+      <c r="F122" s="10" t="inlineStr">
+        <is>
+          <t>SU-1093</t>
+        </is>
+      </c>
+      <c r="G122" s="5" t="inlineStr">
+        <is>
+          <t>28.10 06:05 (мест.)</t>
+        </is>
+      </c>
+      <c r="H122" s="5" t="inlineStr">
+        <is>
+          <t>28.10 06:45</t>
+        </is>
+      </c>
+      <c r="I122" s="5" t="inlineStr">
         <is>
           <t>Шереметьево</t>
         </is>
       </c>
-      <c r="J121" s="6" t="n">
-        <v>11097</v>
-      </c>
-      <c r="K121" s="6" t="n">
-        <v>14765</v>
-      </c>
-      <c r="L121" s="5" t="inlineStr">
-        <is>
-          <t>Выезд из гостиницы 18:15; в аэропорту за 2 ч до вылета</t>
-        </is>
-      </c>
-      <c r="M121" s="5" t="inlineStr"/>
-      <c r="N121" s="5" t="inlineStr"/>
-      <c r="O121" s="20" t="inlineStr">
-        <is>
-          <t>https://avia.tutu.ru/f/Moskva/Magnitogorsk/?class=Y&amp;travelers=1&amp;route[0]=491-30102026-45</t>
-        </is>
-      </c>
-      <c r="P121" s="5" t="inlineStr">
-        <is>
-          <t>Ночной рейс сразу после конференции, гостиница не нужна. Время по расписанию 30.10 — проверить на 31.10. Альтернатива: SU-1434 31.10 07:40 + ночь</t>
-        </is>
-      </c>
-      <c r="Q121" s="5" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="15" t="inlineStr">
-        <is>
-          <t>Челябинск</t>
-        </is>
-      </c>
-      <c r="B122" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C122" s="17" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D122" s="17" t="inlineStr">
-        <is>
-          <t>Самый дешёвый</t>
-        </is>
-      </c>
-      <c r="E122" s="17" t="inlineStr">
-        <is>
-          <t>Самолёт, Победа</t>
-        </is>
-      </c>
-      <c r="F122" s="17" t="inlineStr">
-        <is>
-          <t>DP-414</t>
-        </is>
-      </c>
-      <c r="G122" s="16" t="inlineStr">
-        <is>
-          <t>28.10 06:30 (мест.)</t>
-        </is>
-      </c>
-      <c r="H122" s="16" t="inlineStr">
-        <is>
-          <t>28.10 07:15</t>
-        </is>
-      </c>
-      <c r="I122" s="16" t="inlineStr">
-        <is>
-          <t>Внуково</t>
-        </is>
-      </c>
-      <c r="J122" s="18" t="n">
-        <v>6196</v>
-      </c>
-      <c r="K122" s="18" t="n">
-        <v>8991</v>
-      </c>
-      <c r="L122" s="16" t="inlineStr">
-        <is>
-          <t>Внуково: метро → Казанский вокзал + электричка, или такси ~2 ч 45 мин</t>
-        </is>
-      </c>
-      <c r="M122" s="16" t="inlineStr">
-        <is>
-          <t>~10:40</t>
-        </is>
-      </c>
-      <c r="N122" s="16" t="inlineStr"/>
-      <c r="O122" s="19" t="inlineStr">
+      <c r="J122" s="9" t="n">
+        <v>10408</v>
+      </c>
+      <c r="K122" s="9" t="n">
+        <v>14081</v>
+      </c>
+      <c r="L122" s="5" t="inlineStr">
+        <is>
+          <t>Шереметьево: такси ~3 ч или аэроэкспресс → Белорусский + метро → Казанский + электричка</t>
+        </is>
+      </c>
+      <c r="M122" s="5" t="inlineStr">
+        <is>
+          <t>~10:25</t>
+        </is>
+      </c>
+      <c r="N122" s="5" t="inlineStr"/>
+      <c r="O122" s="20" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/f/Chelyabinsk/Moskva/?class=Y&amp;travelers=1&amp;route[0]=98-28102026-491</t>
         </is>
       </c>
-      <c r="P122" s="16" t="inlineStr">
-        <is>
-          <t>Также DP-6568 05:30→SVO 06:10, та же цена</t>
-        </is>
-      </c>
-      <c r="Q122" s="16" t="inlineStr">
+      <c r="P122" s="5" t="inlineStr"/>
+      <c r="Q122" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -13615,34 +13611,34 @@
       <c r="B123" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C123" s="10" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D123" s="10" t="inlineStr">
-        <is>
-          <t>Удобный</t>
-        </is>
-      </c>
-      <c r="E123" s="10" t="inlineStr">
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>В2: после 15:00 28.10 / В3: к утру 29.10</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
         <is>
           <t>Самолёт, Аэрофлот</t>
         </is>
       </c>
-      <c r="F123" s="10" t="inlineStr">
-        <is>
-          <t>SU-1093</t>
+      <c r="F123" s="5" t="inlineStr">
+        <is>
+          <t>SU-1427</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>28.10 06:05 (мест.)</t>
+          <t>28.10 22:30 (мест.)</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr">
         <is>
-          <t>28.10 06:45</t>
+          <t>28.10 23:20</t>
         </is>
       </c>
       <c r="I123" s="5" t="inlineStr">
@@ -13650,11 +13646,11 @@
           <t>Шереметьево</t>
         </is>
       </c>
-      <c r="J123" s="9" t="n">
-        <v>10408</v>
-      </c>
-      <c r="K123" s="9" t="n">
-        <v>14081</v>
+      <c r="J123" s="21" t="n">
+        <v>8190</v>
+      </c>
+      <c r="K123" s="21" t="n">
+        <v>11788</v>
       </c>
       <c r="L123" s="5" t="inlineStr">
         <is>
@@ -13663,7 +13659,7 @@
       </c>
       <c r="M123" s="5" t="inlineStr">
         <is>
-          <t>~10:25</t>
+          <t>~02:30</t>
         </is>
       </c>
       <c r="N123" s="5" t="inlineStr"/>
@@ -13672,7 +13668,11 @@
           <t>https://avia.tutu.ru/f/Chelyabinsk/Moskva/?class=Y&amp;travelers=1&amp;route[0]=98-28102026-491</t>
         </is>
       </c>
-      <c r="P123" s="5" t="inlineStr"/>
+      <c r="P123" s="5" t="inlineStr">
+        <is>
+          <t>Поздно; лучше В1</t>
+        </is>
+      </c>
       <c r="Q123" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
@@ -13688,211 +13688,207 @@
       <c r="B124" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C124" s="5" t="inlineStr">
-        <is>
-          <t>В2: после 15:00 28.10 / В3: к утру 29.10</t>
-        </is>
-      </c>
-      <c r="D124" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E124" s="5" t="inlineStr">
-        <is>
-          <t>Самолёт, Аэрофлот</t>
-        </is>
-      </c>
-      <c r="F124" s="5" t="inlineStr">
-        <is>
-          <t>SU-1427</t>
+      <c r="C124" s="7" t="inlineStr">
+        <is>
+          <t>Обратно</t>
+        </is>
+      </c>
+      <c r="D124" s="7" t="inlineStr">
+        <is>
+          <t>Самый дешёвый = Удобный</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
+          <t>Самолёт, Победа</t>
+        </is>
+      </c>
+      <c r="F124" s="7" t="inlineStr">
+        <is>
+          <t>DP-413</t>
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr">
         <is>
-          <t>28.10 22:30 (мест.)</t>
+          <t>30.10 23:45</t>
         </is>
       </c>
       <c r="H124" s="5" t="inlineStr">
         <is>
-          <t>28.10 23:20</t>
+          <t>31.10 04:25 (мест.)</t>
         </is>
       </c>
       <c r="I124" s="5" t="inlineStr">
         <is>
-          <t>Шереметьево</t>
-        </is>
-      </c>
-      <c r="J124" s="21" t="n">
-        <v>8190</v>
-      </c>
-      <c r="K124" s="21" t="n">
-        <v>11788</v>
+          <t>Внуково</t>
+        </is>
+      </c>
+      <c r="J124" s="6" t="n">
+        <v>7789</v>
+      </c>
+      <c r="K124" s="6" t="n">
+        <v>10643</v>
       </c>
       <c r="L124" s="5" t="inlineStr">
         <is>
-          <t>Шереметьево: такси ~3 ч или аэроэкспресс → Белорусский + метро → Казанский + электричка</t>
-        </is>
-      </c>
-      <c r="M124" s="5" t="inlineStr">
-        <is>
-          <t>~02:30</t>
-        </is>
-      </c>
+          <t>Выезд из гостиницы 18:15; в аэропорту за 2 ч до вылета</t>
+        </is>
+      </c>
+      <c r="M124" s="5" t="inlineStr"/>
       <c r="N124" s="5" t="inlineStr"/>
       <c r="O124" s="20" t="inlineStr">
         <is>
-          <t>https://avia.tutu.ru/f/Chelyabinsk/Moskva/?class=Y&amp;travelers=1&amp;route[0]=98-28102026-491</t>
+          <t>https://avia.tutu.ru/f/Moskva/Chelyabinsk/?class=Y&amp;travelers=1&amp;route[0]=491-30102026-98</t>
         </is>
       </c>
       <c r="P124" s="5" t="inlineStr">
         <is>
-          <t>Поздно; лучше В1</t>
-        </is>
-      </c>
-      <c r="Q124" s="5" t="inlineStr">
+          <t>Рейсы Победы из SVO в 23:00/23:30 не проходят правило 2 ч</t>
+        </is>
+      </c>
+      <c r="Q124" s="5" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="15" t="inlineStr">
+        <is>
+          <t>Тюмень</t>
+        </is>
+      </c>
+      <c r="B125" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C125" s="17" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D125" s="17" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E125" s="17" t="inlineStr">
+        <is>
+          <t>Самолёт, Победа</t>
+        </is>
+      </c>
+      <c r="F125" s="17" t="inlineStr">
+        <is>
+          <t>DP-6562</t>
+        </is>
+      </c>
+      <c r="G125" s="16" t="inlineStr">
+        <is>
+          <t>28.10 06:25 (мест.)</t>
+        </is>
+      </c>
+      <c r="H125" s="16" t="inlineStr">
+        <is>
+          <t>28.10 07:30</t>
+        </is>
+      </c>
+      <c r="I125" s="16" t="inlineStr">
+        <is>
+          <t>Шереметьево</t>
+        </is>
+      </c>
+      <c r="J125" s="18" t="n">
+        <v>5873</v>
+      </c>
+      <c r="K125" s="18" t="n">
+        <v>8712</v>
+      </c>
+      <c r="L125" s="16" t="inlineStr">
+        <is>
+          <t>Шереметьево: такси ~3 ч или аэроэкспресс → Белорусский + метро → Казанский + электричка</t>
+        </is>
+      </c>
+      <c r="M125" s="16" t="inlineStr">
+        <is>
+          <t>~11:10</t>
+        </is>
+      </c>
+      <c r="N125" s="16" t="inlineStr"/>
+      <c r="O125" s="19" t="inlineStr">
+        <is>
+          <t>https://avia.tutu.ru/f/Tyumen/Moskva/?class=Y&amp;travelers=1&amp;route[0]=86-28102026-491</t>
+        </is>
+      </c>
+      <c r="P125" s="16" t="inlineStr"/>
+      <c r="Q125" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="5" t="inlineStr">
-        <is>
-          <t>Челябинск</t>
-        </is>
-      </c>
-      <c r="B125" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C125" s="7" t="inlineStr">
-        <is>
-          <t>Обратно</t>
-        </is>
-      </c>
-      <c r="D125" s="7" t="inlineStr">
-        <is>
-          <t>Самый дешёвый = Удобный</t>
-        </is>
-      </c>
-      <c r="E125" s="7" t="inlineStr">
-        <is>
-          <t>Самолёт, Победа</t>
-        </is>
-      </c>
-      <c r="F125" s="7" t="inlineStr">
-        <is>
-          <t>DP-413</t>
-        </is>
-      </c>
-      <c r="G125" s="5" t="inlineStr">
-        <is>
-          <t>30.10 23:45</t>
-        </is>
-      </c>
-      <c r="H125" s="5" t="inlineStr">
-        <is>
-          <t>31.10 04:25 (мест.)</t>
-        </is>
-      </c>
-      <c r="I125" s="5" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>Тюмень</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C126" s="10" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D126" s="10" t="inlineStr">
+        <is>
+          <t>Удобный</t>
+        </is>
+      </c>
+      <c r="E126" s="10" t="inlineStr">
+        <is>
+          <t>Самолёт, ЮТэйр</t>
+        </is>
+      </c>
+      <c r="F126" s="10" t="inlineStr">
+        <is>
+          <t>UT-454</t>
+        </is>
+      </c>
+      <c r="G126" s="5" t="inlineStr">
+        <is>
+          <t>28.10 07:15 (мест.)</t>
+        </is>
+      </c>
+      <c r="H126" s="5" t="inlineStr">
+        <is>
+          <t>28.10 08:10</t>
+        </is>
+      </c>
+      <c r="I126" s="5" t="inlineStr">
         <is>
           <t>Внуково</t>
         </is>
       </c>
-      <c r="J125" s="6" t="n">
-        <v>7789</v>
-      </c>
-      <c r="K125" s="6" t="n">
-        <v>10643</v>
-      </c>
-      <c r="L125" s="5" t="inlineStr">
-        <is>
-          <t>Выезд из гостиницы 18:15; в аэропорту за 2 ч до вылета</t>
-        </is>
-      </c>
-      <c r="M125" s="5" t="inlineStr"/>
-      <c r="N125" s="5" t="inlineStr"/>
-      <c r="O125" s="20" t="inlineStr">
-        <is>
-          <t>https://avia.tutu.ru/f/Moskva/Chelyabinsk/?class=Y&amp;travelers=1&amp;route[0]=491-30102026-98</t>
-        </is>
-      </c>
-      <c r="P125" s="5" t="inlineStr">
-        <is>
-          <t>Рейсы Победы из SVO в 23:00/23:30 не проходят правило 2 ч</t>
-        </is>
-      </c>
-      <c r="Q125" s="5" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="15" t="inlineStr">
-        <is>
-          <t>Тюмень</t>
-        </is>
-      </c>
-      <c r="B126" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C126" s="17" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D126" s="17" t="inlineStr">
-        <is>
-          <t>Самый дешёвый</t>
-        </is>
-      </c>
-      <c r="E126" s="17" t="inlineStr">
-        <is>
-          <t>Самолёт, Победа</t>
-        </is>
-      </c>
-      <c r="F126" s="17" t="inlineStr">
-        <is>
-          <t>DP-6562</t>
-        </is>
-      </c>
-      <c r="G126" s="16" t="inlineStr">
-        <is>
-          <t>28.10 06:25 (мест.)</t>
-        </is>
-      </c>
-      <c r="H126" s="16" t="inlineStr">
-        <is>
-          <t>28.10 07:30</t>
-        </is>
-      </c>
-      <c r="I126" s="16" t="inlineStr">
-        <is>
-          <t>Шереметьево</t>
-        </is>
-      </c>
-      <c r="J126" s="18" t="n">
-        <v>5873</v>
-      </c>
-      <c r="K126" s="18" t="n">
-        <v>8712</v>
-      </c>
-      <c r="L126" s="16" t="inlineStr">
-        <is>
-          <t>Шереметьево: такси ~3 ч или аэроэкспресс → Белорусский + метро → Казанский + электричка</t>
-        </is>
-      </c>
-      <c r="M126" s="16" t="inlineStr">
-        <is>
-          <t>~11:10</t>
-        </is>
-      </c>
-      <c r="N126" s="16" t="inlineStr"/>
-      <c r="O126" s="19" t="inlineStr">
+      <c r="J126" s="9" t="n">
+        <v>7065</v>
+      </c>
+      <c r="K126" s="9" t="n">
+        <v>10125</v>
+      </c>
+      <c r="L126" s="5" t="inlineStr">
+        <is>
+          <t>Внуково: метро → Казанский вокзал + электричка, или такси ~2 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="M126" s="5" t="inlineStr">
+        <is>
+          <t>~11:35</t>
+        </is>
+      </c>
+      <c r="N126" s="5" t="inlineStr"/>
+      <c r="O126" s="20" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/f/Tyumen/Moskva/?class=Y&amp;travelers=1&amp;route[0]=86-28102026-491</t>
         </is>
       </c>
-      <c r="P126" s="16" t="inlineStr"/>
-      <c r="Q126" s="16" t="inlineStr">
+      <c r="P126" s="5" t="inlineStr"/>
+      <c r="Q126" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -13907,69 +13903,37 @@
       <c r="B127" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C127" s="10" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D127" s="10" t="inlineStr">
-        <is>
-          <t>Удобный</t>
-        </is>
-      </c>
-      <c r="E127" s="10" t="inlineStr">
-        <is>
-          <t>Самолёт, ЮТэйр</t>
-        </is>
-      </c>
-      <c r="F127" s="10" t="inlineStr">
-        <is>
-          <t>UT-454</t>
-        </is>
-      </c>
-      <c r="G127" s="5" t="inlineStr">
-        <is>
-          <t>28.10 07:15 (мест.)</t>
-        </is>
-      </c>
-      <c r="H127" s="5" t="inlineStr">
-        <is>
-          <t>28.10 08:10</t>
-        </is>
-      </c>
-      <c r="I127" s="5" t="inlineStr">
-        <is>
-          <t>Внуково</t>
-        </is>
-      </c>
-      <c r="J127" s="9" t="n">
-        <v>7065</v>
-      </c>
-      <c r="K127" s="9" t="n">
-        <v>10125</v>
-      </c>
-      <c r="L127" s="5" t="inlineStr">
-        <is>
-          <t>Внуково: метро → Казанский вокзал + электричка, или такси ~2 ч 45 мин</t>
-        </is>
-      </c>
-      <c r="M127" s="5" t="inlineStr">
-        <is>
-          <t>~11:35</t>
-        </is>
-      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>В2: после 15:00 28.10 / В3: к утру 29.10</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>не требуется</t>
+        </is>
+      </c>
+      <c r="F127" s="5" t="inlineStr"/>
+      <c r="G127" s="5" t="inlineStr"/>
+      <c r="H127" s="5" t="inlineStr"/>
+      <c r="I127" s="5" t="inlineStr"/>
+      <c r="J127" s="5" t="n"/>
+      <c r="K127" s="5" t="n"/>
+      <c r="L127" s="5" t="inlineStr"/>
+      <c r="M127" s="5" t="inlineStr"/>
       <c r="N127" s="5" t="inlineStr"/>
-      <c r="O127" s="20" t="inlineStr">
-        <is>
-          <t>https://avia.tutu.ru/f/Tyumen/Moskva/?class=Y&amp;travelers=1&amp;route[0]=86-28102026-491</t>
-        </is>
-      </c>
-      <c r="P127" s="5" t="inlineStr"/>
-      <c r="Q127" s="5" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
-      </c>
+      <c r="O127" s="5" t="inlineStr"/>
+      <c r="P127" s="5" t="inlineStr">
+        <is>
+          <t>Подходит В1</t>
+        </is>
+      </c>
+      <c r="Q127" s="5" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
@@ -13980,183 +13944,219 @@
       <c r="B128" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C128" s="5" t="inlineStr">
-        <is>
-          <t>В2: после 15:00 28.10 / В3: к утру 29.10</t>
-        </is>
-      </c>
-      <c r="D128" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E128" s="5" t="inlineStr">
-        <is>
-          <t>не требуется</t>
-        </is>
-      </c>
-      <c r="F128" s="5" t="inlineStr"/>
-      <c r="G128" s="5" t="inlineStr"/>
-      <c r="H128" s="5" t="inlineStr"/>
-      <c r="I128" s="5" t="inlineStr"/>
-      <c r="J128" s="5" t="n"/>
-      <c r="K128" s="5" t="n"/>
-      <c r="L128" s="5" t="inlineStr"/>
+      <c r="C128" s="7" t="inlineStr">
+        <is>
+          <t>Обратно</t>
+        </is>
+      </c>
+      <c r="D128" s="7" t="inlineStr">
+        <is>
+          <t>Самый дешёвый = Удобный</t>
+        </is>
+      </c>
+      <c r="E128" s="7" t="inlineStr">
+        <is>
+          <t>Самолёт, Победа</t>
+        </is>
+      </c>
+      <c r="F128" s="7" t="inlineStr">
+        <is>
+          <t>DP-6561</t>
+        </is>
+      </c>
+      <c r="G128" s="5" t="inlineStr">
+        <is>
+          <t>30.10 23:50</t>
+        </is>
+      </c>
+      <c r="H128" s="5" t="inlineStr">
+        <is>
+          <t>31.10 04:40 (мест.)</t>
+        </is>
+      </c>
+      <c r="I128" s="5" t="inlineStr">
+        <is>
+          <t>Шереметьево</t>
+        </is>
+      </c>
+      <c r="J128" s="6" t="n">
+        <v>8168</v>
+      </c>
+      <c r="K128" s="6" t="n">
+        <v>11154</v>
+      </c>
+      <c r="L128" s="5" t="inlineStr">
+        <is>
+          <t>Выезд из гостиницы 18:15; в аэропорту за 2 ч до вылета</t>
+        </is>
+      </c>
       <c r="M128" s="5" t="inlineStr"/>
       <c r="N128" s="5" t="inlineStr"/>
-      <c r="O128" s="5" t="inlineStr"/>
+      <c r="O128" s="20" t="inlineStr">
+        <is>
+          <t>https://avia.tutu.ru/f/Moskva/Tyumen/?class=Y&amp;travelers=1&amp;route[0]=491-30102026-86</t>
+        </is>
+      </c>
       <c r="P128" s="5" t="inlineStr">
         <is>
-          <t>Подходит В1</t>
+          <t>Впритык по правилу 2 ч. UT-453 20:30 не успевает</t>
         </is>
       </c>
       <c r="Q128" s="5" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="5" t="inlineStr">
-        <is>
-          <t>Тюмень</t>
-        </is>
-      </c>
-      <c r="B129" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C129" s="7" t="inlineStr">
-        <is>
-          <t>Обратно</t>
-        </is>
-      </c>
-      <c r="D129" s="7" t="inlineStr">
-        <is>
-          <t>Самый дешёвый = Удобный</t>
-        </is>
-      </c>
-      <c r="E129" s="7" t="inlineStr">
-        <is>
-          <t>Самолёт, Победа</t>
-        </is>
-      </c>
-      <c r="F129" s="7" t="inlineStr">
-        <is>
-          <t>DP-6561</t>
-        </is>
-      </c>
-      <c r="G129" s="5" t="inlineStr">
-        <is>
-          <t>30.10 23:50</t>
-        </is>
-      </c>
-      <c r="H129" s="5" t="inlineStr">
-        <is>
-          <t>31.10 04:40 (мест.)</t>
-        </is>
-      </c>
-      <c r="I129" s="5" t="inlineStr">
-        <is>
-          <t>Шереметьево</t>
-        </is>
-      </c>
-      <c r="J129" s="6" t="n">
-        <v>8168</v>
-      </c>
-      <c r="K129" s="6" t="n">
-        <v>11154</v>
-      </c>
-      <c r="L129" s="5" t="inlineStr">
-        <is>
-          <t>Выезд из гостиницы 18:15; в аэропорту за 2 ч до вылета</t>
-        </is>
-      </c>
-      <c r="M129" s="5" t="inlineStr"/>
-      <c r="N129" s="5" t="inlineStr"/>
-      <c r="O129" s="20" t="inlineStr">
-        <is>
-          <t>https://avia.tutu.ru/f/Moskva/Tyumen/?class=Y&amp;travelers=1&amp;route[0]=491-30102026-86</t>
-        </is>
-      </c>
-      <c r="P129" s="5" t="inlineStr">
-        <is>
-          <t>Впритык по правилу 2 ч. UT-453 20:30 не успевает</t>
-        </is>
-      </c>
-      <c r="Q129" s="5" t="inlineStr"/>
+      <c r="A129" s="15" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="B129" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C129" s="17" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D129" s="17" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E129" s="17" t="inlineStr">
+        <is>
+          <t>Поезд, купе (сидячий 2 283)</t>
+        </is>
+      </c>
+      <c r="F129" s="17" t="inlineStr">
+        <is>
+          <t>081А</t>
+        </is>
+      </c>
+      <c r="G129" s="16" t="inlineStr">
+        <is>
+          <t>27.10 21:21</t>
+        </is>
+      </c>
+      <c r="H129" s="16" t="inlineStr">
+        <is>
+          <t>28.10 06:04</t>
+        </is>
+      </c>
+      <c r="I129" s="16" t="inlineStr">
+        <is>
+          <t>Москва, Восточный</t>
+        </is>
+      </c>
+      <c r="J129" s="18" t="n">
+        <v>3272</v>
+      </c>
+      <c r="K129" s="18" t="n">
+        <v>3272</v>
+      </c>
+      <c r="L129" s="16" t="inlineStr">
+        <is>
+          <t>Восточный вокзал → МЦД/метро до Казанского (~30 мин) → электричка + такси (07:22 → 09:15)</t>
+        </is>
+      </c>
+      <c r="M129" s="16" t="inlineStr">
+        <is>
+          <t>~09:30</t>
+        </is>
+      </c>
+      <c r="N129" s="16" t="inlineStr">
+        <is>
+          <t>ранний заезд</t>
+        </is>
+      </c>
+      <c r="O129" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2004000&amp;nnst2=2000000</t>
+        </is>
+      </c>
+      <c r="P129" s="16" t="inlineStr">
+        <is>
+          <t>Вечером сел — утром в Москве</t>
+        </is>
+      </c>
+      <c r="Q129" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
     </row>
     <row r="130">
-      <c r="A130" s="15" t="inlineStr">
+      <c r="A130" s="5" t="inlineStr">
         <is>
           <t>Санкт-Петербург</t>
         </is>
       </c>
-      <c r="B130" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C130" s="17" t="inlineStr">
+      <c r="B130" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C130" s="10" t="inlineStr">
         <is>
           <t>В1: к 15:00 28.10</t>
         </is>
       </c>
-      <c r="D130" s="17" t="inlineStr">
-        <is>
-          <t>Самый дешёвый</t>
-        </is>
-      </c>
-      <c r="E130" s="17" t="inlineStr">
-        <is>
-          <t>Поезд, купе (сидячий 2 283)</t>
-        </is>
-      </c>
-      <c r="F130" s="17" t="inlineStr">
-        <is>
-          <t>081А</t>
-        </is>
-      </c>
-      <c r="G130" s="16" t="inlineStr">
-        <is>
-          <t>27.10 21:21</t>
-        </is>
-      </c>
-      <c r="H130" s="16" t="inlineStr">
-        <is>
-          <t>28.10 06:04</t>
-        </is>
-      </c>
-      <c r="I130" s="16" t="inlineStr">
-        <is>
-          <t>Москва, Восточный</t>
-        </is>
-      </c>
-      <c r="J130" s="18" t="n">
-        <v>3272</v>
-      </c>
-      <c r="K130" s="18" t="n">
-        <v>3272</v>
-      </c>
-      <c r="L130" s="16" t="inlineStr">
-        <is>
-          <t>Восточный вокзал → МЦД/метро до Казанского (~30 мин) → электричка + такси (07:22 → 09:15)</t>
-        </is>
-      </c>
-      <c r="M130" s="16" t="inlineStr">
-        <is>
-          <t>~09:30</t>
-        </is>
-      </c>
-      <c r="N130" s="16" t="inlineStr">
-        <is>
-          <t>ранний заезд</t>
-        </is>
-      </c>
-      <c r="O130" s="19" t="inlineStr">
+      <c r="D130" s="10" t="inlineStr">
+        <is>
+          <t>Удобный</t>
+        </is>
+      </c>
+      <c r="E130" s="10" t="inlineStr">
+        <is>
+          <t>Поезд «Смена — А. Бетанкур», купе</t>
+        </is>
+      </c>
+      <c r="F130" s="10" t="inlineStr">
+        <is>
+          <t>025А</t>
+        </is>
+      </c>
+      <c r="G130" s="5" t="inlineStr">
+        <is>
+          <t>27.10 23:40</t>
+        </is>
+      </c>
+      <c r="H130" s="5" t="inlineStr">
+        <is>
+          <t>28.10 07:45</t>
+        </is>
+      </c>
+      <c r="I130" s="5" t="inlineStr">
+        <is>
+          <t>Москва, Ленинградский</t>
+        </is>
+      </c>
+      <c r="J130" s="9" t="n">
+        <v>3975</v>
+      </c>
+      <c r="K130" s="9" t="n">
+        <v>3975</v>
+      </c>
+      <c r="L130" s="5" t="inlineStr">
+        <is>
+          <t>Ленинградский вокзал → через площадь на Казанский (5 мин) → электричка + такси (08:47 РЭКС → 10:28)</t>
+        </is>
+      </c>
+      <c r="M130" s="5" t="inlineStr">
+        <is>
+          <t>~10:45</t>
+        </is>
+      </c>
+      <c r="N130" s="5" t="inlineStr"/>
+      <c r="O130" s="20" t="inlineStr">
         <is>
           <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2004000&amp;nnst2=2000000</t>
         </is>
       </c>
-      <c r="P130" s="16" t="inlineStr">
-        <is>
-          <t>Вечером сел — утром в Москве</t>
-        </is>
-      </c>
-      <c r="Q130" s="16" t="inlineStr">
+      <c r="P130" s="5" t="inlineStr">
+        <is>
+          <t>Ленинградский и Казанский — на одной площади. Также «Сапсан» 28.10 05:30→09:23, 3 830 ₽ (→ 09:48 → 11:36)</t>
+        </is>
+      </c>
+      <c r="Q130" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -14171,34 +14171,34 @@
       <c r="B131" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C131" s="10" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D131" s="10" t="inlineStr">
-        <is>
-          <t>Удобный</t>
-        </is>
-      </c>
-      <c r="E131" s="10" t="inlineStr">
-        <is>
-          <t>Поезд «Смена — А. Бетанкур», купе</t>
-        </is>
-      </c>
-      <c r="F131" s="10" t="inlineStr">
-        <is>
-          <t>025А</t>
+      <c r="C131" s="7" t="inlineStr">
+        <is>
+          <t>В2: после 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D131" s="7" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E131" s="7" t="inlineStr">
+        <is>
+          <t>Ласточка, сидячий</t>
+        </is>
+      </c>
+      <c r="F131" s="7" t="inlineStr">
+        <is>
+          <t>723Р</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>27.10 23:40</t>
+          <t>28.10 05:35</t>
         </is>
       </c>
       <c r="H131" s="5" t="inlineStr">
         <is>
-          <t>28.10 07:45</t>
+          <t>28.10 11:13</t>
         </is>
       </c>
       <c r="I131" s="5" t="inlineStr">
@@ -14206,31 +14206,31 @@
           <t>Москва, Ленинградский</t>
         </is>
       </c>
-      <c r="J131" s="9" t="n">
-        <v>3975</v>
-      </c>
-      <c r="K131" s="9" t="n">
-        <v>3975</v>
+      <c r="J131" s="6" t="n">
+        <v>1121</v>
+      </c>
+      <c r="K131" s="6" t="n">
+        <v>1121</v>
       </c>
       <c r="L131" s="5" t="inlineStr">
         <is>
-          <t>Ленинградский вокзал → через площадь на Казанский (5 мин) → электричка + такси (08:47 РЭКС → 10:28)</t>
+          <t>Ленинградский вокзал → через площадь на Казанский (5 мин) → электричка + такси (12:54 → 15:15)</t>
         </is>
       </c>
       <c r="M131" s="5" t="inlineStr">
         <is>
-          <t>~10:45</t>
+          <t>~15:30</t>
         </is>
       </c>
       <c r="N131" s="5" t="inlineStr"/>
       <c r="O131" s="20" t="inlineStr">
         <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2004000&amp;nnst2=2000000</t>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2004000&amp;nnst2=2000000</t>
         </is>
       </c>
       <c r="P131" s="5" t="inlineStr">
         <is>
-          <t>Ленинградский и Казанский — на одной площади. Также «Сапсан» 28.10 05:30→09:23, 3 830 ₽ (→ 09:48 → 11:36)</t>
+          <t>Самый дешёвый; к экскурсии в 16:00 успевает</t>
         </is>
       </c>
       <c r="Q131" s="5" t="inlineStr">
@@ -14250,7 +14250,7 @@
       </c>
       <c r="C132" s="7" t="inlineStr">
         <is>
-          <t>В2: после 15:00 28.10</t>
+          <t>Обратно</t>
         </is>
       </c>
       <c r="D132" s="7" t="inlineStr">
@@ -14260,61 +14260,49 @@
       </c>
       <c r="E132" s="7" t="inlineStr">
         <is>
-          <t>Ласточка, сидячий</t>
+          <t>Поезд «Аврора», сидячий</t>
         </is>
       </c>
       <c r="F132" s="7" t="inlineStr">
         <is>
-          <t>723Р</t>
+          <t>750У</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
-          <t>28.10 05:35</t>
+          <t>30.10 22:30</t>
         </is>
       </c>
       <c r="H132" s="5" t="inlineStr">
         <is>
-          <t>28.10 11:13</t>
+          <t>31.10 05:00</t>
         </is>
       </c>
       <c r="I132" s="5" t="inlineStr">
         <is>
-          <t>Москва, Ленинградский</t>
+          <t>СПб, Московский вокзал</t>
         </is>
       </c>
       <c r="J132" s="6" t="n">
-        <v>1121</v>
+        <v>2185</v>
       </c>
       <c r="K132" s="6" t="n">
-        <v>1121</v>
+        <v>2185</v>
       </c>
       <c r="L132" s="5" t="inlineStr">
         <is>
-          <t>Ленинградский вокзал → через площадь на Казанский (5 мин) → электричка + такси (12:54 → 15:15)</t>
-        </is>
-      </c>
-      <c r="M132" s="5" t="inlineStr">
-        <is>
-          <t>~15:30</t>
-        </is>
-      </c>
+          <t>Электричка 18:43 → Казанский 20:47 → Ленинградский</t>
+        </is>
+      </c>
+      <c r="M132" s="5" t="inlineStr"/>
       <c r="N132" s="5" t="inlineStr"/>
       <c r="O132" s="20" t="inlineStr">
         <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2004000&amp;nnst2=2000000</t>
-        </is>
-      </c>
-      <c r="P132" s="5" t="inlineStr">
-        <is>
-          <t>Самый дешёвый; к экскурсии в 16:00 успевает</t>
-        </is>
-      </c>
-      <c r="Q132" s="5" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
-      </c>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2004000</t>
+        </is>
+      </c>
+      <c r="P132" s="5" t="inlineStr"/>
+      <c r="Q132" s="5" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
@@ -14325,34 +14313,34 @@
       <c r="B133" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C133" s="7" t="inlineStr">
+      <c r="C133" s="10" t="inlineStr">
         <is>
           <t>Обратно</t>
         </is>
       </c>
-      <c r="D133" s="7" t="inlineStr">
-        <is>
-          <t>Самый дешёвый</t>
-        </is>
-      </c>
-      <c r="E133" s="7" t="inlineStr">
-        <is>
-          <t>Поезд «Аврора», сидячий</t>
-        </is>
-      </c>
-      <c r="F133" s="7" t="inlineStr">
-        <is>
-          <t>750У</t>
+      <c r="D133" s="10" t="inlineStr">
+        <is>
+          <t>Удобный</t>
+        </is>
+      </c>
+      <c r="E133" s="10" t="inlineStr">
+        <is>
+          <t>Поезд «Смена — А. Бетанкур», купе</t>
+        </is>
+      </c>
+      <c r="F133" s="10" t="inlineStr">
+        <is>
+          <t>026А</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>30.10 22:30</t>
+          <t>30.10 23:10</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
         <is>
-          <t>31.10 05:00</t>
+          <t>31.10 07:07</t>
         </is>
       </c>
       <c r="I133" s="5" t="inlineStr">
@@ -14360,15 +14348,15 @@
           <t>СПб, Московский вокзал</t>
         </is>
       </c>
-      <c r="J133" s="6" t="n">
-        <v>2185</v>
-      </c>
-      <c r="K133" s="6" t="n">
-        <v>2185</v>
+      <c r="J133" s="9" t="n">
+        <v>5093</v>
+      </c>
+      <c r="K133" s="9" t="n">
+        <v>5093</v>
       </c>
       <c r="L133" s="5" t="inlineStr">
         <is>
-          <t>Электричка 18:43 → Казанский 20:47 → Ленинградский</t>
+          <t>Электричка 18:43 или 19:43 → Казанский → Ленинградский</t>
         </is>
       </c>
       <c r="M133" s="5" t="inlineStr"/>
@@ -14378,150 +14366,162 @@
           <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2004000</t>
         </is>
       </c>
-      <c r="P133" s="5" t="inlineStr"/>
+      <c r="P133" s="5" t="inlineStr">
+        <is>
+          <t>Ночь в купе. Также 028А 22:08, купе 4 256</t>
+        </is>
+      </c>
       <c r="Q133" s="5" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="5" t="inlineStr">
-        <is>
-          <t>Санкт-Петербург</t>
-        </is>
-      </c>
-      <c r="B134" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C134" s="10" t="inlineStr">
-        <is>
-          <t>Обратно</t>
-        </is>
-      </c>
-      <c r="D134" s="10" t="inlineStr">
+      <c r="A134" s="15" t="inlineStr">
+        <is>
+          <t>Нижний Новгород</t>
+        </is>
+      </c>
+      <c r="B134" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C134" s="17" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D134" s="17" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E134" s="17" t="inlineStr">
+        <is>
+          <t>Ласточка, сидячий</t>
+        </is>
+      </c>
+      <c r="F134" s="17" t="inlineStr">
+        <is>
+          <t>723А</t>
+        </is>
+      </c>
+      <c r="G134" s="16" t="inlineStr">
+        <is>
+          <t>28.10 04:51</t>
+        </is>
+      </c>
+      <c r="H134" s="16" t="inlineStr">
+        <is>
+          <t>28.10 09:09</t>
+        </is>
+      </c>
+      <c r="I134" s="16" t="inlineStr">
+        <is>
+          <t>Москва, Восточный</t>
+        </is>
+      </c>
+      <c r="J134" s="18" t="n">
+        <v>2435</v>
+      </c>
+      <c r="K134" s="18" t="n">
+        <v>2435</v>
+      </c>
+      <c r="L134" s="16" t="inlineStr">
+        <is>
+          <t>Восточный вокзал → МЦД/метро до Казанского (~30 мин) → электричка + такси (09:48 впритык, иначе 12:54 → 15:15)</t>
+        </is>
+      </c>
+      <c r="M134" s="16" t="inlineStr">
+        <is>
+          <t>~12:00 / ~15:30</t>
+        </is>
+      </c>
+      <c r="N134" s="16" t="inlineStr"/>
+      <c r="O134" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2060000&amp;nnst2=2000000</t>
+        </is>
+      </c>
+      <c r="P134" s="16" t="inlineStr">
+        <is>
+          <t>Или своя машина: ~430 км, ~6 ч</t>
+        </is>
+      </c>
+      <c r="Q134" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>Нижний Новгород</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C135" s="10" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D135" s="10" t="inlineStr">
         <is>
           <t>Удобный</t>
         </is>
       </c>
-      <c r="E134" s="10" t="inlineStr">
-        <is>
-          <t>Поезд «Смена — А. Бетанкур», купе</t>
-        </is>
-      </c>
-      <c r="F134" s="10" t="inlineStr">
-        <is>
-          <t>026А</t>
-        </is>
-      </c>
-      <c r="G134" s="5" t="inlineStr">
-        <is>
-          <t>30.10 23:10</t>
-        </is>
-      </c>
-      <c r="H134" s="5" t="inlineStr">
-        <is>
-          <t>31.10 07:07</t>
-        </is>
-      </c>
-      <c r="I134" s="5" t="inlineStr">
-        <is>
-          <t>СПб, Московский вокзал</t>
-        </is>
-      </c>
-      <c r="J134" s="9" t="n">
-        <v>5093</v>
-      </c>
-      <c r="K134" s="9" t="n">
-        <v>5093</v>
-      </c>
-      <c r="L134" s="5" t="inlineStr">
-        <is>
-          <t>Электричка 18:43 или 19:43 → Казанский → Ленинградский</t>
-        </is>
-      </c>
-      <c r="M134" s="5" t="inlineStr"/>
-      <c r="N134" s="5" t="inlineStr"/>
-      <c r="O134" s="20" t="inlineStr">
-        <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2004000</t>
-        </is>
-      </c>
-      <c r="P134" s="5" t="inlineStr">
-        <is>
-          <t>Ночь в купе. Также 028А 22:08, купе 4 256</t>
-        </is>
-      </c>
-      <c r="Q134" s="5" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="15" t="inlineStr">
-        <is>
-          <t>Нижний Новгород</t>
-        </is>
-      </c>
-      <c r="B135" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C135" s="17" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D135" s="17" t="inlineStr">
-        <is>
-          <t>Самый дешёвый</t>
-        </is>
-      </c>
-      <c r="E135" s="17" t="inlineStr">
-        <is>
-          <t>Ласточка, сидячий</t>
-        </is>
-      </c>
-      <c r="F135" s="17" t="inlineStr">
-        <is>
-          <t>723А</t>
-        </is>
-      </c>
-      <c r="G135" s="16" t="inlineStr">
-        <is>
-          <t>28.10 04:51</t>
-        </is>
-      </c>
-      <c r="H135" s="16" t="inlineStr">
-        <is>
-          <t>28.10 09:09</t>
-        </is>
-      </c>
-      <c r="I135" s="16" t="inlineStr">
-        <is>
-          <t>Москва, Восточный</t>
-        </is>
-      </c>
-      <c r="J135" s="18" t="n">
-        <v>2435</v>
-      </c>
-      <c r="K135" s="18" t="n">
-        <v>2435</v>
-      </c>
-      <c r="L135" s="16" t="inlineStr">
-        <is>
-          <t>Восточный вокзал → МЦД/метро до Казанского (~30 мин) → электричка + такси (09:48 впритык, иначе 12:54 → 15:15)</t>
-        </is>
-      </c>
-      <c r="M135" s="16" t="inlineStr">
-        <is>
-          <t>~12:00 / ~15:30</t>
-        </is>
-      </c>
-      <c r="N135" s="16" t="inlineStr"/>
-      <c r="O135" s="19" t="inlineStr">
+      <c r="E135" s="10" t="inlineStr">
+        <is>
+          <t>Поезд «Вятка», купе</t>
+        </is>
+      </c>
+      <c r="F135" s="10" t="inlineStr">
+        <is>
+          <t>031Г</t>
+        </is>
+      </c>
+      <c r="G135" s="5" t="inlineStr">
+        <is>
+          <t>28.10 03:05</t>
+        </is>
+      </c>
+      <c r="H135" s="5" t="inlineStr">
+        <is>
+          <t>28.10 09:27</t>
+        </is>
+      </c>
+      <c r="I135" s="5" t="inlineStr">
+        <is>
+          <t>Москва, Ярославский</t>
+        </is>
+      </c>
+      <c r="J135" s="9" t="n">
+        <v>4460</v>
+      </c>
+      <c r="K135" s="9" t="n">
+        <v>4460</v>
+      </c>
+      <c r="L135" s="5" t="inlineStr">
+        <is>
+          <t>Ярославский вокзал → через площадь на Казанский (5 мин) → электричка + такси (09:48 → 11:36)</t>
+        </is>
+      </c>
+      <c r="M135" s="5" t="inlineStr">
+        <is>
+          <t>~12:00</t>
+        </is>
+      </c>
+      <c r="N135" s="5" t="inlineStr"/>
+      <c r="O135" s="20" t="inlineStr">
         <is>
           <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2060000&amp;nnst2=2000000</t>
         </is>
       </c>
-      <c r="P135" s="16" t="inlineStr">
-        <is>
-          <t>Или своя машина: ~430 км, ~6 ч</t>
-        </is>
-      </c>
-      <c r="Q135" s="16" t="inlineStr">
+      <c r="P135" s="5" t="inlineStr">
+        <is>
+          <t>Ночной поезд, посадка в 03:05</t>
+        </is>
+      </c>
+      <c r="Q135" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -14536,55 +14536,55 @@
       <c r="B136" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C136" s="10" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D136" s="10" t="inlineStr">
-        <is>
-          <t>Удобный</t>
-        </is>
-      </c>
-      <c r="E136" s="10" t="inlineStr">
-        <is>
-          <t>Поезд «Вятка», купе</t>
-        </is>
-      </c>
-      <c r="F136" s="10" t="inlineStr">
-        <is>
-          <t>031Г</t>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>В2: после 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="inlineStr">
+        <is>
+          <t>Поезд «Буревестник», сидячий</t>
+        </is>
+      </c>
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>705Э</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
         <is>
-          <t>28.10 03:05</t>
+          <t>28.10 07:20</t>
         </is>
       </c>
       <c r="H136" s="5" t="inlineStr">
         <is>
-          <t>28.10 09:27</t>
+          <t>28.10 11:34</t>
         </is>
       </c>
       <c r="I136" s="5" t="inlineStr">
         <is>
-          <t>Москва, Ярославский</t>
-        </is>
-      </c>
-      <c r="J136" s="9" t="n">
-        <v>4460</v>
-      </c>
-      <c r="K136" s="9" t="n">
-        <v>4460</v>
+          <t>Москва, Восточный</t>
+        </is>
+      </c>
+      <c r="J136" s="21" t="n">
+        <v>2136</v>
+      </c>
+      <c r="K136" s="21" t="n">
+        <v>2136</v>
       </c>
       <c r="L136" s="5" t="inlineStr">
         <is>
-          <t>Ярославский вокзал → через площадь на Казанский (5 мин) → электричка + такси (09:48 → 11:36)</t>
+          <t>Восточный вокзал → МЦД/метро до Казанского (~30 мин) → электричка + такси (12:54 → 15:15)</t>
         </is>
       </c>
       <c r="M136" s="5" t="inlineStr">
         <is>
-          <t>~12:00</t>
+          <t>~15:30</t>
         </is>
       </c>
       <c r="N136" s="5" t="inlineStr"/>
@@ -14593,11 +14593,7 @@
           <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2060000&amp;nnst2=2000000</t>
         </is>
       </c>
-      <c r="P136" s="5" t="inlineStr">
-        <is>
-          <t>Ночной поезд, посадка в 03:05</t>
-        </is>
-      </c>
+      <c r="P136" s="5" t="inlineStr"/>
       <c r="Q136" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
@@ -14613,69 +14609,65 @@
       <c r="B137" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C137" s="5" t="inlineStr">
-        <is>
-          <t>В2: после 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D137" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E137" s="5" t="inlineStr">
-        <is>
-          <t>Поезд «Буревестник», сидячий</t>
-        </is>
-      </c>
-      <c r="F137" s="5" t="inlineStr">
-        <is>
-          <t>705Э</t>
+      <c r="C137" s="7" t="inlineStr">
+        <is>
+          <t>Обратно</t>
+        </is>
+      </c>
+      <c r="D137" s="7" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E137" s="7" t="inlineStr">
+        <is>
+          <t>Ласточка, сидячий</t>
+        </is>
+      </c>
+      <c r="F137" s="7" t="inlineStr">
+        <is>
+          <t>723Я</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>28.10 07:20</t>
+          <t>30.10 21:15</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
         <is>
-          <t>28.10 11:34</t>
+          <t>31.10 01:15</t>
         </is>
       </c>
       <c r="I137" s="5" t="inlineStr">
         <is>
-          <t>Москва, Восточный</t>
-        </is>
-      </c>
-      <c r="J137" s="21" t="n">
-        <v>2136</v>
-      </c>
-      <c r="K137" s="21" t="n">
-        <v>2136</v>
+          <t>Нижний Новгород</t>
+        </is>
+      </c>
+      <c r="J137" s="6" t="n">
+        <v>2347</v>
+      </c>
+      <c r="K137" s="6" t="n">
+        <v>2347</v>
       </c>
       <c r="L137" s="5" t="inlineStr">
         <is>
-          <t>Восточный вокзал → МЦД/метро до Казанского (~30 мин) → электричка + такси (12:54 → 15:15)</t>
-        </is>
-      </c>
-      <c r="M137" s="5" t="inlineStr">
-        <is>
-          <t>~15:30</t>
-        </is>
-      </c>
+          <t>Электричка 18:43 → Казанский 20:47 → Восточный</t>
+        </is>
+      </c>
+      <c r="M137" s="5" t="inlineStr"/>
       <c r="N137" s="5" t="inlineStr"/>
       <c r="O137" s="20" t="inlineStr">
         <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2060000&amp;nnst2=2000000</t>
-        </is>
-      </c>
-      <c r="P137" s="5" t="inlineStr"/>
-      <c r="Q137" s="5" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
-      </c>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2060000</t>
+        </is>
+      </c>
+      <c r="P137" s="5" t="inlineStr">
+        <is>
+          <t>Дома ночью</t>
+        </is>
+      </c>
+      <c r="Q137" s="5" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
@@ -14686,34 +14678,34 @@
       <c r="B138" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C138" s="7" t="inlineStr">
+      <c r="C138" s="10" t="inlineStr">
         <is>
           <t>Обратно</t>
         </is>
       </c>
-      <c r="D138" s="7" t="inlineStr">
-        <is>
-          <t>Самый дешёвый</t>
-        </is>
-      </c>
-      <c r="E138" s="7" t="inlineStr">
-        <is>
-          <t>Ласточка, сидячий</t>
-        </is>
-      </c>
-      <c r="F138" s="7" t="inlineStr">
-        <is>
-          <t>723Я</t>
+      <c r="D138" s="10" t="inlineStr">
+        <is>
+          <t>Удобный</t>
+        </is>
+      </c>
+      <c r="E138" s="10" t="inlineStr">
+        <is>
+          <t>Поезд «Нижегородец», купе</t>
+        </is>
+      </c>
+      <c r="F138" s="10" t="inlineStr">
+        <is>
+          <t>036Щ</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>30.10 21:15</t>
+          <t>30.10 23:10</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
         <is>
-          <t>31.10 01:15</t>
+          <t>31.10 07:10</t>
         </is>
       </c>
       <c r="I138" s="5" t="inlineStr">
@@ -14721,15 +14713,15 @@
           <t>Нижний Новгород</t>
         </is>
       </c>
-      <c r="J138" s="6" t="n">
-        <v>2347</v>
-      </c>
-      <c r="K138" s="6" t="n">
-        <v>2347</v>
+      <c r="J138" s="9" t="n">
+        <v>5172</v>
+      </c>
+      <c r="K138" s="9" t="n">
+        <v>5172</v>
       </c>
       <c r="L138" s="5" t="inlineStr">
         <is>
-          <t>Электричка 18:43 → Казанский 20:47 → Восточный</t>
+          <t>Электричка → Казанский → Ярославский (через площадь)</t>
         </is>
       </c>
       <c r="M138" s="5" t="inlineStr"/>
@@ -14741,152 +14733,160 @@
       </c>
       <c r="P138" s="5" t="inlineStr">
         <is>
-          <t>Дома ночью</t>
+          <t>Ночь в купе. Также 010Н 22:30, купе 4 040</t>
         </is>
       </c>
       <c r="Q138" s="5" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="5" t="inlineStr">
-        <is>
-          <t>Нижний Новгород</t>
-        </is>
-      </c>
-      <c r="B139" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C139" s="10" t="inlineStr">
-        <is>
-          <t>Обратно</t>
-        </is>
-      </c>
-      <c r="D139" s="10" t="inlineStr">
+      <c r="A139" s="15" t="inlineStr">
+        <is>
+          <t>Смоленск</t>
+        </is>
+      </c>
+      <c r="B139" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C139" s="17" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D139" s="17" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E139" s="17" t="inlineStr">
+        <is>
+          <t>Ласточка-премиум, сидячий</t>
+        </is>
+      </c>
+      <c r="F139" s="17" t="inlineStr">
+        <is>
+          <t>738М</t>
+        </is>
+      </c>
+      <c r="G139" s="16" t="inlineStr">
+        <is>
+          <t>28.10 07:29</t>
+        </is>
+      </c>
+      <c r="H139" s="16" t="inlineStr">
+        <is>
+          <t>28.10 11:53</t>
+        </is>
+      </c>
+      <c r="I139" s="16" t="inlineStr">
+        <is>
+          <t>Москва, Белорусский</t>
+        </is>
+      </c>
+      <c r="J139" s="18" t="n">
+        <v>1832</v>
+      </c>
+      <c r="K139" s="18" t="n">
+        <v>1832</v>
+      </c>
+      <c r="L139" s="16" t="inlineStr">
+        <is>
+          <t>Белорусский → метро до Комсомольской (~15 мин) → электричка + такси (12:54 → 15:15)</t>
+        </is>
+      </c>
+      <c r="M139" s="16" t="inlineStr">
+        <is>
+          <t>~15:30</t>
+        </is>
+      </c>
+      <c r="N139" s="16" t="inlineStr"/>
+      <c r="O139" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2000170&amp;nnst2=2000000</t>
+        </is>
+      </c>
+      <c r="P139" s="16" t="inlineStr">
+        <is>
+          <t>К экскурсии в 16:00 успевает</t>
+        </is>
+      </c>
+      <c r="Q139" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t>Смоленск</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C140" s="10" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D140" s="10" t="inlineStr">
         <is>
           <t>Удобный</t>
         </is>
       </c>
-      <c r="E139" s="10" t="inlineStr">
-        <is>
-          <t>Поезд «Нижегородец», купе</t>
-        </is>
-      </c>
-      <c r="F139" s="10" t="inlineStr">
-        <is>
-          <t>036Щ</t>
-        </is>
-      </c>
-      <c r="G139" s="5" t="inlineStr">
-        <is>
-          <t>30.10 23:10</t>
-        </is>
-      </c>
-      <c r="H139" s="5" t="inlineStr">
-        <is>
-          <t>31.10 07:10</t>
-        </is>
-      </c>
-      <c r="I139" s="5" t="inlineStr">
-        <is>
-          <t>Нижний Новгород</t>
-        </is>
-      </c>
-      <c r="J139" s="9" t="n">
-        <v>5172</v>
-      </c>
-      <c r="K139" s="9" t="n">
-        <v>5172</v>
-      </c>
-      <c r="L139" s="5" t="inlineStr">
-        <is>
-          <t>Электричка → Казанский → Ярославский (через площадь)</t>
-        </is>
-      </c>
-      <c r="M139" s="5" t="inlineStr"/>
-      <c r="N139" s="5" t="inlineStr"/>
-      <c r="O139" s="20" t="inlineStr">
-        <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2060000</t>
-        </is>
-      </c>
-      <c r="P139" s="5" t="inlineStr">
-        <is>
-          <t>Ночь в купе. Также 010Н 22:30, купе 4 040</t>
-        </is>
-      </c>
-      <c r="Q139" s="5" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="15" t="inlineStr">
-        <is>
-          <t>Смоленск</t>
-        </is>
-      </c>
-      <c r="B140" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C140" s="17" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D140" s="17" t="inlineStr">
-        <is>
-          <t>Самый дешёвый</t>
-        </is>
-      </c>
-      <c r="E140" s="17" t="inlineStr">
-        <is>
-          <t>Ласточка-премиум, сидячий</t>
-        </is>
-      </c>
-      <c r="F140" s="17" t="inlineStr">
-        <is>
-          <t>738М</t>
-        </is>
-      </c>
-      <c r="G140" s="16" t="inlineStr">
-        <is>
-          <t>28.10 07:29</t>
-        </is>
-      </c>
-      <c r="H140" s="16" t="inlineStr">
-        <is>
-          <t>28.10 11:53</t>
-        </is>
-      </c>
-      <c r="I140" s="16" t="inlineStr">
+      <c r="E140" s="10" t="inlineStr">
+        <is>
+          <t>Поезд, купе</t>
+        </is>
+      </c>
+      <c r="F140" s="10" t="inlineStr">
+        <is>
+          <t>008Б</t>
+        </is>
+      </c>
+      <c r="G140" s="5" t="inlineStr">
+        <is>
+          <t>28.10 01:35</t>
+        </is>
+      </c>
+      <c r="H140" s="5" t="inlineStr">
+        <is>
+          <t>28.10 06:56</t>
+        </is>
+      </c>
+      <c r="I140" s="5" t="inlineStr">
         <is>
           <t>Москва, Белорусский</t>
         </is>
       </c>
-      <c r="J140" s="18" t="n">
-        <v>1832</v>
-      </c>
-      <c r="K140" s="18" t="n">
-        <v>1832</v>
-      </c>
-      <c r="L140" s="16" t="inlineStr">
-        <is>
-          <t>Белорусский → метро до Комсомольской (~15 мин) → электричка + такси (12:54 → 15:15)</t>
-        </is>
-      </c>
-      <c r="M140" s="16" t="inlineStr">
-        <is>
-          <t>~15:30</t>
-        </is>
-      </c>
-      <c r="N140" s="16" t="inlineStr"/>
-      <c r="O140" s="19" t="inlineStr">
+      <c r="J140" s="9" t="n">
+        <v>4656</v>
+      </c>
+      <c r="K140" s="9" t="n">
+        <v>4656</v>
+      </c>
+      <c r="L140" s="5" t="inlineStr">
+        <is>
+          <t>Белорусский → метро до Комсомольской (~15 мин) → электричка + такси (08:47 РЭКС → 10:28)</t>
+        </is>
+      </c>
+      <c r="M140" s="5" t="inlineStr">
+        <is>
+          <t>~10:45</t>
+        </is>
+      </c>
+      <c r="N140" s="5" t="inlineStr"/>
+      <c r="O140" s="20" t="inlineStr">
         <is>
           <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2000170&amp;nnst2=2000000</t>
         </is>
       </c>
-      <c r="P140" s="16" t="inlineStr">
-        <is>
-          <t>К экскурсии в 16:00 успевает</t>
-        </is>
-      </c>
-      <c r="Q140" s="16" t="inlineStr">
+      <c r="P140" s="5" t="inlineStr">
+        <is>
+          <t>Ночной поезд</t>
+        </is>
+      </c>
+      <c r="Q140" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -14901,73 +14901,61 @@
       <c r="B141" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C141" s="10" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D141" s="10" t="inlineStr">
-        <is>
-          <t>Удобный</t>
-        </is>
-      </c>
-      <c r="E141" s="10" t="inlineStr">
+      <c r="C141" s="7" t="inlineStr">
+        <is>
+          <t>Обратно</t>
+        </is>
+      </c>
+      <c r="D141" s="7" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E141" s="7" t="inlineStr">
         <is>
           <t>Поезд, купе</t>
         </is>
       </c>
-      <c r="F141" s="10" t="inlineStr">
-        <is>
-          <t>008Б</t>
+      <c r="F141" s="7" t="inlineStr">
+        <is>
+          <t>027Б</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>28.10 01:35</t>
+          <t>30.10 23:30</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
         <is>
-          <t>28.10 06:56</t>
+          <t>31.10 04:39</t>
         </is>
       </c>
       <c r="I141" s="5" t="inlineStr">
         <is>
-          <t>Москва, Белорусский</t>
-        </is>
-      </c>
-      <c r="J141" s="9" t="n">
-        <v>4656</v>
-      </c>
-      <c r="K141" s="9" t="n">
-        <v>4656</v>
+          <t>Смоленск</t>
+        </is>
+      </c>
+      <c r="J141" s="6" t="n">
+        <v>4022</v>
+      </c>
+      <c r="K141" s="6" t="n">
+        <v>4022</v>
       </c>
       <c r="L141" s="5" t="inlineStr">
         <is>
-          <t>Белорусский → метро до Комсомольской (~15 мин) → электричка + такси (08:47 РЭКС → 10:28)</t>
-        </is>
-      </c>
-      <c r="M141" s="5" t="inlineStr">
-        <is>
-          <t>~10:45</t>
-        </is>
-      </c>
+          <t>Электричка 18:43 → Казанский → метро до Белорусской</t>
+        </is>
+      </c>
+      <c r="M141" s="5" t="inlineStr"/>
       <c r="N141" s="5" t="inlineStr"/>
       <c r="O141" s="20" t="inlineStr">
         <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2000170&amp;nnst2=2000000</t>
-        </is>
-      </c>
-      <c r="P141" s="5" t="inlineStr">
-        <is>
-          <t>Ночной поезд</t>
-        </is>
-      </c>
-      <c r="Q141" s="5" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
-      </c>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2000170</t>
+        </is>
+      </c>
+      <c r="P141" s="5" t="inlineStr"/>
+      <c r="Q141" s="5" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
@@ -14978,34 +14966,34 @@
       <c r="B142" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C142" s="7" t="inlineStr">
+      <c r="C142" s="10" t="inlineStr">
         <is>
           <t>Обратно</t>
         </is>
       </c>
-      <c r="D142" s="7" t="inlineStr">
-        <is>
-          <t>Самый дешёвый</t>
-        </is>
-      </c>
-      <c r="E142" s="7" t="inlineStr">
+      <c r="D142" s="10" t="inlineStr">
+        <is>
+          <t>Удобный</t>
+        </is>
+      </c>
+      <c r="E142" s="10" t="inlineStr">
         <is>
           <t>Поезд, купе</t>
         </is>
       </c>
-      <c r="F142" s="7" t="inlineStr">
-        <is>
-          <t>027Б</t>
+      <c r="F142" s="10" t="inlineStr">
+        <is>
+          <t>007М</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>30.10 23:30</t>
+          <t>30.10 22:12</t>
         </is>
       </c>
       <c r="H142" s="5" t="inlineStr">
         <is>
-          <t>31.10 04:39</t>
+          <t>31.10 02:39</t>
         </is>
       </c>
       <c r="I142" s="5" t="inlineStr">
@@ -15013,11 +15001,11 @@
           <t>Смоленск</t>
         </is>
       </c>
-      <c r="J142" s="6" t="n">
-        <v>4022</v>
-      </c>
-      <c r="K142" s="6" t="n">
-        <v>4022</v>
+      <c r="J142" s="9" t="n">
+        <v>4656</v>
+      </c>
+      <c r="K142" s="9" t="n">
+        <v>4656</v>
       </c>
       <c r="L142" s="5" t="inlineStr">
         <is>
@@ -15031,154 +15019,154 @@
           <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2000170</t>
         </is>
       </c>
-      <c r="P142" s="5" t="inlineStr"/>
+      <c r="P142" s="5" t="inlineStr">
+        <is>
+          <t>Или машина ~520 км, ~7 ч</t>
+        </is>
+      </c>
       <c r="Q142" s="5" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="5" t="inlineStr">
-        <is>
-          <t>Смоленск</t>
-        </is>
-      </c>
-      <c r="B143" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C143" s="10" t="inlineStr">
-        <is>
-          <t>Обратно</t>
-        </is>
-      </c>
-      <c r="D143" s="10" t="inlineStr">
+      <c r="A143" s="15" t="inlineStr">
+        <is>
+          <t>Тверь</t>
+        </is>
+      </c>
+      <c r="B143" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C143" s="17" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D143" s="17" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E143" s="17" t="inlineStr">
+        <is>
+          <t>Поезд «Аврора», сидячий</t>
+        </is>
+      </c>
+      <c r="F143" s="17" t="inlineStr">
+        <is>
+          <t>741У</t>
+        </is>
+      </c>
+      <c r="G143" s="16" t="inlineStr">
+        <is>
+          <t>28.10 10:16</t>
+        </is>
+      </c>
+      <c r="H143" s="16" t="inlineStr">
+        <is>
+          <t>28.10 11:55</t>
+        </is>
+      </c>
+      <c r="I143" s="16" t="inlineStr">
+        <is>
+          <t>Москва, Ленинградский</t>
+        </is>
+      </c>
+      <c r="J143" s="18" t="n">
+        <v>695</v>
+      </c>
+      <c r="K143" s="18" t="n">
+        <v>695</v>
+      </c>
+      <c r="L143" s="16" t="inlineStr">
+        <is>
+          <t>Ленинградский вокзал → через площадь на Казанский (5 мин) → электричка + такси (12:54 → 15:15)</t>
+        </is>
+      </c>
+      <c r="M143" s="16" t="inlineStr">
+        <is>
+          <t>~15:30</t>
+        </is>
+      </c>
+      <c r="N143" s="16" t="inlineStr"/>
+      <c r="O143" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2004600&amp;nnst2=2000000</t>
+        </is>
+      </c>
+      <c r="P143" s="16" t="inlineStr">
+        <is>
+          <t>Также Ласточка 723Р 09:19→11:13, 611 ₽</t>
+        </is>
+      </c>
+      <c r="Q143" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t>Тверь</t>
+        </is>
+      </c>
+      <c r="B144" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C144" s="10" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D144" s="10" t="inlineStr">
         <is>
           <t>Удобный</t>
         </is>
       </c>
-      <c r="E143" s="10" t="inlineStr">
-        <is>
-          <t>Поезд, купе</t>
-        </is>
-      </c>
-      <c r="F143" s="10" t="inlineStr">
-        <is>
-          <t>007М</t>
-        </is>
-      </c>
-      <c r="G143" s="5" t="inlineStr">
-        <is>
-          <t>30.10 22:12</t>
-        </is>
-      </c>
-      <c r="H143" s="5" t="inlineStr">
-        <is>
-          <t>31.10 02:39</t>
-        </is>
-      </c>
-      <c r="I143" s="5" t="inlineStr">
-        <is>
-          <t>Смоленск</t>
-        </is>
-      </c>
-      <c r="J143" s="9" t="n">
-        <v>4656</v>
-      </c>
-      <c r="K143" s="9" t="n">
-        <v>4656</v>
-      </c>
-      <c r="L143" s="5" t="inlineStr">
-        <is>
-          <t>Электричка 18:43 → Казанский → метро до Белорусской</t>
-        </is>
-      </c>
-      <c r="M143" s="5" t="inlineStr"/>
-      <c r="N143" s="5" t="inlineStr"/>
-      <c r="O143" s="20" t="inlineStr">
-        <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2000170</t>
-        </is>
-      </c>
-      <c r="P143" s="5" t="inlineStr">
-        <is>
-          <t>Или машина ~520 км, ~7 ч</t>
-        </is>
-      </c>
-      <c r="Q143" s="5" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="15" t="inlineStr">
-        <is>
-          <t>Тверь</t>
-        </is>
-      </c>
-      <c r="B144" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C144" s="17" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D144" s="17" t="inlineStr">
-        <is>
-          <t>Самый дешёвый</t>
-        </is>
-      </c>
-      <c r="E144" s="17" t="inlineStr">
-        <is>
-          <t>Поезд «Аврора», сидячий</t>
-        </is>
-      </c>
-      <c r="F144" s="17" t="inlineStr">
-        <is>
-          <t>741У</t>
-        </is>
-      </c>
-      <c r="G144" s="16" t="inlineStr">
-        <is>
-          <t>28.10 10:16</t>
-        </is>
-      </c>
-      <c r="H144" s="16" t="inlineStr">
-        <is>
-          <t>28.10 11:55</t>
-        </is>
-      </c>
-      <c r="I144" s="16" t="inlineStr">
-        <is>
-          <t>Москва, Ленинградский</t>
-        </is>
-      </c>
-      <c r="J144" s="18" t="n">
-        <v>695</v>
-      </c>
-      <c r="K144" s="18" t="n">
-        <v>695</v>
-      </c>
-      <c r="L144" s="16" t="inlineStr">
-        <is>
-          <t>Ленинградский вокзал → через площадь на Казанский (5 мин) → электричка + такси (12:54 → 15:15)</t>
-        </is>
-      </c>
-      <c r="M144" s="16" t="inlineStr">
-        <is>
-          <t>~15:30</t>
-        </is>
-      </c>
-      <c r="N144" s="16" t="inlineStr"/>
-      <c r="O144" s="19" t="inlineStr">
-        <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2004600&amp;nnst2=2000000</t>
-        </is>
-      </c>
-      <c r="P144" s="16" t="inlineStr">
-        <is>
-          <t>Также Ласточка 723Р 09:19→11:13, 611 ₽</t>
-        </is>
-      </c>
-      <c r="Q144" s="16" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
-      </c>
+      <c r="E144" s="10" t="inlineStr">
+        <is>
+          <t>Своя машина</t>
+        </is>
+      </c>
+      <c r="F144" s="10" t="inlineStr"/>
+      <c r="G144" s="5" t="inlineStr">
+        <is>
+          <t>28.10 ~09:30</t>
+        </is>
+      </c>
+      <c r="H144" s="5" t="inlineStr">
+        <is>
+          <t>28.10 ~13:30</t>
+        </is>
+      </c>
+      <c r="I144" s="5" t="inlineStr">
+        <is>
+          <t>Коломна</t>
+        </is>
+      </c>
+      <c r="J144" s="9" t="n">
+        <v>1885</v>
+      </c>
+      <c r="K144" s="9" t="n">
+        <v>1885</v>
+      </c>
+      <c r="L144" s="5" t="inlineStr">
+        <is>
+          <t>~290 км через ЦКАД, ~4 ч</t>
+        </is>
+      </c>
+      <c r="M144" s="5" t="inlineStr">
+        <is>
+          <t>~13:30</t>
+        </is>
+      </c>
+      <c r="N144" s="5" t="inlineStr"/>
+      <c r="O144" s="5" t="inlineStr"/>
+      <c r="P144" s="5" t="inlineStr">
+        <is>
+          <t>Топливо ~3 770 ₽ туда-обратно на машину</t>
+        </is>
+      </c>
+      <c r="Q144" s="5" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
@@ -15189,211 +15177,211 @@
       <c r="B145" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C145" s="10" t="inlineStr">
+      <c r="C145" s="7" t="inlineStr">
+        <is>
+          <t>Обратно</t>
+        </is>
+      </c>
+      <c r="D145" s="7" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E145" s="7" t="inlineStr">
+        <is>
+          <t>Поезд «Аврора», сидячий</t>
+        </is>
+      </c>
+      <c r="F145" s="7" t="inlineStr">
+        <is>
+          <t>750У</t>
+        </is>
+      </c>
+      <c r="G145" s="5" t="inlineStr">
+        <is>
+          <t>30.10 22:30</t>
+        </is>
+      </c>
+      <c r="H145" s="5" t="inlineStr">
+        <is>
+          <t>31.10 ~00:05</t>
+        </is>
+      </c>
+      <c r="I145" s="5" t="inlineStr">
+        <is>
+          <t>Тверь</t>
+        </is>
+      </c>
+      <c r="J145" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K145" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L145" s="5" t="inlineStr">
+        <is>
+          <t>Электричка 18:43 → Казанский 20:47 → Ленинградский</t>
+        </is>
+      </c>
+      <c r="M145" s="5" t="inlineStr"/>
+      <c r="N145" s="5" t="inlineStr"/>
+      <c r="O145" s="20" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2004600</t>
+        </is>
+      </c>
+      <c r="P145" s="5" t="inlineStr">
+        <is>
+          <t>Цена ориентировочная, проверить</t>
+        </is>
+      </c>
+      <c r="Q145" s="5" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="15" t="inlineStr">
+        <is>
+          <t>Рязань</t>
+        </is>
+      </c>
+      <c r="B146" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C146" s="17" t="inlineStr">
         <is>
           <t>В1: к 15:00 28.10</t>
         </is>
       </c>
-      <c r="D145" s="10" t="inlineStr">
+      <c r="D146" s="17" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E146" s="17" t="inlineStr">
+        <is>
+          <t>Электричка «Стандарт плюс»</t>
+        </is>
+      </c>
+      <c r="F146" s="17" t="inlineStr">
+        <is>
+          <t>6993</t>
+        </is>
+      </c>
+      <c r="G146" s="16" t="inlineStr">
+        <is>
+          <t>28.10 05:18</t>
+        </is>
+      </c>
+      <c r="H146" s="16" t="inlineStr">
+        <is>
+          <t>28.10 06:54</t>
+        </is>
+      </c>
+      <c r="I146" s="16" t="inlineStr">
+        <is>
+          <t>Коломна</t>
+        </is>
+      </c>
+      <c r="J146" s="18" t="n">
+        <v>306</v>
+      </c>
+      <c r="K146" s="18" t="n">
+        <v>306</v>
+      </c>
+      <c r="L146" s="16" t="inlineStr">
+        <is>
+          <t>Ст. Коломна → такси 10 мин (~300 ₽)</t>
+        </is>
+      </c>
+      <c r="M146" s="16" t="inlineStr">
+        <is>
+          <t>~07:10</t>
+        </is>
+      </c>
+      <c r="N146" s="16" t="inlineStr">
+        <is>
+          <t>ранний заезд</t>
+        </is>
+      </c>
+      <c r="O146" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/rasp.php?st1=92502&amp;st2=11902&amp;date=28.10.2026</t>
+        </is>
+      </c>
+      <c r="P146" s="16" t="inlineStr">
+        <is>
+          <t>Следующая электричка только 14:36 (→16:17) — к экскурсии не успевает</t>
+        </is>
+      </c>
+      <c r="Q146" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="5" t="inlineStr">
+        <is>
+          <t>Рязань</t>
+        </is>
+      </c>
+      <c r="B147" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C147" s="10" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D147" s="10" t="inlineStr">
         <is>
           <t>Удобный</t>
         </is>
       </c>
-      <c r="E145" s="10" t="inlineStr">
+      <c r="E147" s="10" t="inlineStr">
         <is>
           <t>Своя машина</t>
         </is>
       </c>
-      <c r="F145" s="10" t="inlineStr"/>
-      <c r="G145" s="5" t="inlineStr">
-        <is>
-          <t>28.10 ~09:30</t>
-        </is>
-      </c>
-      <c r="H145" s="5" t="inlineStr">
-        <is>
-          <t>28.10 ~13:30</t>
-        </is>
-      </c>
-      <c r="I145" s="5" t="inlineStr">
+      <c r="F147" s="10" t="inlineStr"/>
+      <c r="G147" s="5" t="inlineStr">
+        <is>
+          <t>28.10 ~12:30</t>
+        </is>
+      </c>
+      <c r="H147" s="5" t="inlineStr">
+        <is>
+          <t>28.10 ~14:00</t>
+        </is>
+      </c>
+      <c r="I147" s="5" t="inlineStr">
         <is>
           <t>Коломна</t>
         </is>
       </c>
-      <c r="J145" s="9" t="n">
-        <v>1885</v>
-      </c>
-      <c r="K145" s="9" t="n">
-        <v>1885</v>
-      </c>
-      <c r="L145" s="5" t="inlineStr">
-        <is>
-          <t>~290 км через ЦКАД, ~4 ч</t>
-        </is>
-      </c>
-      <c r="M145" s="5" t="inlineStr">
-        <is>
-          <t>~13:30</t>
-        </is>
-      </c>
-      <c r="N145" s="5" t="inlineStr"/>
-      <c r="O145" s="5" t="inlineStr"/>
-      <c r="P145" s="5" t="inlineStr">
-        <is>
-          <t>Топливо ~3 770 ₽ туда-обратно на машину</t>
-        </is>
-      </c>
-      <c r="Q145" s="5" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="5" t="inlineStr">
-        <is>
-          <t>Тверь</t>
-        </is>
-      </c>
-      <c r="B146" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C146" s="7" t="inlineStr">
-        <is>
-          <t>Обратно</t>
-        </is>
-      </c>
-      <c r="D146" s="7" t="inlineStr">
-        <is>
-          <t>Самый дешёвый</t>
-        </is>
-      </c>
-      <c r="E146" s="7" t="inlineStr">
-        <is>
-          <t>Поезд «Аврора», сидячий</t>
-        </is>
-      </c>
-      <c r="F146" s="7" t="inlineStr">
-        <is>
-          <t>750У</t>
-        </is>
-      </c>
-      <c r="G146" s="5" t="inlineStr">
-        <is>
-          <t>30.10 22:30</t>
-        </is>
-      </c>
-      <c r="H146" s="5" t="inlineStr">
-        <is>
-          <t>31.10 ~00:05</t>
-        </is>
-      </c>
-      <c r="I146" s="5" t="inlineStr">
-        <is>
-          <t>Тверь</t>
-        </is>
-      </c>
-      <c r="J146" s="6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K146" s="6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L146" s="5" t="inlineStr">
-        <is>
-          <t>Электричка 18:43 → Казанский 20:47 → Ленинградский</t>
-        </is>
-      </c>
-      <c r="M146" s="5" t="inlineStr"/>
-      <c r="N146" s="5" t="inlineStr"/>
-      <c r="O146" s="20" t="inlineStr">
-        <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2004600</t>
-        </is>
-      </c>
-      <c r="P146" s="5" t="inlineStr">
-        <is>
-          <t>Цена ориентировочная, проверить</t>
-        </is>
-      </c>
-      <c r="Q146" s="5" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="15" t="inlineStr">
-        <is>
-          <t>Рязань</t>
-        </is>
-      </c>
-      <c r="B147" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C147" s="17" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D147" s="17" t="inlineStr">
-        <is>
-          <t>Самый дешёвый</t>
-        </is>
-      </c>
-      <c r="E147" s="17" t="inlineStr">
-        <is>
-          <t>Электричка «Стандарт плюс»</t>
-        </is>
-      </c>
-      <c r="F147" s="17" t="inlineStr">
-        <is>
-          <t>6993</t>
-        </is>
-      </c>
-      <c r="G147" s="16" t="inlineStr">
-        <is>
-          <t>28.10 05:18</t>
-        </is>
-      </c>
-      <c r="H147" s="16" t="inlineStr">
-        <is>
-          <t>28.10 06:54</t>
-        </is>
-      </c>
-      <c r="I147" s="16" t="inlineStr">
-        <is>
-          <t>Коломна</t>
-        </is>
-      </c>
-      <c r="J147" s="18" t="n">
-        <v>306</v>
-      </c>
-      <c r="K147" s="18" t="n">
-        <v>306</v>
-      </c>
-      <c r="L147" s="16" t="inlineStr">
-        <is>
-          <t>Ст. Коломна → такси 10 мин (~300 ₽)</t>
-        </is>
-      </c>
-      <c r="M147" s="16" t="inlineStr">
-        <is>
-          <t>~07:10</t>
-        </is>
-      </c>
-      <c r="N147" s="16" t="inlineStr">
-        <is>
-          <t>ранний заезд</t>
-        </is>
-      </c>
-      <c r="O147" s="19" t="inlineStr">
-        <is>
-          <t>https://www.tutu.ru/rasp.php?st1=92502&amp;st2=11902&amp;date=28.10.2026</t>
-        </is>
-      </c>
-      <c r="P147" s="16" t="inlineStr">
-        <is>
-          <t>Следующая электричка только 14:36 (→16:17) — к экскурсии не успевает</t>
-        </is>
-      </c>
-      <c r="Q147" s="16" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
-      </c>
+      <c r="J147" s="9" t="n">
+        <v>650</v>
+      </c>
+      <c r="K147" s="9" t="n">
+        <v>650</v>
+      </c>
+      <c r="L147" s="5" t="inlineStr">
+        <is>
+          <t>~100 км, ~1 ч 30 мин</t>
+        </is>
+      </c>
+      <c r="M147" s="5" t="inlineStr">
+        <is>
+          <t>~14:00</t>
+        </is>
+      </c>
+      <c r="N147" s="5" t="inlineStr"/>
+      <c r="O147" s="5" t="inlineStr"/>
+      <c r="P147" s="5" t="inlineStr">
+        <is>
+          <t>Топливо ~1 300 ₽ туда-обратно</t>
+        </is>
+      </c>
+      <c r="Q147" s="5" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
@@ -15404,199 +15392,199 @@
       <c r="B148" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C148" s="10" t="inlineStr">
+      <c r="C148" s="7" t="inlineStr">
+        <is>
+          <t>Обратно</t>
+        </is>
+      </c>
+      <c r="D148" s="7" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E148" s="7" t="inlineStr">
+        <is>
+          <t>Электричка «Стандарт плюс»</t>
+        </is>
+      </c>
+      <c r="F148" s="7" t="inlineStr">
+        <is>
+          <t>6996</t>
+        </is>
+      </c>
+      <c r="G148" s="5" t="inlineStr">
+        <is>
+          <t>30.10 21:16</t>
+        </is>
+      </c>
+      <c r="H148" s="5" t="inlineStr">
+        <is>
+          <t>30.10 22:49</t>
+        </is>
+      </c>
+      <c r="I148" s="5" t="inlineStr">
+        <is>
+          <t>Рязань-1</t>
+        </is>
+      </c>
+      <c r="J148" s="6" t="n">
+        <v>306</v>
+      </c>
+      <c r="K148" s="6" t="n">
+        <v>306</v>
+      </c>
+      <c r="L148" s="5" t="inlineStr">
+        <is>
+          <t>Такси до ст. Коломна (~300 ₽)</t>
+        </is>
+      </c>
+      <c r="M148" s="5" t="inlineStr"/>
+      <c r="N148" s="5" t="inlineStr"/>
+      <c r="O148" s="20" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/rasp.php?st1=11902&amp;st2=92502&amp;date=30.10.2026</t>
+        </is>
+      </c>
+      <c r="P148" s="5" t="inlineStr"/>
+      <c r="Q148" s="5" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="15" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="B149" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C149" s="17" t="inlineStr">
         <is>
           <t>В1: к 15:00 28.10</t>
         </is>
       </c>
-      <c r="D148" s="10" t="inlineStr">
+      <c r="D149" s="17" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E149" s="17" t="inlineStr">
+        <is>
+          <t>Электричка / РЭКС</t>
+        </is>
+      </c>
+      <c r="F149" s="17" t="inlineStr"/>
+      <c r="G149" s="16" t="inlineStr">
+        <is>
+          <t>28.10 09:48 или 12:54</t>
+        </is>
+      </c>
+      <c r="H149" s="16" t="inlineStr">
+        <is>
+          <t>11:36 / 15:15</t>
+        </is>
+      </c>
+      <c r="I149" s="16" t="inlineStr">
+        <is>
+          <t>Коломна</t>
+        </is>
+      </c>
+      <c r="J149" s="18" t="n">
+        <v>490</v>
+      </c>
+      <c r="K149" s="18" t="n">
+        <v>490</v>
+      </c>
+      <c r="L149" s="16" t="inlineStr">
+        <is>
+          <t>Казанский вокзал → электричка до ст. Коломна (490–620 ₽) + такси 10 мин (~300 ₽)</t>
+        </is>
+      </c>
+      <c r="M149" s="16" t="inlineStr">
+        <is>
+          <t>~12:00 / ~15:30</t>
+        </is>
+      </c>
+      <c r="N149" s="16" t="inlineStr"/>
+      <c r="O149" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/prigorod/</t>
+        </is>
+      </c>
+      <c r="P149" s="16" t="inlineStr">
+        <is>
+          <t>РЭКС 620 ₽</t>
+        </is>
+      </c>
+      <c r="Q149" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="5" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="B150" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C150" s="10" t="inlineStr">
+        <is>
+          <t>В1: к 15:00 28.10</t>
+        </is>
+      </c>
+      <c r="D150" s="10" t="inlineStr">
         <is>
           <t>Удобный</t>
         </is>
       </c>
-      <c r="E148" s="10" t="inlineStr">
+      <c r="E150" s="10" t="inlineStr">
         <is>
           <t>Своя машина</t>
         </is>
       </c>
-      <c r="F148" s="10" t="inlineStr"/>
-      <c r="G148" s="5" t="inlineStr">
-        <is>
-          <t>28.10 ~12:30</t>
-        </is>
-      </c>
-      <c r="H148" s="5" t="inlineStr">
+      <c r="F150" s="10" t="inlineStr"/>
+      <c r="G150" s="5" t="inlineStr">
+        <is>
+          <t>28.10 ~12:00</t>
+        </is>
+      </c>
+      <c r="H150" s="5" t="inlineStr">
         <is>
           <t>28.10 ~14:00</t>
         </is>
       </c>
-      <c r="I148" s="5" t="inlineStr">
+      <c r="I150" s="5" t="inlineStr">
         <is>
           <t>Коломна</t>
         </is>
       </c>
-      <c r="J148" s="9" t="n">
-        <v>650</v>
-      </c>
-      <c r="K148" s="9" t="n">
-        <v>650</v>
-      </c>
-      <c r="L148" s="5" t="inlineStr">
-        <is>
-          <t>~100 км, ~1 ч 30 мин</t>
-        </is>
-      </c>
-      <c r="M148" s="5" t="inlineStr">
+      <c r="J150" s="9" t="n">
+        <v>750</v>
+      </c>
+      <c r="K150" s="9" t="n">
+        <v>750</v>
+      </c>
+      <c r="L150" s="5" t="inlineStr">
+        <is>
+          <t>~115 км по Новорязанскому ш., ~2 ч с пробками</t>
+        </is>
+      </c>
+      <c r="M150" s="5" t="inlineStr">
         <is>
           <t>~14:00</t>
         </is>
       </c>
-      <c r="N148" s="5" t="inlineStr"/>
-      <c r="O148" s="5" t="inlineStr"/>
-      <c r="P148" s="5" t="inlineStr">
-        <is>
-          <t>Топливо ~1 300 ₽ туда-обратно</t>
-        </is>
-      </c>
-      <c r="Q148" s="5" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="5" t="inlineStr">
-        <is>
-          <t>Рязань</t>
-        </is>
-      </c>
-      <c r="B149" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C149" s="7" t="inlineStr">
-        <is>
-          <t>Обратно</t>
-        </is>
-      </c>
-      <c r="D149" s="7" t="inlineStr">
-        <is>
-          <t>Самый дешёвый</t>
-        </is>
-      </c>
-      <c r="E149" s="7" t="inlineStr">
-        <is>
-          <t>Электричка «Стандарт плюс»</t>
-        </is>
-      </c>
-      <c r="F149" s="7" t="inlineStr">
-        <is>
-          <t>6996</t>
-        </is>
-      </c>
-      <c r="G149" s="5" t="inlineStr">
-        <is>
-          <t>30.10 21:16</t>
-        </is>
-      </c>
-      <c r="H149" s="5" t="inlineStr">
-        <is>
-          <t>30.10 22:49</t>
-        </is>
-      </c>
-      <c r="I149" s="5" t="inlineStr">
-        <is>
-          <t>Рязань-1</t>
-        </is>
-      </c>
-      <c r="J149" s="6" t="n">
-        <v>306</v>
-      </c>
-      <c r="K149" s="6" t="n">
-        <v>306</v>
-      </c>
-      <c r="L149" s="5" t="inlineStr">
-        <is>
-          <t>Такси до ст. Коломна (~300 ₽)</t>
-        </is>
-      </c>
-      <c r="M149" s="5" t="inlineStr"/>
-      <c r="N149" s="5" t="inlineStr"/>
-      <c r="O149" s="20" t="inlineStr">
-        <is>
-          <t>https://www.tutu.ru/rasp.php?st1=11902&amp;st2=92502&amp;date=30.10.2026</t>
-        </is>
-      </c>
-      <c r="P149" s="5" t="inlineStr"/>
-      <c r="Q149" s="5" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="15" t="inlineStr">
-        <is>
-          <t>Москва</t>
-        </is>
-      </c>
-      <c r="B150" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="C150" s="17" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D150" s="17" t="inlineStr">
-        <is>
-          <t>Самый дешёвый</t>
-        </is>
-      </c>
-      <c r="E150" s="17" t="inlineStr">
-        <is>
-          <t>Электричка / РЭКС</t>
-        </is>
-      </c>
-      <c r="F150" s="17" t="inlineStr"/>
-      <c r="G150" s="16" t="inlineStr">
-        <is>
-          <t>28.10 09:48 или 12:54</t>
-        </is>
-      </c>
-      <c r="H150" s="16" t="inlineStr">
-        <is>
-          <t>11:36 / 15:15</t>
-        </is>
-      </c>
-      <c r="I150" s="16" t="inlineStr">
-        <is>
-          <t>Коломна</t>
-        </is>
-      </c>
-      <c r="J150" s="18" t="n">
-        <v>490</v>
-      </c>
-      <c r="K150" s="18" t="n">
-        <v>490</v>
-      </c>
-      <c r="L150" s="16" t="inlineStr">
-        <is>
-          <t>Казанский вокзал → электричка до ст. Коломна (490–620 ₽) + такси 10 мин (~300 ₽)</t>
-        </is>
-      </c>
-      <c r="M150" s="16" t="inlineStr">
-        <is>
-          <t>~12:00 / ~15:30</t>
-        </is>
-      </c>
-      <c r="N150" s="16" t="inlineStr"/>
-      <c r="O150" s="19" t="inlineStr">
-        <is>
-          <t>https://www.tutu.ru/prigorod/</t>
-        </is>
-      </c>
-      <c r="P150" s="16" t="inlineStr">
-        <is>
-          <t>РЭКС 620 ₽</t>
-        </is>
-      </c>
-      <c r="Q150" s="16" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
-      </c>
+      <c r="N150" s="5" t="inlineStr"/>
+      <c r="O150" s="5" t="inlineStr"/>
+      <c r="P150" s="5" t="inlineStr">
+        <is>
+          <t>Топливо ~1 500 ₽ туда-обратно</t>
+        </is>
+      </c>
+      <c r="Q150" s="5" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
@@ -15607,127 +15595,139 @@
       <c r="B151" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C151" s="10" t="inlineStr">
+      <c r="C151" s="7" t="inlineStr">
+        <is>
+          <t>Обратно</t>
+        </is>
+      </c>
+      <c r="D151" s="7" t="inlineStr">
+        <is>
+          <t>Самый дешёвый = Удобный</t>
+        </is>
+      </c>
+      <c r="E151" s="7" t="inlineStr">
+        <is>
+          <t>Электричка или машина</t>
+        </is>
+      </c>
+      <c r="F151" s="7" t="inlineStr"/>
+      <c r="G151" s="5" t="inlineStr">
+        <is>
+          <t>30.10 18:43</t>
+        </is>
+      </c>
+      <c r="H151" s="5" t="inlineStr">
+        <is>
+          <t>30.10 20:47</t>
+        </is>
+      </c>
+      <c r="I151" s="5" t="inlineStr">
+        <is>
+          <t>Москва, Казанский</t>
+        </is>
+      </c>
+      <c r="J151" s="6" t="n">
+        <v>490</v>
+      </c>
+      <c r="K151" s="6" t="n">
+        <v>490</v>
+      </c>
+      <c r="L151" s="5" t="inlineStr">
+        <is>
+          <t>Электричка 18:43 → 20:47</t>
+        </is>
+      </c>
+      <c r="M151" s="5" t="inlineStr"/>
+      <c r="N151" s="5" t="inlineStr"/>
+      <c r="O151" s="20" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/prigorod/</t>
+        </is>
+      </c>
+      <c r="P151" s="5" t="inlineStr"/>
+      <c r="Q151" s="5" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="15" t="inlineStr">
+        <is>
+          <t>Пенза</t>
+        </is>
+      </c>
+      <c r="B152" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C152" s="16" t="inlineStr">
         <is>
           <t>В1: к 15:00 28.10</t>
         </is>
       </c>
-      <c r="D151" s="10" t="inlineStr">
-        <is>
-          <t>Удобный</t>
-        </is>
-      </c>
-      <c r="E151" s="10" t="inlineStr">
-        <is>
-          <t>Своя машина</t>
-        </is>
-      </c>
-      <c r="F151" s="10" t="inlineStr"/>
-      <c r="G151" s="5" t="inlineStr">
-        <is>
-          <t>28.10 ~12:00</t>
-        </is>
-      </c>
-      <c r="H151" s="5" t="inlineStr">
-        <is>
-          <t>28.10 ~14:00</t>
-        </is>
-      </c>
-      <c r="I151" s="5" t="inlineStr">
-        <is>
-          <t>Коломна</t>
-        </is>
-      </c>
-      <c r="J151" s="9" t="n">
-        <v>750</v>
-      </c>
-      <c r="K151" s="9" t="n">
-        <v>750</v>
-      </c>
-      <c r="L151" s="5" t="inlineStr">
-        <is>
-          <t>~115 км по Новорязанскому ш., ~2 ч с пробками</t>
-        </is>
-      </c>
-      <c r="M151" s="5" t="inlineStr">
-        <is>
-          <t>~14:00</t>
-        </is>
-      </c>
-      <c r="N151" s="5" t="inlineStr"/>
-      <c r="O151" s="5" t="inlineStr"/>
-      <c r="P151" s="5" t="inlineStr">
-        <is>
-          <t>Топливо ~1 500 ₽ туда-обратно</t>
-        </is>
-      </c>
-      <c r="Q151" s="5" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="5" t="inlineStr">
-        <is>
-          <t>Москва</t>
-        </is>
-      </c>
-      <c r="B152" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C152" s="7" t="inlineStr">
-        <is>
-          <t>Обратно</t>
-        </is>
-      </c>
-      <c r="D152" s="7" t="inlineStr">
-        <is>
-          <t>Самый дешёвый = Удобный</t>
-        </is>
-      </c>
-      <c r="E152" s="7" t="inlineStr">
-        <is>
-          <t>Электричка или машина</t>
-        </is>
-      </c>
-      <c r="F152" s="7" t="inlineStr"/>
-      <c r="G152" s="5" t="inlineStr">
-        <is>
-          <t>30.10 18:43</t>
-        </is>
-      </c>
-      <c r="H152" s="5" t="inlineStr">
-        <is>
-          <t>30.10 20:47</t>
-        </is>
-      </c>
-      <c r="I152" s="5" t="inlineStr">
+      <c r="D152" s="16" t="inlineStr">
+        <is>
+          <t>Альтернатива: поезд</t>
+        </is>
+      </c>
+      <c r="E152" s="16" t="inlineStr">
+        <is>
+          <t>Поезд «Сура», купе (сидячий 3 030)</t>
+        </is>
+      </c>
+      <c r="F152" s="16" t="inlineStr">
+        <is>
+          <t>052М</t>
+        </is>
+      </c>
+      <c r="G152" s="16" t="inlineStr">
+        <is>
+          <t>27.10 21:35</t>
+        </is>
+      </c>
+      <c r="H152" s="16" t="inlineStr">
+        <is>
+          <t>28.10 07:59</t>
+        </is>
+      </c>
+      <c r="I152" s="16" t="inlineStr">
         <is>
           <t>Москва, Казанский</t>
         </is>
       </c>
-      <c r="J152" s="6" t="n">
-        <v>490</v>
-      </c>
-      <c r="K152" s="6" t="n">
-        <v>490</v>
-      </c>
-      <c r="L152" s="5" t="inlineStr">
-        <is>
-          <t>Электричка 18:43 → 20:47</t>
-        </is>
-      </c>
-      <c r="M152" s="5" t="inlineStr"/>
-      <c r="N152" s="5" t="inlineStr"/>
-      <c r="O152" s="20" t="inlineStr">
-        <is>
-          <t>https://www.tutu.ru/prigorod/</t>
-        </is>
-      </c>
-      <c r="P152" s="5" t="inlineStr"/>
-      <c r="Q152" s="5" t="inlineStr"/>
+      <c r="J152" s="24" t="n">
+        <v>3967</v>
+      </c>
+      <c r="K152" s="24" t="n">
+        <v>3967</v>
+      </c>
+      <c r="L152" s="16" t="inlineStr">
+        <is>
+          <t>Казанский вокзал → электричка до ст. Коломна (490–620 ₽) + такси 10 мин (~300 ₽) (09:48 → 11:36)</t>
+        </is>
+      </c>
+      <c r="M152" s="16" t="inlineStr">
+        <is>
+          <t>~12:00</t>
+        </is>
+      </c>
+      <c r="N152" s="16" t="inlineStr"/>
+      <c r="O152" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2024120&amp;nnst2=2000000</t>
+        </is>
+      </c>
+      <c r="P152" s="16" t="inlineStr">
+        <is>
+          <t>Основной вариант — машина (лист «Авто»)</t>
+        </is>
+      </c>
+      <c r="Q152" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="15" t="inlineStr">
         <is>
-          <t>Пенза</t>
+          <t>Саранск</t>
         </is>
       </c>
       <c r="B153" s="16" t="n">
@@ -15745,22 +15745,22 @@
       </c>
       <c r="E153" s="16" t="inlineStr">
         <is>
-          <t>Поезд «Сура», купе (сидячий 3 030)</t>
+          <t>Поезд, купе</t>
         </is>
       </c>
       <c r="F153" s="16" t="inlineStr">
         <is>
-          <t>052М</t>
+          <t>041Й</t>
         </is>
       </c>
       <c r="G153" s="16" t="inlineStr">
         <is>
-          <t>27.10 21:35</t>
+          <t>27.10 20:40</t>
         </is>
       </c>
       <c r="H153" s="16" t="inlineStr">
         <is>
-          <t>28.10 07:59</t>
+          <t>28.10 05:50</t>
         </is>
       </c>
       <c r="I153" s="16" t="inlineStr">
@@ -15769,30 +15769,34 @@
         </is>
       </c>
       <c r="J153" s="24" t="n">
-        <v>3967</v>
+        <v>4394</v>
       </c>
       <c r="K153" s="24" t="n">
-        <v>3967</v>
+        <v>4394</v>
       </c>
       <c r="L153" s="16" t="inlineStr">
         <is>
-          <t>Казанский вокзал → электричка до ст. Коломна (490–620 ₽) + такси 10 мин (~300 ₽) (09:48 → 11:36)</t>
+          <t>Казанский вокзал → электричка до ст. Коломна (490–620 ₽) + такси 10 мин (~300 ₽) (07:22 → 09:15)</t>
         </is>
       </c>
       <c r="M153" s="16" t="inlineStr">
         <is>
-          <t>~12:00</t>
-        </is>
-      </c>
-      <c r="N153" s="16" t="inlineStr"/>
+          <t>~09:30</t>
+        </is>
+      </c>
+      <c r="N153" s="16" t="inlineStr">
+        <is>
+          <t>ранний заезд</t>
+        </is>
+      </c>
       <c r="O153" s="19" t="inlineStr">
         <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2024120&amp;nnst2=2000000</t>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2024700&amp;nnst2=2000000</t>
         </is>
       </c>
       <c r="P153" s="16" t="inlineStr">
         <is>
-          <t>Основной вариант — машина (лист «Авто»)</t>
+          <t>Основной вариант — машина</t>
         </is>
       </c>
       <c r="Q153" s="16" t="inlineStr">
@@ -15804,7 +15808,7 @@
     <row r="154">
       <c r="A154" s="15" t="inlineStr">
         <is>
-          <t>Саранск</t>
+          <t>Тамбов</t>
         </is>
       </c>
       <c r="B154" s="16" t="n">
@@ -15822,58 +15826,54 @@
       </c>
       <c r="E154" s="16" t="inlineStr">
         <is>
-          <t>Поезд, купе</t>
+          <t>Поезд, сидячий (купе 2 868)</t>
         </is>
       </c>
       <c r="F154" s="16" t="inlineStr">
         <is>
-          <t>041Й</t>
+          <t>135Ж</t>
         </is>
       </c>
       <c r="G154" s="16" t="inlineStr">
         <is>
-          <t>27.10 20:40</t>
+          <t>27.10 21:56</t>
         </is>
       </c>
       <c r="H154" s="16" t="inlineStr">
         <is>
-          <t>28.10 05:50</t>
+          <t>28.10 07:22</t>
         </is>
       </c>
       <c r="I154" s="16" t="inlineStr">
         <is>
-          <t>Москва, Казанский</t>
+          <t>Москва, Павелецкий</t>
         </is>
       </c>
       <c r="J154" s="24" t="n">
-        <v>4394</v>
+        <v>1979</v>
       </c>
       <c r="K154" s="24" t="n">
-        <v>4394</v>
+        <v>1979</v>
       </c>
       <c r="L154" s="16" t="inlineStr">
         <is>
-          <t>Казанский вокзал → электричка до ст. Коломна (490–620 ₽) + такси 10 мин (~300 ₽) (07:22 → 09:15)</t>
+          <t>Павелецкий → метро до Комсомольской (~20 мин) → электричка от Казанского + такси (08:47 РЭКС → 10:28)</t>
         </is>
       </c>
       <c r="M154" s="16" t="inlineStr">
         <is>
-          <t>~09:30</t>
-        </is>
-      </c>
-      <c r="N154" s="16" t="inlineStr">
-        <is>
-          <t>ранний заезд</t>
-        </is>
-      </c>
+          <t>~10:45</t>
+        </is>
+      </c>
+      <c r="N154" s="16" t="inlineStr"/>
       <c r="O154" s="19" t="inlineStr">
         <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2024700&amp;nnst2=2000000</t>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2014700&amp;nnst2=2000000</t>
         </is>
       </c>
       <c r="P154" s="16" t="inlineStr">
         <is>
-          <t>Основной вариант — машина</t>
+          <t>Основной вариант — машина. Купе осталось 1 место</t>
         </is>
       </c>
       <c r="Q154" s="16" t="inlineStr">
@@ -15885,11 +15885,11 @@
     <row r="155">
       <c r="A155" s="15" t="inlineStr">
         <is>
-          <t>Тамбов</t>
+          <t>Липецк</t>
         </is>
       </c>
       <c r="B155" s="16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C155" s="16" t="inlineStr">
         <is>
@@ -15903,22 +15903,22 @@
       </c>
       <c r="E155" s="16" t="inlineStr">
         <is>
-          <t>Поезд, сидячий (купе 2 868)</t>
+          <t>Поезд, купе</t>
         </is>
       </c>
       <c r="F155" s="16" t="inlineStr">
         <is>
-          <t>135Ж</t>
+          <t>033С</t>
         </is>
       </c>
       <c r="G155" s="16" t="inlineStr">
         <is>
-          <t>27.10 21:56</t>
+          <t>27.10 23:15</t>
         </is>
       </c>
       <c r="H155" s="16" t="inlineStr">
         <is>
-          <t>28.10 07:22</t>
+          <t>28.10 08:08</t>
         </is>
       </c>
       <c r="I155" s="16" t="inlineStr">
@@ -15927,30 +15927,30 @@
         </is>
       </c>
       <c r="J155" s="24" t="n">
-        <v>1979</v>
+        <v>4049</v>
       </c>
       <c r="K155" s="24" t="n">
-        <v>1979</v>
+        <v>4049</v>
       </c>
       <c r="L155" s="16" t="inlineStr">
         <is>
-          <t>Павелецкий → метро до Комсомольской (~20 мин) → электричка от Казанского + такси (08:47 РЭКС → 10:28)</t>
+          <t>Павелецкий → метро до Комсомольской (~20 мин) → электричка от Казанского + такси (09:48 → 11:36)</t>
         </is>
       </c>
       <c r="M155" s="16" t="inlineStr">
         <is>
-          <t>~10:45</t>
+          <t>~12:00</t>
         </is>
       </c>
       <c r="N155" s="16" t="inlineStr"/>
       <c r="O155" s="19" t="inlineStr">
         <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2014700&amp;nnst2=2000000</t>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2014130&amp;nnst2=2000000</t>
         </is>
       </c>
       <c r="P155" s="16" t="inlineStr">
         <is>
-          <t>Основной вариант — машина. Купе осталось 1 место</t>
+          <t>Основной вариант — одна машина на троих</t>
         </is>
       </c>
       <c r="Q155" s="16" t="inlineStr">
@@ -15962,11 +15962,11 @@
     <row r="156">
       <c r="A156" s="15" t="inlineStr">
         <is>
-          <t>Липецк</t>
+          <t>Воронеж</t>
         </is>
       </c>
       <c r="B156" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C156" s="16" t="inlineStr">
         <is>
@@ -15980,54 +15980,54 @@
       </c>
       <c r="E156" s="16" t="inlineStr">
         <is>
-          <t>Поезд, купе</t>
+          <t>Поезд «Ингушетия», купе</t>
         </is>
       </c>
       <c r="F156" s="16" t="inlineStr">
         <is>
-          <t>033С</t>
+          <t>145С</t>
         </is>
       </c>
       <c r="G156" s="16" t="inlineStr">
         <is>
-          <t>27.10 23:15</t>
+          <t>27.10 23:17</t>
         </is>
       </c>
       <c r="H156" s="16" t="inlineStr">
         <is>
-          <t>28.10 08:08</t>
+          <t>28.10 07:24</t>
         </is>
       </c>
       <c r="I156" s="16" t="inlineStr">
         <is>
-          <t>Москва, Павелецкий</t>
+          <t>Москва, Казанский</t>
         </is>
       </c>
       <c r="J156" s="24" t="n">
-        <v>4049</v>
+        <v>4045</v>
       </c>
       <c r="K156" s="24" t="n">
-        <v>4049</v>
+        <v>4045</v>
       </c>
       <c r="L156" s="16" t="inlineStr">
         <is>
-          <t>Павелецкий → метро до Комсомольской (~20 мин) → электричка от Казанского + такси (09:48 → 11:36)</t>
+          <t>Казанский вокзал → электричка до ст. Коломна (490–620 ₽) + такси 10 мин (~300 ₽) (08:47 РЭКС → 10:28)</t>
         </is>
       </c>
       <c r="M156" s="16" t="inlineStr">
         <is>
-          <t>~12:00</t>
+          <t>~10:45</t>
         </is>
       </c>
       <c r="N156" s="16" t="inlineStr"/>
       <c r="O156" s="19" t="inlineStr">
         <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2014130&amp;nnst2=2000000</t>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2014000&amp;nnst2=2000000</t>
         </is>
       </c>
       <c r="P156" s="16" t="inlineStr">
         <is>
-          <t>Основной вариант — одна машина на троих</t>
+          <t>Или 213*С 21:09 — прямо до Голутвина (Коломна) в 04:50</t>
         </is>
       </c>
       <c r="Q156" s="16" t="inlineStr">
@@ -16039,11 +16039,11 @@
     <row r="157">
       <c r="A157" s="15" t="inlineStr">
         <is>
-          <t>Воронеж</t>
+          <t>Орёл</t>
         </is>
       </c>
       <c r="B157" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C157" s="16" t="inlineStr">
         <is>
@@ -16057,54 +16057,54 @@
       </c>
       <c r="E157" s="16" t="inlineStr">
         <is>
-          <t>Поезд «Ингушетия», купе</t>
+          <t>Поезд, купе</t>
         </is>
       </c>
       <c r="F157" s="16" t="inlineStr">
         <is>
-          <t>145С</t>
+          <t>084С</t>
         </is>
       </c>
       <c r="G157" s="16" t="inlineStr">
         <is>
-          <t>27.10 23:17</t>
+          <t>27.10 23:37</t>
         </is>
       </c>
       <c r="H157" s="16" t="inlineStr">
         <is>
-          <t>28.10 07:24</t>
+          <t>28.10 08:40</t>
         </is>
       </c>
       <c r="I157" s="16" t="inlineStr">
         <is>
-          <t>Москва, Казанский</t>
+          <t>Москва, Киевский</t>
         </is>
       </c>
       <c r="J157" s="24" t="n">
-        <v>4045</v>
+        <v>3655</v>
       </c>
       <c r="K157" s="24" t="n">
-        <v>4045</v>
+        <v>3655</v>
       </c>
       <c r="L157" s="16" t="inlineStr">
         <is>
-          <t>Казанский вокзал → электричка до ст. Коломна (490–620 ₽) + такси 10 мин (~300 ₽) (08:47 РЭКС → 10:28)</t>
+          <t>Киевский → метро до Комсомольской (~25 мин) → электричка + такси (09:48 → 11:36)</t>
         </is>
       </c>
       <c r="M157" s="16" t="inlineStr">
         <is>
-          <t>~10:45</t>
+          <t>~12:00</t>
         </is>
       </c>
       <c r="N157" s="16" t="inlineStr"/>
       <c r="O157" s="19" t="inlineStr">
         <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2014000&amp;nnst2=2000000</t>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2000140&amp;nnst2=2000000</t>
         </is>
       </c>
       <c r="P157" s="16" t="inlineStr">
         <is>
-          <t>Или 213*С 21:09 — прямо до Голутвина (Коломна) в 04:50</t>
+          <t>Основной вариант — машина вместе с Брянском</t>
         </is>
       </c>
       <c r="Q157" s="16" t="inlineStr">
@@ -16116,7 +16116,7 @@
     <row r="158">
       <c r="A158" s="15" t="inlineStr">
         <is>
-          <t>Орёл</t>
+          <t>Брянск</t>
         </is>
       </c>
       <c r="B158" s="16" t="n">
@@ -16134,22 +16134,22 @@
       </c>
       <c r="E158" s="16" t="inlineStr">
         <is>
-          <t>Поезд, купе</t>
+          <t>Поезд, сидячий (купе 3 180)</t>
         </is>
       </c>
       <c r="F158" s="16" t="inlineStr">
         <is>
-          <t>084С</t>
+          <t>086Щ</t>
         </is>
       </c>
       <c r="G158" s="16" t="inlineStr">
         <is>
-          <t>27.10 23:37</t>
+          <t>28.10 00:20</t>
         </is>
       </c>
       <c r="H158" s="16" t="inlineStr">
         <is>
-          <t>28.10 08:40</t>
+          <t>28.10 06:20</t>
         </is>
       </c>
       <c r="I158" s="16" t="inlineStr">
@@ -16158,30 +16158,34 @@
         </is>
       </c>
       <c r="J158" s="24" t="n">
-        <v>3655</v>
+        <v>1749</v>
       </c>
       <c r="K158" s="24" t="n">
-        <v>3655</v>
+        <v>1749</v>
       </c>
       <c r="L158" s="16" t="inlineStr">
         <is>
-          <t>Киевский → метро до Комсомольской (~25 мин) → электричка + такси (09:48 → 11:36)</t>
+          <t>Киевский → метро до Комсомольской (~25 мин) → электричка + такси (07:22 → 09:15)</t>
         </is>
       </c>
       <c r="M158" s="16" t="inlineStr">
         <is>
-          <t>~12:00</t>
-        </is>
-      </c>
-      <c r="N158" s="16" t="inlineStr"/>
+          <t>~09:30</t>
+        </is>
+      </c>
+      <c r="N158" s="16" t="inlineStr">
+        <is>
+          <t>ранний заезд</t>
+        </is>
+      </c>
       <c r="O158" s="19" t="inlineStr">
         <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2000140&amp;nnst2=2000000</t>
+          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2000427&amp;nnst2=2000000</t>
         </is>
       </c>
       <c r="P158" s="16" t="inlineStr">
         <is>
-          <t>Основной вариант — машина вместе с Брянском</t>
+          <t>Время по расписанию 27.10. Основной вариант — машина</t>
         </is>
       </c>
       <c r="Q158" s="16" t="inlineStr">
@@ -16190,89 +16194,8 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="15" t="inlineStr">
-        <is>
-          <t>Брянск</t>
-        </is>
-      </c>
-      <c r="B159" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C159" s="16" t="inlineStr">
-        <is>
-          <t>В1: к 15:00 28.10</t>
-        </is>
-      </c>
-      <c r="D159" s="16" t="inlineStr">
-        <is>
-          <t>Альтернатива: поезд</t>
-        </is>
-      </c>
-      <c r="E159" s="16" t="inlineStr">
-        <is>
-          <t>Поезд, сидячий (купе 3 180)</t>
-        </is>
-      </c>
-      <c r="F159" s="16" t="inlineStr">
-        <is>
-          <t>086Щ</t>
-        </is>
-      </c>
-      <c r="G159" s="16" t="inlineStr">
-        <is>
-          <t>28.10 00:20</t>
-        </is>
-      </c>
-      <c r="H159" s="16" t="inlineStr">
-        <is>
-          <t>28.10 06:20</t>
-        </is>
-      </c>
-      <c r="I159" s="16" t="inlineStr">
-        <is>
-          <t>Москва, Киевский</t>
-        </is>
-      </c>
-      <c r="J159" s="24" t="n">
-        <v>1749</v>
-      </c>
-      <c r="K159" s="24" t="n">
-        <v>1749</v>
-      </c>
-      <c r="L159" s="16" t="inlineStr">
-        <is>
-          <t>Киевский → метро до Комсомольской (~25 мин) → электричка + такси (07:22 → 09:15)</t>
-        </is>
-      </c>
-      <c r="M159" s="16" t="inlineStr">
-        <is>
-          <t>~09:30</t>
-        </is>
-      </c>
-      <c r="N159" s="16" t="inlineStr">
-        <is>
-          <t>ранний заезд</t>
-        </is>
-      </c>
-      <c r="O159" s="19" t="inlineStr">
-        <is>
-          <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2000427&amp;nnst2=2000000</t>
-        </is>
-      </c>
-      <c r="P159" s="16" t="inlineStr">
-        <is>
-          <t>Время по расписанию 27.10. Основной вариант — машина</t>
-        </is>
-      </c>
-      <c r="Q159" s="16" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:Q159"/>
+  <autoFilter ref="A1:Q158"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
@@ -16379,7 +16302,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O124" r:id="rId103"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O125" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O126" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O127" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O128" r:id="rId106"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O129" r:id="rId107"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O130" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O131" r:id="rId109"/>
@@ -16395,11 +16318,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O141" r:id="rId119"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O142" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O143" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O144" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O145" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O146" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O147" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O148" r:id="rId124"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O149" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O150" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O151" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O152" r:id="rId127"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O153" r:id="rId128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O154" r:id="rId129"/>
@@ -16407,7 +16330,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O156" r:id="rId131"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O157" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O158" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O159" r:id="rId134"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17902,7 +17824,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>В1 — к 15:00 28.10 (в т. ч. с ночью 27→28); В2 — после 15:00 28.10; В3 — к утру 29.10 отдохнувшим. В каждом: «Самый дешёвый» и «Удобный».</t>
+          <t>В1 — к 15:00 28.10 (в т. ч. с ночью 27→28); В2 — после 15:00 28.10; В3 — к утру 29.10 отдохнувшим. В каждом: «Самый дешёвый» и «Удобный». Если самый дешёвый вариант и есть удобный — показан один.</t>
         </is>
       </c>
     </row>

--- a/Коломна_маршруты_28-30.10.2026.xlsx
+++ b/Коломна_маршруты_28-30.10.2026.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Сводка по сотрудникам'!$A$4:$S$64</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Маршруты'!$A$1:$Q$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Маршруты'!$A$1:$S$113</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -183,6 +183,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -195,9 +198,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4212,7 +4212,7 @@
       </c>
       <c r="S52" s="5" t="inlineStr">
         <is>
-          <t>Едет вместе с дочерью (Смирнова Ю.И.). Группа 9 чел. одним рейсом; минивэны</t>
+          <t>Едет вместе с дочерью (Смирнова Ю.И.). 9 чел. одним рейсом (обычные билеты, без групповых скидок); минивэны</t>
         </is>
       </c>
     </row>
@@ -4284,7 +4284,7 @@
       </c>
       <c r="S53" s="5" t="inlineStr">
         <is>
-          <t>Группа 9 чел. одним рейсом; минивэны</t>
+          <t>9 чел. одним рейсом (обычные билеты, без групповых скидок); минивэны</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="S54" s="5" t="inlineStr">
         <is>
-          <t>Группа 9 чел. одним рейсом; минивэны</t>
+          <t>9 чел. одним рейсом (обычные билеты, без групповых скидок); минивэны</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="S55" s="5" t="inlineStr">
         <is>
-          <t>Группа 9 чел. одним рейсом; минивэны</t>
+          <t>9 чел. одним рейсом (обычные билеты, без групповых скидок); минивэны</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="S56" s="5" t="inlineStr">
         <is>
-          <t>Группа 9 чел. одним рейсом; минивэны</t>
+          <t>9 чел. одним рейсом (обычные билеты, без групповых скидок); минивэны</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="S57" s="5" t="inlineStr">
         <is>
-          <t>Группа 9 чел. одним рейсом; минивэны</t>
+          <t>9 чел. одним рейсом (обычные билеты, без групповых скидок); минивэны</t>
         </is>
       </c>
     </row>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="S58" s="5" t="inlineStr">
         <is>
-          <t>Едет вместе с отцом (Смирнов И.А.). Группа 9 чел. одним рейсом; минивэны</t>
+          <t>Едет вместе с отцом (Смирнов И.А.). 9 чел. одним рейсом (обычные билеты, без групповых скидок); минивэны</t>
         </is>
       </c>
     </row>
@@ -4716,7 +4716,7 @@
       </c>
       <c r="S59" s="5" t="inlineStr">
         <is>
-          <t>Группа 9 чел. одним рейсом; минивэны</t>
+          <t>9 чел. одним рейсом (обычные билеты, без групповых скидок); минивэны</t>
         </is>
       </c>
     </row>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="S60" s="5" t="inlineStr">
         <is>
-          <t>Группа 9 чел. одним рейсом; минивэны</t>
+          <t>9 чел. одним рейсом (обычные билеты, без групповых скидок); минивэны</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q113"/>
+  <dimension ref="A1:S115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -5126,10 +5126,12 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="42" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="48" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
+    <col width="48" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="45" customHeight="1">
@@ -5200,20 +5202,30 @@
       </c>
       <c r="N1" s="2" t="inlineStr">
         <is>
+          <t>Выход из дома → в гостинице / выезд из гостиницы → дома</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>Время в пути (дверь–дверь)</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
           <t>Доп. ночь</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Ссылка (Туту.ру)</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>Примечание</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>Проверка пробок (Яндекс/2ГИС)</t>
         </is>
@@ -5279,18 +5291,28 @@
           <t>~11:30</t>
         </is>
       </c>
-      <c r="N2" s="16" t="inlineStr"/>
-      <c r="O2" s="19" t="inlineStr">
+      <c r="N2" s="16" t="inlineStr">
+        <is>
+          <t>28.10 04:05 (мест.) → 28.10 11:30 МСК</t>
+        </is>
+      </c>
+      <c r="O2" s="15" t="inlineStr">
+        <is>
+          <t>10 ч 25 мин</t>
+        </is>
+      </c>
+      <c r="P2" s="16" t="inlineStr"/>
+      <c r="Q2" s="19" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/f/Omsk/Moskva/?class=Y&amp;travelers=1&amp;route[0]=62-28102026-491</t>
         </is>
       </c>
-      <c r="P2" s="16" t="inlineStr">
+      <c r="R2" s="16" t="inlineStr">
         <is>
           <t>Ранний подъём (~04:00). Все прямые рейсы 28.10 вылетают до 08:05</t>
         </is>
       </c>
-      <c r="Q2" s="16" t="inlineStr">
+      <c r="S2" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -5358,20 +5380,30 @@
       </c>
       <c r="N3" s="5" t="inlineStr">
         <is>
+          <t>27.10 14:15 (мест.) → 27.10 22:00 МСК</t>
+        </is>
+      </c>
+      <c r="O3" s="20" t="inlineStr">
+        <is>
+          <t>10 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
           <t>+1 ночь 27→28</t>
         </is>
       </c>
-      <c r="O3" s="20" t="inlineStr">
+      <c r="Q3" s="21" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/f/Omsk/Moskva/?class=Y&amp;travelers=1&amp;route[0]=62-27102026-491</t>
         </is>
       </c>
-      <c r="P3" s="5" t="inlineStr">
+      <c r="R3" s="5" t="inlineStr">
         <is>
           <t>Вылет днём накануне, ночь в гостинице — утром 28.10 отдохнувший</t>
         </is>
       </c>
-      <c r="Q3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -5429,18 +5461,28 @@
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr"/>
-      <c r="N4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>30.10 18:15 МСК → 31.10 07:45 (мест.)</t>
+        </is>
+      </c>
       <c r="O4" s="20" t="inlineStr">
         <is>
+          <t>10 ч 30 мин</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="21" t="inlineStr">
+        <is>
           <t>https://avia.tutu.ru/f/Moskva/Omsk/?class=Y&amp;travelers=1&amp;route[0]=491-30102026-62</t>
         </is>
       </c>
-      <c r="P4" s="5" t="inlineStr">
+      <c r="R4" s="5" t="inlineStr">
         <is>
           <t>Ночной рейс сразу после конференции</t>
         </is>
       </c>
-      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -5500,20 +5542,30 @@
       <c r="M5" s="5" t="inlineStr"/>
       <c r="N5" s="5" t="inlineStr">
         <is>
+          <t>31.10 17:30 МСК → 01.11 06:00 (мест.)</t>
+        </is>
+      </c>
+      <c r="O5" s="20" t="inlineStr">
+        <is>
+          <t>9 ч 30 мин</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="inlineStr">
+        <is>
           <t>+1 ночь 30→31</t>
         </is>
       </c>
-      <c r="O5" s="20" t="inlineStr">
+      <c r="Q5" s="21" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/f/Moskva/Omsk/?class=Y&amp;travelers=1&amp;route[0]=491-31102026-62</t>
         </is>
       </c>
-      <c r="P5" s="5" t="inlineStr">
+      <c r="R5" s="5" t="inlineStr">
         <is>
           <t>Дневных рейсов в Омск нет. День 31.10 на отдых, вечерний вылет</t>
         </is>
       </c>
-      <c r="Q5" s="5" t="inlineStr">
+      <c r="S5" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -5579,18 +5631,28 @@
           <t>~10:45</t>
         </is>
       </c>
-      <c r="N6" s="16" t="inlineStr"/>
-      <c r="O6" s="19" t="inlineStr">
+      <c r="N6" s="16" t="inlineStr">
+        <is>
+          <t>28.10 04:00 (мест.) → 28.10 10:45 МСК</t>
+        </is>
+      </c>
+      <c r="O6" s="15" t="inlineStr">
+        <is>
+          <t>8 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="P6" s="16" t="inlineStr"/>
+      <c r="Q6" s="19" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/f/Ufa/Moskva/?class=Y&amp;travelers=1&amp;route[0]=93-28102026-491</t>
         </is>
       </c>
-      <c r="P6" s="16" t="inlineStr">
+      <c r="R6" s="16" t="inlineStr">
         <is>
           <t>Ранний подъём</t>
         </is>
       </c>
-      <c r="Q6" s="16" t="inlineStr">
+      <c r="S6" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -5656,18 +5718,28 @@
           <t>~18:40</t>
         </is>
       </c>
-      <c r="N7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>28.10 12:55 (мест.) → 28.10 18:40 МСК</t>
+        </is>
+      </c>
       <c r="O7" s="20" t="inlineStr">
         <is>
+          <t>7 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="P7" s="5" t="inlineStr"/>
+      <c r="Q7" s="21" t="inlineStr">
+        <is>
           <t>https://avia.tutu.ru/f/Ufa/Moskva/?class=Y&amp;travelers=1&amp;route[0]=93-28102026-491</t>
         </is>
       </c>
-      <c r="P7" s="5" t="inlineStr">
+      <c r="R7" s="5" t="inlineStr">
         <is>
           <t>Без экскурсии. Для экскурсии: SU-1237 12:45 → SVO 13:05, 8 521 / 11 889</t>
         </is>
       </c>
-      <c r="Q7" s="5" t="inlineStr">
+      <c r="S7" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -5729,18 +5801,28 @@
         </is>
       </c>
       <c r="M8" s="5" t="inlineStr"/>
-      <c r="N8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>30.10 18:15 МСК → 31.10 05:30 (мест.)</t>
+        </is>
+      </c>
       <c r="O8" s="20" t="inlineStr">
         <is>
+          <t>9 ч 15 мин</t>
+        </is>
+      </c>
+      <c r="P8" s="5" t="inlineStr"/>
+      <c r="Q8" s="21" t="inlineStr">
+        <is>
           <t>https://avia.tutu.ru/f/Moskva/Ufa/?class=Y&amp;travelers=1&amp;route[0]=491-30102026-93</t>
         </is>
       </c>
-      <c r="P8" s="5" t="inlineStr">
+      <c r="R8" s="5" t="inlineStr">
         <is>
           <t>Ночной рейс</t>
         </is>
       </c>
-      <c r="Q8" s="5" t="inlineStr"/>
+      <c r="S8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -5800,16 +5882,26 @@
       <c r="M9" s="5" t="inlineStr"/>
       <c r="N9" s="5" t="inlineStr">
         <is>
+          <t>31.10 07:30 МСК → 31.10 16:50 (мест.)</t>
+        </is>
+      </c>
+      <c r="O9" s="20" t="inlineStr">
+        <is>
+          <t>7 ч 20 мин</t>
+        </is>
+      </c>
+      <c r="P9" s="5" t="inlineStr">
+        <is>
           <t>+1 ночь 30→31</t>
         </is>
       </c>
-      <c r="O9" s="20" t="inlineStr">
+      <c r="Q9" s="21" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/f/Moskva/Ufa/?class=Y&amp;travelers=1&amp;route[0]=491-31102026-93</t>
         </is>
       </c>
-      <c r="P9" s="5" t="inlineStr"/>
-      <c r="Q9" s="5" t="inlineStr">
+      <c r="R9" s="5" t="inlineStr"/>
+      <c r="S9" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -5875,18 +5967,28 @@
           <t>~10:55</t>
         </is>
       </c>
-      <c r="N10" s="16" t="inlineStr"/>
-      <c r="O10" s="19" t="inlineStr">
+      <c r="N10" s="16" t="inlineStr">
+        <is>
+          <t>28.10 03:40 (мест.) → 28.10 10:55 МСК</t>
+        </is>
+      </c>
+      <c r="O10" s="15" t="inlineStr">
+        <is>
+          <t>9 ч 15 мин</t>
+        </is>
+      </c>
+      <c r="P10" s="16" t="inlineStr"/>
+      <c r="Q10" s="19" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/f/Ekaterinburg/Moskva/?class=Y&amp;travelers=1&amp;route[0]=29-28102026-491</t>
         </is>
       </c>
-      <c r="P10" s="16" t="inlineStr">
+      <c r="R10" s="16" t="inlineStr">
         <is>
           <t>Выезд из Ревды ~03:50</t>
         </is>
       </c>
-      <c r="Q10" s="16" t="inlineStr">
+      <c r="S10" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -5952,18 +6054,28 @@
           <t>~15:05</t>
         </is>
       </c>
-      <c r="N11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>28.10 08:50 (мест.) → 28.10 15:05 МСК</t>
+        </is>
+      </c>
       <c r="O11" s="20" t="inlineStr">
         <is>
+          <t>8 ч 15 мин</t>
+        </is>
+      </c>
+      <c r="P11" s="5" t="inlineStr"/>
+      <c r="Q11" s="21" t="inlineStr">
+        <is>
           <t>https://avia.tutu.ru/f/Ekaterinburg/Moskva/?class=Y&amp;travelers=1&amp;route[0]=29-28102026-491</t>
         </is>
       </c>
-      <c r="P11" s="5" t="inlineStr">
+      <c r="R11" s="5" t="inlineStr">
         <is>
           <t>Выезд из Ревды ~09:00; к экскурсии успевает</t>
         </is>
       </c>
-      <c r="Q11" s="5" t="inlineStr">
+      <c r="S11" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -6025,18 +6137,28 @@
         </is>
       </c>
       <c r="M12" s="5" t="inlineStr"/>
-      <c r="N12" s="5" t="inlineStr"/>
+      <c r="N12" s="5" t="inlineStr">
+        <is>
+          <t>30.10 18:15 МСК → 31.10 06:05 (мест.)</t>
+        </is>
+      </c>
       <c r="O12" s="20" t="inlineStr">
         <is>
+          <t>9 ч 50 мин</t>
+        </is>
+      </c>
+      <c r="P12" s="5" t="inlineStr"/>
+      <c r="Q12" s="21" t="inlineStr">
+        <is>
           <t>https://avia.tutu.ru/f/Moskva/Ekaterinburg/?class=Y&amp;travelers=1&amp;route[0]=491-30102026-29</t>
         </is>
       </c>
-      <c r="P12" s="5" t="inlineStr">
+      <c r="R12" s="5" t="inlineStr">
         <is>
           <t>Ночной рейс</t>
         </is>
       </c>
-      <c r="Q12" s="5" t="inlineStr"/>
+      <c r="S12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -6096,16 +6218,26 @@
       <c r="M13" s="5" t="inlineStr"/>
       <c r="N13" s="5" t="inlineStr">
         <is>
+          <t>31.10 06:30 МСК → 31.10 16:20 (мест.)</t>
+        </is>
+      </c>
+      <c r="O13" s="20" t="inlineStr">
+        <is>
+          <t>7 ч 50 мин</t>
+        </is>
+      </c>
+      <c r="P13" s="5" t="inlineStr">
+        <is>
           <t>+1 ночь 30→31</t>
         </is>
       </c>
-      <c r="O13" s="20" t="inlineStr">
+      <c r="Q13" s="21" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/f/Moskva/Ekaterinburg/?class=Y&amp;travelers=1&amp;route[0]=491-31102026-29</t>
         </is>
       </c>
-      <c r="P13" s="5" t="inlineStr"/>
-      <c r="Q13" s="5" t="inlineStr">
+      <c r="R13" s="5" t="inlineStr"/>
+      <c r="S13" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -6171,18 +6303,28 @@
           <t>~12:00</t>
         </is>
       </c>
-      <c r="N14" s="16" t="inlineStr"/>
-      <c r="O14" s="19" t="inlineStr">
+      <c r="N14" s="16" t="inlineStr">
+        <is>
+          <t>28.10 04:50 (мест.) → 28.10 12:00 МСК</t>
+        </is>
+      </c>
+      <c r="O14" s="15" t="inlineStr">
+        <is>
+          <t>11 ч 10 мин</t>
+        </is>
+      </c>
+      <c r="P14" s="16" t="inlineStr"/>
+      <c r="Q14" s="19" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/f/Novosibirsk/Moskva/?class=Y&amp;travelers=1&amp;route[0]=58-28102026-491</t>
         </is>
       </c>
-      <c r="P14" s="16" t="inlineStr">
+      <c r="R14" s="16" t="inlineStr">
         <is>
           <t>Цена за 1 человека</t>
         </is>
       </c>
-      <c r="Q14" s="16" t="inlineStr">
+      <c r="S14" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -6248,18 +6390,28 @@
           <t>~14:30</t>
         </is>
       </c>
-      <c r="N15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>28.10 07:15 (мест.) → 28.10 14:30 МСК</t>
+        </is>
+      </c>
       <c r="O15" s="20" t="inlineStr">
         <is>
+          <t>11 ч 15 мин</t>
+        </is>
+      </c>
+      <c r="P15" s="5" t="inlineStr"/>
+      <c r="Q15" s="21" t="inlineStr">
+        <is>
           <t>https://avia.tutu.ru/f/Novosibirsk/Moskva/?class=Y&amp;travelers=1&amp;route[0]=58-28102026-491</t>
         </is>
       </c>
-      <c r="P15" s="5" t="inlineStr">
+      <c r="R15" s="5" t="inlineStr">
         <is>
           <t>К экскурсии успевают</t>
         </is>
       </c>
-      <c r="Q15" s="5" t="inlineStr"/>
+      <c r="S15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -6319,20 +6471,30 @@
       <c r="M16" s="5" t="inlineStr"/>
       <c r="N16" s="5" t="inlineStr">
         <is>
+          <t>31.10 18:15 МСК → 01.11 08:45 (мест.)</t>
+        </is>
+      </c>
+      <c r="O16" s="20" t="inlineStr">
+        <is>
+          <t>10 ч 30 мин</t>
+        </is>
+      </c>
+      <c r="P16" s="5" t="inlineStr">
+        <is>
           <t>+1 ночь 30→31</t>
         </is>
       </c>
-      <c r="O16" s="20" t="inlineStr">
+      <c r="Q16" s="21" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/f/Moskva/Novosibirsk/?class=Y&amp;travelers=1&amp;route[0]=491-31102026-58</t>
         </is>
       </c>
-      <c r="P16" s="5" t="inlineStr">
+      <c r="R16" s="5" t="inlineStr">
         <is>
           <t>Ночной рейс</t>
         </is>
       </c>
-      <c r="Q16" s="5" t="inlineStr">
+      <c r="S16" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -6396,20 +6558,30 @@
       <c r="M17" s="5" t="inlineStr"/>
       <c r="N17" s="5" t="inlineStr">
         <is>
+          <t>31.10 07:50 МСК → 31.10 22:05 (мест.)</t>
+        </is>
+      </c>
+      <c r="O17" s="20" t="inlineStr">
+        <is>
+          <t>10 ч 15 мин</t>
+        </is>
+      </c>
+      <c r="P17" s="5" t="inlineStr">
+        <is>
           <t>+1 ночь 30→31</t>
         </is>
       </c>
-      <c r="O17" s="20" t="inlineStr">
+      <c r="Q17" s="21" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/f/Moskva/Novosibirsk/?class=Y&amp;travelers=1&amp;route[0]=491-31102026-58</t>
         </is>
       </c>
-      <c r="P17" s="5" t="inlineStr">
+      <c r="R17" s="5" t="inlineStr">
         <is>
           <t>Дома вечером 31.10</t>
         </is>
       </c>
-      <c r="Q17" s="5" t="inlineStr">
+      <c r="S17" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -6475,18 +6647,28 @@
           <t>~13:05</t>
         </is>
       </c>
-      <c r="N18" s="16" t="inlineStr"/>
-      <c r="O18" s="19" t="inlineStr">
+      <c r="N18" s="16" t="inlineStr">
+        <is>
+          <t>28.10 05:10 (мест.) → 28.10 13:05 МСК</t>
+        </is>
+      </c>
+      <c r="O18" s="15" t="inlineStr">
+        <is>
+          <t>11 ч 55 мин</t>
+        </is>
+      </c>
+      <c r="P18" s="16" t="inlineStr"/>
+      <c r="Q18" s="19" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/</t>
         </is>
       </c>
-      <c r="P18" s="16" t="inlineStr">
+      <c r="R18" s="16" t="inlineStr">
         <is>
           <t>Подъём ~05:00</t>
         </is>
       </c>
-      <c r="Q18" s="16" t="inlineStr">
+      <c r="S18" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -6552,14 +6734,24 @@
           <t>~16:00</t>
         </is>
       </c>
-      <c r="N19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>28.10 08:05 (мест.) → 28.10 16:00 МСК</t>
+        </is>
+      </c>
       <c r="O19" s="20" t="inlineStr">
         <is>
+          <t>11 ч 55 мин</t>
+        </is>
+      </c>
+      <c r="P19" s="5" t="inlineStr"/>
+      <c r="Q19" s="21" t="inlineStr">
+        <is>
           <t>https://avia.tutu.ru/</t>
         </is>
       </c>
-      <c r="P19" s="5" t="inlineStr"/>
-      <c r="Q19" s="5" t="inlineStr">
+      <c r="R19" s="5" t="inlineStr"/>
+      <c r="S19" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -6623,20 +6815,30 @@
       <c r="M20" s="5" t="inlineStr"/>
       <c r="N20" s="5" t="inlineStr">
         <is>
+          <t>31.10 18:05 МСК → 01.11 08:45 (мест.)</t>
+        </is>
+      </c>
+      <c r="O20" s="20" t="inlineStr">
+        <is>
+          <t>10 ч 40 мин</t>
+        </is>
+      </c>
+      <c r="P20" s="5" t="inlineStr">
+        <is>
           <t>+1 ночь 30→31</t>
         </is>
       </c>
-      <c r="O20" s="20" t="inlineStr">
+      <c r="Q20" s="21" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/</t>
         </is>
       </c>
-      <c r="P20" s="5" t="inlineStr">
+      <c r="R20" s="5" t="inlineStr">
         <is>
           <t>Ночной рейс</t>
         </is>
       </c>
-      <c r="Q20" s="5" t="inlineStr">
+      <c r="S20" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -6700,20 +6902,30 @@
       <c r="M21" s="5" t="inlineStr"/>
       <c r="N21" s="5" t="inlineStr">
         <is>
+          <t>31.10 08:35 МСК → 31.10 23:15 (мест.)</t>
+        </is>
+      </c>
+      <c r="O21" s="20" t="inlineStr">
+        <is>
+          <t>10 ч 40 мин</t>
+        </is>
+      </c>
+      <c r="P21" s="5" t="inlineStr">
+        <is>
           <t>+1 ночь 30→31</t>
         </is>
       </c>
-      <c r="O21" s="20" t="inlineStr">
+      <c r="Q21" s="21" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/</t>
         </is>
       </c>
-      <c r="P21" s="5" t="inlineStr">
+      <c r="R21" s="5" t="inlineStr">
         <is>
           <t>Дома вечером 31.10</t>
         </is>
       </c>
-      <c r="Q21" s="5" t="inlineStr">
+      <c r="S21" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -6779,18 +6991,28 @@
           <t>~10:50</t>
         </is>
       </c>
-      <c r="N22" s="16" t="inlineStr"/>
-      <c r="O22" s="19" t="inlineStr">
+      <c r="N22" s="16" t="inlineStr">
+        <is>
+          <t>28.10 05:00 (мест.) → 28.10 10:50 МСК</t>
+        </is>
+      </c>
+      <c r="O22" s="15" t="inlineStr">
+        <is>
+          <t>9 ч 50 мин</t>
+        </is>
+      </c>
+      <c r="P22" s="16" t="inlineStr"/>
+      <c r="Q22" s="19" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/</t>
         </is>
       </c>
-      <c r="P22" s="16" t="inlineStr">
+      <c r="R22" s="16" t="inlineStr">
         <is>
           <t>Ранний подъём</t>
         </is>
       </c>
-      <c r="Q22" s="16" t="inlineStr">
+      <c r="S22" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -6856,18 +7078,28 @@
           <t>~14:40</t>
         </is>
       </c>
-      <c r="N23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>28.10 07:40 (мест.) → 28.10 14:40 МСК</t>
+        </is>
+      </c>
       <c r="O23" s="20" t="inlineStr">
         <is>
+          <t>11 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="P23" s="5" t="inlineStr"/>
+      <c r="Q23" s="21" t="inlineStr">
+        <is>
           <t>https://avia.tutu.ru/</t>
         </is>
       </c>
-      <c r="P23" s="5" t="inlineStr">
+      <c r="R23" s="5" t="inlineStr">
         <is>
           <t>С багажом дешевле S7</t>
         </is>
       </c>
-      <c r="Q23" s="5" t="inlineStr">
+      <c r="S23" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -6931,20 +7163,30 @@
       <c r="M24" s="5" t="inlineStr"/>
       <c r="N24" s="5" t="inlineStr">
         <is>
+          <t>31.10 19:25 МСК → 01.11 09:55 (мест.)</t>
+        </is>
+      </c>
+      <c r="O24" s="20" t="inlineStr">
+        <is>
+          <t>10 ч 30 мин</t>
+        </is>
+      </c>
+      <c r="P24" s="5" t="inlineStr">
+        <is>
           <t>+1 ночь 30→31</t>
         </is>
       </c>
-      <c r="O24" s="20" t="inlineStr">
+      <c r="Q24" s="21" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/</t>
         </is>
       </c>
-      <c r="P24" s="5" t="inlineStr">
+      <c r="R24" s="5" t="inlineStr">
         <is>
           <t>Дневных рейсов в Абакан нет (есть только вечерние/ночные). День 31.10 на отдых</t>
         </is>
       </c>
-      <c r="Q24" s="5" t="inlineStr">
+      <c r="S24" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -7010,14 +7252,24 @@
           <t>~12:25</t>
         </is>
       </c>
-      <c r="N25" s="16" t="inlineStr"/>
-      <c r="O25" s="19" t="inlineStr">
+      <c r="N25" s="16" t="inlineStr">
+        <is>
+          <t>28.10 06:45 (мест.) → 28.10 12:25 МСК</t>
+        </is>
+      </c>
+      <c r="O25" s="15" t="inlineStr">
+        <is>
+          <t>9 ч 40 мин</t>
+        </is>
+      </c>
+      <c r="P25" s="16" t="inlineStr"/>
+      <c r="Q25" s="19" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/</t>
         </is>
       </c>
-      <c r="P25" s="16" t="inlineStr"/>
-      <c r="Q25" s="16" t="inlineStr">
+      <c r="R25" s="16" t="inlineStr"/>
+      <c r="S25" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -7079,18 +7331,28 @@
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr"/>
-      <c r="N26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr">
+        <is>
+          <t>30.10 18:15 МСК → 31.10 09:00 (мест.)</t>
+        </is>
+      </c>
       <c r="O26" s="20" t="inlineStr">
         <is>
+          <t>10 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="P26" s="5" t="inlineStr"/>
+      <c r="Q26" s="21" t="inlineStr">
+        <is>
           <t>https://avia.tutu.ru/</t>
         </is>
       </c>
-      <c r="P26" s="5" t="inlineStr">
+      <c r="R26" s="5" t="inlineStr">
         <is>
           <t>Ночной рейс сразу после конференции</t>
         </is>
       </c>
-      <c r="Q26" s="5" t="inlineStr"/>
+      <c r="S26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -7150,20 +7412,30 @@
       <c r="M27" s="5" t="inlineStr"/>
       <c r="N27" s="5" t="inlineStr">
         <is>
+          <t>31.10 18:05 МСК → 01.11 08:00 (мест.)</t>
+        </is>
+      </c>
+      <c r="O27" s="20" t="inlineStr">
+        <is>
+          <t>9 ч 55 мин</t>
+        </is>
+      </c>
+      <c r="P27" s="5" t="inlineStr">
+        <is>
           <t>+1 ночь 30→31</t>
         </is>
       </c>
-      <c r="O27" s="20" t="inlineStr">
+      <c r="Q27" s="21" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/</t>
         </is>
       </c>
-      <c r="P27" s="5" t="inlineStr">
+      <c r="R27" s="5" t="inlineStr">
         <is>
           <t>Дневных рейсов нет. День 31.10 на отдых, вечерний вылет</t>
         </is>
       </c>
-      <c r="Q27" s="5" t="inlineStr">
+      <c r="S27" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -7229,18 +7501,28 @@
           <t>~11:35</t>
         </is>
       </c>
-      <c r="N28" s="16" t="inlineStr"/>
-      <c r="O28" s="19" t="inlineStr">
+      <c r="N28" s="16" t="inlineStr">
+        <is>
+          <t>28.10 04:35 (мест.) → 28.10 11:35 МСК</t>
+        </is>
+      </c>
+      <c r="O28" s="15" t="inlineStr">
+        <is>
+          <t>12 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="P28" s="16" t="inlineStr"/>
+      <c r="Q28" s="19" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/</t>
         </is>
       </c>
-      <c r="P28" s="16" t="inlineStr">
+      <c r="R28" s="16" t="inlineStr">
         <is>
           <t>Цена за 1 человека</t>
         </is>
       </c>
-      <c r="Q28" s="16" t="inlineStr">
+      <c r="S28" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -7306,18 +7588,28 @@
           <t>~16:05</t>
         </is>
       </c>
-      <c r="N29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr">
+        <is>
+          <t>28.10 08:05 (мест.) → 28.10 16:05 МСК</t>
+        </is>
+      </c>
       <c r="O29" s="20" t="inlineStr">
         <is>
+          <t>13 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="P29" s="5" t="inlineStr"/>
+      <c r="Q29" s="21" t="inlineStr">
+        <is>
           <t>https://avia.tutu.ru/</t>
         </is>
       </c>
-      <c r="P29" s="5" t="inlineStr">
+      <c r="R29" s="5" t="inlineStr">
         <is>
           <t>Вылет днём</t>
         </is>
       </c>
-      <c r="Q29" s="5" t="inlineStr"/>
+      <c r="S29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -7377,20 +7669,30 @@
       <c r="M30" s="5" t="inlineStr"/>
       <c r="N30" s="5" t="inlineStr">
         <is>
+          <t>31.10 15:55 МСК → 01.11 07:40 (мест.)</t>
+        </is>
+      </c>
+      <c r="O30" s="20" t="inlineStr">
+        <is>
+          <t>10 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="P30" s="5" t="inlineStr">
+        <is>
           <t>+1 ночь 30→31</t>
         </is>
       </c>
-      <c r="O30" s="20" t="inlineStr">
+      <c r="Q30" s="21" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/</t>
         </is>
       </c>
-      <c r="P30" s="5" t="inlineStr">
+      <c r="R30" s="5" t="inlineStr">
         <is>
           <t>Ночной перелёт</t>
         </is>
       </c>
-      <c r="Q30" s="5" t="inlineStr">
+      <c r="S30" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -7454,20 +7756,30 @@
       <c r="M31" s="5" t="inlineStr"/>
       <c r="N31" s="5" t="inlineStr">
         <is>
+          <t>31.10 08:35 МСК → 01.11 00:20 (мест.)</t>
+        </is>
+      </c>
+      <c r="O31" s="20" t="inlineStr">
+        <is>
+          <t>10 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="P31" s="5" t="inlineStr">
+        <is>
           <t>+1 ночь 30→31</t>
         </is>
       </c>
-      <c r="O31" s="20" t="inlineStr">
+      <c r="Q31" s="21" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/</t>
         </is>
       </c>
-      <c r="P31" s="5" t="inlineStr">
+      <c r="R31" s="5" t="inlineStr">
         <is>
           <t>Дома вечером 31.10</t>
         </is>
       </c>
-      <c r="Q31" s="5" t="inlineStr">
+      <c r="S31" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -7533,14 +7845,24 @@
           <t>~15:25</t>
         </is>
       </c>
-      <c r="N32" s="16" t="inlineStr"/>
-      <c r="O32" s="19" t="inlineStr">
+      <c r="N32" s="16" t="inlineStr">
+        <is>
+          <t>28.10 07:50 (мест.) → 28.10 15:25 МСК</t>
+        </is>
+      </c>
+      <c r="O32" s="15" t="inlineStr">
+        <is>
+          <t>12 ч 35 мин</t>
+        </is>
+      </c>
+      <c r="P32" s="16" t="inlineStr"/>
+      <c r="Q32" s="19" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/</t>
         </is>
       </c>
-      <c r="P32" s="16" t="inlineStr"/>
-      <c r="Q32" s="16" t="inlineStr">
+      <c r="R32" s="16" t="inlineStr"/>
+      <c r="S32" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -7602,18 +7924,28 @@
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr"/>
-      <c r="N33" s="5" t="inlineStr"/>
+      <c r="N33" s="5" t="inlineStr">
+        <is>
+          <t>30.10 18:15 МСК → 31.10 10:35 (мест.)</t>
+        </is>
+      </c>
       <c r="O33" s="20" t="inlineStr">
         <is>
+          <t>11 ч 20 мин</t>
+        </is>
+      </c>
+      <c r="P33" s="5" t="inlineStr"/>
+      <c r="Q33" s="21" t="inlineStr">
+        <is>
           <t>https://avia.tutu.ru/</t>
         </is>
       </c>
-      <c r="P33" s="5" t="inlineStr">
+      <c r="R33" s="5" t="inlineStr">
         <is>
           <t>Ночной рейс сразу после конференции</t>
         </is>
       </c>
-      <c r="Q33" s="5" t="inlineStr"/>
+      <c r="S33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -7673,20 +8005,30 @@
       <c r="M34" s="5" t="inlineStr"/>
       <c r="N34" s="5" t="inlineStr">
         <is>
+          <t>31.10 17:25 МСК → 01.11 10:00 (мест.)</t>
+        </is>
+      </c>
+      <c r="O34" s="20" t="inlineStr">
+        <is>
+          <t>11 ч 35 мин</t>
+        </is>
+      </c>
+      <c r="P34" s="5" t="inlineStr">
+        <is>
           <t>+1 ночь 30→31</t>
         </is>
       </c>
-      <c r="O34" s="20" t="inlineStr">
+      <c r="Q34" s="21" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/</t>
         </is>
       </c>
-      <c r="P34" s="5" t="inlineStr">
+      <c r="R34" s="5" t="inlineStr">
         <is>
           <t>Дневных рейсов нет. День 31.10 на отдых; прилёт утром</t>
         </is>
       </c>
-      <c r="Q34" s="5" t="inlineStr">
+      <c r="S34" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -7752,18 +8094,28 @@
           <t>~13:20</t>
         </is>
       </c>
-      <c r="N35" s="16" t="inlineStr"/>
-      <c r="O35" s="19" t="inlineStr">
+      <c r="N35" s="16" t="inlineStr">
+        <is>
+          <t>28.10 01:05 (мест.) → 28.10 13:20 МСК</t>
+        </is>
+      </c>
+      <c r="O35" s="15" t="inlineStr">
+        <is>
+          <t>18 ч 15 мин</t>
+        </is>
+      </c>
+      <c r="P35" s="16" t="inlineStr"/>
+      <c r="Q35" s="19" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/f/Chita/Moskva/?class=Y&amp;travelers=1&amp;route[0]=100-28102026-491</t>
         </is>
       </c>
-      <c r="P35" s="16" t="inlineStr">
+      <c r="R35" s="16" t="inlineStr">
         <is>
           <t>Ночной вылет</t>
         </is>
       </c>
-      <c r="Q35" s="16" t="inlineStr">
+      <c r="S35" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -7829,18 +8181,28 @@
           <t>~12:45</t>
         </is>
       </c>
-      <c r="N36" s="5" t="inlineStr"/>
+      <c r="N36" s="5" t="inlineStr">
+        <is>
+          <t>28.10 07:05 (мест.) → 28.10 12:45 МСК</t>
+        </is>
+      </c>
       <c r="O36" s="20" t="inlineStr">
         <is>
+          <t>11 ч 40 мин</t>
+        </is>
+      </c>
+      <c r="P36" s="5" t="inlineStr"/>
+      <c r="Q36" s="21" t="inlineStr">
+        <is>
           <t>https://avia.tutu.ru/f/Chita/Moskva/?class=Y&amp;travelers=1&amp;route[0]=100-28102026-491</t>
         </is>
       </c>
-      <c r="P36" s="5" t="inlineStr">
+      <c r="R36" s="5" t="inlineStr">
         <is>
           <t>Прямой рейс днём</t>
         </is>
       </c>
-      <c r="Q36" s="5" t="inlineStr">
+      <c r="S36" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -7904,20 +8266,30 @@
       <c r="M37" s="5" t="inlineStr"/>
       <c r="N37" s="5" t="inlineStr">
         <is>
+          <t>31.10 16:10 МСК → 01.11 09:05 (мест.)</t>
+        </is>
+      </c>
+      <c r="O37" s="20" t="inlineStr">
+        <is>
+          <t>10 ч 55 мин</t>
+        </is>
+      </c>
+      <c r="P37" s="5" t="inlineStr">
+        <is>
           <t>+1 ночь 30→31</t>
         </is>
       </c>
-      <c r="O37" s="20" t="inlineStr">
+      <c r="Q37" s="21" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/f/Moskva/Chita/?class=Y&amp;travelers=1&amp;route[0]=491-31102026-100</t>
         </is>
       </c>
-      <c r="P37" s="5" t="inlineStr">
+      <c r="R37" s="5" t="inlineStr">
         <is>
           <t>Дневных рейсов нет; вылет вечером после отдыха</t>
         </is>
       </c>
-      <c r="Q37" s="5" t="inlineStr">
+      <c r="S37" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -7985,20 +8357,30 @@
       </c>
       <c r="N38" s="16" t="inlineStr">
         <is>
+          <t>27.10 14:55 (мест.) → 28.10 09:30 МСК</t>
+        </is>
+      </c>
+      <c r="O38" s="15" t="inlineStr">
+        <is>
+          <t>19 ч 35 мин</t>
+        </is>
+      </c>
+      <c r="P38" s="16" t="inlineStr">
+        <is>
           <t>ранний заезд</t>
         </is>
       </c>
-      <c r="O38" s="19" t="inlineStr">
+      <c r="Q38" s="19" t="inlineStr">
         <is>
           <t>https://www.tutu.ru/poezda/</t>
         </is>
       </c>
-      <c r="P38" s="16" t="inlineStr">
+      <c r="R38" s="16" t="inlineStr">
         <is>
           <t>Ночь в поезде</t>
         </is>
       </c>
-      <c r="Q38" s="16" t="inlineStr">
+      <c r="S38" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -8064,18 +8446,28 @@
           <t>~19:10</t>
         </is>
       </c>
-      <c r="N39" s="5" t="inlineStr"/>
+      <c r="N39" s="5" t="inlineStr">
+        <is>
+          <t>28.10 11:45 (мест.) → 28.10 19:10 МСК</t>
+        </is>
+      </c>
       <c r="O39" s="20" t="inlineStr">
         <is>
+          <t>8 ч 25 мин</t>
+        </is>
+      </c>
+      <c r="P39" s="5" t="inlineStr"/>
+      <c r="Q39" s="21" t="inlineStr">
+        <is>
           <t>https://avia.tutu.ru/f/Samara/Moskva/?class=Y&amp;travelers=1&amp;route[0]=74-28102026-491</t>
         </is>
       </c>
-      <c r="P39" s="5" t="inlineStr">
+      <c r="R39" s="5" t="inlineStr">
         <is>
           <t>Для экскурсии: SU-1603 10:25 → SVO 11:15, 6 454 / 9 763</t>
         </is>
       </c>
-      <c r="Q39" s="5" t="inlineStr">
+      <c r="S39" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -8137,18 +8529,28 @@
         </is>
       </c>
       <c r="M40" s="5" t="inlineStr"/>
-      <c r="N40" s="5" t="inlineStr"/>
+      <c r="N40" s="5" t="inlineStr">
+        <is>
+          <t>30.10 18:15 МСК → 31.10 13:05 (мест.)</t>
+        </is>
+      </c>
       <c r="O40" s="20" t="inlineStr">
         <is>
+          <t>17 ч 50 мин</t>
+        </is>
+      </c>
+      <c r="P40" s="5" t="inlineStr"/>
+      <c r="Q40" s="21" t="inlineStr">
+        <is>
           <t>https://www.tutu.ru/poezda/</t>
         </is>
       </c>
-      <c r="P40" s="5" t="inlineStr">
+      <c r="R40" s="5" t="inlineStr">
         <is>
           <t>Ночь в поезде</t>
         </is>
       </c>
-      <c r="Q40" s="5" t="inlineStr"/>
+      <c r="S40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -8208,20 +8610,30 @@
       <c r="M41" s="5" t="inlineStr"/>
       <c r="N41" s="5" t="inlineStr">
         <is>
+          <t>31.10 09:45 МСК → 31.10 18:40 (мест.)</t>
+        </is>
+      </c>
+      <c r="O41" s="20" t="inlineStr">
+        <is>
+          <t>7 ч 55 мин</t>
+        </is>
+      </c>
+      <c r="P41" s="5" t="inlineStr">
+        <is>
           <t>+1 ночь 30→31</t>
         </is>
       </c>
-      <c r="O41" s="20" t="inlineStr">
+      <c r="Q41" s="21" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/f/Moskva/Samara/?class=Y&amp;travelers=1&amp;route[0]=491-31102026-74</t>
         </is>
       </c>
-      <c r="P41" s="5" t="inlineStr">
+      <c r="R41" s="5" t="inlineStr">
         <is>
           <t>Также SU-1604 10:10, 6 410 / 9 760</t>
         </is>
       </c>
-      <c r="Q41" s="5" t="inlineStr">
+      <c r="S41" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -8287,18 +8699,28 @@
           <t>~10:45</t>
         </is>
       </c>
-      <c r="N42" s="16" t="inlineStr"/>
-      <c r="O42" s="19" t="inlineStr">
+      <c r="N42" s="16" t="inlineStr">
+        <is>
+          <t>27.10 14:35 (мест.) → 28.10 10:45 МСК</t>
+        </is>
+      </c>
+      <c r="O42" s="15" t="inlineStr">
+        <is>
+          <t>21 ч 10 мин</t>
+        </is>
+      </c>
+      <c r="P42" s="16" t="inlineStr"/>
+      <c r="Q42" s="19" t="inlineStr">
         <is>
           <t>https://www.tutu.ru/poezda/</t>
         </is>
       </c>
-      <c r="P42" s="16" t="inlineStr">
+      <c r="R42" s="16" t="inlineStr">
         <is>
           <t>Ночь в поезде</t>
         </is>
       </c>
-      <c r="Q42" s="16" t="inlineStr">
+      <c r="S42" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -8364,18 +8786,28 @@
           <t>~22:00</t>
         </is>
       </c>
-      <c r="N43" s="5" t="inlineStr"/>
+      <c r="N43" s="5" t="inlineStr">
+        <is>
+          <t>28.10 15:15 (мест.) → 28.10 22:00 МСК</t>
+        </is>
+      </c>
       <c r="O43" s="20" t="inlineStr">
         <is>
+          <t>7 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="P43" s="5" t="inlineStr"/>
+      <c r="Q43" s="21" t="inlineStr">
+        <is>
           <t>https://avia.tutu.ru/f/Saratov/Moskva/?class=Y&amp;travelers=1&amp;route[0]=77-28102026-491</t>
         </is>
       </c>
-      <c r="P43" s="5" t="inlineStr">
+      <c r="R43" s="5" t="inlineStr">
         <is>
           <t>Для экскурсии: SU-1357 11:05 → SVO 11:50, 8 078 / 11 390</t>
         </is>
       </c>
-      <c r="Q43" s="5" t="inlineStr"/>
+      <c r="S43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -8435,20 +8867,30 @@
       <c r="M44" s="5" t="inlineStr"/>
       <c r="N44" s="5" t="inlineStr">
         <is>
+          <t>31.10 13:40 МСК → 31.10 22:00 (мест.)</t>
+        </is>
+      </c>
+      <c r="O44" s="20" t="inlineStr">
+        <is>
+          <t>7 ч 20 мин</t>
+        </is>
+      </c>
+      <c r="P44" s="5" t="inlineStr">
+        <is>
           <t>+1 ночь 30→31</t>
         </is>
       </c>
-      <c r="O44" s="20" t="inlineStr">
+      <c r="Q44" s="21" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/f/Moskva/Saratov/?class=Y&amp;travelers=1&amp;route[0]=491-31102026-77</t>
         </is>
       </c>
-      <c r="P44" s="5" t="inlineStr">
+      <c r="R44" s="5" t="inlineStr">
         <is>
           <t>30.10 уехать нельзя: последний поезд 19:27, рейсы до 18:00</t>
         </is>
       </c>
-      <c r="Q44" s="5" t="inlineStr">
+      <c r="S44" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -8514,18 +8956,28 @@
           <t>~13:30</t>
         </is>
       </c>
-      <c r="N45" s="16" t="inlineStr"/>
-      <c r="O45" s="19" t="inlineStr">
+      <c r="N45" s="16" t="inlineStr">
+        <is>
+          <t>28.10 05:05 МСК → 28.10 13:30 МСК</t>
+        </is>
+      </c>
+      <c r="O45" s="15" t="inlineStr">
+        <is>
+          <t>8 ч 25 мин</t>
+        </is>
+      </c>
+      <c r="P45" s="16" t="inlineStr"/>
+      <c r="Q45" s="19" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/f/Kazan/Moskva/?class=Y&amp;travelers=1&amp;route[0]=33-28102026-491</t>
         </is>
       </c>
-      <c r="P45" s="16" t="inlineStr">
+      <c r="R45" s="16" t="inlineStr">
         <is>
           <t>Дешевле поезда; подъём ~05:30</t>
         </is>
       </c>
-      <c r="Q45" s="16" t="inlineStr">
+      <c r="S45" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -8591,18 +9043,28 @@
           <t>~15:35</t>
         </is>
       </c>
-      <c r="N46" s="5" t="inlineStr"/>
+      <c r="N46" s="5" t="inlineStr">
+        <is>
+          <t>28.10 07:10 МСК → 28.10 15:35 МСК</t>
+        </is>
+      </c>
       <c r="O46" s="20" t="inlineStr">
         <is>
+          <t>8 ч 25 мин</t>
+        </is>
+      </c>
+      <c r="P46" s="5" t="inlineStr"/>
+      <c r="Q46" s="21" t="inlineStr">
+        <is>
           <t>https://avia.tutu.ru/f/Kazan/Moskva/?class=Y&amp;travelers=1&amp;route[0]=33-28102026-491</t>
         </is>
       </c>
-      <c r="P46" s="5" t="inlineStr">
+      <c r="R46" s="5" t="inlineStr">
         <is>
           <t>К экскурсии успевает</t>
         </is>
       </c>
-      <c r="Q46" s="5" t="inlineStr">
+      <c r="S46" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -8664,18 +9126,28 @@
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr"/>
-      <c r="N47" s="5" t="inlineStr"/>
+      <c r="N47" s="5" t="inlineStr">
+        <is>
+          <t>30.10 20:30 МСК → 31.10 13:15 МСК</t>
+        </is>
+      </c>
       <c r="O47" s="20" t="inlineStr">
         <is>
+          <t>16 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="P47" s="5" t="inlineStr"/>
+      <c r="Q47" s="21" t="inlineStr">
+        <is>
           <t>https://www.tutu.ru/poezda/</t>
         </is>
       </c>
-      <c r="P47" s="5" t="inlineStr">
+      <c r="R47" s="5" t="inlineStr">
         <is>
           <t>Ночь в поезде</t>
         </is>
       </c>
-      <c r="Q47" s="5" t="inlineStr"/>
+      <c r="S47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -8735,20 +9207,30 @@
       <c r="M48" s="5" t="inlineStr"/>
       <c r="N48" s="5" t="inlineStr">
         <is>
+          <t>31.10 13:00 МСК → 31.10 20:50 МСК</t>
+        </is>
+      </c>
+      <c r="O48" s="20" t="inlineStr">
+        <is>
+          <t>7 ч 50 мин</t>
+        </is>
+      </c>
+      <c r="P48" s="5" t="inlineStr">
+        <is>
           <t>+1 ночь 30→31</t>
         </is>
       </c>
-      <c r="O48" s="20" t="inlineStr">
+      <c r="Q48" s="21" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/f/Moskva/Kazan/?class=Y&amp;travelers=1&amp;route[0]=491-31102026-33</t>
         </is>
       </c>
-      <c r="P48" s="5" t="inlineStr">
+      <c r="R48" s="5" t="inlineStr">
         <is>
           <t>Также N4-63 16:10, 7 323 / 10 492</t>
         </is>
       </c>
-      <c r="Q48" s="5" t="inlineStr">
+      <c r="S48" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -8814,18 +9296,28 @@
           <t>~22:30</t>
         </is>
       </c>
-      <c r="N49" s="16" t="inlineStr"/>
-      <c r="O49" s="19" t="inlineStr">
+      <c r="N49" s="16" t="inlineStr">
+        <is>
+          <t>28.10 16:40 (мест.) → 28.10 22:30 МСК</t>
+        </is>
+      </c>
+      <c r="O49" s="15" t="inlineStr">
+        <is>
+          <t>6 ч 50 мин</t>
+        </is>
+      </c>
+      <c r="P49" s="16" t="inlineStr"/>
+      <c r="Q49" s="19" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/f/Izhevsk/Moskva/?class=Y&amp;travelers=1&amp;route[0]=30-28102026-491</t>
         </is>
       </c>
-      <c r="P49" s="16" t="inlineStr">
+      <c r="R49" s="16" t="inlineStr">
         <is>
           <t>Без экскурсии. Для экскурсии: SU-1295 10:40 → SVO 11:35, 9 802 / 13 186</t>
         </is>
       </c>
-      <c r="Q49" s="16" t="inlineStr">
+      <c r="S49" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -8889,20 +9381,30 @@
       <c r="M50" s="5" t="inlineStr"/>
       <c r="N50" s="5" t="inlineStr">
         <is>
+          <t>31.10 11:40 МСК → 31.10 19:35 (мест.)</t>
+        </is>
+      </c>
+      <c r="O50" s="20" t="inlineStr">
+        <is>
+          <t>6 ч 55 мин</t>
+        </is>
+      </c>
+      <c r="P50" s="5" t="inlineStr">
+        <is>
           <t>+1 ночь 30→31</t>
         </is>
       </c>
-      <c r="O50" s="20" t="inlineStr">
+      <c r="Q50" s="21" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/f/Moskva/Izhevsk/?class=Y&amp;travelers=1&amp;route[0]=491-31102026-30</t>
         </is>
       </c>
-      <c r="P50" s="5" t="inlineStr">
+      <c r="R50" s="5" t="inlineStr">
         <is>
           <t>Вечером 30.10 рейсов нет</t>
         </is>
       </c>
-      <c r="Q50" s="5" t="inlineStr">
+      <c r="S50" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -8968,18 +9470,28 @@
           <t>~22:10</t>
         </is>
       </c>
-      <c r="N51" s="16" t="inlineStr"/>
-      <c r="O51" s="19" t="inlineStr">
+      <c r="N51" s="16" t="inlineStr">
+        <is>
+          <t>28.10 14:15 МСК → 28.10 22:10 МСК</t>
+        </is>
+      </c>
+      <c r="O51" s="15" t="inlineStr">
+        <is>
+          <t>7 ч 55 мин</t>
+        </is>
+      </c>
+      <c r="P51" s="16" t="inlineStr"/>
+      <c r="Q51" s="19" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/f/Nizhnekamsk/Moskva/?class=Y&amp;travelers=1&amp;route[0]=537-28102026-491</t>
         </is>
       </c>
-      <c r="P51" s="16" t="inlineStr">
+      <c r="R51" s="16" t="inlineStr">
         <is>
           <t>Без экскурсии. Для экскурсии: SU-6248 09:55, 8 847 / 12 189</t>
         </is>
       </c>
-      <c r="Q51" s="16" t="inlineStr">
+      <c r="S51" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -9043,20 +9555,30 @@
       <c r="M52" s="5" t="inlineStr"/>
       <c r="N52" s="5" t="inlineStr">
         <is>
+          <t>31.10 09:40 МСК → 31.10 17:25 МСК</t>
+        </is>
+      </c>
+      <c r="O52" s="20" t="inlineStr">
+        <is>
+          <t>7 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="P52" s="5" t="inlineStr">
+        <is>
           <t>+1 ночь 30→31</t>
         </is>
       </c>
-      <c r="O52" s="20" t="inlineStr">
+      <c r="Q52" s="21" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/f/Moskva/Nizhnekamsk/?class=Y&amp;travelers=1&amp;route[0]=491-31102026-537</t>
         </is>
       </c>
-      <c r="P52" s="5" t="inlineStr">
+      <c r="R52" s="5" t="inlineStr">
         <is>
           <t>Вечером 30.10 рейсов нет</t>
         </is>
       </c>
-      <c r="Q52" s="5" t="inlineStr">
+      <c r="S52" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -9122,18 +9644,28 @@
           <t>~22:35</t>
         </is>
       </c>
-      <c r="N53" s="16" t="inlineStr"/>
-      <c r="O53" s="19" t="inlineStr">
+      <c r="N53" s="16" t="inlineStr">
+        <is>
+          <t>28.10 16:20 (мест.) → 28.10 22:35 МСК</t>
+        </is>
+      </c>
+      <c r="O53" s="15" t="inlineStr">
+        <is>
+          <t>8 ч 15 мин</t>
+        </is>
+      </c>
+      <c r="P53" s="16" t="inlineStr"/>
+      <c r="Q53" s="19" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/</t>
         </is>
       </c>
-      <c r="P53" s="16" t="inlineStr">
+      <c r="R53" s="16" t="inlineStr">
         <is>
           <t>Без экскурсии. Для экскурсии: SU-1247 12:20, 11 352 / 14 698</t>
         </is>
       </c>
-      <c r="Q53" s="16" t="inlineStr">
+      <c r="S53" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -9193,18 +9725,28 @@
         </is>
       </c>
       <c r="M54" s="5" t="inlineStr"/>
-      <c r="N54" s="5" t="inlineStr"/>
+      <c r="N54" s="5" t="inlineStr">
+        <is>
+          <t>30.10 19:00 МСК → 31.10 08:10 (мест.)</t>
+        </is>
+      </c>
       <c r="O54" s="20" t="inlineStr">
         <is>
+          <t>11 ч 10 мин</t>
+        </is>
+      </c>
+      <c r="P54" s="5" t="inlineStr"/>
+      <c r="Q54" s="21" t="inlineStr">
+        <is>
           <t>https://avia.tutu.ru/</t>
         </is>
       </c>
-      <c r="P54" s="5" t="inlineStr">
+      <c r="R54" s="5" t="inlineStr">
         <is>
           <t>Ночной рейс, гостиница не нужна. Проверить наличие</t>
         </is>
       </c>
-      <c r="Q54" s="5" t="inlineStr"/>
+      <c r="S54" s="5" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
@@ -9264,16 +9806,26 @@
       <c r="M55" s="5" t="inlineStr"/>
       <c r="N55" s="5" t="inlineStr">
         <is>
+          <t>31.10 11:00 МСК → 31.10 21:10 (мест.)</t>
+        </is>
+      </c>
+      <c r="O55" s="20" t="inlineStr">
+        <is>
+          <t>8 ч 10 мин</t>
+        </is>
+      </c>
+      <c r="P55" s="5" t="inlineStr">
+        <is>
           <t>+1 ночь 30→31</t>
         </is>
       </c>
-      <c r="O55" s="20" t="inlineStr">
+      <c r="Q55" s="21" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/</t>
         </is>
       </c>
-      <c r="P55" s="5" t="inlineStr"/>
-      <c r="Q55" s="5" t="inlineStr">
+      <c r="R55" s="5" t="inlineStr"/>
+      <c r="S55" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -9339,18 +9891,28 @@
           <t>~15:15</t>
         </is>
       </c>
-      <c r="N56" s="16" t="inlineStr"/>
-      <c r="O56" s="19" t="inlineStr">
+      <c r="N56" s="16" t="inlineStr">
+        <is>
+          <t>28.10 08:55 (мест.) → 28.10 15:15 МСК</t>
+        </is>
+      </c>
+      <c r="O56" s="15" t="inlineStr">
+        <is>
+          <t>7 ч 20 мин</t>
+        </is>
+      </c>
+      <c r="P56" s="16" t="inlineStr"/>
+      <c r="Q56" s="19" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/f/Ulyanovsk/Moskva/?class=Y&amp;travelers=1&amp;route[0]=88-28102026-491</t>
         </is>
       </c>
-      <c r="P56" s="16" t="inlineStr">
+      <c r="R56" s="16" t="inlineStr">
         <is>
           <t>К экскурсии успевают</t>
         </is>
       </c>
-      <c r="Q56" s="16" t="inlineStr">
+      <c r="S56" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -9414,20 +9976,30 @@
       <c r="M57" s="5" t="inlineStr"/>
       <c r="N57" s="5" t="inlineStr">
         <is>
+          <t>31.10 15:20 МСК → 31.10 23:40 (мест.)</t>
+        </is>
+      </c>
+      <c r="O57" s="20" t="inlineStr">
+        <is>
+          <t>7 ч 20 мин</t>
+        </is>
+      </c>
+      <c r="P57" s="5" t="inlineStr">
+        <is>
           <t>+1 ночь 30→31</t>
         </is>
       </c>
-      <c r="O57" s="20" t="inlineStr">
+      <c r="Q57" s="21" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/f/Moskva/Ulyanovsk/?class=Y&amp;travelers=1&amp;route[0]=491-31102026-88</t>
         </is>
       </c>
-      <c r="P57" s="5" t="inlineStr">
+      <c r="R57" s="5" t="inlineStr">
         <is>
           <t>30.10 уехать нельзя</t>
         </is>
       </c>
-      <c r="Q57" s="5" t="inlineStr">
+      <c r="S57" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -9493,18 +10065,28 @@
           <t>~15:30</t>
         </is>
       </c>
-      <c r="N58" s="16" t="inlineStr"/>
-      <c r="O58" s="19" t="inlineStr">
+      <c r="N58" s="16" t="inlineStr">
+        <is>
+          <t>28.10 07:55 МСК → 28.10 15:30 МСК</t>
+        </is>
+      </c>
+      <c r="O58" s="15" t="inlineStr">
+        <is>
+          <t>7 ч 35 мин</t>
+        </is>
+      </c>
+      <c r="P58" s="16" t="inlineStr"/>
+      <c r="Q58" s="19" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/f/Cheboksary/Moskva/?class=Y&amp;travelers=1&amp;route[0]=97-28102026-491</t>
         </is>
       </c>
-      <c r="P58" s="16" t="inlineStr">
+      <c r="R58" s="16" t="inlineStr">
         <is>
           <t>Дешевле поезда, к экскурсии успевает</t>
         </is>
       </c>
-      <c r="Q58" s="16" t="inlineStr">
+      <c r="S58" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -9566,18 +10148,28 @@
         </is>
       </c>
       <c r="M59" s="5" t="inlineStr"/>
-      <c r="N59" s="5" t="inlineStr"/>
+      <c r="N59" s="5" t="inlineStr">
+        <is>
+          <t>30.10 19:40 МСК → 31.10 12:45 МСК</t>
+        </is>
+      </c>
       <c r="O59" s="20" t="inlineStr">
         <is>
+          <t>17 ч 05 мин</t>
+        </is>
+      </c>
+      <c r="P59" s="5" t="inlineStr"/>
+      <c r="Q59" s="21" t="inlineStr">
+        <is>
           <t>https://www.tutu.ru/poezda/</t>
         </is>
       </c>
-      <c r="P59" s="5" t="inlineStr">
+      <c r="R59" s="5" t="inlineStr">
         <is>
           <t>Ночь в поезде</t>
         </is>
       </c>
-      <c r="Q59" s="5" t="inlineStr"/>
+      <c r="S59" s="5" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
@@ -9637,20 +10229,30 @@
       <c r="M60" s="5" t="inlineStr"/>
       <c r="N60" s="5" t="inlineStr">
         <is>
+          <t>31.10 15:00 МСК → 31.10 22:20 МСК</t>
+        </is>
+      </c>
+      <c r="O60" s="20" t="inlineStr">
+        <is>
+          <t>7 ч 20 мин</t>
+        </is>
+      </c>
+      <c r="P60" s="5" t="inlineStr">
+        <is>
           <t>+1 ночь 30→31</t>
         </is>
       </c>
-      <c r="O60" s="20" t="inlineStr">
+      <c r="Q60" s="21" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/f/Moskva/Cheboksary/?class=Y&amp;travelers=1&amp;route[0]=491-31102026-97</t>
         </is>
       </c>
-      <c r="P60" s="5" t="inlineStr">
+      <c r="R60" s="5" t="inlineStr">
         <is>
           <t>Также SU-1586 16:25, 6 582 / 9 919</t>
         </is>
       </c>
-      <c r="Q60" s="5" t="inlineStr">
+      <c r="S60" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -9716,14 +10318,24 @@
           <t>~17:25</t>
         </is>
       </c>
-      <c r="N61" s="16" t="inlineStr"/>
-      <c r="O61" s="19" t="inlineStr">
+      <c r="N61" s="16" t="inlineStr">
+        <is>
+          <t>28.10 09:45 (мест.) → 28.10 17:25 МСК</t>
+        </is>
+      </c>
+      <c r="O61" s="15" t="inlineStr">
+        <is>
+          <t>8 ч 40 мин</t>
+        </is>
+      </c>
+      <c r="P61" s="16" t="inlineStr"/>
+      <c r="Q61" s="19" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/f/Astrakhan/Moskva/?class=Y&amp;travelers=1&amp;route[0]=12-28102026-491</t>
         </is>
       </c>
-      <c r="P61" s="16" t="inlineStr"/>
-      <c r="Q61" s="16" t="inlineStr">
+      <c r="R61" s="16" t="inlineStr"/>
+      <c r="S61" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -9787,20 +10399,30 @@
       <c r="M62" s="5" t="inlineStr"/>
       <c r="N62" s="5" t="inlineStr">
         <is>
+          <t>31.10 09:20 МСК → 31.10 18:55 (мест.)</t>
+        </is>
+      </c>
+      <c r="O62" s="20" t="inlineStr">
+        <is>
+          <t>8 ч 35 мин</t>
+        </is>
+      </c>
+      <c r="P62" s="5" t="inlineStr">
+        <is>
           <t>+1 ночь 30→31</t>
         </is>
       </c>
-      <c r="O62" s="20" t="inlineStr">
+      <c r="Q62" s="21" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/f/Moskva/Astrakhan/?class=Y&amp;travelers=1&amp;route[0]=491-31102026-12</t>
         </is>
       </c>
-      <c r="P62" s="5" t="inlineStr">
+      <c r="R62" s="5" t="inlineStr">
         <is>
           <t>Вечером 30.10 подходящих рейсов нет</t>
         </is>
       </c>
-      <c r="Q62" s="5" t="inlineStr">
+      <c r="S62" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -9866,18 +10488,28 @@
           <t>~15:50</t>
         </is>
       </c>
-      <c r="N63" s="16" t="inlineStr"/>
-      <c r="O63" s="19" t="inlineStr">
+      <c r="N63" s="16" t="inlineStr">
+        <is>
+          <t>28.10 07:10 МСК → 28.10 15:50 МСК</t>
+        </is>
+      </c>
+      <c r="O63" s="15" t="inlineStr">
+        <is>
+          <t>8 ч 40 мин</t>
+        </is>
+      </c>
+      <c r="P63" s="16" t="inlineStr"/>
+      <c r="Q63" s="19" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/f/Volgograd/Moskva/?class=Y&amp;travelers=1&amp;route[0]=23-28102026-491</t>
         </is>
       </c>
-      <c r="P63" s="16" t="inlineStr">
+      <c r="R63" s="16" t="inlineStr">
         <is>
           <t>Дешевле ночного поезда (6 615)</t>
         </is>
       </c>
-      <c r="Q63" s="16" t="inlineStr">
+      <c r="S63" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -9941,20 +10573,30 @@
       <c r="M64" s="5" t="inlineStr"/>
       <c r="N64" s="5" t="inlineStr">
         <is>
+          <t>31.10 14:05 МСК → 31.10 22:15 МСК</t>
+        </is>
+      </c>
+      <c r="O64" s="20" t="inlineStr">
+        <is>
+          <t>8 ч 10 мин</t>
+        </is>
+      </c>
+      <c r="P64" s="5" t="inlineStr">
+        <is>
           <t>+1 ночь 30→31</t>
         </is>
       </c>
-      <c r="O64" s="20" t="inlineStr">
+      <c r="Q64" s="21" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/f/Moskva/Volgograd/?class=Y&amp;travelers=1&amp;route[0]=491-31102026-23</t>
         </is>
       </c>
-      <c r="P64" s="5" t="inlineStr">
+      <c r="R64" s="5" t="inlineStr">
         <is>
           <t>30.10 уехать нельзя. Также S7-2143 DME 11:05, 9 889 / 13 255</t>
         </is>
       </c>
-      <c r="Q64" s="5" t="inlineStr">
+      <c r="S64" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -10020,18 +10662,28 @@
           <t>~17:40</t>
         </is>
       </c>
-      <c r="N65" s="16" t="inlineStr"/>
-      <c r="O65" s="19" t="inlineStr">
+      <c r="N65" s="16" t="inlineStr">
+        <is>
+          <t>28.10 06:45 МСК → 28.10 17:40 МСК</t>
+        </is>
+      </c>
+      <c r="O65" s="15" t="inlineStr">
+        <is>
+          <t>10 ч 55 мин</t>
+        </is>
+      </c>
+      <c r="P65" s="16" t="inlineStr"/>
+      <c r="Q65" s="19" t="inlineStr">
         <is>
           <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2014370&amp;nnst2=2000000</t>
         </is>
       </c>
-      <c r="P65" s="16" t="inlineStr">
+      <c r="R65" s="16" t="inlineStr">
         <is>
           <t>~650 км — больше лимита для машины</t>
         </is>
       </c>
-      <c r="Q65" s="16" t="inlineStr">
+      <c r="S65" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -10093,18 +10745,28 @@
         </is>
       </c>
       <c r="M66" s="5" t="inlineStr"/>
-      <c r="N66" s="5" t="inlineStr"/>
+      <c r="N66" s="5" t="inlineStr">
+        <is>
+          <t>30.10 18:15 МСК → 31.10 15:15 МСК</t>
+        </is>
+      </c>
       <c r="O66" s="20" t="inlineStr">
         <is>
+          <t>21 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="P66" s="5" t="inlineStr"/>
+      <c r="Q66" s="21" t="inlineStr">
+        <is>
           <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2014370</t>
         </is>
       </c>
-      <c r="P66" s="5" t="inlineStr">
+      <c r="R66" s="5" t="inlineStr">
         <is>
           <t>Ночь в поезде</t>
         </is>
       </c>
-      <c r="Q66" s="5" t="inlineStr"/>
+      <c r="S66" s="5" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
@@ -10164,20 +10826,30 @@
       <c r="M67" s="5" t="inlineStr"/>
       <c r="N67" s="5" t="inlineStr">
         <is>
+          <t>31.10 08:45 МСК → 31.10 19:50 МСК</t>
+        </is>
+      </c>
+      <c r="O67" s="20" t="inlineStr">
+        <is>
+          <t>11 ч 05 мин</t>
+        </is>
+      </c>
+      <c r="P67" s="5" t="inlineStr">
+        <is>
           <t>+1 ночь 30→31</t>
         </is>
       </c>
-      <c r="O67" s="20" t="inlineStr">
+      <c r="Q67" s="21" t="inlineStr">
         <is>
           <t>https://www.tutu.ru/poezda/rasp_d.php?date=31.10.2026&amp;nnst1=2000000&amp;nnst2=2014370</t>
         </is>
       </c>
-      <c r="P67" s="5" t="inlineStr">
+      <c r="R67" s="5" t="inlineStr">
         <is>
           <t>Днём, без ночи в дороге</t>
         </is>
       </c>
-      <c r="Q67" s="5" t="inlineStr"/>
+      <c r="S67" s="5" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="15" t="inlineStr">
@@ -10239,18 +10911,28 @@
           <t>~11:00–12:00</t>
         </is>
       </c>
-      <c r="N68" s="16" t="inlineStr"/>
-      <c r="O68" s="19" t="inlineStr">
+      <c r="N68" s="16" t="inlineStr">
+        <is>
+          <t>27.10 08:30 МСК → 28.10 11:30 МСК</t>
+        </is>
+      </c>
+      <c r="O68" s="15" t="inlineStr">
+        <is>
+          <t>27 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="P68" s="16" t="inlineStr"/>
+      <c r="Q68" s="19" t="inlineStr">
         <is>
           <t>https://vekspress-bus.ru/marshrutyi/doneczk-moskva.html</t>
         </is>
       </c>
-      <c r="P68" s="16" t="inlineStr">
+      <c r="R68" s="16" t="inlineStr">
         <is>
           <t>~20 ч в автобусе, ночь сидя. Многие рейсы через день — уточнить</t>
         </is>
       </c>
-      <c r="Q68" s="16" t="inlineStr">
+      <c r="S68" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -10316,18 +10998,28 @@
           <t>~10:45</t>
         </is>
       </c>
-      <c r="N69" s="5" t="inlineStr"/>
+      <c r="N69" s="5" t="inlineStr">
+        <is>
+          <t>27.10 05:30 МСК → 28.10 10:45 МСК</t>
+        </is>
+      </c>
       <c r="O69" s="20" t="inlineStr">
         <is>
+          <t>29 ч 15 мин</t>
+        </is>
+      </c>
+      <c r="P69" s="5" t="inlineStr"/>
+      <c r="Q69" s="21" t="inlineStr">
+        <is>
           <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2064000&amp;nnst2=2000000</t>
         </is>
       </c>
-      <c r="P69" s="5" t="inlineStr">
+      <c r="R69" s="5" t="inlineStr">
         <is>
           <t>Ночь в купе — дневного варианта из Донецка нет. Донецк → Ростов ~4 ч (~1 500 ₽)</t>
         </is>
       </c>
-      <c r="Q69" s="5" t="inlineStr">
+      <c r="S69" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -10391,20 +11083,30 @@
       <c r="M70" s="5" t="inlineStr"/>
       <c r="N70" s="5" t="inlineStr">
         <is>
+          <t>31.10 08:30 МСК → 01.11 09:00 МСК</t>
+        </is>
+      </c>
+      <c r="O70" s="20" t="inlineStr">
+        <is>
+          <t>24 ч 30 мин</t>
+        </is>
+      </c>
+      <c r="P70" s="5" t="inlineStr">
+        <is>
           <t>+1 ночь 30→31</t>
         </is>
       </c>
-      <c r="O70" s="20" t="inlineStr">
+      <c r="Q70" s="21" t="inlineStr">
         <is>
           <t>https://vekspress-bus.ru/marshrutyi/doneczk-moskva.html</t>
         </is>
       </c>
-      <c r="P70" s="5" t="inlineStr">
+      <c r="R70" s="5" t="inlineStr">
         <is>
           <t>Ночь сидя в автобусе</t>
         </is>
       </c>
-      <c r="Q70" s="5" t="inlineStr"/>
+      <c r="S70" s="5" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
@@ -10462,18 +11164,28 @@
         </is>
       </c>
       <c r="M71" s="5" t="inlineStr"/>
-      <c r="N71" s="5" t="inlineStr"/>
+      <c r="N71" s="5" t="inlineStr">
+        <is>
+          <t>30.10 18:15 МСК → 01.11 00:00 МСК</t>
+        </is>
+      </c>
       <c r="O71" s="20" t="inlineStr">
         <is>
+          <t>29 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="P71" s="5" t="inlineStr"/>
+      <c r="Q71" s="21" t="inlineStr">
+        <is>
           <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2064000</t>
         </is>
       </c>
-      <c r="P71" s="5" t="inlineStr">
+      <c r="R71" s="5" t="inlineStr">
         <is>
           <t>Ночь в купе; дома ~00:00. Также 092М «Таврия» 23:30, 9 721 ₽</t>
         </is>
       </c>
-      <c r="Q71" s="5" t="inlineStr"/>
+      <c r="S71" s="5" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="15" t="inlineStr">
@@ -10535,18 +11247,28 @@
           <t>~09:50</t>
         </is>
       </c>
-      <c r="N72" s="16" t="inlineStr"/>
-      <c r="O72" s="19" t="inlineStr">
+      <c r="N72" s="16" t="inlineStr">
+        <is>
+          <t>28.10 03:50 (мест.) → 28.10 09:50 МСК</t>
+        </is>
+      </c>
+      <c r="O72" s="15" t="inlineStr">
+        <is>
+          <t>8 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="P72" s="16" t="inlineStr"/>
+      <c r="Q72" s="19" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/f/Ekaterinburg/Moskva/?class=Y&amp;travelers=1&amp;route[0]=29-28102026-491</t>
         </is>
       </c>
-      <c r="P72" s="16" t="inlineStr">
-        <is>
-          <t>Подъём ~03:30. Цена за 1 чел. при покупке 9 билетов сразу</t>
-        </is>
-      </c>
-      <c r="Q72" s="16" t="inlineStr">
+      <c r="R72" s="16" t="inlineStr">
+        <is>
+          <t>Подъём ~03:30. Цена одного билета; 10 билетов на один рейс — покупать заранее, пока есть места по этой цене</t>
+        </is>
+      </c>
+      <c r="S72" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -10612,18 +11334,28 @@
           <t>~12:40</t>
         </is>
       </c>
-      <c r="N73" s="5" t="inlineStr"/>
+      <c r="N73" s="5" t="inlineStr">
+        <is>
+          <t>28.10 06:30 (мест.) → 28.10 12:40 МСК</t>
+        </is>
+      </c>
       <c r="O73" s="20" t="inlineStr">
         <is>
+          <t>8 ч 10 мин</t>
+        </is>
+      </c>
+      <c r="P73" s="5" t="inlineStr"/>
+      <c r="Q73" s="21" t="inlineStr">
+        <is>
           <t>https://avia.tutu.ru/f/Ekaterinburg/Moskva/?class=Y&amp;travelers=1&amp;route[0]=29-28102026-491</t>
         </is>
       </c>
-      <c r="P73" s="5" t="inlineStr">
+      <c r="R73" s="5" t="inlineStr">
         <is>
           <t>Подъём ~06:00; к экскурсии успевают. Также U6-300 12:00, 10 289 / 13 395</t>
         </is>
       </c>
-      <c r="Q73" s="5" t="inlineStr">
+      <c r="S73" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -10685,18 +11417,28 @@
         </is>
       </c>
       <c r="M74" s="5" t="inlineStr"/>
-      <c r="N74" s="5" t="inlineStr"/>
+      <c r="N74" s="5" t="inlineStr">
+        <is>
+          <t>30.10 18:15 МСК → 31.10 06:00 (мест.)</t>
+        </is>
+      </c>
       <c r="O74" s="20" t="inlineStr">
         <is>
+          <t>9 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="P74" s="5" t="inlineStr"/>
+      <c r="Q74" s="21" t="inlineStr">
+        <is>
           <t>https://avia.tutu.ru/f/Moskva/Ekaterinburg/?class=Y&amp;travelers=1&amp;route[0]=491-30102026-29</t>
         </is>
       </c>
-      <c r="P74" s="5" t="inlineStr">
+      <c r="R74" s="5" t="inlineStr">
         <is>
           <t>Ночной рейс</t>
         </is>
       </c>
-      <c r="Q74" s="5" t="inlineStr">
+      <c r="S74" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -10760,20 +11502,30 @@
       <c r="M75" s="5" t="inlineStr"/>
       <c r="N75" s="5" t="inlineStr">
         <is>
+          <t>31.10 06:30 МСК → 31.10 16:10 (мест.)</t>
+        </is>
+      </c>
+      <c r="O75" s="20" t="inlineStr">
+        <is>
+          <t>7 ч 40 мин</t>
+        </is>
+      </c>
+      <c r="P75" s="5" t="inlineStr">
+        <is>
           <t>+1 ночь 30→31</t>
         </is>
       </c>
-      <c r="O75" s="20" t="inlineStr">
+      <c r="Q75" s="21" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/f/Moskva/Ekaterinburg/?class=Y&amp;travelers=1&amp;route[0]=491-31102026-29</t>
         </is>
       </c>
-      <c r="P75" s="5" t="inlineStr">
-        <is>
-          <t>Цена за 1 чел. при покупке 9 билетов. Также U6-273 08:25</t>
-        </is>
-      </c>
-      <c r="Q75" s="5" t="inlineStr">
+      <c r="R75" s="5" t="inlineStr">
+        <is>
+          <t>Цена одного билета. Также U6-273 08:25</t>
+        </is>
+      </c>
+      <c r="S75" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -10819,10 +11571,10 @@
           <t>Екатеринбург, Кольцово</t>
         </is>
       </c>
-      <c r="J76" s="21" t="n">
+      <c r="J76" s="22" t="n">
         <v>1200</v>
       </c>
-      <c r="K76" s="21" t="n">
+      <c r="K76" s="22" t="n">
         <v>4000</v>
       </c>
       <c r="L76" s="16" t="inlineStr">
@@ -10833,12 +11585,14 @@
       <c r="M76" s="16" t="inlineStr"/>
       <c r="N76" s="16" t="inlineStr"/>
       <c r="O76" s="16" t="inlineStr"/>
-      <c r="P76" s="16" t="inlineStr">
+      <c r="P76" s="16" t="inlineStr"/>
+      <c r="Q76" s="16" t="inlineStr"/>
+      <c r="R76" s="16" t="inlineStr">
         <is>
           <t>Для удобного варианта — приехать в Екатеринбург накануне</t>
         </is>
       </c>
-      <c r="Q76" s="16" t="inlineStr">
+      <c r="S76" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -10904,18 +11658,28 @@
           <t>~16:25</t>
         </is>
       </c>
-      <c r="N77" s="16" t="inlineStr"/>
-      <c r="O77" s="19" t="inlineStr">
+      <c r="N77" s="16" t="inlineStr">
+        <is>
+          <t>28.10 10:05 (мест.) → 28.10 16:25 МСК</t>
+        </is>
+      </c>
+      <c r="O77" s="15" t="inlineStr">
+        <is>
+          <t>8 ч 20 мин</t>
+        </is>
+      </c>
+      <c r="P77" s="16" t="inlineStr"/>
+      <c r="Q77" s="19" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/f/Magnitogorsk/Moskva/?class=Y&amp;travelers=1&amp;route[0]=45-28102026-491</t>
         </is>
       </c>
-      <c r="P77" s="16" t="inlineStr">
+      <c r="R77" s="16" t="inlineStr">
         <is>
           <t>Выезд из дома ~10:00. Другие рейсы неудобны (06:15)</t>
         </is>
       </c>
-      <c r="Q77" s="16" t="inlineStr">
+      <c r="S77" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -10977,18 +11741,28 @@
         </is>
       </c>
       <c r="M78" s="5" t="inlineStr"/>
-      <c r="N78" s="5" t="inlineStr"/>
+      <c r="N78" s="5" t="inlineStr">
+        <is>
+          <t>30.10 18:15 МСК → 31.10 06:30 (мест.)</t>
+        </is>
+      </c>
       <c r="O78" s="20" t="inlineStr">
         <is>
+          <t>10 ч 15 мин</t>
+        </is>
+      </c>
+      <c r="P78" s="5" t="inlineStr"/>
+      <c r="Q78" s="21" t="inlineStr">
+        <is>
           <t>https://avia.tutu.ru/f/Moskva/Magnitogorsk/?class=Y&amp;travelers=1&amp;route[0]=491-31102026-45</t>
         </is>
       </c>
-      <c r="P78" s="5" t="inlineStr">
+      <c r="R78" s="5" t="inlineStr">
         <is>
           <t>Ночной рейс сразу после конференции</t>
         </is>
       </c>
-      <c r="Q78" s="5" t="inlineStr"/>
+      <c r="S78" s="5" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
@@ -11048,20 +11822,30 @@
       <c r="M79" s="5" t="inlineStr"/>
       <c r="N79" s="5" t="inlineStr">
         <is>
+          <t>31.10 06:20 МСК → 31.10 21:00 (мест.)</t>
+        </is>
+      </c>
+      <c r="O79" s="20" t="inlineStr">
+        <is>
+          <t>12 ч 40 мин</t>
+        </is>
+      </c>
+      <c r="P79" s="5" t="inlineStr">
+        <is>
           <t>+1 ночь 30→31</t>
         </is>
       </c>
-      <c r="O79" s="20" t="inlineStr">
+      <c r="Q79" s="21" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/f/Moskva/Chelyabinsk/?class=Y&amp;travelers=1&amp;route[0]=491-31102026-98</t>
         </is>
       </c>
-      <c r="P79" s="5" t="inlineStr">
+      <c r="R79" s="5" t="inlineStr">
         <is>
           <t>Прямые рейсы в Магнитогорск — только 00:40 и 07:40. Челябинск → Магнитогорск автобус ~4,5 ч, ~1 500 ₽ (включено)</t>
         </is>
       </c>
-      <c r="Q79" s="5" t="inlineStr">
+      <c r="S79" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -11127,18 +11911,28 @@
           <t>~10:40</t>
         </is>
       </c>
-      <c r="N80" s="16" t="inlineStr"/>
-      <c r="O80" s="19" t="inlineStr">
+      <c r="N80" s="16" t="inlineStr">
+        <is>
+          <t>28.10 03:30 (мест.) → 28.10 10:40 МСК</t>
+        </is>
+      </c>
+      <c r="O80" s="15" t="inlineStr">
+        <is>
+          <t>9 ч 10 мин</t>
+        </is>
+      </c>
+      <c r="P80" s="16" t="inlineStr"/>
+      <c r="Q80" s="19" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/f/Chelyabinsk/Moskva/?class=Y&amp;travelers=1&amp;route[0]=98-28102026-491</t>
         </is>
       </c>
-      <c r="P80" s="16" t="inlineStr">
+      <c r="R80" s="16" t="inlineStr">
         <is>
           <t>Ранний подъём</t>
         </is>
       </c>
-      <c r="Q80" s="16" t="inlineStr">
+      <c r="S80" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -11204,18 +11998,28 @@
           <t>~20:50</t>
         </is>
       </c>
-      <c r="N81" s="5" t="inlineStr"/>
+      <c r="N81" s="5" t="inlineStr">
+        <is>
+          <t>28.10 13:20 (мест.) → 28.10 20:50 МСК</t>
+        </is>
+      </c>
       <c r="O81" s="20" t="inlineStr">
         <is>
+          <t>9 ч 30 мин</t>
+        </is>
+      </c>
+      <c r="P81" s="5" t="inlineStr"/>
+      <c r="Q81" s="21" t="inlineStr">
+        <is>
           <t>https://avia.tutu.ru/f/Chelyabinsk/Moskva/?class=Y&amp;travelers=1&amp;route[0]=98-28102026-491</t>
         </is>
       </c>
-      <c r="P81" s="5" t="inlineStr">
+      <c r="R81" s="5" t="inlineStr">
         <is>
           <t>Без экскурсии. Для экскурсии: SU-1535 12:30, 10 408 / 14 081</t>
         </is>
       </c>
-      <c r="Q81" s="5" t="inlineStr">
+      <c r="S81" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -11277,18 +12081,28 @@
         </is>
       </c>
       <c r="M82" s="5" t="inlineStr"/>
-      <c r="N82" s="5" t="inlineStr"/>
+      <c r="N82" s="5" t="inlineStr">
+        <is>
+          <t>30.10 18:15 МСК → 31.10 06:05 (мест.)</t>
+        </is>
+      </c>
       <c r="O82" s="20" t="inlineStr">
         <is>
+          <t>9 ч 50 мин</t>
+        </is>
+      </c>
+      <c r="P82" s="5" t="inlineStr"/>
+      <c r="Q82" s="21" t="inlineStr">
+        <is>
           <t>https://avia.tutu.ru/f/Moskva/Chelyabinsk/?class=Y&amp;travelers=1&amp;route[0]=491-30102026-98</t>
         </is>
       </c>
-      <c r="P82" s="5" t="inlineStr">
+      <c r="R82" s="5" t="inlineStr">
         <is>
           <t>Ночной рейс</t>
         </is>
       </c>
-      <c r="Q82" s="5" t="inlineStr"/>
+      <c r="S82" s="5" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
@@ -11348,16 +12162,26 @@
       <c r="M83" s="5" t="inlineStr"/>
       <c r="N83" s="5" t="inlineStr">
         <is>
+          <t>31.10 06:20 МСК → 31.10 17:05 (мест.)</t>
+        </is>
+      </c>
+      <c r="O83" s="20" t="inlineStr">
+        <is>
+          <t>8 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="P83" s="5" t="inlineStr">
+        <is>
           <t>+1 ночь 30→31</t>
         </is>
       </c>
-      <c r="O83" s="20" t="inlineStr">
+      <c r="Q83" s="21" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/f/Moskva/Chelyabinsk/?class=Y&amp;travelers=1&amp;route[0]=491-31102026-98</t>
         </is>
       </c>
-      <c r="P83" s="5" t="inlineStr"/>
-      <c r="Q83" s="5" t="inlineStr">
+      <c r="R83" s="5" t="inlineStr"/>
+      <c r="S83" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -11423,18 +12247,28 @@
           <t>~11:10</t>
         </is>
       </c>
-      <c r="N84" s="16" t="inlineStr"/>
-      <c r="O84" s="19" t="inlineStr">
+      <c r="N84" s="16" t="inlineStr">
+        <is>
+          <t>28.10 04:10 (мест.) → 28.10 11:10 МСК</t>
+        </is>
+      </c>
+      <c r="O84" s="15" t="inlineStr">
+        <is>
+          <t>9 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="P84" s="16" t="inlineStr"/>
+      <c r="Q84" s="19" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/f/Tyumen/Moskva/?class=Y&amp;travelers=1&amp;route[0]=86-28102026-491</t>
         </is>
       </c>
-      <c r="P84" s="16" t="inlineStr">
+      <c r="R84" s="16" t="inlineStr">
         <is>
           <t>Ранний подъём</t>
         </is>
       </c>
-      <c r="Q84" s="16" t="inlineStr">
+      <c r="S84" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -11500,18 +12334,28 @@
           <t>~22:30</t>
         </is>
       </c>
-      <c r="N85" s="5" t="inlineStr"/>
+      <c r="N85" s="5" t="inlineStr">
+        <is>
+          <t>28.10 15:45 (мест.) → 28.10 22:30 МСК</t>
+        </is>
+      </c>
       <c r="O85" s="20" t="inlineStr">
         <is>
+          <t>8 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="P85" s="5" t="inlineStr"/>
+      <c r="Q85" s="21" t="inlineStr">
+        <is>
           <t>https://avia.tutu.ru/f/Tyumen/Moskva/?class=Y&amp;travelers=1&amp;route[0]=86-28102026-491</t>
         </is>
       </c>
-      <c r="P85" s="5" t="inlineStr">
+      <c r="R85" s="5" t="inlineStr">
         <is>
           <t>Без экскурсии. Для экскурсии: SU-1505 13:25, 9 980 / 13 589</t>
         </is>
       </c>
-      <c r="Q85" s="5" t="inlineStr"/>
+      <c r="S85" s="5" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
@@ -11569,18 +12413,28 @@
         </is>
       </c>
       <c r="M86" s="5" t="inlineStr"/>
-      <c r="N86" s="5" t="inlineStr"/>
+      <c r="N86" s="5" t="inlineStr">
+        <is>
+          <t>30.10 18:15 МСК → 31.10 06:05 (мест.)</t>
+        </is>
+      </c>
       <c r="O86" s="20" t="inlineStr">
         <is>
+          <t>9 ч 50 мин</t>
+        </is>
+      </c>
+      <c r="P86" s="5" t="inlineStr"/>
+      <c r="Q86" s="21" t="inlineStr">
+        <is>
           <t>https://avia.tutu.ru/f/Moskva/Tyumen/?class=Y&amp;travelers=1&amp;route[0]=491-30102026-86</t>
         </is>
       </c>
-      <c r="P86" s="5" t="inlineStr">
+      <c r="R86" s="5" t="inlineStr">
         <is>
           <t>Ночной рейс, впритык по правилу 2 ч</t>
         </is>
       </c>
-      <c r="Q86" s="5" t="inlineStr"/>
+      <c r="S86" s="5" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
@@ -11640,16 +12494,26 @@
       <c r="M87" s="5" t="inlineStr"/>
       <c r="N87" s="5" t="inlineStr">
         <is>
+          <t>31.10 05:45 МСК → 31.10 16:10 (мест.)</t>
+        </is>
+      </c>
+      <c r="O87" s="20" t="inlineStr">
+        <is>
+          <t>8 ч 25 мин</t>
+        </is>
+      </c>
+      <c r="P87" s="5" t="inlineStr">
+        <is>
           <t>+1 ночь 30→31</t>
         </is>
       </c>
-      <c r="O87" s="20" t="inlineStr">
+      <c r="Q87" s="21" t="inlineStr">
         <is>
           <t>https://avia.tutu.ru/f/Moskva/Tyumen/?class=Y&amp;travelers=1&amp;route[0]=491-31102026-86</t>
         </is>
       </c>
-      <c r="P87" s="5" t="inlineStr"/>
-      <c r="Q87" s="5" t="inlineStr">
+      <c r="R87" s="5" t="inlineStr"/>
+      <c r="S87" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -11715,18 +12579,28 @@
           <t>~15:30</t>
         </is>
       </c>
-      <c r="N88" s="16" t="inlineStr"/>
-      <c r="O88" s="19" t="inlineStr">
+      <c r="N88" s="16" t="inlineStr">
+        <is>
+          <t>28.10 04:50 МСК → 28.10 15:30 МСК</t>
+        </is>
+      </c>
+      <c r="O88" s="15" t="inlineStr">
+        <is>
+          <t>10 ч 40 мин</t>
+        </is>
+      </c>
+      <c r="P88" s="16" t="inlineStr"/>
+      <c r="Q88" s="19" t="inlineStr">
         <is>
           <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2004000&amp;nnst2=2000000</t>
         </is>
       </c>
-      <c r="P88" s="16" t="inlineStr">
+      <c r="R88" s="16" t="inlineStr">
         <is>
           <t>Самый дешёвый, но подъём ~04:00</t>
         </is>
       </c>
-      <c r="Q88" s="16" t="inlineStr">
+      <c r="S88" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -11792,18 +12666,28 @@
           <t>~15:40</t>
         </is>
       </c>
-      <c r="N89" s="5" t="inlineStr"/>
+      <c r="N89" s="5" t="inlineStr">
+        <is>
+          <t>28.10 08:15 МСК → 28.10 15:40 МСК</t>
+        </is>
+      </c>
       <c r="O89" s="20" t="inlineStr">
         <is>
+          <t>7 ч 25 мин</t>
+        </is>
+      </c>
+      <c r="P89" s="5" t="inlineStr"/>
+      <c r="Q89" s="21" t="inlineStr">
+        <is>
           <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2004000&amp;nnst2=2000000</t>
         </is>
       </c>
-      <c r="P89" s="5" t="inlineStr">
+      <c r="R89" s="5" t="inlineStr">
         <is>
           <t>Днём, 4 ч; к экскурсии почти успевает</t>
         </is>
       </c>
-      <c r="Q89" s="5" t="inlineStr">
+      <c r="S89" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -11865,18 +12749,28 @@
         </is>
       </c>
       <c r="M90" s="5" t="inlineStr"/>
-      <c r="N90" s="5" t="inlineStr"/>
+      <c r="N90" s="5" t="inlineStr">
+        <is>
+          <t>30.10 18:15 МСК → 31.10 05:45 МСК</t>
+        </is>
+      </c>
       <c r="O90" s="20" t="inlineStr">
         <is>
+          <t>11 ч 30 мин</t>
+        </is>
+      </c>
+      <c r="P90" s="5" t="inlineStr"/>
+      <c r="Q90" s="21" t="inlineStr">
+        <is>
           <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2004000</t>
         </is>
       </c>
-      <c r="P90" s="5" t="inlineStr">
+      <c r="R90" s="5" t="inlineStr">
         <is>
           <t>Ночь сидя</t>
         </is>
       </c>
-      <c r="Q90" s="5" t="inlineStr"/>
+      <c r="S90" s="5" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
@@ -11936,20 +12830,30 @@
       <c r="M91" s="5" t="inlineStr"/>
       <c r="N91" s="5" t="inlineStr">
         <is>
+          <t>31.10 10:30 МСК → 31.10 20:00 МСК</t>
+        </is>
+      </c>
+      <c r="O91" s="20" t="inlineStr">
+        <is>
+          <t>9 ч 30 мин</t>
+        </is>
+      </c>
+      <c r="P91" s="5" t="inlineStr">
+        <is>
           <t>+1 ночь 30→31</t>
         </is>
       </c>
-      <c r="O91" s="20" t="inlineStr">
+      <c r="Q91" s="21" t="inlineStr">
         <is>
           <t>https://www.tutu.ru/poezda/rasp_d.php?date=31.10.2026&amp;nnst1=2000000&amp;nnst2=2004000</t>
         </is>
       </c>
-      <c r="P91" s="5" t="inlineStr">
+      <c r="R91" s="5" t="inlineStr">
         <is>
           <t>Днём. Или Сапсан 768А 13:30 → 17:30, 4 666 ₽</t>
         </is>
       </c>
-      <c r="Q91" s="5" t="inlineStr"/>
+      <c r="S91" s="5" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="15" t="inlineStr">
@@ -12011,18 +12915,28 @@
           <t>~15:30</t>
         </is>
       </c>
-      <c r="N92" s="16" t="inlineStr"/>
-      <c r="O92" s="19" t="inlineStr">
+      <c r="N92" s="16" t="inlineStr">
+        <is>
+          <t>28.10 06:35 МСК → 28.10 15:30 МСК</t>
+        </is>
+      </c>
+      <c r="O92" s="15" t="inlineStr">
+        <is>
+          <t>8 ч 55 мин</t>
+        </is>
+      </c>
+      <c r="P92" s="16" t="inlineStr"/>
+      <c r="Q92" s="19" t="inlineStr">
         <is>
           <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2060000&amp;nnst2=2000000</t>
         </is>
       </c>
-      <c r="P92" s="16" t="inlineStr">
+      <c r="R92" s="16" t="inlineStr">
         <is>
           <t>Или своя машина: ~430 км, ~6 ч</t>
         </is>
       </c>
-      <c r="Q92" s="16" t="inlineStr">
+      <c r="S92" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -12084,18 +12998,28 @@
         </is>
       </c>
       <c r="M93" s="5" t="inlineStr"/>
-      <c r="N93" s="5" t="inlineStr"/>
+      <c r="N93" s="5" t="inlineStr">
+        <is>
+          <t>30.10 18:15 МСК → 31.10 02:00 МСК</t>
+        </is>
+      </c>
       <c r="O93" s="20" t="inlineStr">
         <is>
+          <t>7 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="P93" s="5" t="inlineStr"/>
+      <c r="Q93" s="21" t="inlineStr">
+        <is>
           <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2060000</t>
         </is>
       </c>
-      <c r="P93" s="5" t="inlineStr">
+      <c r="R93" s="5" t="inlineStr">
         <is>
           <t>Дома глубокой ночью</t>
         </is>
       </c>
-      <c r="Q93" s="5" t="inlineStr"/>
+      <c r="S93" s="5" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
@@ -12155,20 +13079,30 @@
       <c r="M94" s="5" t="inlineStr"/>
       <c r="N94" s="5" t="inlineStr">
         <is>
+          <t>31.10 10:45 МСК → 31.10 18:30 МСК</t>
+        </is>
+      </c>
+      <c r="O94" s="20" t="inlineStr">
+        <is>
+          <t>7 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="P94" s="5" t="inlineStr">
+        <is>
           <t>+1 ночь 30→31</t>
         </is>
       </c>
-      <c r="O94" s="20" t="inlineStr">
+      <c r="Q94" s="21" t="inlineStr">
         <is>
           <t>https://www.tutu.ru/poezda/rasp_d.php?date=31.10.2026&amp;nnst1=2000000&amp;nnst2=2060000</t>
         </is>
       </c>
-      <c r="P94" s="5" t="inlineStr">
+      <c r="R94" s="5" t="inlineStr">
         <is>
           <t>Днём</t>
         </is>
       </c>
-      <c r="Q94" s="5" t="inlineStr"/>
+      <c r="S94" s="5" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="15" t="inlineStr">
@@ -12230,18 +13164,28 @@
           <t>~15:30</t>
         </is>
       </c>
-      <c r="N95" s="16" t="inlineStr"/>
-      <c r="O95" s="19" t="inlineStr">
+      <c r="N95" s="16" t="inlineStr">
+        <is>
+          <t>28.10 06:45 МСК → 28.10 15:30 МСК</t>
+        </is>
+      </c>
+      <c r="O95" s="15" t="inlineStr">
+        <is>
+          <t>8 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="P95" s="16" t="inlineStr"/>
+      <c r="Q95" s="19" t="inlineStr">
         <is>
           <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2000170&amp;nnst2=2000000</t>
         </is>
       </c>
-      <c r="P95" s="16" t="inlineStr">
+      <c r="R95" s="16" t="inlineStr">
         <is>
           <t>К экскурсии в 16:00 успевает</t>
         </is>
       </c>
-      <c r="Q95" s="16" t="inlineStr">
+      <c r="S95" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -12303,18 +13247,28 @@
         </is>
       </c>
       <c r="M96" s="5" t="inlineStr"/>
-      <c r="N96" s="5" t="inlineStr"/>
+      <c r="N96" s="5" t="inlineStr">
+        <is>
+          <t>30.10 18:15 МСК → 31.10 05:25 МСК</t>
+        </is>
+      </c>
       <c r="O96" s="20" t="inlineStr">
         <is>
+          <t>11 ч 10 мин</t>
+        </is>
+      </c>
+      <c r="P96" s="5" t="inlineStr"/>
+      <c r="Q96" s="21" t="inlineStr">
+        <is>
           <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2000170</t>
         </is>
       </c>
-      <c r="P96" s="5" t="inlineStr">
+      <c r="R96" s="5" t="inlineStr">
         <is>
           <t>Дома ночью</t>
         </is>
       </c>
-      <c r="Q96" s="5" t="inlineStr"/>
+      <c r="S96" s="5" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
@@ -12374,20 +13328,30 @@
       <c r="M97" s="5" t="inlineStr"/>
       <c r="N97" s="5" t="inlineStr">
         <is>
+          <t>31.10 06:45 МСК → 31.10 14:50 МСК</t>
+        </is>
+      </c>
+      <c r="O97" s="20" t="inlineStr">
+        <is>
+          <t>8 ч 05 мин</t>
+        </is>
+      </c>
+      <c r="P97" s="5" t="inlineStr">
+        <is>
           <t>+1 ночь 30→31</t>
         </is>
       </c>
-      <c r="O97" s="20" t="inlineStr">
+      <c r="Q97" s="21" t="inlineStr">
         <is>
           <t>https://www.tutu.ru/poezda/rasp_d.php?date=31.10.2026&amp;nnst1=2000000&amp;nnst2=2000170</t>
         </is>
       </c>
-      <c r="P97" s="5" t="inlineStr">
+      <c r="R97" s="5" t="inlineStr">
         <is>
           <t>Днём. Или машина ~520 км</t>
         </is>
       </c>
-      <c r="Q97" s="5" t="inlineStr"/>
+      <c r="S97" s="5" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="15" t="inlineStr">
@@ -12449,14 +13413,24 @@
           <t>~15:30</t>
         </is>
       </c>
-      <c r="N98" s="16" t="inlineStr"/>
-      <c r="O98" s="19" t="inlineStr">
+      <c r="N98" s="16" t="inlineStr">
+        <is>
+          <t>28.10 09:30 МСК → 28.10 15:30 МСК</t>
+        </is>
+      </c>
+      <c r="O98" s="15" t="inlineStr">
+        <is>
+          <t>6 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="P98" s="16" t="inlineStr"/>
+      <c r="Q98" s="19" t="inlineStr">
         <is>
           <t>https://www.tutu.ru/poezda/rasp_d.php?date=28.10.2026&amp;nnst1=2004600&amp;nnst2=2000000</t>
         </is>
       </c>
-      <c r="P98" s="16" t="inlineStr"/>
-      <c r="Q98" s="16" t="inlineStr">
+      <c r="R98" s="16" t="inlineStr"/>
+      <c r="S98" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -12518,14 +13492,24 @@
           <t>~13:30</t>
         </is>
       </c>
-      <c r="N99" s="5" t="inlineStr"/>
-      <c r="O99" s="5" t="inlineStr"/>
-      <c r="P99" s="5" t="inlineStr">
+      <c r="N99" s="5" t="inlineStr">
+        <is>
+          <t>28.10 09:30 МСК → 28.10 13:30 МСК</t>
+        </is>
+      </c>
+      <c r="O99" s="20" t="inlineStr">
+        <is>
+          <t>4 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="P99" s="5" t="inlineStr"/>
+      <c r="Q99" s="5" t="inlineStr"/>
+      <c r="R99" s="5" t="inlineStr">
         <is>
           <t>Топливо ~3 770 ₽ туда-обратно на машину</t>
         </is>
       </c>
-      <c r="Q99" s="5" t="inlineStr"/>
+      <c r="S99" s="5" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
@@ -12583,18 +13567,28 @@
         </is>
       </c>
       <c r="M100" s="5" t="inlineStr"/>
-      <c r="N100" s="5" t="inlineStr"/>
+      <c r="N100" s="5" t="inlineStr">
+        <is>
+          <t>30.10 18:15 МСК → 31.10 00:50 МСК</t>
+        </is>
+      </c>
       <c r="O100" s="20" t="inlineStr">
         <is>
+          <t>6 ч 35 мин</t>
+        </is>
+      </c>
+      <c r="P100" s="5" t="inlineStr"/>
+      <c r="Q100" s="21" t="inlineStr">
+        <is>
           <t>https://www.tutu.ru/poezda/rasp_d.php?date=30.10.2026&amp;nnst1=2000000&amp;nnst2=2004600</t>
         </is>
       </c>
-      <c r="P100" s="5" t="inlineStr">
+      <c r="R100" s="5" t="inlineStr">
         <is>
           <t>Цена ориентировочная</t>
         </is>
       </c>
-      <c r="Q100" s="5" t="inlineStr"/>
+      <c r="S100" s="5" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="15" t="inlineStr">
@@ -12658,20 +13652,30 @@
       </c>
       <c r="N101" s="16" t="inlineStr">
         <is>
+          <t>28.10 04:45 МСК → 28.10 07:10 МСК</t>
+        </is>
+      </c>
+      <c r="O101" s="15" t="inlineStr">
+        <is>
+          <t>2 ч 25 мин</t>
+        </is>
+      </c>
+      <c r="P101" s="16" t="inlineStr">
+        <is>
           <t>ранний заезд</t>
         </is>
       </c>
-      <c r="O101" s="19" t="inlineStr">
+      <c r="Q101" s="19" t="inlineStr">
         <is>
           <t>https://www.tutu.ru/rasp.php?st1=92502&amp;st2=11902&amp;date=28.10.2026</t>
         </is>
       </c>
-      <c r="P101" s="16" t="inlineStr">
+      <c r="R101" s="16" t="inlineStr">
         <is>
           <t>Следующая только 14:36 (→16:17)</t>
         </is>
       </c>
-      <c r="Q101" s="16" t="inlineStr">
+      <c r="S101" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -12733,14 +13737,24 @@
           <t>~14:00</t>
         </is>
       </c>
-      <c r="N102" s="5" t="inlineStr"/>
-      <c r="O102" s="5" t="inlineStr"/>
-      <c r="P102" s="5" t="inlineStr">
+      <c r="N102" s="5" t="inlineStr">
+        <is>
+          <t>28.10 12:30 МСК → 28.10 14:00 МСК</t>
+        </is>
+      </c>
+      <c r="O102" s="20" t="inlineStr">
+        <is>
+          <t>1 ч 30 мин</t>
+        </is>
+      </c>
+      <c r="P102" s="5" t="inlineStr"/>
+      <c r="Q102" s="5" t="inlineStr"/>
+      <c r="R102" s="5" t="inlineStr">
         <is>
           <t>Топливо ~1 300 ₽ туда-обратно</t>
         </is>
       </c>
-      <c r="Q102" s="5" t="inlineStr"/>
+      <c r="S102" s="5" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
@@ -12798,14 +13812,24 @@
         </is>
       </c>
       <c r="M103" s="5" t="inlineStr"/>
-      <c r="N103" s="5" t="inlineStr"/>
+      <c r="N103" s="5" t="inlineStr">
+        <is>
+          <t>30.10 21:00 МСК → 30.10 23:35 МСК</t>
+        </is>
+      </c>
       <c r="O103" s="20" t="inlineStr">
         <is>
+          <t>2 ч 35 мин</t>
+        </is>
+      </c>
+      <c r="P103" s="5" t="inlineStr"/>
+      <c r="Q103" s="21" t="inlineStr">
+        <is>
           <t>https://www.tutu.ru/rasp.php?st1=11902&amp;st2=92502&amp;date=30.10.2026</t>
         </is>
       </c>
-      <c r="P103" s="5" t="inlineStr"/>
-      <c r="Q103" s="5" t="inlineStr"/>
+      <c r="R103" s="5" t="inlineStr"/>
+      <c r="S103" s="5" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="15" t="inlineStr">
@@ -12863,18 +13887,28 @@
           <t>~12:00 / ~15:30</t>
         </is>
       </c>
-      <c r="N104" s="16" t="inlineStr"/>
-      <c r="O104" s="19" t="inlineStr">
+      <c r="N104" s="16" t="inlineStr">
+        <is>
+          <t>28.10 08:45 МСК → 28.10 12:00 МСК</t>
+        </is>
+      </c>
+      <c r="O104" s="15" t="inlineStr">
+        <is>
+          <t>3 ч 15 мин</t>
+        </is>
+      </c>
+      <c r="P104" s="16" t="inlineStr"/>
+      <c r="Q104" s="19" t="inlineStr">
         <is>
           <t>https://www.tutu.ru/prigorod/</t>
         </is>
       </c>
-      <c r="P104" s="16" t="inlineStr">
+      <c r="R104" s="16" t="inlineStr">
         <is>
           <t>РЭКС 620 ₽</t>
         </is>
       </c>
-      <c r="Q104" s="16" t="inlineStr">
+      <c r="S104" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -12936,14 +13970,24 @@
           <t>~14:00</t>
         </is>
       </c>
-      <c r="N105" s="5" t="inlineStr"/>
-      <c r="O105" s="5" t="inlineStr"/>
-      <c r="P105" s="5" t="inlineStr">
+      <c r="N105" s="5" t="inlineStr">
+        <is>
+          <t>28.10 12:00 МСК → 28.10 14:00 МСК</t>
+        </is>
+      </c>
+      <c r="O105" s="20" t="inlineStr">
+        <is>
+          <t>2 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="P105" s="5" t="inlineStr"/>
+      <c r="Q105" s="5" t="inlineStr"/>
+      <c r="R105" s="5" t="inlineStr">
         <is>
           <t>Топливо ~1 500 ₽ туда-обратно</t>
         </is>
       </c>
-      <c r="Q105" s="5" t="inlineStr"/>
+      <c r="S105" s="5" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
@@ -12997,14 +14041,24 @@
         </is>
       </c>
       <c r="M106" s="5" t="inlineStr"/>
-      <c r="N106" s="5" t="inlineStr"/>
+      <c r="N106" s="5" t="inlineStr">
+        <is>
+          <t>30.10 18:15 МСК → 30.10 21:45 МСК</t>
+        </is>
+      </c>
       <c r="O106" s="20" t="inlineStr">
         <is>
+          <t>3 ч 30 мин</t>
+        </is>
+      </c>
+      <c r="P106" s="5" t="inlineStr"/>
+      <c r="Q106" s="21" t="inlineStr">
+        <is>
           <t>https://www.tutu.ru/prigorod/</t>
         </is>
       </c>
-      <c r="P106" s="5" t="inlineStr"/>
-      <c r="Q106" s="5" t="inlineStr"/>
+      <c r="R106" s="5" t="inlineStr"/>
+      <c r="S106" s="5" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="15" t="inlineStr">
@@ -13050,10 +14104,10 @@
           <t>Москва, Казанский</t>
         </is>
       </c>
-      <c r="J107" s="21" t="n">
+      <c r="J107" s="22" t="n">
         <v>3967</v>
       </c>
-      <c r="K107" s="21" t="n">
+      <c r="K107" s="22" t="n">
         <v>3967</v>
       </c>
       <c r="L107" s="16" t="inlineStr">
@@ -13066,18 +14120,28 @@
           <t>~12:00</t>
         </is>
       </c>
-      <c r="N107" s="16" t="inlineStr"/>
-      <c r="O107" s="19" t="inlineStr">
+      <c r="N107" s="16" t="inlineStr">
+        <is>
+          <t>27.10 20:50 МСК → 28.10 12:00 МСК</t>
+        </is>
+      </c>
+      <c r="O107" s="15" t="inlineStr">
+        <is>
+          <t>15 ч 10 мин</t>
+        </is>
+      </c>
+      <c r="P107" s="16" t="inlineStr"/>
+      <c r="Q107" s="19" t="inlineStr">
         <is>
           <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2024120&amp;nnst2=2000000</t>
         </is>
       </c>
-      <c r="P107" s="16" t="inlineStr">
+      <c r="R107" s="16" t="inlineStr">
         <is>
           <t>Основной вариант — машина (лист «Авто»)</t>
         </is>
       </c>
-      <c r="Q107" s="16" t="inlineStr">
+      <c r="S107" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -13127,10 +14191,10 @@
           <t>Москва, Казанский</t>
         </is>
       </c>
-      <c r="J108" s="21" t="n">
+      <c r="J108" s="22" t="n">
         <v>4394</v>
       </c>
-      <c r="K108" s="21" t="n">
+      <c r="K108" s="22" t="n">
         <v>4394</v>
       </c>
       <c r="L108" s="16" t="inlineStr">
@@ -13145,20 +14209,30 @@
       </c>
       <c r="N108" s="16" t="inlineStr">
         <is>
+          <t>27.10 19:55 МСК → 28.10 09:30 МСК</t>
+        </is>
+      </c>
+      <c r="O108" s="15" t="inlineStr">
+        <is>
+          <t>13 ч 35 мин</t>
+        </is>
+      </c>
+      <c r="P108" s="16" t="inlineStr">
+        <is>
           <t>ранний заезд</t>
         </is>
       </c>
-      <c r="O108" s="19" t="inlineStr">
+      <c r="Q108" s="19" t="inlineStr">
         <is>
           <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2024700&amp;nnst2=2000000</t>
         </is>
       </c>
-      <c r="P108" s="16" t="inlineStr">
+      <c r="R108" s="16" t="inlineStr">
         <is>
           <t>Основной вариант — машина</t>
         </is>
       </c>
-      <c r="Q108" s="16" t="inlineStr">
+      <c r="S108" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -13208,10 +14282,10 @@
           <t>Москва, Павелецкий</t>
         </is>
       </c>
-      <c r="J109" s="21" t="n">
+      <c r="J109" s="22" t="n">
         <v>2868</v>
       </c>
-      <c r="K109" s="21" t="n">
+      <c r="K109" s="22" t="n">
         <v>2868</v>
       </c>
       <c r="L109" s="16" t="inlineStr">
@@ -13224,18 +14298,28 @@
           <t>~10:45</t>
         </is>
       </c>
-      <c r="N109" s="16" t="inlineStr"/>
-      <c r="O109" s="19" t="inlineStr">
+      <c r="N109" s="16" t="inlineStr">
+        <is>
+          <t>27.10 21:10 МСК → 28.10 10:45 МСК</t>
+        </is>
+      </c>
+      <c r="O109" s="15" t="inlineStr">
+        <is>
+          <t>13 ч 35 мин</t>
+        </is>
+      </c>
+      <c r="P109" s="16" t="inlineStr"/>
+      <c r="Q109" s="19" t="inlineStr">
         <is>
           <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2014700&amp;nnst2=2000000</t>
         </is>
       </c>
-      <c r="P109" s="16" t="inlineStr">
+      <c r="R109" s="16" t="inlineStr">
         <is>
           <t>Основной вариант — машина</t>
         </is>
       </c>
-      <c r="Q109" s="16" t="inlineStr">
+      <c r="S109" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -13285,10 +14369,10 @@
           <t>Москва, Павелецкий</t>
         </is>
       </c>
-      <c r="J110" s="21" t="n">
+      <c r="J110" s="22" t="n">
         <v>4049</v>
       </c>
-      <c r="K110" s="21" t="n">
+      <c r="K110" s="22" t="n">
         <v>4049</v>
       </c>
       <c r="L110" s="16" t="inlineStr">
@@ -13301,18 +14385,28 @@
           <t>~12:00</t>
         </is>
       </c>
-      <c r="N110" s="16" t="inlineStr"/>
-      <c r="O110" s="19" t="inlineStr">
+      <c r="N110" s="16" t="inlineStr">
+        <is>
+          <t>27.10 22:30 МСК → 28.10 12:00 МСК</t>
+        </is>
+      </c>
+      <c r="O110" s="15" t="inlineStr">
+        <is>
+          <t>13 ч 30 мин</t>
+        </is>
+      </c>
+      <c r="P110" s="16" t="inlineStr"/>
+      <c r="Q110" s="19" t="inlineStr">
         <is>
           <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2014130&amp;nnst2=2000000</t>
         </is>
       </c>
-      <c r="P110" s="16" t="inlineStr">
+      <c r="R110" s="16" t="inlineStr">
         <is>
           <t>Основной вариант — одна машина на троих</t>
         </is>
       </c>
-      <c r="Q110" s="16" t="inlineStr">
+      <c r="S110" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -13362,10 +14456,10 @@
           <t>Москва, Казанский</t>
         </is>
       </c>
-      <c r="J111" s="21" t="n">
+      <c r="J111" s="22" t="n">
         <v>4045</v>
       </c>
-      <c r="K111" s="21" t="n">
+      <c r="K111" s="22" t="n">
         <v>4045</v>
       </c>
       <c r="L111" s="16" t="inlineStr">
@@ -13378,18 +14472,28 @@
           <t>~10:45</t>
         </is>
       </c>
-      <c r="N111" s="16" t="inlineStr"/>
-      <c r="O111" s="19" t="inlineStr">
+      <c r="N111" s="16" t="inlineStr">
+        <is>
+          <t>27.10 22:30 МСК → 28.10 10:45 МСК</t>
+        </is>
+      </c>
+      <c r="O111" s="15" t="inlineStr">
+        <is>
+          <t>12 ч 15 мин</t>
+        </is>
+      </c>
+      <c r="P111" s="16" t="inlineStr"/>
+      <c r="Q111" s="19" t="inlineStr">
         <is>
           <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2014000&amp;nnst2=2000000</t>
         </is>
       </c>
-      <c r="P111" s="16" t="inlineStr">
+      <c r="R111" s="16" t="inlineStr">
         <is>
           <t>Основной вариант — машина</t>
         </is>
       </c>
-      <c r="Q111" s="16" t="inlineStr">
+      <c r="S111" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -13439,10 +14543,10 @@
           <t>Москва, Киевский</t>
         </is>
       </c>
-      <c r="J112" s="21" t="n">
+      <c r="J112" s="22" t="n">
         <v>3655</v>
       </c>
-      <c r="K112" s="21" t="n">
+      <c r="K112" s="22" t="n">
         <v>3655</v>
       </c>
       <c r="L112" s="16" t="inlineStr">
@@ -13455,18 +14559,28 @@
           <t>~12:00</t>
         </is>
       </c>
-      <c r="N112" s="16" t="inlineStr"/>
-      <c r="O112" s="19" t="inlineStr">
+      <c r="N112" s="16" t="inlineStr">
+        <is>
+          <t>27.10 22:50 МСК → 28.10 12:00 МСК</t>
+        </is>
+      </c>
+      <c r="O112" s="15" t="inlineStr">
+        <is>
+          <t>13 ч 10 мин</t>
+        </is>
+      </c>
+      <c r="P112" s="16" t="inlineStr"/>
+      <c r="Q112" s="19" t="inlineStr">
         <is>
           <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2000140&amp;nnst2=2000000</t>
         </is>
       </c>
-      <c r="P112" s="16" t="inlineStr">
+      <c r="R112" s="16" t="inlineStr">
         <is>
           <t>Основной вариант — машина вместе с Брянском</t>
         </is>
       </c>
-      <c r="Q112" s="16" t="inlineStr">
+      <c r="S112" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
@@ -13516,10 +14630,10 @@
           <t>Москва, Киевский</t>
         </is>
       </c>
-      <c r="J113" s="21" t="n">
+      <c r="J113" s="22" t="n">
         <v>3180</v>
       </c>
-      <c r="K113" s="21" t="n">
+      <c r="K113" s="22" t="n">
         <v>3180</v>
       </c>
       <c r="L113" s="16" t="inlineStr">
@@ -13534,136 +14648,153 @@
       </c>
       <c r="N113" s="16" t="inlineStr">
         <is>
+          <t>27.10 23:35 МСК → 28.10 09:30 МСК</t>
+        </is>
+      </c>
+      <c r="O113" s="15" t="inlineStr">
+        <is>
+          <t>9 ч 55 мин</t>
+        </is>
+      </c>
+      <c r="P113" s="16" t="inlineStr">
+        <is>
           <t>ранний заезд</t>
         </is>
       </c>
-      <c r="O113" s="19" t="inlineStr">
+      <c r="Q113" s="19" t="inlineStr">
         <is>
           <t>https://www.tutu.ru/poezda/rasp_d.php?date=27.10.2026&amp;nnst1=2000427&amp;nnst2=2000000</t>
         </is>
       </c>
-      <c r="P113" s="16" t="inlineStr">
+      <c r="R113" s="16" t="inlineStr">
         <is>
           <t>Основной вариант — машина</t>
         </is>
       </c>
-      <c r="Q113" s="16" t="inlineStr">
+      <c r="S113" s="16" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" s="14" t="inlineStr">
+        <is>
+          <t>Время в пути «дверь–дверь»: туда — от выхода из дома до заселения в гостиницу, обратно — от выезда из гостиницы до прихода домой. Считается с учётом разницы во времени; включает дорогу до аэропорта/вокзала (в аэропорту за 2 ч в крупных городах, за 1,5 ч в небольших), ожидание и трансфер. Ночи в поезде входят во время в пути.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q113"/>
+  <autoFilter ref="A1:S113"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O56" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O60" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O66" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O67" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O68" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O69" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O70" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O71" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O72" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O73" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O74" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O75" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O77" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O78" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O79" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O80" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O81" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O82" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O83" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O84" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O85" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O86" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O87" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O88" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O89" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O90" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O91" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O92" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O93" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O94" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O95" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O96" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O97" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O98" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O100" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O101" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O103" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O104" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O106" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O107" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O108" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O109" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O110" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O111" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O112" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O113" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q77" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q78" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q79" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q80" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q81" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q82" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q83" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q84" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q85" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q86" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q87" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q88" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q89" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q90" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q91" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q92" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q93" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q94" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q95" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q96" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q97" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q98" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q100" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q101" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q103" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q104" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q106" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q107" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q108" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q109" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q110" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q111" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q112" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q113" r:id="rId108"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13781,18 +14912,18 @@
           <t>~7 ч 30 мин</t>
         </is>
       </c>
-      <c r="G2" s="22">
+      <c r="G2" s="23">
         <f>E2*2*'Правила и допущения'!$B$4/100*'Правила и допущения'!$B$5</f>
         <v/>
       </c>
-      <c r="H2" s="22" t="n">
+      <c r="H2" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="22">
+      <c r="I2" s="23">
         <f>G2+H2</f>
         <v/>
       </c>
-      <c r="J2" s="22">
+      <c r="J2" s="23">
         <f>I2/C2</f>
         <v/>
       </c>
@@ -13834,18 +14965,18 @@
           <t>~7 ч</t>
         </is>
       </c>
-      <c r="G3" s="22">
+      <c r="G3" s="23">
         <f>E3*2*'Правила и допущения'!$B$4/100*'Правила и допущения'!$B$5</f>
         <v/>
       </c>
-      <c r="H3" s="22" t="n">
+      <c r="H3" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3" s="23">
         <f>G3+H3</f>
         <v/>
       </c>
-      <c r="J3" s="22">
+      <c r="J3" s="23">
         <f>I3/C3</f>
         <v/>
       </c>
@@ -13887,18 +15018,18 @@
           <t>~5 ч</t>
         </is>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="23">
         <f>E4*2*'Правила и допущения'!$B$4/100*'Правила и допущения'!$B$5</f>
         <v/>
       </c>
-      <c r="H4" s="22" t="n">
+      <c r="H4" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="22">
+      <c r="I4" s="23">
         <f>G4+H4</f>
         <v/>
       </c>
-      <c r="J4" s="22">
+      <c r="J4" s="23">
         <f>I4/C4</f>
         <v/>
       </c>
@@ -13940,18 +15071,18 @@
           <t>~5 ч</t>
         </is>
       </c>
-      <c r="G5" s="22">
+      <c r="G5" s="23">
         <f>E5*2*'Правила и допущения'!$B$4/100*'Правила и допущения'!$B$5</f>
         <v/>
       </c>
-      <c r="H5" s="22" t="n">
+      <c r="H5" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="22">
+      <c r="I5" s="23">
         <f>G5+H5</f>
         <v/>
       </c>
-      <c r="J5" s="22">
+      <c r="J5" s="23">
         <f>I5/C5</f>
         <v/>
       </c>
@@ -13993,18 +15124,18 @@
           <t>~5 ч 30 мин</t>
         </is>
       </c>
-      <c r="G6" s="22">
+      <c r="G6" s="23">
         <f>E6*2*'Правила и допущения'!$B$4/100*'Правила и допущения'!$B$5</f>
         <v/>
       </c>
-      <c r="H6" s="22" t="n">
+      <c r="H6" s="23" t="n">
         <v>3600</v>
       </c>
-      <c r="I6" s="22">
+      <c r="I6" s="23">
         <f>G6+H6</f>
         <v/>
       </c>
-      <c r="J6" s="22">
+      <c r="J6" s="23">
         <f>I6/C6</f>
         <v/>
       </c>
@@ -14046,18 +15177,18 @@
           <t>~6 ч 30 мин</t>
         </is>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="23">
         <f>E7*2*'Правила и допущения'!$B$4/100*'Правила и допущения'!$B$5</f>
         <v/>
       </c>
-      <c r="H7" s="22" t="n">
+      <c r="H7" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="22">
+      <c r="I7" s="23">
         <f>G7+H7</f>
         <v/>
       </c>
-      <c r="J7" s="22">
+      <c r="J7" s="23">
         <f>I7/C7</f>
         <v/>
       </c>
@@ -14178,10 +15309,10 @@
       <c r="F2" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G2" s="22" t="n">
+      <c r="G2" s="23" t="n">
         <v>5000</v>
       </c>
-      <c r="H2" s="22">
+      <c r="H2" s="23">
         <f>G2*F2/D2</f>
         <v/>
       </c>
@@ -14218,10 +15349,10 @@
       <c r="F3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G3" s="22" t="n">
+      <c r="G3" s="23" t="n">
         <v>4000</v>
       </c>
-      <c r="H3" s="22">
+      <c r="H3" s="23">
         <f>G3*F3/D3</f>
         <v/>
       </c>
@@ -14258,10 +15389,10 @@
       <c r="F4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="22" t="n">
+      <c r="G4" s="23" t="n">
         <v>3000</v>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="23">
         <f>G4*F4/D4</f>
         <v/>
       </c>
@@ -14294,10 +15425,10 @@
       <c r="F5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="22" t="n">
+      <c r="G5" s="23" t="n">
         <v>3000</v>
       </c>
-      <c r="H5" s="22">
+      <c r="H5" s="23">
         <f>G5*F5/D5</f>
         <v/>
       </c>
@@ -14334,10 +15465,10 @@
       <c r="F6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="22" t="n">
+      <c r="G6" s="23" t="n">
         <v>7000</v>
       </c>
-      <c r="H6" s="22">
+      <c r="H6" s="23">
         <f>G6*F6/D6</f>
         <v/>
       </c>
@@ -14374,10 +15505,10 @@
       <c r="F7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="22" t="n">
+      <c r="G7" s="23" t="n">
         <v>7000</v>
       </c>
-      <c r="H7" s="22">
+      <c r="H7" s="23">
         <f>G7*F7/D7</f>
         <v/>
       </c>
@@ -14414,10 +15545,10 @@
       <c r="F8" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="22" t="n">
+      <c r="G8" s="23" t="n">
         <v>5000</v>
       </c>
-      <c r="H8" s="22">
+      <c r="H8" s="23">
         <f>G8*F8/D8</f>
         <v/>
       </c>
@@ -14454,10 +15585,10 @@
       <c r="F9" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="22" t="n">
+      <c r="G9" s="23" t="n">
         <v>7000</v>
       </c>
-      <c r="H9" s="22">
+      <c r="H9" s="23">
         <f>G9*F9/D9</f>
         <v/>
       </c>
@@ -14494,10 +15625,10 @@
       <c r="F10" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="22" t="n">
+      <c r="G10" s="23" t="n">
         <v>4500</v>
       </c>
-      <c r="H10" s="22">
+      <c r="H10" s="23">
         <f>G10*F10/D10</f>
         <v/>
       </c>
@@ -14530,10 +15661,10 @@
       <c r="F11" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="22" t="n">
+      <c r="G11" s="23" t="n">
         <v>4500</v>
       </c>
-      <c r="H11" s="22">
+      <c r="H11" s="23">
         <f>G11*F11/D11</f>
         <v/>
       </c>
@@ -14570,10 +15701,10 @@
       <c r="F12" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G12" s="22" t="n">
+      <c r="G12" s="23" t="n">
         <v>4000</v>
       </c>
-      <c r="H12" s="22">
+      <c r="H12" s="23">
         <f>G12*F12/D12</f>
         <v/>
       </c>
@@ -14610,10 +15741,10 @@
       <c r="F13" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="22" t="n">
+      <c r="G13" s="23" t="n">
         <v>4000</v>
       </c>
-      <c r="H13" s="22">
+      <c r="H13" s="23">
         <f>G13*F13/D13</f>
         <v/>
       </c>
@@ -14650,10 +15781,10 @@
       <c r="F14" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="22" t="n">
+      <c r="G14" s="23" t="n">
         <v>3000</v>
       </c>
-      <c r="H14" s="22">
+      <c r="H14" s="23">
         <f>G14*F14/D14</f>
         <v/>
       </c>
@@ -14690,10 +15821,10 @@
       <c r="F15" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G15" s="22" t="n">
+      <c r="G15" s="23" t="n">
         <v>5000</v>
       </c>
-      <c r="H15" s="22">
+      <c r="H15" s="23">
         <f>G15*F15/D15</f>
         <v/>
       </c>
@@ -14726,10 +15857,10 @@
       <c r="F16" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G16" s="22" t="n">
+      <c r="G16" s="23" t="n">
         <v>5000</v>
       </c>
-      <c r="H16" s="22">
+      <c r="H16" s="23">
         <f>G16*F16/D16</f>
         <v/>
       </c>
@@ -14762,10 +15893,10 @@
       <c r="F17" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G17" s="22" t="n">
+      <c r="G17" s="23" t="n">
         <v>5000</v>
       </c>
-      <c r="H17" s="22">
+      <c r="H17" s="23">
         <f>G17*F17/D17</f>
         <v/>
       </c>
@@ -14802,10 +15933,10 @@
       <c r="F18" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="22" t="n">
+      <c r="G18" s="23" t="n">
         <v>5000</v>
       </c>
-      <c r="H18" s="22">
+      <c r="H18" s="23">
         <f>G18*F18/D18</f>
         <v/>
       </c>
@@ -14838,10 +15969,10 @@
       <c r="F19" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="22" t="n">
+      <c r="G19" s="23" t="n">
         <v>5000</v>
       </c>
-      <c r="H19" s="22">
+      <c r="H19" s="23">
         <f>G19*F19/D19</f>
         <v/>
       </c>
@@ -14878,10 +16009,10 @@
       <c r="F20" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="22" t="n">
+      <c r="G20" s="23" t="n">
         <v>4500</v>
       </c>
-      <c r="H20" s="22">
+      <c r="H20" s="23">
         <f>G20*F20/D20</f>
         <v/>
       </c>
@@ -14914,10 +16045,10 @@
       <c r="F21" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G21" s="22" t="n">
+      <c r="G21" s="23" t="n">
         <v>4500</v>
       </c>
-      <c r="H21" s="22">
+      <c r="H21" s="23">
         <f>G21*F21/D21</f>
         <v/>
       </c>
@@ -14950,10 +16081,10 @@
       <c r="F22" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="G22" s="22" t="n">
+      <c r="G22" s="23" t="n">
         <v>6000</v>
       </c>
-      <c r="H22" s="22">
+      <c r="H22" s="23">
         <f>G22*F22/D22</f>
         <v/>
       </c>
@@ -15339,45 +16470,45 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="23" t="inlineStr">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>Доп. ночь в гостинице «Коломна», ₽</t>
         </is>
       </c>
-      <c r="B3" s="24" t="n">
+      <c r="B3" s="25" t="n">
         <v>4000</v>
       </c>
-      <c r="C3" s="25" t="inlineStr">
+      <c r="C3" s="26" t="inlineStr">
         <is>
           <t>Номер от ~3 050 ₽; уточнить корпоративный тариф: +7 (496) 612-18-96</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="23" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>Расход топлива, л/100 км</t>
         </is>
       </c>
-      <c r="B4" s="24" t="n">
+      <c r="B4" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="26" t="inlineStr">
         <is>
           <t>Средний легковой автомобиль</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>Цена бензина, ₽/л</t>
         </is>
       </c>
-      <c r="B5" s="24" t="n">
+      <c r="B5" s="25" t="n">
         <v>65</v>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>АИ-95, октябрь 2026 — ориентир</t>
         </is>
@@ -15391,7 +16522,7 @@
       </c>
     </row>
     <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>Ключевые даты</t>
         </is>
@@ -15403,7 +16534,7 @@
       </c>
     </row>
     <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>Гостиница</t>
         </is>
@@ -15415,7 +16546,7 @@
       </c>
     </row>
     <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>Два варианта</t>
         </is>
@@ -15427,7 +16558,7 @@
       </c>
     </row>
     <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="26" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>Критерии удобного варианта</t>
         </is>
@@ -15439,7 +16570,7 @@
       </c>
     </row>
     <row r="12" ht="48" customHeight="1">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>Где удобного обратного рейса нет</t>
         </is>
@@ -15451,19 +16582,19 @@
       </c>
     </row>
     <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>Самолёты</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Только эконом. Две цены: без багажа (только ручная кладь) и с багажом. Цены — за 1 человека, на 28.09.2026, быстро меняются.</t>
+          <t>Только эконом. Две цены: без багажа (только ручная кладь) и с багажом. Цены — обычные, за один билет (групповых тарифов и скидок нет), на 28.09.2026, быстро меняются. Когда на один рейс летят несколько человек, билеты лучше купить заранее и сразу.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1">
-      <c r="A14" s="26" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>Аэропорт</t>
         </is>
@@ -15475,7 +16606,7 @@
       </c>
     </row>
     <row r="15" ht="48" customHeight="1">
-      <c r="A15" s="26" t="inlineStr">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>Пробки</t>
         </is>
@@ -15487,7 +16618,7 @@
       </c>
     </row>
     <row r="16" ht="48" customHeight="1">
-      <c r="A16" s="26" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>Вечерний вылет 30.10 возможен, если</t>
         </is>
@@ -15499,7 +16630,7 @@
       </c>
     </row>
     <row r="17" ht="48" customHeight="1">
-      <c r="A17" s="26" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>Поезда</t>
         </is>
@@ -15511,7 +16642,7 @@
       </c>
     </row>
     <row r="18" ht="48" customHeight="1">
-      <c r="A18" s="26" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>Машина</t>
         </is>
@@ -15523,7 +16654,7 @@
       </c>
     </row>
     <row r="19" ht="48" customHeight="1">
-      <c r="A19" s="26" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>Проверка пробок</t>
         </is>
@@ -15535,7 +16666,7 @@
       </c>
     </row>
     <row r="20" ht="48" customHeight="1">
-      <c r="A20" s="26" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>Ссылки</t>
         </is>
@@ -15547,7 +16678,7 @@
       </c>
     </row>
     <row r="21" ht="48" customHeight="1">
-      <c r="A21" s="26" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>Что проверить</t>
         </is>

--- a/Коломна_маршруты_28-30.10.2026.xlsx
+++ b/Коломна_маршруты_28-30.10.2026.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Правила и допущения" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Сводка по сотрудникам'!$A$4:$S$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Сводка по сотрудникам'!$A$4:$U$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Маршруты'!$A$1:$S$113</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -565,7 +565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S66"/>
+  <dimension ref="A1:U66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -586,7 +586,9 @@
     <col width="11" customWidth="1" min="16" max="16"/>
     <col width="8" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="55" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="55" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -694,7 +696,17 @@
           <t>ИТОГО удобный</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr">
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>В ПУТИ эконом (туда + обратно, дверь–дверь)</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>В ПУТИ удобный (туда + обратно, дверь–дверь)</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
@@ -766,7 +778,17 @@
         <f>N5+O5+P5+Q5*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S5" s="5" t="inlineStr">
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>20 ч 55 мин</t>
+        </is>
+      </c>
+      <c r="T5" s="10" t="inlineStr">
+        <is>
+          <t>20 ч 15 мин</t>
+        </is>
+      </c>
+      <c r="U5" s="5" t="inlineStr">
         <is>
           <t>Удобный: вылет днём 27.10 + ночь; обратно дневных рейсов нет — вечер 31.10</t>
         </is>
@@ -838,7 +860,17 @@
         <f>N6+O6+P6+Q6*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S6" s="5" t="inlineStr">
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>18 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="T6" s="10" t="inlineStr">
+        <is>
+          <t>15 ч 05 мин</t>
+        </is>
+      </c>
+      <c r="U6" s="5" t="inlineStr">
         <is>
           <t>Эконом: вылет 07:00 и ночной обратно</t>
         </is>
@@ -910,7 +942,17 @@
         <f>N7+O7+P7+Q7*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S7" s="5" t="inlineStr">
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>19 ч 05 мин</t>
+        </is>
+      </c>
+      <c r="T7" s="10" t="inlineStr">
+        <is>
+          <t>16 ч 05 мин</t>
+        </is>
+      </c>
+      <c r="U7" s="5" t="inlineStr">
         <is>
           <t>Вкл. такси Ревда—Кольцово</t>
         </is>
@@ -982,7 +1024,17 @@
         <f>N8+O8+P8+Q8*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S8" s="5" t="inlineStr">
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>21 ч 40 мин</t>
+        </is>
+      </c>
+      <c r="T8" s="10" t="inlineStr">
+        <is>
+          <t>21 ч 30 мин</t>
+        </is>
+      </c>
+      <c r="U8" s="5" t="inlineStr">
         <is>
           <t>Удобный: днём в обе стороны</t>
         </is>
@@ -1054,7 +1106,17 @@
         <f>N9+O9+P9+Q9*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S9" s="5" t="inlineStr">
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>20 ч 20 мин</t>
+        </is>
+      </c>
+      <c r="T9" s="10" t="inlineStr">
+        <is>
+          <t>21 ч 30 мин</t>
+        </is>
+      </c>
+      <c r="U9" s="5" t="inlineStr">
         <is>
           <t>Обратно только ночной рейс (дневных нет)</t>
         </is>
@@ -1126,7 +1188,17 @@
         <f>N10+O10+P10+Q10*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S10" s="5" t="inlineStr">
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>22 ч 35 мин</t>
+        </is>
+      </c>
+      <c r="T10" s="10" t="inlineStr">
+        <is>
+          <t>22 ч 35 мин</t>
+        </is>
+      </c>
+      <c r="U10" s="5" t="inlineStr">
         <is>
           <t>Удобный: днём в обе стороны</t>
         </is>
@@ -1198,7 +1270,17 @@
         <f>N11+O11+P11+Q11*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S11" s="5" t="inlineStr">
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>20 ч 25 мин</t>
+        </is>
+      </c>
+      <c r="T11" s="10" t="inlineStr">
+        <is>
+          <t>19 ч 35 мин</t>
+        </is>
+      </c>
+      <c r="U11" s="5" t="inlineStr">
         <is>
           <t>Обратно дневных рейсов нет — вечер 31.10 после отдыха</t>
         </is>
@@ -1270,7 +1352,17 @@
         <f>N12+O12+P12+Q12*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S12" s="5" t="inlineStr">
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>21 ч 40 мин</t>
+        </is>
+      </c>
+      <c r="T12" s="10" t="inlineStr">
+        <is>
+          <t>21 ч 30 мин</t>
+        </is>
+      </c>
+      <c r="U12" s="5" t="inlineStr">
         <is>
           <t>Удобный: днём в обе стороны</t>
         </is>
@@ -1342,7 +1434,17 @@
         <f>N13+O13+P13+Q13*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S13" s="5" t="inlineStr">
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>21 ч 40 мин</t>
+        </is>
+      </c>
+      <c r="T13" s="10" t="inlineStr">
+        <is>
+          <t>21 ч 30 мин</t>
+        </is>
+      </c>
+      <c r="U13" s="5" t="inlineStr">
         <is>
           <t>Удобный: днём в обе стороны</t>
         </is>
@@ -1414,7 +1516,17 @@
         <f>N14+O14+P14+Q14*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S14" s="5" t="inlineStr">
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>13 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="T14" s="10" t="inlineStr">
+        <is>
+          <t>13 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="U14" s="5" t="inlineStr">
         <is>
           <t>Эконом = удобный</t>
         </is>
@@ -1486,7 +1598,17 @@
         <f>N15+O15+P15+Q15*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S15" s="5" t="inlineStr">
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>25 ч 10 мин</t>
+        </is>
+      </c>
+      <c r="T15" s="10" t="inlineStr">
+        <is>
+          <t>16 ч 15 мин</t>
+        </is>
+      </c>
+      <c r="U15" s="5" t="inlineStr">
         <is>
           <t>Самолёт дешевле поезда; эконом обратно — ночной поезд</t>
         </is>
@@ -1558,7 +1680,17 @@
         <f>N16+O16+P16+Q16*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S16" s="5" t="inlineStr">
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>15 ч 40 мин</t>
+        </is>
+      </c>
+      <c r="T16" s="10" t="inlineStr">
+        <is>
+          <t>15 ч 40 мин</t>
+        </is>
+      </c>
+      <c r="U16" s="5" t="inlineStr">
         <is>
           <t>Эконом = удобный</t>
         </is>
@@ -1630,7 +1762,17 @@
         <f>N17+O17+P17+Q17*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S17" s="5" t="inlineStr">
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>19 ч 25 мин</t>
+        </is>
+      </c>
+      <c r="T17" s="10" t="inlineStr">
+        <is>
+          <t>16 ч 25 мин</t>
+        </is>
+      </c>
+      <c r="U17" s="5" t="inlineStr">
         <is>
           <t>Эконом обратно — ночной рейс 02:40</t>
         </is>
@@ -1708,7 +1850,17 @@
         <f>N18+O18+P18+Q18*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S18" s="5" t="inlineStr">
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>15 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="T18" s="10" t="inlineStr">
+        <is>
+          <t>15 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="U18" s="5" t="inlineStr">
         <is>
           <t>Экипаж: Пенза. Удобный = обратно 31.10 утром + ночь</t>
         </is>
@@ -1780,7 +1932,17 @@
         <f>N19+O19+P19+Q19*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S19" s="5" t="inlineStr">
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>28 ч 30 мин</t>
+        </is>
+      </c>
+      <c r="T19" s="10" t="inlineStr">
+        <is>
+          <t>15 ч 05 мин</t>
+        </is>
+      </c>
+      <c r="U19" s="5" t="inlineStr">
         <is>
           <t>Эконом: ночной поезд туда. Удобный: самолёт днём</t>
         </is>
@@ -1852,7 +2014,17 @@
         <f>N20+O20+P20+Q20*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S20" s="5" t="inlineStr">
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>37 ч 25 мин</t>
+        </is>
+      </c>
+      <c r="T20" s="10" t="inlineStr">
+        <is>
+          <t>16 ч 20 мин</t>
+        </is>
+      </c>
+      <c r="U20" s="5" t="inlineStr">
         <is>
           <t>Эконом: ночные поезда. Удобный: дневные рейсы</t>
         </is>
@@ -1930,7 +2102,17 @@
         <f>N21+O21+P21+Q21*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S21" s="5" t="inlineStr">
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>14 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="T21" s="10" t="inlineStr">
+        <is>
+          <t>14 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="U21" s="5" t="inlineStr">
         <is>
           <t>Экипаж: Саранск. Удобный = обратно 31.10 утром + ночь</t>
         </is>
@@ -2002,7 +2184,17 @@
         <f>N22+O22+P22+Q22*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S22" s="5" t="inlineStr">
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>28 ч 30 мин</t>
+        </is>
+      </c>
+      <c r="T22" s="10" t="inlineStr">
+        <is>
+          <t>15 ч 05 мин</t>
+        </is>
+      </c>
+      <c r="U22" s="5" t="inlineStr">
         <is>
           <t>Эконом: ночной поезд туда. Удобный: самолёт днём</t>
         </is>
@@ -2074,7 +2266,17 @@
         <f>N23+O23+P23+Q23*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S23" s="5" t="inlineStr">
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>14 ч 40 мин</t>
+        </is>
+      </c>
+      <c r="T23" s="10" t="inlineStr">
+        <is>
+          <t>14 ч 40 мин</t>
+        </is>
+      </c>
+      <c r="U23" s="5" t="inlineStr">
         <is>
           <t>Эконом = удобный</t>
         </is>
@@ -2146,7 +2348,17 @@
         <f>N24+O24+P24+Q24*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S24" s="5" t="inlineStr">
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>24 ч 40 мин</t>
+        </is>
+      </c>
+      <c r="T24" s="10" t="inlineStr">
+        <is>
+          <t>14 ч 55 мин</t>
+        </is>
+      </c>
+      <c r="U24" s="5" t="inlineStr">
         <is>
           <t>Туда самолёт днём; эконом обратно — ночной поезд</t>
         </is>
@@ -2218,7 +2430,17 @@
         <f>N25+O25+P25+Q25*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S25" s="5" t="inlineStr">
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>14 ч 40 мин</t>
+        </is>
+      </c>
+      <c r="T25" s="10" t="inlineStr">
+        <is>
+          <t>14 ч 40 мин</t>
+        </is>
+      </c>
+      <c r="U25" s="5" t="inlineStr">
         <is>
           <t>Эконом = удобный</t>
         </is>
@@ -2290,7 +2512,17 @@
         <f>N26+O26+P26+Q26*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S26" s="5" t="inlineStr">
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>23 ч 55 мин</t>
+        </is>
+      </c>
+      <c r="T26" s="10" t="inlineStr">
+        <is>
+          <t>24 ч 10 мин</t>
+        </is>
+      </c>
+      <c r="U26" s="5" t="inlineStr">
         <is>
           <t>Обратно дневных рейсов нет — вечер 31.10, прилёт утром</t>
         </is>
@@ -2362,7 +2594,17 @@
         <f>N27+O27+P27+Q27*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S27" s="5" t="inlineStr">
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>22 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="T27" s="10" t="inlineStr">
+        <is>
+          <t>23 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="U27" s="5" t="inlineStr">
         <is>
           <t>Группа 5 чел.: минивэн</t>
         </is>
@@ -2434,7 +2676,17 @@
         <f>N28+O28+P28+Q28*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S28" s="5" t="inlineStr">
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>22 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="T28" s="10" t="inlineStr">
+        <is>
+          <t>23 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="U28" s="5" t="inlineStr">
         <is>
           <t>Группа 5 чел.: минивэн</t>
         </is>
@@ -2506,7 +2758,17 @@
         <f>N29+O29+P29+Q29*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S29" s="5" t="inlineStr">
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>22 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="T29" s="10" t="inlineStr">
+        <is>
+          <t>23 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="U29" s="5" t="inlineStr">
         <is>
           <t>Едет вместе с отцом (Друсалевич В.А.). Группа 5 чел.: минивэн</t>
         </is>
@@ -2578,7 +2840,17 @@
         <f>N30+O30+P30+Q30*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S30" s="5" t="inlineStr">
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>29 ч 10 мин</t>
+        </is>
+      </c>
+      <c r="T30" s="10" t="inlineStr">
+        <is>
+          <t>22 ч 35 мин</t>
+        </is>
+      </c>
+      <c r="U30" s="5" t="inlineStr">
         <is>
           <t>Удобный: прямой рейс днём; обратно только вечерние рейсы</t>
         </is>
@@ -2650,7 +2922,17 @@
         <f>N31+O31+P31+Q31*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S31" s="5" t="inlineStr">
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>22 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="T31" s="10" t="inlineStr">
+        <is>
+          <t>23 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="U31" s="5" t="inlineStr">
         <is>
           <t>Группа 5 чел.: минивэн</t>
         </is>
@@ -2728,7 +3010,17 @@
         <f>N32+O32+P32+Q32*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S32" s="5" t="inlineStr">
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>11 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="T32" s="10" t="inlineStr">
+        <is>
+          <t>11 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="U32" s="5" t="inlineStr">
         <is>
           <t>Экипаж: Воронеж (2 чел.). Удобный = обратно 31.10 утром + ночь</t>
         </is>
@@ -2806,7 +3098,17 @@
         <f>N33+O33+P33+Q33*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S33" s="5" t="inlineStr">
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>10 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="T33" s="10" t="inlineStr">
+        <is>
+          <t>10 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="U33" s="5" t="inlineStr">
         <is>
           <t>Экипаж: Липецк (3 чел.). Удобный = обратно 31.10 утром + ночь</t>
         </is>
@@ -2878,7 +3180,17 @@
         <f>N34+O34+P34+Q34*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S34" s="5" t="inlineStr">
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>17 ч 15 мин</t>
+        </is>
+      </c>
+      <c r="T34" s="10" t="inlineStr">
+        <is>
+          <t>17 ч 15 мин</t>
+        </is>
+      </c>
+      <c r="U34" s="5" t="inlineStr">
         <is>
           <t>Эконом = удобный</t>
         </is>
@@ -2950,7 +3262,17 @@
         <f>N35+O35+P35+Q35*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S35" s="5" t="inlineStr">
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>31 ч 55 мин</t>
+        </is>
+      </c>
+      <c r="T35" s="10" t="inlineStr">
+        <is>
+          <t>22 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="U35" s="5" t="inlineStr">
         <is>
           <t>Туда Ласточка днём; эконом обратно — ночной поезд</t>
         </is>
@@ -3028,7 +3350,17 @@
         <f>N36+O36+P36+Q36*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S36" s="5" t="inlineStr">
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>13 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="T36" s="10" t="inlineStr">
+        <is>
+          <t>13 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="U36" s="5" t="inlineStr">
         <is>
           <t>Экипаж: Брянск + Орёл. Удобный = обратно 31.10 утром + ночь</t>
         </is>
@@ -3100,7 +3432,17 @@
         <f>N37+O37+P37+Q37*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S37" s="5" t="inlineStr">
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>16 ч 50 мин</t>
+        </is>
+      </c>
+      <c r="T37" s="10" t="inlineStr">
+        <is>
+          <t>16 ч 50 мин</t>
+        </is>
+      </c>
+      <c r="U37" s="5" t="inlineStr">
         <is>
           <t>Эконом = удобный</t>
         </is>
@@ -3178,7 +3520,17 @@
         <f>N38+O38+P38+Q38*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S38" s="5" t="inlineStr">
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>11 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="T38" s="10" t="inlineStr">
+        <is>
+          <t>11 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="U38" s="5" t="inlineStr">
         <is>
           <t>Экипаж: Воронеж (2 чел.). Удобный = обратно 31.10 утром + ночь</t>
         </is>
@@ -3256,7 +3608,17 @@
         <f>N39+O39+P39+Q39*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S39" s="5" t="inlineStr">
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>10 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="T39" s="10" t="inlineStr">
+        <is>
+          <t>10 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="U39" s="5" t="inlineStr">
         <is>
           <t>Экипаж: Липецк (3 чел.). Удобный = обратно 31.10 утром + ночь</t>
         </is>
@@ -3334,7 +3696,17 @@
         <f>N40+O40+P40+Q40*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S40" s="5" t="inlineStr">
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>13 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="T40" s="10" t="inlineStr">
+        <is>
+          <t>13 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="U40" s="5" t="inlineStr">
         <is>
           <t>Экипаж: Брянск + Орёл. Удобный = обратно 31.10 утром + ночь</t>
         </is>
@@ -3406,7 +3778,17 @@
         <f>N41+O41+P41+Q41*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S41" s="5" t="inlineStr">
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>51 ч 30 мин</t>
+        </is>
+      </c>
+      <c r="T41" s="10" t="inlineStr">
+        <is>
+          <t>59 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="U41" s="5" t="inlineStr">
         <is>
           <t>Ночь в дороге неизбежна; удобный — в купе. Вкл. Донецк—Ростов ~1 500 ₽ в каждую сторону</t>
         </is>
@@ -3484,7 +3866,17 @@
         <f>N42+O42+P42+Q42*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S42" s="5" t="inlineStr">
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>10 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="T42" s="10" t="inlineStr">
+        <is>
+          <t>10 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="U42" s="5" t="inlineStr">
         <is>
           <t>Экипаж: Тамбов. Удобный = обратно 31.10 утром + ночь</t>
         </is>
@@ -3562,7 +3954,17 @@
         <f>N43+O43+P43+Q43*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S43" s="5" t="inlineStr">
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>10 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="T43" s="10" t="inlineStr">
+        <is>
+          <t>10 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="U43" s="5" t="inlineStr">
         <is>
           <t>Экипаж: Липецк (3 чел.). Удобный = обратно 31.10 утром + ночь</t>
         </is>
@@ -3634,7 +4036,17 @@
         <f>N44+O44+P44+Q44*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S44" s="5" t="inlineStr">
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>22 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="T44" s="10" t="inlineStr">
+        <is>
+          <t>23 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="U44" s="5" t="inlineStr">
         <is>
           <t>Едет вместе с сыном (Друсалевич В.В.). Группа 5 чел.: минивэн</t>
         </is>
@@ -3706,7 +4118,17 @@
         <f>N45+O45+P45+Q45*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S45" s="5" t="inlineStr">
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>6 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="T45" s="10" t="inlineStr">
+        <is>
+          <t>4 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="U45" s="5" t="inlineStr">
         <is>
           <t>Удобный — своя машина</t>
         </is>
@@ -3778,7 +4200,17 @@
         <f>N46+O46+P46+Q46*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S46" s="5" t="inlineStr">
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>6 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="T46" s="10" t="inlineStr">
+        <is>
+          <t>4 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="U46" s="5" t="inlineStr">
         <is>
           <t>Удобный — своя машина</t>
         </is>
@@ -3850,7 +4282,17 @@
         <f>N47+O47+P47+Q47*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S47" s="5" t="inlineStr">
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>16 ч 40 мин</t>
+        </is>
+      </c>
+      <c r="T47" s="10" t="inlineStr">
+        <is>
+          <t>16 ч 40 мин</t>
+        </is>
+      </c>
+      <c r="U47" s="5" t="inlineStr">
         <is>
           <t>Дневные поезда</t>
         </is>
@@ -3922,7 +4364,17 @@
         <f>N48+O48+P48+Q48*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S48" s="5" t="inlineStr">
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>5 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="T48" s="10" t="inlineStr">
+        <is>
+          <t>3 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="U48" s="5" t="inlineStr">
         <is>
           <t>Удобный — своя машина (~100 км)</t>
         </is>
@@ -3994,7 +4446,17 @@
         <f>N49+O49+P49+Q49*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S49" s="5" t="inlineStr">
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>22 ч 10 мин</t>
+        </is>
+      </c>
+      <c r="T49" s="10" t="inlineStr">
+        <is>
+          <t>16 ч 55 мин</t>
+        </is>
+      </c>
+      <c r="U49" s="5" t="inlineStr">
         <is>
           <t>Удобный: Сапсан туда, Аврора днём обратно</t>
         </is>
@@ -4066,7 +4528,17 @@
         <f>N50+O50+P50+Q50*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S50" s="5" t="inlineStr">
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>19 ч 55 мин</t>
+        </is>
+      </c>
+      <c r="T50" s="10" t="inlineStr">
+        <is>
+          <t>16 ч 50 мин</t>
+        </is>
+      </c>
+      <c r="U50" s="5" t="inlineStr">
         <is>
           <t>Ласточка туда; удобный обратно — Ласточка днём 31.10</t>
         </is>
@@ -4138,7 +4610,17 @@
         <f>N51+O51+P51+Q51*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S51" s="5" t="inlineStr">
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>12 ч 35 мин</t>
+        </is>
+      </c>
+      <c r="T51" s="10" t="inlineStr">
+        <is>
+          <t>8 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="U51" s="5" t="inlineStr">
         <is>
           <t>Удобный — своя машина</t>
         </is>
@@ -4210,7 +4692,17 @@
         <f>N52+O52+P52+Q52*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S52" s="5" t="inlineStr">
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>17 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="T52" s="10" t="inlineStr">
+        <is>
+          <t>15 ч 50 мин</t>
+        </is>
+      </c>
+      <c r="U52" s="5" t="inlineStr">
         <is>
           <t>Едет вместе с дочерью (Смирнова Ю.И.). 9 чел. одним рейсом (обычные билеты, без групповых скидок); минивэны</t>
         </is>
@@ -4282,7 +4774,17 @@
         <f>N53+O53+P53+Q53*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S53" s="5" t="inlineStr">
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>17 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="T53" s="10" t="inlineStr">
+        <is>
+          <t>15 ч 50 мин</t>
+        </is>
+      </c>
+      <c r="U53" s="5" t="inlineStr">
         <is>
           <t>9 чел. одним рейсом (обычные билеты, без групповых скидок); минивэны</t>
         </is>
@@ -4354,7 +4856,17 @@
         <f>N54+O54+P54+Q54*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S54" s="5" t="inlineStr">
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>17 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="T54" s="10" t="inlineStr">
+        <is>
+          <t>15 ч 50 мин</t>
+        </is>
+      </c>
+      <c r="U54" s="5" t="inlineStr">
         <is>
           <t>9 чел. одним рейсом (обычные билеты, без групповых скидок); минивэны</t>
         </is>
@@ -4426,7 +4938,17 @@
         <f>N55+O55+P55+Q55*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S55" s="5" t="inlineStr">
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>17 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="T55" s="10" t="inlineStr">
+        <is>
+          <t>15 ч 50 мин</t>
+        </is>
+      </c>
+      <c r="U55" s="5" t="inlineStr">
         <is>
           <t>9 чел. одним рейсом (обычные билеты, без групповых скидок); минивэны</t>
         </is>
@@ -4498,7 +5020,17 @@
         <f>N56+O56+P56+Q56*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S56" s="5" t="inlineStr">
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>17 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="T56" s="10" t="inlineStr">
+        <is>
+          <t>15 ч 50 мин</t>
+        </is>
+      </c>
+      <c r="U56" s="5" t="inlineStr">
         <is>
           <t>9 чел. одним рейсом (обычные билеты, без групповых скидок); минивэны</t>
         </is>
@@ -4570,7 +5102,17 @@
         <f>N57+O57+P57+Q57*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S57" s="5" t="inlineStr">
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>17 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="T57" s="10" t="inlineStr">
+        <is>
+          <t>15 ч 50 мин</t>
+        </is>
+      </c>
+      <c r="U57" s="5" t="inlineStr">
         <is>
           <t>9 чел. одним рейсом (обычные билеты, без групповых скидок); минивэны</t>
         </is>
@@ -4642,7 +5184,17 @@
         <f>N58+O58+P58+Q58*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S58" s="5" t="inlineStr">
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>17 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="T58" s="10" t="inlineStr">
+        <is>
+          <t>15 ч 50 мин</t>
+        </is>
+      </c>
+      <c r="U58" s="5" t="inlineStr">
         <is>
           <t>Едет вместе с отцом (Смирнов И.А.). 9 чел. одним рейсом (обычные билеты, без групповых скидок); минивэны</t>
         </is>
@@ -4714,7 +5266,17 @@
         <f>N59+O59+P59+Q59*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S59" s="5" t="inlineStr">
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>17 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="T59" s="10" t="inlineStr">
+        <is>
+          <t>15 ч 50 мин</t>
+        </is>
+      </c>
+      <c r="U59" s="5" t="inlineStr">
         <is>
           <t>9 чел. одним рейсом (обычные билеты, без групповых скидок); минивэны</t>
         </is>
@@ -4786,7 +5348,17 @@
         <f>N60+O60+P60+Q60*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S60" s="5" t="inlineStr">
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>17 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="T60" s="10" t="inlineStr">
+        <is>
+          <t>15 ч 50 мин</t>
+        </is>
+      </c>
+      <c r="U60" s="5" t="inlineStr">
         <is>
           <t>9 чел. одним рейсом (обычные билеты, без групповых скидок); минивэны</t>
         </is>
@@ -4858,7 +5430,17 @@
         <f>N61+O61+P61+Q61*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S61" s="5" t="inlineStr">
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>18 ч 35 мин</t>
+        </is>
+      </c>
+      <c r="T61" s="10" t="inlineStr">
+        <is>
+          <t>21 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="U61" s="5" t="inlineStr">
         <is>
           <t>Обратно удобный: самолёт до Челябинска + автобус (прямые — только 00:40 и 07:40)</t>
         </is>
@@ -4930,7 +5512,17 @@
         <f>N62+O62+P62+Q62*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S62" s="5" t="inlineStr"/>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>19 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="T62" s="10" t="inlineStr">
+        <is>
+          <t>18 ч 15 мин</t>
+        </is>
+      </c>
+      <c r="U62" s="5" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n">
@@ -4998,7 +5590,17 @@
         <f>N63+O63+P63+Q63*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S63" s="5" t="inlineStr"/>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>18 ч 50 мин</t>
+        </is>
+      </c>
+      <c r="T63" s="10" t="inlineStr">
+        <is>
+          <t>17 ч 10 мин</t>
+        </is>
+      </c>
+      <c r="U63" s="5" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="n">
@@ -5066,7 +5668,17 @@
         <f>N64+O64+P64+Q64*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="S64" s="5" t="inlineStr">
+      <c r="S64" s="7" t="inlineStr">
+        <is>
+          <t>22 ч 45 мин</t>
+        </is>
+      </c>
+      <c r="T64" s="10" t="inlineStr">
+        <is>
+          <t>20 ч 50 мин</t>
+        </is>
+      </c>
+      <c r="U64" s="5" t="inlineStr">
         <is>
           <t>С группой Екатеринбурга; удобный — ночь в Екатеринбурге накануне (~3 000 ₽)</t>
         </is>
@@ -5099,7 +5711,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:S64"/>
+  <autoFilter ref="A4:U64"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Коломна_маршруты_28-30.10.2026.xlsx
+++ b/Коломна_маршруты_28-30.10.2026.xlsx
@@ -15,8 +15,8 @@
     <sheet name="Правила и допущения" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Сводка по сотрудникам'!$A$4:$U$64</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Маршруты'!$A$1:$S$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Сводка по сотрудникам'!$A$4:$U$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Маршруты'!$A$1:$S$120</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -565,7 +565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U66"/>
+  <dimension ref="A1:U70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4237,23 +4237,27 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Поезд</t>
-        </is>
-      </c>
-      <c r="F47" s="6" t="n">
-        <v>2136</v>
-      </c>
-      <c r="G47" s="6" t="n">
-        <v>2136</v>
-      </c>
-      <c r="H47" s="6" t="n">
-        <v>2347</v>
-      </c>
-      <c r="I47" s="6" t="n">
-        <v>2347</v>
+          <t>Авто</t>
+        </is>
+      </c>
+      <c r="F47" s="6">
+        <f>'Авто'!J8/2</f>
+        <v/>
+      </c>
+      <c r="G47" s="6">
+        <f>'Авто'!J8/2</f>
+        <v/>
+      </c>
+      <c r="H47" s="6">
+        <f>'Авто'!J8/2</f>
+        <v/>
+      </c>
+      <c r="I47" s="6">
+        <f>'Авто'!J8/2</f>
+        <v/>
       </c>
       <c r="J47" s="6" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="K47" s="7" t="n">
         <v>0</v>
@@ -4266,14 +4270,16 @@
         <f>G47+I47+J47+K47*'Правила и допущения'!$B$3</f>
         <v/>
       </c>
-      <c r="N47" s="9" t="n">
-        <v>2136</v>
-      </c>
-      <c r="O47" s="9" t="n">
-        <v>2985</v>
+      <c r="N47" s="9">
+        <f>'Авто'!J8/2</f>
+        <v/>
+      </c>
+      <c r="O47" s="9">
+        <f>'Авто'!J8/2</f>
+        <v/>
       </c>
       <c r="P47" s="9" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="Q47" s="10" t="n">
         <v>1</v>
@@ -4284,17 +4290,17 @@
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>16 ч 40 мин</t>
+          <t>12 ч 00 мин</t>
         </is>
       </c>
       <c r="T47" s="10" t="inlineStr">
         <is>
-          <t>16 ч 40 мин</t>
+          <t>12 ч 00 мин</t>
         </is>
       </c>
       <c r="U47" s="5" t="inlineStr">
         <is>
-          <t>Дневные поезда</t>
+          <t>Экипаж: Н. Новгород + Владимир (3 чел.). Удобный = обратно 31.10 утром + ночь</t>
         </is>
       </c>
     </row>
@@ -5685,33 +5691,379 @@
       </c>
     </row>
     <row r="65">
-      <c r="B65" s="12" t="inlineStr">
+      <c r="A65" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Меднов Владимир Александрович</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>Руководитель ЦР Нижний Новгород</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Нижний Новгород</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>Авто</t>
+        </is>
+      </c>
+      <c r="F65" s="6">
+        <f>'Авто'!J8/2</f>
+        <v/>
+      </c>
+      <c r="G65" s="6">
+        <f>'Авто'!J8/2</f>
+        <v/>
+      </c>
+      <c r="H65" s="6">
+        <f>'Авто'!J8/2</f>
+        <v/>
+      </c>
+      <c r="I65" s="6">
+        <f>'Авто'!J8/2</f>
+        <v/>
+      </c>
+      <c r="J65" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" s="8">
+        <f>F65+H65+J65+K65*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="M65" s="8">
+        <f>G65+I65+J65+K65*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="N65" s="9">
+        <f>'Авто'!J8/2</f>
+        <v/>
+      </c>
+      <c r="O65" s="9">
+        <f>'Авто'!J8/2</f>
+        <v/>
+      </c>
+      <c r="P65" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R65" s="11">
+        <f>N65+O65+P65+Q65*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="S65" s="7" t="inlineStr">
+        <is>
+          <t>12 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="T65" s="10" t="inlineStr">
+        <is>
+          <t>12 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="U65" s="5" t="inlineStr">
+        <is>
+          <t>Экипаж: Н. Новгород + Владимир (3 чел.). Удобный = обратно 31.10 утром + ночь</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>Шабанов Роман Васильевич</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>уточнить</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>Владимир</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>Авто</t>
+        </is>
+      </c>
+      <c r="F66" s="6">
+        <f>'Авто'!J8/2</f>
+        <v/>
+      </c>
+      <c r="G66" s="6">
+        <f>'Авто'!J8/2</f>
+        <v/>
+      </c>
+      <c r="H66" s="6">
+        <f>'Авто'!J8/2</f>
+        <v/>
+      </c>
+      <c r="I66" s="6">
+        <f>'Авто'!J8/2</f>
+        <v/>
+      </c>
+      <c r="J66" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" s="8">
+        <f>F66+H66+J66+K66*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="M66" s="8">
+        <f>G66+I66+J66+K66*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="N66" s="9">
+        <f>'Авто'!J8/2</f>
+        <v/>
+      </c>
+      <c r="O66" s="9">
+        <f>'Авто'!J8/2</f>
+        <v/>
+      </c>
+      <c r="P66" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R66" s="11">
+        <f>N66+O66+P66+Q66*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="S66" s="7" t="inlineStr">
+        <is>
+          <t>7 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="T66" s="10" t="inlineStr">
+        <is>
+          <t>7 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="U66" s="5" t="inlineStr">
+        <is>
+          <t>Экипаж: Н. Новгород + Владимир (3 чел.). Удобный = обратно 31.10 утром + ночь</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Викторов Максим Сергеевич</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>уточнить</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Ярославль</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>Поезд</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="n">
+        <v>1106</v>
+      </c>
+      <c r="G67" s="6" t="n">
+        <v>1106</v>
+      </c>
+      <c r="H67" s="6" t="n">
+        <v>3058</v>
+      </c>
+      <c r="I67" s="6" t="n">
+        <v>3058</v>
+      </c>
+      <c r="J67" s="6" t="n">
+        <v>1800</v>
+      </c>
+      <c r="K67" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" s="8">
+        <f>F67+H67+J67+K67*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="M67" s="8">
+        <f>G67+I67+J67+K67*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="N67" s="9" t="n">
+        <v>1106</v>
+      </c>
+      <c r="O67" s="9" t="n">
+        <v>1716</v>
+      </c>
+      <c r="P67" s="9" t="n">
+        <v>1800</v>
+      </c>
+      <c r="Q67" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R67" s="11">
+        <f>N67+O67+P67+Q67*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="S67" s="7" t="inlineStr">
+        <is>
+          <t>16 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="T67" s="10" t="inlineStr">
+        <is>
+          <t>14 ч 40 мин</t>
+        </is>
+      </c>
+      <c r="U67" s="5" t="inlineStr">
+        <is>
+          <t>Ярославский вокзал рядом с Казанским; обратно удобный — днём 31.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>Макеев Сергей Иванович</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>уточнить</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>Калуга</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>Авто</t>
+        </is>
+      </c>
+      <c r="F68" s="6">
+        <f>'Авто'!J9/2</f>
+        <v/>
+      </c>
+      <c r="G68" s="6">
+        <f>'Авто'!J9/2</f>
+        <v/>
+      </c>
+      <c r="H68" s="6">
+        <f>'Авто'!J9/2</f>
+        <v/>
+      </c>
+      <c r="I68" s="6">
+        <f>'Авто'!J9/2</f>
+        <v/>
+      </c>
+      <c r="J68" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" s="8">
+        <f>F68+H68+J68+K68*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="M68" s="8">
+        <f>G68+I68+J68+K68*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="N68" s="9">
+        <f>'Авто'!J9/2</f>
+        <v/>
+      </c>
+      <c r="O68" s="9">
+        <f>'Авто'!J9/2</f>
+        <v/>
+      </c>
+      <c r="P68" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R68" s="11">
+        <f>N68+O68+P68+Q68*'Правила и допущения'!$B$3</f>
+        <v/>
+      </c>
+      <c r="S68" s="7" t="inlineStr">
+        <is>
+          <t>7 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="T68" s="10" t="inlineStr">
+        <is>
+          <t>7 ч 00 мин</t>
+        </is>
+      </c>
+      <c r="U68" s="5" t="inlineStr">
+        <is>
+          <t>Экипаж: Калуга. Удобный = обратно 31.10 утром + ночь</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="12" t="inlineStr">
         <is>
           <t>ИТОГО по списку</t>
         </is>
       </c>
-      <c r="L65" s="13">
-        <f>SUM(L5:L64)</f>
-        <v/>
-      </c>
-      <c r="M65" s="13">
-        <f>SUM(M5:M64)</f>
-        <v/>
-      </c>
-      <c r="R65" s="13">
-        <f>SUM(R5:R64)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Сотрудников в списке: 60 . </t>
+      <c r="L69" s="13">
+        <f>SUM(L5:L68)</f>
+        <v/>
+      </c>
+      <c r="M69" s="13">
+        <f>SUM(M5:M68)</f>
+        <v/>
+      </c>
+      <c r="R69" s="13">
+        <f>SUM(R5:R68)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сотрудников в списке: 64 . </t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:U64"/>
+  <autoFilter ref="A4:U68"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5722,7 +6074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S115"/>
+  <dimension ref="A1:S122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13545,7 +13897,7 @@
       </c>
       <c r="R92" s="16" t="inlineStr">
         <is>
-          <t>Или своя машина: ~430 км, ~6 ч</t>
+          <t>Основной вариант — машина с заездом во Владимир (лист «Авто»)</t>
         </is>
       </c>
       <c r="S92" s="16" t="inlineStr">
@@ -15289,15 +15641,592 @@
         </is>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" s="15" t="inlineStr">
+        <is>
+          <t>Ярославль</t>
+        </is>
+      </c>
+      <c r="B114" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C114" s="17" t="inlineStr">
+        <is>
+          <t>Туда</t>
+        </is>
+      </c>
+      <c r="D114" s="17" t="inlineStr">
+        <is>
+          <t>Самый дешёвый = Удобный</t>
+        </is>
+      </c>
+      <c r="E114" s="17" t="inlineStr">
+        <is>
+          <t>Поезд, сидячий</t>
+        </is>
+      </c>
+      <c r="F114" s="17" t="inlineStr">
+        <is>
+          <t>107Я</t>
+        </is>
+      </c>
+      <c r="G114" s="16" t="inlineStr">
+        <is>
+          <t>28.10 08:26</t>
+        </is>
+      </c>
+      <c r="H114" s="16" t="inlineStr">
+        <is>
+          <t>28.10 11:51</t>
+        </is>
+      </c>
+      <c r="I114" s="16" t="inlineStr">
+        <is>
+          <t>Москва, Ярославский</t>
+        </is>
+      </c>
+      <c r="J114" s="18" t="n">
+        <v>1106</v>
+      </c>
+      <c r="K114" s="18" t="n">
+        <v>1106</v>
+      </c>
+      <c r="L114" s="16" t="inlineStr">
+        <is>
+          <t>Ярославский вокзал → через площадь на Казанский (5 мин) → электричка + такси (12:54 → 15:15)</t>
+        </is>
+      </c>
+      <c r="M114" s="16" t="inlineStr">
+        <is>
+          <t>~15:30</t>
+        </is>
+      </c>
+      <c r="N114" s="16" t="inlineStr">
+        <is>
+          <t>28.10 07:40 МСК → 28.10 15:30 МСК</t>
+        </is>
+      </c>
+      <c r="O114" s="15" t="inlineStr">
+        <is>
+          <t>7 ч 50 мин</t>
+        </is>
+      </c>
+      <c r="P114" s="16" t="inlineStr"/>
+      <c r="Q114" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/</t>
+        </is>
+      </c>
+      <c r="R114" s="16" t="inlineStr">
+        <is>
+          <t>Ярославский вокзал — через площадь от Казанского. Для экскурсии: 101Я 06:55 → 10:22, 1 689 ₽</t>
+        </is>
+      </c>
+      <c r="S114" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
     <row r="115">
-      <c r="A115" s="14" t="inlineStr">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>Ярославль</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C115" s="7" t="inlineStr">
+        <is>
+          <t>Обратно</t>
+        </is>
+      </c>
+      <c r="D115" s="7" t="inlineStr">
+        <is>
+          <t>Самый дешёвый</t>
+        </is>
+      </c>
+      <c r="E115" s="7" t="inlineStr">
+        <is>
+          <t>Поезд, купе</t>
+        </is>
+      </c>
+      <c r="F115" s="7" t="inlineStr">
+        <is>
+          <t>042В</t>
+        </is>
+      </c>
+      <c r="G115" s="5" t="inlineStr">
+        <is>
+          <t>30.10 21:50</t>
+        </is>
+      </c>
+      <c r="H115" s="5" t="inlineStr">
+        <is>
+          <t>31.10 01:38</t>
+        </is>
+      </c>
+      <c r="I115" s="5" t="inlineStr">
+        <is>
+          <t>Ярославль</t>
+        </is>
+      </c>
+      <c r="J115" s="6" t="n">
+        <v>3058</v>
+      </c>
+      <c r="K115" s="6" t="n">
+        <v>3058</v>
+      </c>
+      <c r="L115" s="5" t="inlineStr">
+        <is>
+          <t>Электричка 18:43 → Казанский 20:47 → Ярославский</t>
+        </is>
+      </c>
+      <c r="M115" s="5" t="inlineStr"/>
+      <c r="N115" s="5" t="inlineStr">
+        <is>
+          <t>30.10 18:15 МСК → 31.10 02:25 МСК</t>
+        </is>
+      </c>
+      <c r="O115" s="20" t="inlineStr">
+        <is>
+          <t>8 ч 10 мин</t>
+        </is>
+      </c>
+      <c r="P115" s="5" t="inlineStr"/>
+      <c r="Q115" s="21" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/</t>
+        </is>
+      </c>
+      <c r="R115" s="5" t="inlineStr">
+        <is>
+          <t>Дома ночью</t>
+        </is>
+      </c>
+      <c r="S115" s="5" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>Ярославль</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C116" s="10" t="inlineStr">
+        <is>
+          <t>Обратно</t>
+        </is>
+      </c>
+      <c r="D116" s="10" t="inlineStr">
+        <is>
+          <t>Удобный</t>
+        </is>
+      </c>
+      <c r="E116" s="10" t="inlineStr">
+        <is>
+          <t>Поезд, сидячий</t>
+        </is>
+      </c>
+      <c r="F116" s="10" t="inlineStr">
+        <is>
+          <t>748Я</t>
+        </is>
+      </c>
+      <c r="G116" s="5" t="inlineStr">
+        <is>
+          <t>31.10 13:00</t>
+        </is>
+      </c>
+      <c r="H116" s="5" t="inlineStr">
+        <is>
+          <t>31.10 16:04</t>
+        </is>
+      </c>
+      <c r="I116" s="5" t="inlineStr">
+        <is>
+          <t>Ярославль</t>
+        </is>
+      </c>
+      <c r="J116" s="9" t="n">
+        <v>1716</v>
+      </c>
+      <c r="K116" s="9" t="n">
+        <v>1716</v>
+      </c>
+      <c r="L116" s="5" t="inlineStr">
+        <is>
+          <t>31.10 утро: электричка до Казанского → Ярославский (через площадь)</t>
+        </is>
+      </c>
+      <c r="M116" s="5" t="inlineStr"/>
+      <c r="N116" s="5" t="inlineStr">
+        <is>
+          <t>31.10 10:00 МСК → 31.10 16:50 МСК</t>
+        </is>
+      </c>
+      <c r="O116" s="20" t="inlineStr">
+        <is>
+          <t>6 ч 50 мин</t>
+        </is>
+      </c>
+      <c r="P116" s="5" t="inlineStr">
+        <is>
+          <t>+1 ночь 30→31</t>
+        </is>
+      </c>
+      <c r="Q116" s="21" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/</t>
+        </is>
+      </c>
+      <c r="R116" s="5" t="inlineStr">
+        <is>
+          <t>Днём. Время по расписанию 30.10 — проверить</t>
+        </is>
+      </c>
+      <c r="S116" s="5" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="15" t="inlineStr">
+        <is>
+          <t>Владимир</t>
+        </is>
+      </c>
+      <c r="B117" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C117" s="16" t="inlineStr">
+        <is>
+          <t>Туда</t>
+        </is>
+      </c>
+      <c r="D117" s="16" t="inlineStr">
+        <is>
+          <t>Альтернатива: поезд</t>
+        </is>
+      </c>
+      <c r="E117" s="16" t="inlineStr">
+        <is>
+          <t>Поезд «Буревестник», сидячий</t>
+        </is>
+      </c>
+      <c r="F117" s="16" t="inlineStr">
+        <is>
+          <t>705Э</t>
+        </is>
+      </c>
+      <c r="G117" s="16" t="inlineStr">
+        <is>
+          <t>28.10 09:38</t>
+        </is>
+      </c>
+      <c r="H117" s="16" t="inlineStr">
+        <is>
+          <t>28.10 11:34</t>
+        </is>
+      </c>
+      <c r="I117" s="16" t="inlineStr">
+        <is>
+          <t>Москва, Восточный</t>
+        </is>
+      </c>
+      <c r="J117" s="22" t="n">
+        <v>1736</v>
+      </c>
+      <c r="K117" s="22" t="n">
+        <v>1736</v>
+      </c>
+      <c r="L117" s="16" t="inlineStr">
+        <is>
+          <t>Восточный вокзал → МЦД/метро до Казанского (~30 мин) → электричка + такси (12:54 → 15:15)</t>
+        </is>
+      </c>
+      <c r="M117" s="16" t="inlineStr">
+        <is>
+          <t>~15:30</t>
+        </is>
+      </c>
+      <c r="N117" s="16" t="inlineStr">
+        <is>
+          <t>28.10 08:50 МСК → 28.10 15:30 МСК</t>
+        </is>
+      </c>
+      <c r="O117" s="15" t="inlineStr">
+        <is>
+          <t>6 ч 40 мин</t>
+        </is>
+      </c>
+      <c r="P117" s="16" t="inlineStr"/>
+      <c r="Q117" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/</t>
+        </is>
+      </c>
+      <c r="R117" s="16" t="inlineStr">
+        <is>
+          <t>Основной вариант — едет в машине из Нижнего Новгорода (лист «Авто»)</t>
+        </is>
+      </c>
+      <c r="S117" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>Владимир</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>Обратно</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>Альтернатива: поезд</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="inlineStr">
+        <is>
+          <t>Ласточка, сидячий</t>
+        </is>
+      </c>
+      <c r="F118" s="5" t="inlineStr">
+        <is>
+          <t>723Я</t>
+        </is>
+      </c>
+      <c r="G118" s="5" t="inlineStr">
+        <is>
+          <t>30.10 21:15</t>
+        </is>
+      </c>
+      <c r="H118" s="5" t="inlineStr">
+        <is>
+          <t>30.10 23:06</t>
+        </is>
+      </c>
+      <c r="I118" s="5" t="inlineStr">
+        <is>
+          <t>Владимир</t>
+        </is>
+      </c>
+      <c r="J118" s="23" t="n">
+        <v>2103</v>
+      </c>
+      <c r="K118" s="23" t="n">
+        <v>2103</v>
+      </c>
+      <c r="L118" s="5" t="inlineStr">
+        <is>
+          <t>Электричка 18:43 → Казанский 20:47 → МЦД до Восточного</t>
+        </is>
+      </c>
+      <c r="M118" s="5" t="inlineStr"/>
+      <c r="N118" s="5" t="inlineStr">
+        <is>
+          <t>30.10 18:15 МСК → 30.10 23:50 МСК</t>
+        </is>
+      </c>
+      <c r="O118" s="20" t="inlineStr">
+        <is>
+          <t>5 ч 35 мин</t>
+        </is>
+      </c>
+      <c r="P118" s="5" t="inlineStr"/>
+      <c r="Q118" s="21" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/</t>
+        </is>
+      </c>
+      <c r="R118" s="5" t="inlineStr"/>
+      <c r="S118" s="5" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="15" t="inlineStr">
+        <is>
+          <t>Калуга</t>
+        </is>
+      </c>
+      <c r="B119" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C119" s="16" t="inlineStr">
+        <is>
+          <t>Туда</t>
+        </is>
+      </c>
+      <c r="D119" s="16" t="inlineStr">
+        <is>
+          <t>Альтернатива: поезд</t>
+        </is>
+      </c>
+      <c r="E119" s="16" t="inlineStr">
+        <is>
+          <t>Поезд «Иван Паристый», сидячий</t>
+        </is>
+      </c>
+      <c r="F119" s="16" t="inlineStr">
+        <is>
+          <t>738А</t>
+        </is>
+      </c>
+      <c r="G119" s="16" t="inlineStr">
+        <is>
+          <t>28.10 09:08</t>
+        </is>
+      </c>
+      <c r="H119" s="16" t="inlineStr">
+        <is>
+          <t>28.10 11:05</t>
+        </is>
+      </c>
+      <c r="I119" s="16" t="inlineStr">
+        <is>
+          <t>Москва, Киевский</t>
+        </is>
+      </c>
+      <c r="J119" s="22" t="n">
+        <v>1433</v>
+      </c>
+      <c r="K119" s="22" t="n">
+        <v>1433</v>
+      </c>
+      <c r="L119" s="16" t="inlineStr">
+        <is>
+          <t>Киевский → метро до Комсомольской (~25 мин) → электричка + такси (12:54 → 15:15)</t>
+        </is>
+      </c>
+      <c r="M119" s="16" t="inlineStr">
+        <is>
+          <t>~15:30</t>
+        </is>
+      </c>
+      <c r="N119" s="16" t="inlineStr">
+        <is>
+          <t>28.10 08:20 МСК → 28.10 15:30 МСК</t>
+        </is>
+      </c>
+      <c r="O119" s="15" t="inlineStr">
+        <is>
+          <t>7 ч 10 мин</t>
+        </is>
+      </c>
+      <c r="P119" s="16" t="inlineStr"/>
+      <c r="Q119" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/</t>
+        </is>
+      </c>
+      <c r="R119" s="16" t="inlineStr">
+        <is>
+          <t>Основной вариант — своя машина (лист «Авто»). Дешевле: 086Щ 03:38, 993 ₽ — ночной подъём</t>
+        </is>
+      </c>
+      <c r="S119" s="16" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>Калуга</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>Обратно</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>Альтернатива: поезд</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>Поезд, сидячий</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="inlineStr">
+        <is>
+          <t>085Щ</t>
+        </is>
+      </c>
+      <c r="G120" s="5" t="inlineStr">
+        <is>
+          <t>30.10 22:35</t>
+        </is>
+      </c>
+      <c r="H120" s="5" t="inlineStr">
+        <is>
+          <t>31.10 01:10</t>
+        </is>
+      </c>
+      <c r="I120" s="5" t="inlineStr">
+        <is>
+          <t>Калуга</t>
+        </is>
+      </c>
+      <c r="J120" s="23" t="n">
+        <v>968</v>
+      </c>
+      <c r="K120" s="23" t="n">
+        <v>968</v>
+      </c>
+      <c r="L120" s="5" t="inlineStr">
+        <is>
+          <t>Электричка 18:43 → Казанский 20:47 → метро до Киевской</t>
+        </is>
+      </c>
+      <c r="M120" s="5" t="inlineStr"/>
+      <c r="N120" s="5" t="inlineStr">
+        <is>
+          <t>30.10 18:15 МСК → 31.10 01:55 МСК</t>
+        </is>
+      </c>
+      <c r="O120" s="20" t="inlineStr">
+        <is>
+          <t>7 ч 40 мин</t>
+        </is>
+      </c>
+      <c r="P120" s="5" t="inlineStr"/>
+      <c r="Q120" s="21" t="inlineStr">
+        <is>
+          <t>https://www.tutu.ru/poezda/</t>
+        </is>
+      </c>
+      <c r="R120" s="5" t="inlineStr">
+        <is>
+          <t>Дома ночью. Днём 31.10: 739А 13:43 → 15:42, 1 588 ₽</t>
+        </is>
+      </c>
+      <c r="S120" s="5" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="14" t="inlineStr">
         <is>
           <t>Время в пути «дверь–дверь»: туда — от выхода из дома до заселения в гостиницу, обратно — от выезда из гостиницы до прихода домой. Считается с учётом разницы во времени; включает дорогу до аэропорта/вокзала (в аэропорту за 2 ч в крупных городах, за 1,5 ч в небольших), ожидание и трансфер. Ночи в поезде входят во время в пути.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S113"/>
+  <autoFilter ref="A1:S120"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
@@ -15407,6 +16336,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q111" r:id="rId106"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q112" r:id="rId107"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q113" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q114" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q115" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q116" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q117" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q118" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q119" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q120" r:id="rId115"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15418,7 +16354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -15815,8 +16751,114 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Н. Новгород + Владимир (3 чел.)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Бабкин В.А., Меднов В.А. (из Н. Новгорода), Шабанов Р.В. (забрать во Владимире)</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Н. Новгород — М-12 — Владимир — Петушки — Покров — Орехово-Зуево — Егорьевск — Коломна</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>430</v>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>~6 ч</t>
+        </is>
+      </c>
+      <c r="G8" s="23">
+        <f>E8*2*'Правила и допущения'!$B$4/100*'Правила и допущения'!$B$5</f>
+        <v/>
+      </c>
+      <c r="H8" s="23" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I8" s="23">
+        <f>G8+H8</f>
+        <v/>
+      </c>
+      <c r="J8" s="23">
+        <f>I8/C8</f>
+        <v/>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>28.10 выезд из Н. Новгорода 08:00 → Владимир ~10:30 (забрать Шабанова) → Коломна ~14:00</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>Владимир по пути — крюк не нужен. М-12 платная, ~1 500 ₽ в одну сторону (ориентир); по бесплатной М-7 +~40 мин. Обратно 30.10 после 18:00: Владимир ~21:30, Н. Новгород ~00:30 — для водителя лучше 31.10 утром</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Калуга</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Макеев С.И.</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Калуга — Таруса — Серпухов — Ступино — Коломна</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>~3 ч 30 мин</t>
+        </is>
+      </c>
+      <c r="G9" s="23">
+        <f>E9*2*'Правила и допущения'!$B$4/100*'Правила и допущения'!$B$5</f>
+        <v/>
+      </c>
+      <c r="H9" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="23">
+        <f>G9+H9</f>
+        <v/>
+      </c>
+      <c r="J9" s="23">
+        <f>I9/C9</f>
+        <v/>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>28.10 выезд 10:30 → 14:00</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>Если своей машины нет — поезд до Киевского вокзала (лист «Маршруты»)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Расстояния и время — ориентир; точный маршрут и пробки проверить в Яндекс Картах. Обратно: эконом — выезд 30.10 в 18:15; удобный — 31.10 утром + доп. ночь.</t>
         </is>

--- a/Коломна_маршруты_28-30.10.2026.xlsx
+++ b/Коломна_маршруты_28-30.10.2026.xlsx
@@ -16354,7 +16354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -16853,12 +16853,118 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>Если своей машины нет — поезд до Киевского вокзала (лист «Маршруты»)</t>
+          <t>Запасной вариант (непогода, неисправность) — поезд до Киевского вокзала (лист «Маршруты»)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Ярославль (сравнение)</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Викторов М.С.</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Ярославль — М-8 — ЦКАД — Коломна</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>360</v>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>~5 ч</t>
+        </is>
+      </c>
+      <c r="G10" s="23">
+        <f>E10*2*'Правила и допущения'!$B$4/100*'Правила и допущения'!$B$5</f>
+        <v/>
+      </c>
+      <c r="H10" s="23" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I10" s="23">
+        <f>G10+H10</f>
+        <v/>
+      </c>
+      <c r="J10" s="23">
+        <f>I10/C10</f>
+        <v/>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>28.10 выезд 09:30 → 14:30</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>Для сравнения: по цене как поезд (~5 900 ₽), но 5 ч за рулём вместо 3,5 ч в поезде. В расчёте — поезд</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Смоленск (сравнение)</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Понамарёв В.В.</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Смоленск — М-1 — ЦКАД — Коломна</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>470</v>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>~6 ч 30 мин</t>
+        </is>
+      </c>
+      <c r="G11" s="23">
+        <f>E11*2*'Правила и допущения'!$B$4/100*'Правила и допущения'!$B$5</f>
+        <v/>
+      </c>
+      <c r="H11" s="23" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I11" s="23">
+        <f>G11+H11</f>
+        <v/>
+      </c>
+      <c r="J11" s="23">
+        <f>I11/C11</f>
+        <v/>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>28.10 выезд 07:30 → 14:00</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>Для сравнения: дороже поезда (~8 100 ₽ против ~7 700 ₽) и 6,5 ч за рулём. В расчёте — поезд</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>Расстояния и время — ориентир; точный маршрут и пробки проверить в Яндекс Картах. Обратно: эконом — выезд 30.10 в 18:15; удобный — 31.10 утром + доп. ночь.</t>
         </is>
